--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jour par jour" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vidéos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Évolution par vidéo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="À lire" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vues du jour par vidéo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="À lire" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,6 +282,108 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues des stories</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Stories'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="FF8A1F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Stories'!$A$2:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Stories'!$B$2:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -1297,7 +1400,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Vues des stories</a:t>
+              <a:t>Vues gagnées chaque jour, vidéo par vidéo</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1306,35 +1409,129 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Stories'!B1</f>
+              <f>'Vues du jour par vidéo'!B1</f>
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FF8A1F"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$8</f>
+              <f>'Vues du jour par vidéo'!$B$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$C$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$D$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$E$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$F$2</f>
             </numRef>
           </val>
         </ser>
         <gapWidth val="150"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1358,21 +1555,6 @@
         <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1579,6 +1761,33 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2441,6 +2650,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Jour</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>⚠️ Contenu effrayant… ou pas</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>👻 On ne parle que des casseu</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total du jour</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>IF('Évolution par vidéo'!B2="","",'Évolution par vidéo'!B2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="3">
+        <f>IF('Évolution par vidéo'!C2="","",'Évolution par vidéo'!C2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="3">
+        <f>IF('Évolution par vidéo'!D2="","",'Évolution par vidéo'!D2)</f>
+        <v/>
+      </c>
+      <c r="E2" s="3">
+        <f>IF('Évolution par vidéo'!E2="","",'Évolution par vidéo'!E2)</f>
+        <v/>
+      </c>
+      <c r="F2" s="3">
+        <f>IF('Évolution par vidéo'!F2="","",'Évolution par vidéo'!F2)</f>
+        <v/>
+      </c>
+      <c r="G2" s="3">
+        <f>SUM(B2:F2)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2748,13 +3049,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2791,12 +3092,19 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Taux d'engagement = (likes + commentaires + partages + enregistrements) / comptes touchés.</t>
+          <t>« Vues du jour par vidéo » = vues gagnées par chaque vidéo depuis le relevé de la veille.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Taux d'engagement = (likes + commentaires + partages + enregistrements) / comptes touchés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Les statistiques d'une story ne sont lisibles que pendant ses 24 h : dernier relevé conservé.</t>
         </is>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jour par jour" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vidéos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Évolution par vidéo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vues du jour par vidéo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="À lire" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Jour par jour" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vidéos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Évolution par vidéo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Vues du jour par vidéo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stories" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="À lire" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -170,13 +170,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -199,7 +199,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="E5133A"/>
               </a:solidFill>
@@ -210,22 +210,22 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="E5133A"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2</f>
+              <f>'Jour par jour'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -256,8 +256,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -283,13 +283,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -313,21 +313,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF8A1F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$8</f>
+              <f>'Stories'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$8</f>
+              <f>'Stories'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -358,8 +358,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -385,13 +385,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -415,21 +415,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="3D5AFE"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2</f>
+              <f>'Jour par jour'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -442,21 +442,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF8A1F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2</f>
+              <f>'Jour par jour'!$L$2:$L$3</f>
             </numRef>
           </val>
         </ser>
@@ -487,8 +487,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -514,13 +514,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -543,7 +543,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="8E5CFF"/>
               </a:solidFill>
@@ -554,22 +554,22 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8E5CFF"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2</f>
+              <f>'Jour par jour'!$F$2:$F$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -583,7 +583,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="00B8D4"/>
               </a:solidFill>
@@ -594,22 +594,22 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="00B8D4"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2</f>
+              <f>'Jour par jour'!$H$2:$H$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -640,8 +640,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -667,13 +667,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -697,21 +697,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2E7D32"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2</f>
+              <f>'Jour par jour'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -742,8 +742,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -769,13 +769,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -799,21 +799,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="3D5AFE"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$6</f>
+              <f>'Vidéos'!$B$2:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2:$D$6</f>
+              <f>'Vidéos'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -844,8 +844,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -871,13 +871,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -901,21 +901,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF4F81"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$6</f>
+              <f>'Vidéos'!$B$2:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2:$F$6</f>
+              <f>'Vidéos'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -928,21 +928,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="8E5CFF"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$6</f>
+              <f>'Vidéos'!$B$2:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2:$G$6</f>
+              <f>'Vidéos'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -955,21 +955,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2E7D32"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$6</f>
+              <f>'Vidéos'!$B$2:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2:$H$6</f>
+              <f>'Vidéos'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -982,21 +982,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF8A1F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$6</f>
+              <f>'Vidéos'!$B$2:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2:$I$6</f>
+              <f>'Vidéos'!$I$2:$I$11</f>
             </numRef>
           </val>
         </ser>
@@ -1027,8 +1027,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1054,13 +1054,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1084,21 +1084,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E5133A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$6</f>
+              <f>'Vidéos'!$B$2:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2:$K$6</f>
+              <f>'Vidéos'!$K$2:$K$11</f>
             </numRef>
           </val>
         </ser>
@@ -1129,8 +1129,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1156,13 +1156,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1185,26 +1185,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2</f>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2</f>
+              <f>'Évolution par vidéo'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -1217,26 +1217,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2</f>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2</f>
+              <f>'Évolution par vidéo'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -1249,26 +1249,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2</f>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2</f>
+              <f>'Évolution par vidéo'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -1281,26 +1281,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2</f>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2</f>
+              <f>'Évolution par vidéo'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -1313,26 +1313,186 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2</f>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2</f>
+              <f>'Évolution par vidéo'!$F$2:$F$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$G$2:$G$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$H$2:$H$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$I$2:$I$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$J$2:$J$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$K$2:$K$3</f>
             </numRef>
           </val>
         </ser>
@@ -1362,8 +1522,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1389,13 +1549,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1419,18 +1579,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -1443,18 +1603,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -1467,18 +1627,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -1491,18 +1651,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -1515,18 +1675,138 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$G$2:$G$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$H$2:$H$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$I$2:$I$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$J$2:$J$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$K$2:$K$3</f>
             </numRef>
           </val>
         </ser>
@@ -1570,7 +1850,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>14</col>
@@ -1585,9 +1865,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1607,9 +1887,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1629,9 +1909,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1651,9 +1931,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1663,12 +1943,12 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1678,9 +1958,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1690,7 +1970,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1700,9 +1980,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1712,7 +1992,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1722,9 +2002,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1734,12 +2014,12 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1749,9 +2029,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1761,12 +2041,12 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -1776,9 +2056,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1788,7 +2068,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -1803,9 +2083,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2103,7 +2383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2227,9 +2507,54 @@
         <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <f>IF(ROW()=2,"",B3-B2)</f>
+        <v/>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2318</v>
+      </c>
+      <c r="E3" s="3">
+        <f>IF(ROW()=2,D3,D3-D2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1728</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2154</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2245,7 +2570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2341,10 +2666,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
@@ -2387,10 +2712,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2</v>
@@ -2433,10 +2758,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>2</v>
@@ -2479,13 +2804,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -2497,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
@@ -2525,16 +2850,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>174</v>
+        <v>1125</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>156</v>
+        <v>979</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -2543,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -2551,6 +2876,236 @@
       </c>
       <c r="L6" s="6">
         <f>IFERROR(D6/E6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 20:18</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5">
+        <f>IFERROR((F7+G7+H7+I7)/IF(E7&gt;0,E7,D7),0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="6">
+        <f>IFERROR(D7/E7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <f>IFERROR((F8+G8+H8+I8)/IF(E8&gt;0,E8,D8),0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="6">
+        <f>IFERROR(D8/E8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5">
+        <f>IFERROR((F9+G9+H9+I9)/IF(E9&gt;0,E9,D9),0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="6">
+        <f>IFERROR(D9/E9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5">
+        <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="6">
+        <f>IFERROR(D10/E10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>IFERROR(D11/E11,0)</f>
         <v/>
       </c>
     </row>
@@ -2561,9 +3116,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
 </worksheet>
 </file>
 
@@ -2573,7 +3133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2582,6 +3142,11 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2615,6 +3180,31 @@
           <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>😱 Ma réaction à ce qui t'att</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>🧮 Quiz : ta manif dégénère e</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Et soudain, 718 stations san</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Les vitrines d'abord. Toi, a</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2636,6 +3226,48 @@
       </c>
       <c r="F2" s="3" t="n">
         <v>174</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>343</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2650,7 +3282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2659,7 +3291,12 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2695,6 +3332,31 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>😱 Ma réaction à ce qui t'att</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>🧮 Quiz : ta manif dégénère e</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Et soudain, 718 stations san</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Les vitrines d'abord. Toi, a</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -2726,7 +3388,78 @@
         <v/>
       </c>
       <c r="G2" s="3">
-        <f>SUM(B2:F2)</f>
+        <f>IF('Évolution par vidéo'!G2="","",'Évolution par vidéo'!G2)</f>
+        <v/>
+      </c>
+      <c r="H2" s="3">
+        <f>IF('Évolution par vidéo'!H2="","",'Évolution par vidéo'!H2)</f>
+        <v/>
+      </c>
+      <c r="I2" s="3">
+        <f>IF('Évolution par vidéo'!I2="","",'Évolution par vidéo'!I2)</f>
+        <v/>
+      </c>
+      <c r="J2" s="3">
+        <f>IF('Évolution par vidéo'!J2="","",'Évolution par vidéo'!J2)</f>
+        <v/>
+      </c>
+      <c r="K2" s="3">
+        <f>IF('Évolution par vidéo'!K2="","",'Évolution par vidéo'!K2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="3">
+        <f>SUM(B2:K2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>IF('Évolution par vidéo'!B3="","",'Évolution par vidéo'!B3-N('Évolution par vidéo'!B2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>IF('Évolution par vidéo'!C3="","",'Évolution par vidéo'!C3-N('Évolution par vidéo'!C2))</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>IF('Évolution par vidéo'!D3="","",'Évolution par vidéo'!D3-N('Évolution par vidéo'!D2))</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>IF('Évolution par vidéo'!E3="","",'Évolution par vidéo'!E3-N('Évolution par vidéo'!E2))</f>
+        <v/>
+      </c>
+      <c r="F3" s="3">
+        <f>IF('Évolution par vidéo'!F3="","",'Évolution par vidéo'!F3-N('Évolution par vidéo'!F2))</f>
+        <v/>
+      </c>
+      <c r="G3" s="3">
+        <f>IF('Évolution par vidéo'!G3="","",'Évolution par vidéo'!G3-N('Évolution par vidéo'!G2))</f>
+        <v/>
+      </c>
+      <c r="H3" s="3">
+        <f>IF('Évolution par vidéo'!H3="","",'Évolution par vidéo'!H3-N('Évolution par vidéo'!H2))</f>
+        <v/>
+      </c>
+      <c r="I3" s="3">
+        <f>IF('Évolution par vidéo'!I3="","",'Évolution par vidéo'!I3-N('Évolution par vidéo'!I2))</f>
+        <v/>
+      </c>
+      <c r="J3" s="3">
+        <f>IF('Évolution par vidéo'!J3="","",'Évolution par vidéo'!J3-N('Évolution par vidéo'!J2))</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
+        <f>IF('Évolution par vidéo'!K3="","",'Évolution par vidéo'!K3-N('Évolution par vidéo'!K2))</f>
+        <v/>
+      </c>
+      <c r="L3" s="3">
+        <f>SUM(B3:K3)</f>
         <v/>
       </c>
     </row>
@@ -2742,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2876,7 +3609,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -2909,7 +3642,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -2942,7 +3675,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -2975,7 +3708,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -3008,27 +3741,423 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 19:51</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 20:19</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:14</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:57</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:14</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:14</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:18</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:09</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:12</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:13</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:06</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:06</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -3043,9 +4172,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
 </worksheet>
 </file>
 
@@ -3064,7 +4205,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Décodé · suivi du compte @decodeactu</t>
+          <t>Décodé · suivi du compte Décodé · Actu</t>
         </is>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -220,12 +220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$3</f>
+              <f>'Jour par jour'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -322,12 +322,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$20</f>
+              <f>'Stories'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$20</f>
+              <f>'Stories'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$3</f>
+              <f>'Jour par jour'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$3</f>
+              <f>'Jour par jour'!$L$2:$L$4</f>
             </numRef>
           </val>
         </ser>
@@ -564,12 +564,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$3</f>
+              <f>'Jour par jour'!$F$2:$F$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -604,12 +604,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$3</f>
+              <f>'Jour par jour'!$H$2:$H$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -706,12 +706,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$3</f>
+              <f>'Jour par jour'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -808,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$11</f>
+              <f>'Vidéos'!$B$2:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2:$D$11</f>
+              <f>'Vidéos'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -910,12 +910,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$11</f>
+              <f>'Vidéos'!$B$2:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2:$F$11</f>
+              <f>'Vidéos'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -937,12 +937,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$11</f>
+              <f>'Vidéos'!$B$2:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2:$G$11</f>
+              <f>'Vidéos'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$11</f>
+              <f>'Vidéos'!$B$2:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2:$H$11</f>
+              <f>'Vidéos'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -991,12 +991,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$11</f>
+              <f>'Vidéos'!$B$2:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2:$I$11</f>
+              <f>'Vidéos'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -1093,12 +1093,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$11</f>
+              <f>'Vidéos'!$B$2:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2:$K$11</f>
+              <f>'Vidéos'!$K$2:$K$12</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$3</f>
+              <f>'Évolution par vidéo'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -1231,12 +1231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$3</f>
+              <f>'Évolution par vidéo'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -1263,12 +1263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$3</f>
+              <f>'Évolution par vidéo'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1295,12 +1295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$3</f>
+              <f>'Évolution par vidéo'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -1327,12 +1327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$3</f>
+              <f>'Évolution par vidéo'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1359,12 +1359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$3</f>
+              <f>'Évolution par vidéo'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -1391,12 +1391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$3</f>
+              <f>'Évolution par vidéo'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$3</f>
+              <f>'Évolution par vidéo'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -1455,12 +1455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$3</f>
+              <f>'Évolution par vidéo'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -1487,12 +1487,44 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$3</f>
+              <f>'Évolution par vidéo'!$K$2:$K$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$L$2:$L$4</f>
             </numRef>
           </val>
         </ser>
@@ -1585,12 +1617,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$3</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -1609,12 +1641,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$3</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -1633,12 +1665,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$3</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1657,12 +1689,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$3</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -1681,12 +1713,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$3</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1705,12 +1737,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$3</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -1729,12 +1761,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$3</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1753,12 +1785,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$3</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -1777,12 +1809,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$3</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -1801,12 +1833,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$3</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$L$2:$L$4</f>
             </numRef>
           </val>
         </ser>
@@ -1948,7 +2004,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1970,7 +2026,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1992,7 +2048,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2019,7 +2075,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2046,7 +2102,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2383,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2552,10 +2608,55 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3">
+        <f>IF(ROW()=2,"",B4-B3)</f>
+        <v/>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2539</v>
+      </c>
+      <c r="E4" s="3">
+        <f>IF(ROW()=2,D4,D4-D3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>773</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>925</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2570,7 +2671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2666,10 +2767,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
@@ -2850,13 +2951,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1125</v>
+        <v>1155</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>979</v>
+        <v>1003</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>2</v>
@@ -2868,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -2942,10 +3043,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>1</v>
@@ -2988,10 +3089,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1</v>
@@ -3080,10 +3181,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -3106,6 +3207,52 @@
       </c>
       <c r="L11" s="6">
         <f>IFERROR(D11/E11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:59</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5">
+        <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
+        <v/>
+      </c>
+      <c r="L12" s="6">
+        <f>IFERROR(D12/E12,0)</f>
         <v/>
       </c>
     </row>
@@ -3121,9 +3268,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
 </worksheet>
 </file>
 
@@ -3133,7 +3281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3147,6 +3295,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3203,6 +3352,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>📩 « Jeudi 5 novembre, la Fra</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
     </row>
@@ -3232,6 +3386,7 @@
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3268,6 +3423,47 @@
       </c>
       <c r="K3" s="3" t="n">
         <v>7</v>
+      </c>
+      <c r="L3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>344</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3282,7 +3478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3296,7 +3492,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3357,6 +3554,11 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>📖 Il était une fois des agri</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -3408,7 +3610,11 @@
         <v/>
       </c>
       <c r="L2" s="3">
-        <f>SUM(B2:K2)</f>
+        <f>IF('Évolution par vidéo'!L2="","",'Évolution par vidéo'!L2)</f>
+        <v/>
+      </c>
+      <c r="M2" s="3">
+        <f>SUM(B2:L2)</f>
         <v/>
       </c>
     </row>
@@ -3459,7 +3665,66 @@
         <v/>
       </c>
       <c r="L3" s="3">
-        <f>SUM(B3:K3)</f>
+        <f>IF('Évolution par vidéo'!L3="","",'Évolution par vidéo'!L3-N('Évolution par vidéo'!L2))</f>
+        <v/>
+      </c>
+      <c r="M3" s="3">
+        <f>SUM(B3:L3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>IF('Évolution par vidéo'!B4="","",'Évolution par vidéo'!B4-N('Évolution par vidéo'!B3))</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>IF('Évolution par vidéo'!C4="","",'Évolution par vidéo'!C4-N('Évolution par vidéo'!C3))</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>IF('Évolution par vidéo'!D4="","",'Évolution par vidéo'!D4-N('Évolution par vidéo'!D3))</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>IF('Évolution par vidéo'!E4="","",'Évolution par vidéo'!E4-N('Évolution par vidéo'!E3))</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>IF('Évolution par vidéo'!F4="","",'Évolution par vidéo'!F4-N('Évolution par vidéo'!F3))</f>
+        <v/>
+      </c>
+      <c r="G4" s="3">
+        <f>IF('Évolution par vidéo'!G4="","",'Évolution par vidéo'!G4-N('Évolution par vidéo'!G3))</f>
+        <v/>
+      </c>
+      <c r="H4" s="3">
+        <f>IF('Évolution par vidéo'!H4="","",'Évolution par vidéo'!H4-N('Évolution par vidéo'!H3))</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
+        <f>IF('Évolution par vidéo'!I4="","",'Évolution par vidéo'!I4-N('Évolution par vidéo'!I3))</f>
+        <v/>
+      </c>
+      <c r="J4" s="3">
+        <f>IF('Évolution par vidéo'!J4="","",'Évolution par vidéo'!J4-N('Évolution par vidéo'!J3))</f>
+        <v/>
+      </c>
+      <c r="K4" s="3">
+        <f>IF('Évolution par vidéo'!K4="","",'Évolution par vidéo'!K4-N('Évolution par vidéo'!K3))</f>
+        <v/>
+      </c>
+      <c r="L4" s="3">
+        <f>IF('Évolution par vidéo'!L4="","",'Évolution par vidéo'!L4-N('Évolution par vidéo'!L3))</f>
+        <v/>
+      </c>
+      <c r="M4" s="3">
+        <f>SUM(B4:L4)</f>
         <v/>
       </c>
     </row>
@@ -3475,7 +3740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4005,7 +4270,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -4158,6 +4423,39 @@
         <v>0</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:00</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -4184,9 +4482,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -322,12 +322,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$21</f>
+              <f>'Stories'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$21</f>
+              <f>'Stories'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -808,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$12</f>
+              <f>'Vidéos'!$B$2:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2:$D$12</f>
+              <f>'Vidéos'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -910,12 +910,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$12</f>
+              <f>'Vidéos'!$B$2:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2:$F$12</f>
+              <f>'Vidéos'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -937,12 +937,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$12</f>
+              <f>'Vidéos'!$B$2:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2:$G$12</f>
+              <f>'Vidéos'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$12</f>
+              <f>'Vidéos'!$B$2:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2:$H$12</f>
+              <f>'Vidéos'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -991,12 +991,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$12</f>
+              <f>'Vidéos'!$B$2:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2:$I$12</f>
+              <f>'Vidéos'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -1093,12 +1093,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$12</f>
+              <f>'Vidéos'!$B$2:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2:$K$12</f>
+              <f>'Vidéos'!$K$2:$K$13</f>
             </numRef>
           </val>
         </ser>
@@ -1528,6 +1528,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$M$2:$M$4</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1863,6 +1895,30 @@
           <val>
             <numRef>
               <f>'Vues du jour par vidéo'!$L$2:$L$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$M$2:$M$4</f>
             </numRef>
           </val>
         </ser>
@@ -2004,7 +2060,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2026,7 +2082,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2048,7 +2104,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2608,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>4</v>
@@ -2628,26 +2684,26 @@
         <v/>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2539</v>
+        <v>2620</v>
       </c>
       <c r="E4" s="3">
         <f>IF(ROW()=2,D4,D4-D3)</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n">
-        <v>773</v>
+        <v>831</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -2656,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2671,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2767,10 +2823,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
@@ -2813,10 +2869,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2</v>
@@ -2905,10 +2961,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>4</v>
@@ -3089,10 +3145,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1</v>
@@ -3227,10 +3283,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>1</v>
@@ -3253,6 +3309,52 @@
       </c>
       <c r="L12" s="6">
         <f>IFERROR(D12/E12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:33</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="5">
+        <f>IFERROR((F13+G13+H13+I13)/IF(E13&gt;0,E13,D13),0)</f>
+        <v/>
+      </c>
+      <c r="L13" s="6">
+        <f>IFERROR(D13/E13,0)</f>
         <v/>
       </c>
     </row>
@@ -3269,210 +3371,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Jour</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>⚠️ Contenu effrayant… ou pas</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>👻 On ne parle que des casseu</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Et soudain, 718 stations san</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Les vitrines d'abord. Toi, a</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>📖 Il était une fois des agri</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>325</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>343</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1125</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>344</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1155</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>59</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3493,7 +3399,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3559,7 +3465,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Total du jour</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
     </row>
@@ -3569,6 +3475,220 @@
           <t>2026-10-18</t>
         </is>
       </c>
+      <c r="B2" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>343</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>345</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Jour</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>⚠️ Contenu effrayant… ou pas</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>👻 On ne parle que des casseu</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>😱 Ma réaction à ce qui t'att</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>🧮 Quiz : ta manif dégénère e</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Et soudain, 718 stations san</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Les vitrines d'abord. Toi, a</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>📖 Il était une fois des agri</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Couvre-feux, manifs « encadr</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Total du jour</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="B2" s="3">
         <f>IF('Évolution par vidéo'!B2="","",'Évolution par vidéo'!B2)</f>
         <v/>
@@ -3614,7 +3734,11 @@
         <v/>
       </c>
       <c r="M2" s="3">
-        <f>SUM(B2:L2)</f>
+        <f>IF('Évolution par vidéo'!M2="","",'Évolution par vidéo'!M2)</f>
+        <v/>
+      </c>
+      <c r="N2" s="3">
+        <f>SUM(B2:M2)</f>
         <v/>
       </c>
     </row>
@@ -3669,7 +3793,11 @@
         <v/>
       </c>
       <c r="M3" s="3">
-        <f>SUM(B3:L3)</f>
+        <f>IF('Évolution par vidéo'!M3="","",'Évolution par vidéo'!M3-N('Évolution par vidéo'!M2))</f>
+        <v/>
+      </c>
+      <c r="N3" s="3">
+        <f>SUM(B3:M3)</f>
         <v/>
       </c>
     </row>
@@ -3724,7 +3852,11 @@
         <v/>
       </c>
       <c r="M4" s="3">
-        <f>SUM(B4:L4)</f>
+        <f>IF('Évolution par vidéo'!M4="","",'Évolution par vidéo'!M4-N('Évolution par vidéo'!M3))</f>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f>SUM(B4:M4)</f>
         <v/>
       </c>
     </row>
@@ -3740,7 +3872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4435,7 +4567,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -4456,6 +4588,138 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 08:15</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:34</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:34</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:38</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -4483,9 +4747,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -220,12 +220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$4</f>
+              <f>'Jour par jour'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -322,12 +322,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$25</f>
+              <f>'Stories'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$25</f>
+              <f>'Stories'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$4</f>
+              <f>'Jour par jour'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$4</f>
+              <f>'Jour par jour'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -564,12 +564,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$4</f>
+              <f>'Jour par jour'!$F$2:$F$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -604,12 +604,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$4</f>
+              <f>'Jour par jour'!$H$2:$H$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -706,12 +706,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$4</f>
+              <f>'Jour par jour'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -808,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$13</f>
+              <f>'Vidéos'!$B$2:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2:$D$13</f>
+              <f>'Vidéos'!$D$2:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -910,12 +910,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$13</f>
+              <f>'Vidéos'!$B$2:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2:$F$13</f>
+              <f>'Vidéos'!$F$2:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -937,12 +937,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$13</f>
+              <f>'Vidéos'!$B$2:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2:$G$13</f>
+              <f>'Vidéos'!$G$2:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$13</f>
+              <f>'Vidéos'!$B$2:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2:$H$13</f>
+              <f>'Vidéos'!$H$2:$H$14</f>
             </numRef>
           </val>
         </ser>
@@ -991,12 +991,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$13</f>
+              <f>'Vidéos'!$B$2:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2:$I$13</f>
+              <f>'Vidéos'!$I$2:$I$14</f>
             </numRef>
           </val>
         </ser>
@@ -1093,12 +1093,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$13</f>
+              <f>'Vidéos'!$B$2:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2:$K$13</f>
+              <f>'Vidéos'!$K$2:$K$14</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$4</f>
+              <f>'Évolution par vidéo'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1231,12 +1231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$4</f>
+              <f>'Évolution par vidéo'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1263,12 +1263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$4</f>
+              <f>'Évolution par vidéo'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1295,12 +1295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$4</f>
+              <f>'Évolution par vidéo'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1327,12 +1327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$4</f>
+              <f>'Évolution par vidéo'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1359,12 +1359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$4</f>
+              <f>'Évolution par vidéo'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1391,12 +1391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$4</f>
+              <f>'Évolution par vidéo'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$4</f>
+              <f>'Évolution par vidéo'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1455,12 +1455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$4</f>
+              <f>'Évolution par vidéo'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1487,12 +1487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$4</f>
+              <f>'Évolution par vidéo'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -1519,12 +1519,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$4</f>
+              <f>'Évolution par vidéo'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1551,12 +1551,44 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$4</f>
+              <f>'Évolution par vidéo'!$M$2:$M$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$N$2:$N$5</f>
             </numRef>
           </val>
         </ser>
@@ -1649,12 +1681,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$4</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1673,12 +1705,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$4</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1697,12 +1729,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$4</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1721,12 +1753,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$4</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1745,12 +1777,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$4</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1769,12 +1801,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$4</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1825,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$4</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1817,12 +1849,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$4</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1841,12 +1873,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$4</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1865,12 +1897,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$4</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -1889,12 +1921,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$4</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1913,12 +1945,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$4</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$N$2:$N$5</f>
             </numRef>
           </val>
         </ser>
@@ -2060,7 +2116,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2082,7 +2138,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2104,7 +2160,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2131,7 +2187,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2158,7 +2214,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2495,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2709,10 +2765,55 @@
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3">
+        <f>IF(ROW()=2,"",B5-B4)</f>
+        <v/>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2793</v>
+      </c>
+      <c r="E5" s="3">
+        <f>IF(ROW()=2,D5,D5-D4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2727,7 +2828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2823,10 +2924,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
@@ -3283,10 +3384,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>1</v>
@@ -3329,10 +3430,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>2</v>
@@ -3355,6 +3456,52 @@
       </c>
       <c r="L13" s="6">
         <f>IFERROR(D13/E13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:07</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <f>IFERROR((F14+G14+H14+I14)/IF(E14&gt;0,E14,D14),0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="6">
+        <f>IFERROR(D14/E14,0)</f>
         <v/>
       </c>
     </row>
@@ -3372,9 +3519,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -3384,7 +3532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3400,6 +3548,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3466,6 +3615,11 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Couvre-feux, manifs « encadr</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
     </row>
@@ -3497,6 +3651,7 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3536,6 +3691,7 @@
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3578,6 +3734,53 @@
       </c>
       <c r="M4" s="3" t="n">
         <v>63</v>
+      </c>
+      <c r="N4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>348</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3592,7 +3795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3608,7 +3811,8 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3679,6 +3883,11 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Couvre-feu pour les ados, 5,</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -3738,7 +3947,11 @@
         <v/>
       </c>
       <c r="N2" s="3">
-        <f>SUM(B2:M2)</f>
+        <f>IF('Évolution par vidéo'!N2="","",'Évolution par vidéo'!N2)</f>
+        <v/>
+      </c>
+      <c r="O2" s="3">
+        <f>SUM(B2:N2)</f>
         <v/>
       </c>
     </row>
@@ -3797,7 +4010,11 @@
         <v/>
       </c>
       <c r="N3" s="3">
-        <f>SUM(B3:M3)</f>
+        <f>IF('Évolution par vidéo'!N3="","",'Évolution par vidéo'!N3-N('Évolution par vidéo'!N2))</f>
+        <v/>
+      </c>
+      <c r="O3" s="3">
+        <f>SUM(B3:N3)</f>
         <v/>
       </c>
     </row>
@@ -3856,7 +4073,74 @@
         <v/>
       </c>
       <c r="N4" s="3">
-        <f>SUM(B4:M4)</f>
+        <f>IF('Évolution par vidéo'!N4="","",'Évolution par vidéo'!N4-N('Évolution par vidéo'!N3))</f>
+        <v/>
+      </c>
+      <c r="O4" s="3">
+        <f>SUM(B4:N4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>IF('Évolution par vidéo'!B5="","",'Évolution par vidéo'!B5-N('Évolution par vidéo'!B4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>IF('Évolution par vidéo'!C5="","",'Évolution par vidéo'!C5-N('Évolution par vidéo'!C4))</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>IF('Évolution par vidéo'!D5="","",'Évolution par vidéo'!D5-N('Évolution par vidéo'!D4))</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>IF('Évolution par vidéo'!E5="","",'Évolution par vidéo'!E5-N('Évolution par vidéo'!E4))</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>IF('Évolution par vidéo'!F5="","",'Évolution par vidéo'!F5-N('Évolution par vidéo'!F4))</f>
+        <v/>
+      </c>
+      <c r="G5" s="3">
+        <f>IF('Évolution par vidéo'!G5="","",'Évolution par vidéo'!G5-N('Évolution par vidéo'!G4))</f>
+        <v/>
+      </c>
+      <c r="H5" s="3">
+        <f>IF('Évolution par vidéo'!H5="","",'Évolution par vidéo'!H5-N('Évolution par vidéo'!H4))</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
+        <f>IF('Évolution par vidéo'!I5="","",'Évolution par vidéo'!I5-N('Évolution par vidéo'!I4))</f>
+        <v/>
+      </c>
+      <c r="J5" s="3">
+        <f>IF('Évolution par vidéo'!J5="","",'Évolution par vidéo'!J5-N('Évolution par vidéo'!J4))</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
+        <f>IF('Évolution par vidéo'!K5="","",'Évolution par vidéo'!K5-N('Évolution par vidéo'!K4))</f>
+        <v/>
+      </c>
+      <c r="L5" s="3">
+        <f>IF('Évolution par vidéo'!L5="","",'Évolution par vidéo'!L5-N('Évolution par vidéo'!L4))</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
+        <f>IF('Évolution par vidéo'!M5="","",'Évolution par vidéo'!M5-N('Évolution par vidéo'!M4))</f>
+        <v/>
+      </c>
+      <c r="N5" s="3">
+        <f>IF('Évolution par vidéo'!N5="","",'Évolution par vidéo'!N5-N('Évolution par vidéo'!N4))</f>
+        <v/>
+      </c>
+      <c r="O5" s="3">
+        <f>SUM(B5:N5)</f>
         <v/>
       </c>
     </row>
@@ -3872,7 +4156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4600,7 +4884,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -4633,7 +4917,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0</v>
@@ -4648,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0</v>
@@ -4720,6 +5004,72 @@
         <v>0</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:07</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 07:20</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -4751,9 +5101,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -322,12 +322,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$27</f>
+              <f>'Stories'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$27</f>
+              <f>'Stories'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -808,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$14</f>
+              <f>'Vidéos'!$B$2:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2:$D$14</f>
+              <f>'Vidéos'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -910,12 +910,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$14</f>
+              <f>'Vidéos'!$B$2:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2:$F$14</f>
+              <f>'Vidéos'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -937,12 +937,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$14</f>
+              <f>'Vidéos'!$B$2:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2:$G$14</f>
+              <f>'Vidéos'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$14</f>
+              <f>'Vidéos'!$B$2:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2:$H$14</f>
+              <f>'Vidéos'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -991,12 +991,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$14</f>
+              <f>'Vidéos'!$B$2:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2:$I$14</f>
+              <f>'Vidéos'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -1093,12 +1093,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$14</f>
+              <f>'Vidéos'!$B$2:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2:$K$14</f>
+              <f>'Vidéos'!$K$2:$K$16</f>
             </numRef>
           </val>
         </ser>
@@ -1592,6 +1592,70 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!O1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$O$2:$O$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!P1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$P$2:$P$5</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1975,6 +2039,54 @@
           <val>
             <numRef>
               <f>'Vues du jour par vidéo'!$N$2:$N$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!O1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$O$2:$O$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!P1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$P$2:$P$5</f>
             </numRef>
           </val>
         </ser>
@@ -2116,7 +2228,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2138,7 +2250,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2160,7 +2272,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2765,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>1</v>
@@ -2785,17 +2897,17 @@
         <v/>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2793</v>
+        <v>2977</v>
       </c>
       <c r="E5" s="3">
         <f>IF(ROW()=2,D5,D5-D4)</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n">
-        <v>224</v>
+        <v>363</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>264</v>
+        <v>453</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>4</v>
@@ -2804,16 +2916,16 @@
         <v>4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2828,7 +2940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3430,10 +3542,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>140</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>126</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>2</v>
@@ -3476,10 +3588,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -3502,6 +3614,98 @@
       </c>
       <c r="L14" s="6">
         <f>IFERROR(D14/E14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:03</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5">
+        <f>IFERROR((F15+G15+H15+I15)/IF(E15&gt;0,E15,D15),0)</f>
+        <v/>
+      </c>
+      <c r="L15" s="6">
+        <f>IFERROR(D15/E15,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:07</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>À toi de juger : taxer les profits du pétrole</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <f>IFERROR((F16+G16+H16+I16)/IF(E16&gt;0,E16,D16),0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="6">
+        <f>IFERROR(D16/E16,0)</f>
         <v/>
       </c>
     </row>
@@ -3520,9 +3724,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -3532,7 +3738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3549,6 +3755,8 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3620,6 +3828,16 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Couvre-feu pour les ados, 5,</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Les syndicats de salariés au</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
     </row>
@@ -3652,6 +3870,8 @@
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3692,6 +3912,8 @@
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3736,6 +3958,8 @@
         <v>63</v>
       </c>
       <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3777,10 +4001,16 @@
         <v>79</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>87</v>
+        <v>105</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3795,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3812,7 +4042,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3888,6 +4120,16 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Les syndicats de salariés au</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>À toi de juger : taxer les p</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -3951,7 +4193,15 @@
         <v/>
       </c>
       <c r="O2" s="3">
-        <f>SUM(B2:N2)</f>
+        <f>IF('Évolution par vidéo'!O2="","",'Évolution par vidéo'!O2)</f>
+        <v/>
+      </c>
+      <c r="P2" s="3">
+        <f>IF('Évolution par vidéo'!P2="","",'Évolution par vidéo'!P2)</f>
+        <v/>
+      </c>
+      <c r="Q2" s="3">
+        <f>SUM(B2:P2)</f>
         <v/>
       </c>
     </row>
@@ -4014,7 +4264,15 @@
         <v/>
       </c>
       <c r="O3" s="3">
-        <f>SUM(B3:N3)</f>
+        <f>IF('Évolution par vidéo'!O3="","",'Évolution par vidéo'!O3-N('Évolution par vidéo'!O2))</f>
+        <v/>
+      </c>
+      <c r="P3" s="3">
+        <f>IF('Évolution par vidéo'!P3="","",'Évolution par vidéo'!P3-N('Évolution par vidéo'!P2))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="3">
+        <f>SUM(B3:P3)</f>
         <v/>
       </c>
     </row>
@@ -4077,7 +4335,15 @@
         <v/>
       </c>
       <c r="O4" s="3">
-        <f>SUM(B4:N4)</f>
+        <f>IF('Évolution par vidéo'!O4="","",'Évolution par vidéo'!O4-N('Évolution par vidéo'!O3))</f>
+        <v/>
+      </c>
+      <c r="P4" s="3">
+        <f>IF('Évolution par vidéo'!P4="","",'Évolution par vidéo'!P4-N('Évolution par vidéo'!P3))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="3">
+        <f>SUM(B4:P4)</f>
         <v/>
       </c>
     </row>
@@ -4140,7 +4406,15 @@
         <v/>
       </c>
       <c r="O5" s="3">
-        <f>SUM(B5:N5)</f>
+        <f>IF('Évolution par vidéo'!O5="","",'Évolution par vidéo'!O5-N('Évolution par vidéo'!O4))</f>
+        <v/>
+      </c>
+      <c r="P5" s="3">
+        <f>IF('Évolution par vidéo'!P5="","",'Évolution par vidéo'!P5-N('Évolution par vidéo'!P4))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="3">
+        <f>SUM(B5:P5)</f>
         <v/>
       </c>
     </row>
@@ -4156,7 +4430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5016,7 +5290,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>0</v>
@@ -5049,7 +5323,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0</v>
@@ -5070,6 +5344,105 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:03</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:05</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:08</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -5103,9 +5476,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -220,12 +220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$5</f>
+              <f>'Jour par jour'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -322,12 +322,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$30</f>
+              <f>'Stories'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$30</f>
+              <f>'Stories'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$5</f>
+              <f>'Jour par jour'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$5</f>
+              <f>'Jour par jour'!$L$2:$L$6</f>
             </numRef>
           </val>
         </ser>
@@ -564,12 +564,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$5</f>
+              <f>'Jour par jour'!$F$2:$F$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -604,12 +604,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$5</f>
+              <f>'Jour par jour'!$H$2:$H$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -706,12 +706,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$5</f>
+              <f>'Jour par jour'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$5</f>
+              <f>'Évolution par vidéo'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -1231,12 +1231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$5</f>
+              <f>'Évolution par vidéo'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1263,12 +1263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$5</f>
+              <f>'Évolution par vidéo'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -1295,12 +1295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$5</f>
+              <f>'Évolution par vidéo'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -1327,12 +1327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$5</f>
+              <f>'Évolution par vidéo'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -1359,12 +1359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$5</f>
+              <f>'Évolution par vidéo'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -1391,12 +1391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$5</f>
+              <f>'Évolution par vidéo'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$5</f>
+              <f>'Évolution par vidéo'!$I$2:$I$6</f>
             </numRef>
           </val>
         </ser>
@@ -1455,12 +1455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$5</f>
+              <f>'Évolution par vidéo'!$J$2:$J$6</f>
             </numRef>
           </val>
         </ser>
@@ -1487,12 +1487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$5</f>
+              <f>'Évolution par vidéo'!$K$2:$K$6</f>
             </numRef>
           </val>
         </ser>
@@ -1519,12 +1519,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$5</f>
+              <f>'Évolution par vidéo'!$L$2:$L$6</f>
             </numRef>
           </val>
         </ser>
@@ -1551,12 +1551,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$5</f>
+              <f>'Évolution par vidéo'!$M$2:$M$6</f>
             </numRef>
           </val>
         </ser>
@@ -1583,12 +1583,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$5</f>
+              <f>'Évolution par vidéo'!$N$2:$N$6</f>
             </numRef>
           </val>
         </ser>
@@ -1615,12 +1615,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$5</f>
+              <f>'Évolution par vidéo'!$O$2:$O$6</f>
             </numRef>
           </val>
         </ser>
@@ -1647,12 +1647,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$5</f>
+              <f>'Évolution par vidéo'!$P$2:$P$6</f>
             </numRef>
           </val>
         </ser>
@@ -1745,12 +1745,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$5</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -1769,12 +1769,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$5</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$5</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -1817,12 +1817,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$5</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -1841,12 +1841,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$5</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -1865,12 +1865,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$5</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -1889,12 +1889,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$5</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -1913,12 +1913,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$5</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$6</f>
             </numRef>
           </val>
         </ser>
@@ -1937,12 +1937,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$5</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$6</f>
             </numRef>
           </val>
         </ser>
@@ -1961,12 +1961,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$5</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$6</f>
             </numRef>
           </val>
         </ser>
@@ -1985,12 +1985,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$5</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$6</f>
             </numRef>
           </val>
         </ser>
@@ -2009,12 +2009,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$5</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$6</f>
             </numRef>
           </val>
         </ser>
@@ -2033,12 +2033,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$5</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$6</f>
             </numRef>
           </val>
         </ser>
@@ -2057,12 +2057,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$5</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$6</f>
             </numRef>
           </val>
         </ser>
@@ -2081,12 +2081,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$5</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$6</f>
             </numRef>
           </val>
         </ser>
@@ -2299,7 +2299,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2326,7 +2326,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2663,7 +2663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2922,10 +2922,55 @@
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3">
+        <f>IF(ROW()=2,"",B6-B5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2825</v>
+      </c>
+      <c r="E6" s="3">
+        <f>IF(ROW()=2,D6,D6-D5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>319</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>394</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3022,12 +3067,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 19:08</t>
+          <t>2026-10-18 10:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Contenu effrayant… ou pas ? Le 17 octobre,</t>
+          <t>FLASH SPÉCIAL 🚨 550 000 ou 800 000 ? Le bilan</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -3036,13 +3081,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>348</v>
+        <v>133</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -3054,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -3068,12 +3113,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 10:14</t>
+          <t>2026-10-18 10:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FLASH SPÉCIAL 🚨 550 000 ou 800 000 ? Le bilan</t>
+          <t>POV : ta mamie t'écrit « ma retraite va baiss</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3082,10 +3127,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2</v>
@@ -3114,12 +3159,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 10:34</t>
+          <t>2026-10-18 13:04</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>POV : ta mamie t'écrit « ma retraite va baiss</t>
+          <t>👻 On ne parle que des casseurs… et les revend</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3128,13 +3173,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -3146,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -3160,12 +3205,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:04</t>
+          <t>2026-10-18 13:52</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseurs… et les revend</t>
+          <t>👑 Vendredi soir : Macron au concert de Céline</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3174,16 +3219,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>191</v>
+        <v>1155</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>171</v>
+        <v>1003</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -3192,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K5" s="5">
         <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
@@ -3206,12 +3251,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:52</t>
+          <t>2026-10-18 20:18</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>👑 Vendredi soir : Macron au concert de Céline</t>
+          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3220,25 +3265,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1155</v>
+        <v>121</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1003</v>
+        <v>109</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>20</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -3252,12 +3297,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 20:18</t>
+          <t>2026-10-19 06:14</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
+          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3266,13 +3311,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -3284,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5">
         <f>IFERROR((F7+G7+H7+I7)/IF(E7&gt;0,E7,D7),0)</f>
@@ -3298,12 +3343,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 06:14</t>
+          <t>2026-10-19 08:14</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
+          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3312,10 +3357,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>1</v>
@@ -3344,12 +3389,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:14</t>
+          <t>2026-10-19 09:09</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
+          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3358,10 +3403,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1</v>
@@ -3390,12 +3435,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-19 12:05</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3404,13 +3449,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -3422,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
@@ -3436,12 +3481,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3450,13 +3495,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -3468,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
@@ -3482,12 +3527,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3496,13 +3541,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -3511,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
@@ -3528,12 +3573,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3542,13 +3587,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -3557,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="5">
         <f>IFERROR((F13+G13+H13+I13)/IF(E13&gt;0,E13,D13),0)</f>
@@ -3574,12 +3619,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3591,10 +3636,10 @@
         <v>105</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -3606,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="5">
         <f>IFERROR((F14+G14+H14+I14)/IF(E14&gt;0,E14,D14),0)</f>
@@ -3620,12 +3665,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3634,13 +3679,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -3666,12 +3711,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3680,10 +3725,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -3698,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5">
         <f>IFERROR((F16+G16+H16+I16)/IF(E16&gt;0,E16,D16),0)</f>
@@ -3738,7 +3783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3767,77 +3812,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Contenu effrayant… ou pas</t>
+          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
+          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+          <t>👻 On ne parle que des casseu</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseu</t>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
     </row>
@@ -3848,20 +3893,18 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>325</v>
+        <v>118</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="F2" s="3" t="n">
         <v>174</v>
       </c>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
@@ -3880,35 +3923,33 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>343</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1125</v>
-      </c>
       <c r="G3" s="3" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="K3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
@@ -3922,41 +3963,39 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>345</v>
+        <v>133</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1155</v>
-      </c>
       <c r="G4" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="M4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
@@ -3968,49 +4007,99 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>348</v>
+        <v>133</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="P5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="C6" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>1155</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="F6" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>157</v>
-      </c>
-      <c r="N5" s="3" t="n">
+      <c r="L6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="O5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>69</v>
+      <c r="O6" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4025,7 +4114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4055,77 +4144,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Contenu effrayant… ou pas</t>
+          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
+          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+          <t>👻 On ne parle que des casseu</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseu</t>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -4415,6 +4504,77 @@
       </c>
       <c r="Q5" s="3">
         <f>SUM(B5:P5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>IF('Évolution par vidéo'!B6="","",'Évolution par vidéo'!B6-N('Évolution par vidéo'!B5))</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>IF('Évolution par vidéo'!C6="","",'Évolution par vidéo'!C6-N('Évolution par vidéo'!C5))</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>IF('Évolution par vidéo'!D6="","",'Évolution par vidéo'!D6-N('Évolution par vidéo'!D5))</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>IF('Évolution par vidéo'!E6="","",'Évolution par vidéo'!E6-N('Évolution par vidéo'!E5))</f>
+        <v/>
+      </c>
+      <c r="F6" s="3">
+        <f>IF('Évolution par vidéo'!F6="","",'Évolution par vidéo'!F6-N('Évolution par vidéo'!F5))</f>
+        <v/>
+      </c>
+      <c r="G6" s="3">
+        <f>IF('Évolution par vidéo'!G6="","",'Évolution par vidéo'!G6-N('Évolution par vidéo'!G5))</f>
+        <v/>
+      </c>
+      <c r="H6" s="3">
+        <f>IF('Évolution par vidéo'!H6="","",'Évolution par vidéo'!H6-N('Évolution par vidéo'!H5))</f>
+        <v/>
+      </c>
+      <c r="I6" s="3">
+        <f>IF('Évolution par vidéo'!I6="","",'Évolution par vidéo'!I6-N('Évolution par vidéo'!I5))</f>
+        <v/>
+      </c>
+      <c r="J6" s="3">
+        <f>IF('Évolution par vidéo'!J6="","",'Évolution par vidéo'!J6-N('Évolution par vidéo'!J5))</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>IF('Évolution par vidéo'!K6="","",'Évolution par vidéo'!K6-N('Évolution par vidéo'!K5))</f>
+        <v/>
+      </c>
+      <c r="L6" s="3">
+        <f>IF('Évolution par vidéo'!L6="","",'Évolution par vidéo'!L6-N('Évolution par vidéo'!L5))</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
+        <f>IF('Évolution par vidéo'!M6="","",'Évolution par vidéo'!M6-N('Évolution par vidéo'!M5))</f>
+        <v/>
+      </c>
+      <c r="N6" s="3">
+        <f>IF('Évolution par vidéo'!N6="","",'Évolution par vidéo'!N6-N('Évolution par vidéo'!N5))</f>
+        <v/>
+      </c>
+      <c r="O6" s="3">
+        <f>IF('Évolution par vidéo'!O6="","",'Évolution par vidéo'!O6-N('Évolution par vidéo'!O5))</f>
+        <v/>
+      </c>
+      <c r="P6" s="3">
+        <f>IF('Évolution par vidéo'!P6="","",'Évolution par vidéo'!P6-N('Évolution par vidéo'!P5))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="3">
+        <f>SUM(B6:P6)</f>
         <v/>
       </c>
     </row>
@@ -4430,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5356,7 +5516,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -5389,7 +5549,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0</v>
@@ -5443,6 +5603,72 @@
         <v>0</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:05</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 16:09</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -5479,9 +5705,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -322,12 +322,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$32</f>
+              <f>'Stories'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$32</f>
+              <f>'Stories'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -2942,17 +2942,17 @@
         <v/>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2825</v>
+        <v>2728</v>
       </c>
       <c r="E6" s="3">
         <f>IF(ROW()=2,D6,D6-D5)</f>
         <v/>
       </c>
       <c r="F6" s="3" t="n">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>2</v>
@@ -2967,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3067,12 +3067,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 10:14</t>
+          <t>2026-10-18 10:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FLASH SPÉCIAL 🚨 550 000 ou 800 000 ? Le bilan</t>
+          <t>POV : ta mamie t'écrit « ma retraite va baiss</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2</v>
@@ -3113,12 +3113,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 10:34</t>
+          <t>2026-10-18 13:04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>POV : ta mamie t'écrit « ma retraite va baiss</t>
+          <t>👻 On ne parle que des casseurs… et les revend</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
@@ -3159,12 +3159,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:04</t>
+          <t>2026-10-18 13:52</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseurs… et les revend</t>
+          <t>👑 Vendredi soir : Macron au concert de Céline</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3173,16 +3173,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>191</v>
+        <v>1155</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>171</v>
+        <v>1003</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -3205,12 +3205,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:52</t>
+          <t>2026-10-18 20:18</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>👑 Vendredi soir : Macron au concert de Céline</t>
+          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3219,25 +3219,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1155</v>
+        <v>121</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1003</v>
+        <v>109</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>20</v>
       </c>
       <c r="K5" s="5">
         <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
@@ -3251,12 +3251,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 20:18</t>
+          <t>2026-10-19 06:14</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
+          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -3297,12 +3297,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 06:14</t>
+          <t>2026-10-19 08:14</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
+          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>1</v>
@@ -3343,12 +3343,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:14</t>
+          <t>2026-10-19 09:09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
+          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>1</v>
@@ -3389,12 +3389,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-19 12:05</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -3421,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
         <f>IFERROR((F9+G9+H9+I9)/IF(E9&gt;0,E9,D9),0)</f>
@@ -3435,12 +3435,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
@@ -3481,12 +3481,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3495,13 +3495,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -3510,10 +3510,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
@@ -3527,12 +3527,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
@@ -3573,12 +3573,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="5">
         <f>IFERROR((F13+G13+H13+I13)/IF(E13&gt;0,E13,D13),0)</f>
@@ -3619,12 +3619,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3633,13 +3633,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>85</v>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -3665,12 +3665,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="5">
         <f>IFERROR((F15+G15+H15+I15)/IF(E15&gt;0,E15,D15),0)</f>
@@ -3711,12 +3711,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:08</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou non ? Réponds en co</t>
+          <t>Couper les réseaux sociaux pendant les émeute</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -3812,77 +3812,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
+          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+          <t>👻 On ne parle que des casseu</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseu</t>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
     </row>
@@ -3893,17 +3893,15 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="E2" s="3" t="n">
         <v>174</v>
       </c>
+      <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
@@ -3923,32 +3921,30 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1125</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="J3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
@@ -3963,38 +3959,36 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1155</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
@@ -4007,47 +4001,45 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1155</v>
-      </c>
       <c r="F5" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="O5" s="3" t="n">
         <v>69</v>
       </c>
+      <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
     </row>
     <row r="6">
@@ -4057,49 +4049,49 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>191</v>
+        <v>1155</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1155</v>
+        <v>121</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>126</v>
-      </c>
       <c r="P6" s="3" t="n">
-        <v>111</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -4144,77 +4136,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FLASH SPÉCIAL 🚨 550 000 ou 8</t>
+          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+          <t>👻 On ne parle que des casseu</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseu</t>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -4590,7 +4582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5669,6 +5661,72 @@
         <v>1</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 08:13</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:09</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -5707,9 +5765,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId34"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -220,12 +220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$6</f>
+              <f>'Jour par jour'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -424,12 +424,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$6</f>
+              <f>'Jour par jour'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$6</f>
+              <f>'Jour par jour'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -564,12 +564,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$6</f>
+              <f>'Jour par jour'!$F$2:$F$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -604,12 +604,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$6</f>
+              <f>'Jour par jour'!$H$2:$H$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -706,12 +706,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$6</f>
+              <f>'Jour par jour'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$6</f>
+              <f>'Évolution par vidéo'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1231,12 +1231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$6</f>
+              <f>'Évolution par vidéo'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1263,12 +1263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$6</f>
+              <f>'Évolution par vidéo'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1295,12 +1295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$6</f>
+              <f>'Évolution par vidéo'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1327,12 +1327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$6</f>
+              <f>'Évolution par vidéo'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1359,12 +1359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$6</f>
+              <f>'Évolution par vidéo'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1391,12 +1391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$6</f>
+              <f>'Évolution par vidéo'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$6</f>
+              <f>'Évolution par vidéo'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1455,12 +1455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$6</f>
+              <f>'Évolution par vidéo'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1487,12 +1487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$6</f>
+              <f>'Évolution par vidéo'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -1519,12 +1519,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$6</f>
+              <f>'Évolution par vidéo'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -1551,12 +1551,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$6</f>
+              <f>'Évolution par vidéo'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -1583,12 +1583,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$6</f>
+              <f>'Évolution par vidéo'!$N$2:$N$7</f>
             </numRef>
           </val>
         </ser>
@@ -1615,12 +1615,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$6</f>
+              <f>'Évolution par vidéo'!$O$2:$O$7</f>
             </numRef>
           </val>
         </ser>
@@ -1647,12 +1647,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$6</f>
+              <f>'Évolution par vidéo'!$P$2:$P$7</f>
             </numRef>
           </val>
         </ser>
@@ -1745,12 +1745,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$6</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1769,12 +1769,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$6</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$6</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1817,12 +1817,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$6</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1841,12 +1841,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$6</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1865,12 +1865,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$6</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1889,12 +1889,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$6</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1913,12 +1913,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$6</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1937,12 +1937,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$6</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1961,12 +1961,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$6</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -1985,12 +1985,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$6</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -2009,12 +2009,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$6</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -2033,12 +2033,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$6</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$7</f>
             </numRef>
           </val>
         </ser>
@@ -2057,12 +2057,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$6</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$7</f>
             </numRef>
           </val>
         </ser>
@@ -2081,12 +2081,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$6</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$7</f>
             </numRef>
           </val>
         </ser>
@@ -2299,7 +2299,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2326,7 +2326,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2663,7 +2663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2967,10 +2967,55 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3">
+        <f>IF(ROW()=2,"",B7-B6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2749</v>
+      </c>
+      <c r="E7" s="3">
+        <f>IF(ROW()=2,D7,D7-D6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3725,10 +3770,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -3783,7 +3828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4094,6 +4139,58 @@
         <v>32</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4106,7 +4203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4567,6 +4664,77 @@
       </c>
       <c r="Q6" s="3">
         <f>SUM(B6:P6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>IF('Évolution par vidéo'!B7="","",'Évolution par vidéo'!B7-N('Évolution par vidéo'!B6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>IF('Évolution par vidéo'!C7="","",'Évolution par vidéo'!C7-N('Évolution par vidéo'!C6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>IF('Évolution par vidéo'!D7="","",'Évolution par vidéo'!D7-N('Évolution par vidéo'!D6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>IF('Évolution par vidéo'!E7="","",'Évolution par vidéo'!E7-N('Évolution par vidéo'!E6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="3">
+        <f>IF('Évolution par vidéo'!F7="","",'Évolution par vidéo'!F7-N('Évolution par vidéo'!F6))</f>
+        <v/>
+      </c>
+      <c r="G7" s="3">
+        <f>IF('Évolution par vidéo'!G7="","",'Évolution par vidéo'!G7-N('Évolution par vidéo'!G6))</f>
+        <v/>
+      </c>
+      <c r="H7" s="3">
+        <f>IF('Évolution par vidéo'!H7="","",'Évolution par vidéo'!H7-N('Évolution par vidéo'!H6))</f>
+        <v/>
+      </c>
+      <c r="I7" s="3">
+        <f>IF('Évolution par vidéo'!I7="","",'Évolution par vidéo'!I7-N('Évolution par vidéo'!I6))</f>
+        <v/>
+      </c>
+      <c r="J7" s="3">
+        <f>IF('Évolution par vidéo'!J7="","",'Évolution par vidéo'!J7-N('Évolution par vidéo'!J6))</f>
+        <v/>
+      </c>
+      <c r="K7" s="3">
+        <f>IF('Évolution par vidéo'!K7="","",'Évolution par vidéo'!K7-N('Évolution par vidéo'!K6))</f>
+        <v/>
+      </c>
+      <c r="L7" s="3">
+        <f>IF('Évolution par vidéo'!L7="","",'Évolution par vidéo'!L7-N('Évolution par vidéo'!L6))</f>
+        <v/>
+      </c>
+      <c r="M7" s="3">
+        <f>IF('Évolution par vidéo'!M7="","",'Évolution par vidéo'!M7-N('Évolution par vidéo'!M6))</f>
+        <v/>
+      </c>
+      <c r="N7" s="3">
+        <f>IF('Évolution par vidéo'!N7="","",'Évolution par vidéo'!N7-N('Évolution par vidéo'!N6))</f>
+        <v/>
+      </c>
+      <c r="O7" s="3">
+        <f>IF('Évolution par vidéo'!O7="","",'Évolution par vidéo'!O7-N('Évolution par vidéo'!O6))</f>
+        <v/>
+      </c>
+      <c r="P7" s="3">
+        <f>IF('Évolution par vidéo'!P7="","",'Évolution par vidéo'!P7-N('Évolution par vidéo'!P6))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="3">
+        <f>SUM(B7:P7)</f>
         <v/>
       </c>
     </row>
@@ -5673,7 +5841,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>0</v>
@@ -5706,7 +5874,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -2987,17 +2987,17 @@
         <v/>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2749</v>
+        <v>2770</v>
       </c>
       <c r="E7" s="3">
         <f>IF(ROW()=2,D7,D7-D6)</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>113</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -220,12 +220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$7</f>
+              <f>'Jour par jour'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -424,12 +424,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$7</f>
+              <f>'Jour par jour'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$7</f>
+              <f>'Jour par jour'!$L$2:$L$8</f>
             </numRef>
           </val>
         </ser>
@@ -564,12 +564,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$7</f>
+              <f>'Jour par jour'!$F$2:$F$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -604,12 +604,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$7</f>
+              <f>'Jour par jour'!$H$2:$H$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -706,12 +706,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$7</f>
+              <f>'Jour par jour'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$7</f>
+              <f>'Évolution par vidéo'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1231,12 +1231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$7</f>
+              <f>'Évolution par vidéo'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1263,12 +1263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$7</f>
+              <f>'Évolution par vidéo'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -1295,12 +1295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$7</f>
+              <f>'Évolution par vidéo'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -1327,12 +1327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$7</f>
+              <f>'Évolution par vidéo'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -1359,12 +1359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$7</f>
+              <f>'Évolution par vidéo'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -1391,12 +1391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$7</f>
+              <f>'Évolution par vidéo'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$7</f>
+              <f>'Évolution par vidéo'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -1455,12 +1455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$7</f>
+              <f>'Évolution par vidéo'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -1487,12 +1487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$7</f>
+              <f>'Évolution par vidéo'!$K$2:$K$8</f>
             </numRef>
           </val>
         </ser>
@@ -1519,12 +1519,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$7</f>
+              <f>'Évolution par vidéo'!$L$2:$L$8</f>
             </numRef>
           </val>
         </ser>
@@ -1551,12 +1551,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$7</f>
+              <f>'Évolution par vidéo'!$M$2:$M$8</f>
             </numRef>
           </val>
         </ser>
@@ -1583,12 +1583,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$7</f>
+              <f>'Évolution par vidéo'!$N$2:$N$8</f>
             </numRef>
           </val>
         </ser>
@@ -1615,12 +1615,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$7</f>
+              <f>'Évolution par vidéo'!$O$2:$O$8</f>
             </numRef>
           </val>
         </ser>
@@ -1647,12 +1647,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$7</f>
+              <f>'Évolution par vidéo'!$P$2:$P$8</f>
             </numRef>
           </val>
         </ser>
@@ -1745,12 +1745,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$7</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1769,12 +1769,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$7</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$7</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -1817,12 +1817,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$7</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -1841,12 +1841,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$7</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -1865,12 +1865,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$7</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -1889,12 +1889,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$7</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -1913,12 +1913,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$7</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -1937,12 +1937,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$7</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -1961,12 +1961,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$7</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$8</f>
             </numRef>
           </val>
         </ser>
@@ -1985,12 +1985,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$7</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$8</f>
             </numRef>
           </val>
         </ser>
@@ -2009,12 +2009,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$7</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$8</f>
             </numRef>
           </val>
         </ser>
@@ -2033,12 +2033,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$7</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$8</f>
             </numRef>
           </val>
         </ser>
@@ -2057,12 +2057,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$7</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$8</f>
             </numRef>
           </val>
         </ser>
@@ -2081,12 +2081,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$7</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$8</f>
             </numRef>
           </val>
         </ser>
@@ -2299,7 +2299,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2326,7 +2326,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2663,7 +2663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3015,6 +3015,51 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3">
+        <f>IF(ROW()=2,"",B8-B7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2770</v>
+      </c>
+      <c r="E8" s="3">
+        <f>IF(ROW()=2,D8,D8-D7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3828,7 +3873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4191,6 +4236,58 @@
         <v>74</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4203,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4735,6 +4832,77 @@
       </c>
       <c r="Q7" s="3">
         <f>SUM(B7:P7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>IF('Évolution par vidéo'!B8="","",'Évolution par vidéo'!B8-N('Évolution par vidéo'!B7))</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF('Évolution par vidéo'!C8="","",'Évolution par vidéo'!C8-N('Évolution par vidéo'!C7))</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF('Évolution par vidéo'!D8="","",'Évolution par vidéo'!D8-N('Évolution par vidéo'!D7))</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>IF('Évolution par vidéo'!E8="","",'Évolution par vidéo'!E8-N('Évolution par vidéo'!E7))</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>IF('Évolution par vidéo'!F8="","",'Évolution par vidéo'!F8-N('Évolution par vidéo'!F7))</f>
+        <v/>
+      </c>
+      <c r="G8" s="3">
+        <f>IF('Évolution par vidéo'!G8="","",'Évolution par vidéo'!G8-N('Évolution par vidéo'!G7))</f>
+        <v/>
+      </c>
+      <c r="H8" s="3">
+        <f>IF('Évolution par vidéo'!H8="","",'Évolution par vidéo'!H8-N('Évolution par vidéo'!H7))</f>
+        <v/>
+      </c>
+      <c r="I8" s="3">
+        <f>IF('Évolution par vidéo'!I8="","",'Évolution par vidéo'!I8-N('Évolution par vidéo'!I7))</f>
+        <v/>
+      </c>
+      <c r="J8" s="3">
+        <f>IF('Évolution par vidéo'!J8="","",'Évolution par vidéo'!J8-N('Évolution par vidéo'!J7))</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>IF('Évolution par vidéo'!K8="","",'Évolution par vidéo'!K8-N('Évolution par vidéo'!K7))</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>IF('Évolution par vidéo'!L8="","",'Évolution par vidéo'!L8-N('Évolution par vidéo'!L7))</f>
+        <v/>
+      </c>
+      <c r="M8" s="3">
+        <f>IF('Évolution par vidéo'!M8="","",'Évolution par vidéo'!M8-N('Évolution par vidéo'!M7))</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>IF('Évolution par vidéo'!N8="","",'Évolution par vidéo'!N8-N('Évolution par vidéo'!N7))</f>
+        <v/>
+      </c>
+      <c r="O8" s="3">
+        <f>IF('Évolution par vidéo'!O8="","",'Évolution par vidéo'!O8-N('Évolution par vidéo'!O7))</f>
+        <v/>
+      </c>
+      <c r="P8" s="3">
+        <f>IF('Évolution par vidéo'!P8="","",'Évolution par vidéo'!P8-N('Évolution par vidéo'!P7))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="3">
+        <f>SUM(B8:P8)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -322,12 +322,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$34</f>
+              <f>'Stories'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$34</f>
+              <f>'Stories'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -3032,26 +3032,26 @@
         <v/>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2770</v>
+        <v>2589</v>
       </c>
       <c r="E8" s="3">
         <f>IF(ROW()=2,D8,D8-D7)</f>
         <v/>
       </c>
       <c r="F8" s="3" t="n">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3157,12 +3157,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 10:34</t>
+          <t>2026-10-18 13:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>POV : ta mamie t'écrit « ma retraite va baiss</t>
+          <t>👑 Vendredi soir : Macron au concert de Céline</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -3171,17 +3171,17 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>120</v>
+        <v>1155</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>115</v>
+        <v>1003</v>
       </c>
       <c r="F2" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -3203,12 +3203,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:04</t>
+          <t>2026-10-18 20:18</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseurs… et les revend</t>
+          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
@@ -3249,12 +3249,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:52</t>
+          <t>2026-10-19 06:14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>👑 Vendredi soir : Macron au concert de Céline</t>
+          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3263,16 +3263,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1155</v>
+        <v>110</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1003</v>
+        <v>104</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -3295,12 +3295,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 20:18</t>
+          <t>2026-10-19 08:14</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
+          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3309,13 +3309,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
@@ -3341,12 +3341,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 06:14</t>
+          <t>2026-10-19 09:09</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
+          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>1</v>
@@ -3387,12 +3387,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:14</t>
+          <t>2026-10-19 12:05</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <f>IFERROR((F7+G7+H7+I7)/IF(E7&gt;0,E7,D7),0)</f>
@@ -3433,12 +3433,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>1</v>
@@ -3479,12 +3479,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -3508,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K9" s="5">
         <f>IFERROR((F9+G9+H9+I9)/IF(E9&gt;0,E9,D9),0)</f>
@@ -3525,12 +3525,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
@@ -3571,12 +3571,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3585,13 +3585,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -3600,10 +3600,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
@@ -3617,12 +3617,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3631,11 +3631,11 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
@@ -3663,12 +3663,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="5">
         <f>IFERROR((F13+G13+H13+I13)/IF(E13&gt;0,E13,D13),0)</f>
@@ -3709,12 +3709,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Couper les réseaux sociaux pendant les émeute</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5">
         <f>IFERROR((F14+G14+H14+I14)/IF(E14&gt;0,E14,D14),0)</f>
@@ -3755,12 +3755,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:08</t>
+          <t>2026-10-24 12:30</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou non ? Réponds en co</t>
+          <t>À toi de juger : il faut une enquête indépend</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="5">
         <f>IFERROR((F15+G15+H15+I15)/IF(E15&gt;0,E15,D15),0)</f>
@@ -3801,12 +3801,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-24 13:56</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux pendant les émeute</t>
+          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -3902,77 +3902,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseu</t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
     </row>
@@ -3983,14 +3983,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="D2" s="3" t="n">
         <v>174</v>
       </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
@@ -4011,29 +4007,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>190</v>
-      </c>
       <c r="D3" s="3" t="n">
-        <v>1125</v>
+        <v>105</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="I3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
@@ -4049,35 +4041,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>191</v>
-      </c>
       <c r="D4" s="3" t="n">
-        <v>1155</v>
+        <v>110</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="K4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
@@ -4091,44 +4079,40 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>191</v>
-      </c>
       <c r="D5" s="3" t="n">
-        <v>1155</v>
+        <v>110</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N5" s="3" t="n">
         <v>69</v>
       </c>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
     </row>
@@ -4139,50 +4123,46 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>120</v>
+        <v>1155</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1155</v>
+        <v>110</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>105</v>
-      </c>
       <c r="N6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4191,50 +4171,46 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>120</v>
+        <v>1155</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1155</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>105</v>
-      </c>
       <c r="N7" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>74</v>
       </c>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4243,49 +4219,49 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>120</v>
+        <v>1155</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1155</v>
+        <v>110</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4330,77 +4306,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">POV : ta mamie t'écrit « ma </t>
+          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>👻 On ne parle que des casseu</t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -4918,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6063,6 +6039,171 @@
         <v>0</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:04</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:31</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:57</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:57</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:58</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -6103,9 +6244,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId34"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId39"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -11,8 +11,10 @@
     <sheet name="Vidéos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Évolution par vidéo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Vues du jour par vidéo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stories" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="À lire" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Heure par heure" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vues gagnées par heure" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stories" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="À lire" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -283,6 +285,926 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues cumulées de chaque vidéo, heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$C$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$D$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$E$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$F$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$G$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$H$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$I$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$J$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$K$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$L$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Abonnés, heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues totales du compte (vidéos), heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="3D5AFE"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3D5AFE"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$M$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues gagnées chaque heure, vidéo par vidéo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$B$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$C$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$D$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$E$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$F$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$G$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$H$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$I$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$J$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$K$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2348,6 +3270,104 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -4894,6 +5914,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Abonnés</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-19 📩 « Jeudi 5 novembre, </t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>10-19 📖 Il était une fois de</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>10-20 Couvre-feu pour les ad</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>10-21 Les syndicats de salar</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>10-21 À toi de juger : taxer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>10-21 Gel des pensions : oui</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>10-22 Couper les réseaux soc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10-24 À toi de juger : il fa</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10-24 « Oui, nous avons perd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Vues totales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 17:00</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="M2" s="3">
+        <f>SUM(C2:L2)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-19 📩 « Jeudi 5 novembre, </t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>10-19 📖 Il était une fois de</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>10-20 Couvre-feu pour les ad</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>10-21 Les syndicats de salar</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>10-21 À toi de juger : taxer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>10-21 Gel des pensions : oui</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>10-22 Couper les réseaux soc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>10-24 À toi de juger : il fa</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10-24 « Oui, nous avons perd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Total de l'heure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <f>'Heure par heure'!A2</f>
+        <v/>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3">
+        <f>SUM(B2:K2)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6255,13 +7527,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -6305,12 +7577,19 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Taux d'engagement = (likes + commentaires + partages + enregistrements) / comptes touchés.</t>
+          <t>« Heure par heure » : relevé toutes les heures de 7 h à 23 h (Paris) ; le relevé de 7 h inclut la nuit.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Taux d'engagement = (likes + commentaires + partages + enregistrements) / comptes touchés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Les statistiques d'une story ne sont lisibles que pendant ses 24 h : dernier relevé conservé.</t>
         </is>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2</f>
+              <f>'Heure par heure'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2</f>
+              <f>'Heure par heure'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2</f>
+              <f>'Heure par heure'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2</f>
+              <f>'Heure par heure'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2</f>
+              <f>'Heure par heure'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2</f>
+              <f>'Heure par heure'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2</f>
+              <f>'Heure par heure'!$I$2:$I$3</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2</f>
+              <f>'Heure par heure'!$J$2:$J$3</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2</f>
+              <f>'Heure par heure'!$K$2:$K$3</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2</f>
+              <f>'Heure par heure'!$L$2:$L$3</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2</f>
+              <f>'Heure par heure'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2</f>
+              <f>'Heure par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2</f>
+              <f>'Heure par heure'!$M$2:$M$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$3</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$3</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$3</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6043,6 +6043,50 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 18:00</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="M3" s="3">
+        <f>SUM(C3:L3)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6055,7 +6099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6151,6 +6195,56 @@
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3">
         <f>SUM(B2:K2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <f>'Heure par heure'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="3">
+        <f>IF('Heure par heure'!C3="","",'Heure par heure'!C3-N('Heure par heure'!C2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>IF('Heure par heure'!D3="","",'Heure par heure'!D3-N('Heure par heure'!D2))</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>IF('Heure par heure'!E3="","",'Heure par heure'!E3-N('Heure par heure'!E2))</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>IF('Heure par heure'!F3="","",'Heure par heure'!F3-N('Heure par heure'!F2))</f>
+        <v/>
+      </c>
+      <c r="F3" s="3">
+        <f>IF('Heure par heure'!G3="","",'Heure par heure'!G3-N('Heure par heure'!G2))</f>
+        <v/>
+      </c>
+      <c r="G3" s="3">
+        <f>IF('Heure par heure'!H3="","",'Heure par heure'!H3-N('Heure par heure'!H2))</f>
+        <v/>
+      </c>
+      <c r="H3" s="3">
+        <f>IF('Heure par heure'!I3="","",'Heure par heure'!I3-N('Heure par heure'!I2))</f>
+        <v/>
+      </c>
+      <c r="I3" s="3">
+        <f>IF('Heure par heure'!J3="","",'Heure par heure'!J3-N('Heure par heure'!J2))</f>
+        <v/>
+      </c>
+      <c r="J3" s="3">
+        <f>IF('Heure par heure'!K3="","",'Heure par heure'!K3-N('Heure par heure'!K2))</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
+        <f>IF('Heure par heure'!L3="","",'Heure par heure'!L3-N('Heure par heure'!L2))</f>
+        <v/>
+      </c>
+      <c r="L3" s="3">
+        <f>SUM(B3:K3)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$3</f>
+              <f>'Heure par heure'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$3</f>
+              <f>'Heure par heure'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$3</f>
+              <f>'Heure par heure'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$3</f>
+              <f>'Heure par heure'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$3</f>
+              <f>'Heure par heure'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$3</f>
+              <f>'Heure par heure'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$3</f>
+              <f>'Heure par heure'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$3</f>
+              <f>'Heure par heure'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$3</f>
+              <f>'Heure par heure'!$K$2:$K$4</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$3</f>
+              <f>'Heure par heure'!$L$2:$L$4</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$3</f>
+              <f>'Heure par heure'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$3</f>
+              <f>'Heure par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$3</f>
+              <f>'Heure par heure'!$M$2:$M$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$3</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$3</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$3</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$3</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$3</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$3</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$3</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$3</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$3</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$3</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$3</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$4</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6087,6 +6087,50 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 19:00</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="M4" s="3">
+        <f>SUM(C4:L4)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6099,7 +6143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6245,6 +6289,56 @@
       </c>
       <c r="L3" s="3">
         <f>SUM(B3:K3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <f>'Heure par heure'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="3">
+        <f>IF('Heure par heure'!C4="","",'Heure par heure'!C4-N('Heure par heure'!C3))</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>IF('Heure par heure'!D4="","",'Heure par heure'!D4-N('Heure par heure'!D3))</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>IF('Heure par heure'!E4="","",'Heure par heure'!E4-N('Heure par heure'!E3))</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>IF('Heure par heure'!F4="","",'Heure par heure'!F4-N('Heure par heure'!F3))</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>IF('Heure par heure'!G4="","",'Heure par heure'!G4-N('Heure par heure'!G3))</f>
+        <v/>
+      </c>
+      <c r="G4" s="3">
+        <f>IF('Heure par heure'!H4="","",'Heure par heure'!H4-N('Heure par heure'!H3))</f>
+        <v/>
+      </c>
+      <c r="H4" s="3">
+        <f>IF('Heure par heure'!I4="","",'Heure par heure'!I4-N('Heure par heure'!I3))</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
+        <f>IF('Heure par heure'!J4="","",'Heure par heure'!J4-N('Heure par heure'!J3))</f>
+        <v/>
+      </c>
+      <c r="J4" s="3">
+        <f>IF('Heure par heure'!K4="","",'Heure par heure'!K4-N('Heure par heure'!K3))</f>
+        <v/>
+      </c>
+      <c r="K4" s="3">
+        <f>IF('Heure par heure'!L4="","",'Heure par heure'!L4-N('Heure par heure'!L3))</f>
+        <v/>
+      </c>
+      <c r="L4" s="3">
+        <f>SUM(B4:K4)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$4</f>
+              <f>'Heure par heure'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$4</f>
+              <f>'Heure par heure'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$4</f>
+              <f>'Heure par heure'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$4</f>
+              <f>'Heure par heure'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$4</f>
+              <f>'Heure par heure'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$4</f>
+              <f>'Heure par heure'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$4</f>
+              <f>'Heure par heure'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$4</f>
+              <f>'Heure par heure'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$4</f>
+              <f>'Heure par heure'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$4</f>
+              <f>'Heure par heure'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$4</f>
+              <f>'Heure par heure'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$4</f>
+              <f>'Heure par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$4</f>
+              <f>'Heure par heure'!$M$2:$M$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$4</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$4</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$4</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$4</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$4</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$4</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$4</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$4</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$4</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$4</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$4</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5945,52 +5945,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-19 📩 « Jeudi 5 novembre, </t>
+          <t>10-19 📖 Il était une fois de</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-19 📖 Il était une fois de</t>
+          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
+          <t>10-20 Couvre-feu pour les ad</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-20 Couvre-feu pour les ad</t>
+          <t>10-21 Les syndicats de salar</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -6009,35 +6009,33 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="L2" s="3" t="n">
         <v>124</v>
       </c>
+      <c r="L2" s="3" t="n"/>
       <c r="M2" s="3">
         <f>SUM(C2:L2)</f>
         <v/>
@@ -6053,35 +6051,33 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="L3" s="3" t="n">
         <v>130</v>
       </c>
+      <c r="L3" s="3" t="n"/>
       <c r="M3" s="3">
         <f>SUM(C3:L3)</f>
         <v/>
@@ -6097,37 +6093,79 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>135</v>
       </c>
+      <c r="L4" s="3" t="n"/>
       <c r="M4" s="3">
         <f>SUM(C4:L4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 20:00</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <f>SUM(C5:L5)</f>
         <v/>
       </c>
     </row>
@@ -6143,7 +6181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6168,52 +6206,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-19 📩 « Jeudi 5 novembre, </t>
+          <t>10-19 📖 Il était une fois de</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-19 📖 Il était une fois de</t>
+          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
+          <t>10-20 Couvre-feu pour les ad</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-20 Couvre-feu pour les ad</t>
+          <t>10-21 Les syndicats de salar</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -6339,6 +6377,56 @@
       </c>
       <c r="L4" s="3">
         <f>SUM(B4:K4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <f>'Heure par heure'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="3">
+        <f>IF('Heure par heure'!C5="","",'Heure par heure'!C5-N('Heure par heure'!C4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>IF('Heure par heure'!D5="","",'Heure par heure'!D5-N('Heure par heure'!D4))</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>IF('Heure par heure'!E5="","",'Heure par heure'!E5-N('Heure par heure'!E4))</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>IF('Heure par heure'!F5="","",'Heure par heure'!F5-N('Heure par heure'!F4))</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>IF('Heure par heure'!G5="","",'Heure par heure'!G5-N('Heure par heure'!G4))</f>
+        <v/>
+      </c>
+      <c r="G5" s="3">
+        <f>IF('Heure par heure'!H5="","",'Heure par heure'!H5-N('Heure par heure'!H4))</f>
+        <v/>
+      </c>
+      <c r="H5" s="3">
+        <f>IF('Heure par heure'!I5="","",'Heure par heure'!I5-N('Heure par heure'!I4))</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
+        <f>IF('Heure par heure'!J5="","",'Heure par heure'!J5-N('Heure par heure'!J4))</f>
+        <v/>
+      </c>
+      <c r="J5" s="3">
+        <f>IF('Heure par heure'!K5="","",'Heure par heure'!K5-N('Heure par heure'!K4))</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
+        <f>IF('Heure par heure'!L5="","",'Heure par heure'!L5-N('Heure par heure'!L4))</f>
+        <v/>
+      </c>
+      <c r="L5" s="3">
+        <f>SUM(B5:K5)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$5</f>
+              <f>'Heure par heure'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$5</f>
+              <f>'Heure par heure'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$5</f>
+              <f>'Heure par heure'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$5</f>
+              <f>'Heure par heure'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$5</f>
+              <f>'Heure par heure'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$5</f>
+              <f>'Heure par heure'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$5</f>
+              <f>'Heure par heure'!$I$2:$I$6</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$5</f>
+              <f>'Heure par heure'!$J$2:$J$6</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$5</f>
+              <f>'Heure par heure'!$K$2:$K$6</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$5</f>
+              <f>'Heure par heure'!$L$2:$L$6</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$5</f>
+              <f>'Heure par heure'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$5</f>
+              <f>'Heure par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$5</f>
+              <f>'Heure par heure'!$M$2:$M$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$5</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$5</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$5</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$5</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$5</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$5</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$5</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$5</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$6</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$5</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$6</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$5</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$5</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$6</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6169,6 +6169,50 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 21:00</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3">
+        <f>SUM(C6:L6)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6181,7 +6225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6427,6 +6471,56 @@
       </c>
       <c r="L5" s="3">
         <f>SUM(B5:K5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <f>'Heure par heure'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="3">
+        <f>IF('Heure par heure'!C6="","",'Heure par heure'!C6-N('Heure par heure'!C5))</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>IF('Heure par heure'!D6="","",'Heure par heure'!D6-N('Heure par heure'!D5))</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>IF('Heure par heure'!E6="","",'Heure par heure'!E6-N('Heure par heure'!E5))</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>IF('Heure par heure'!F6="","",'Heure par heure'!F6-N('Heure par heure'!F5))</f>
+        <v/>
+      </c>
+      <c r="F6" s="3">
+        <f>IF('Heure par heure'!G6="","",'Heure par heure'!G6-N('Heure par heure'!G5))</f>
+        <v/>
+      </c>
+      <c r="G6" s="3">
+        <f>IF('Heure par heure'!H6="","",'Heure par heure'!H6-N('Heure par heure'!H5))</f>
+        <v/>
+      </c>
+      <c r="H6" s="3">
+        <f>IF('Heure par heure'!I6="","",'Heure par heure'!I6-N('Heure par heure'!I5))</f>
+        <v/>
+      </c>
+      <c r="I6" s="3">
+        <f>IF('Heure par heure'!J6="","",'Heure par heure'!J6-N('Heure par heure'!J5))</f>
+        <v/>
+      </c>
+      <c r="J6" s="3">
+        <f>IF('Heure par heure'!K6="","",'Heure par heure'!K6-N('Heure par heure'!K5))</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>IF('Heure par heure'!L6="","",'Heure par heure'!L6-N('Heure par heure'!L5))</f>
+        <v/>
+      </c>
+      <c r="L6" s="3">
+        <f>SUM(B6:K6)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$6</f>
+              <f>'Heure par heure'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$6</f>
+              <f>'Heure par heure'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$6</f>
+              <f>'Heure par heure'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$6</f>
+              <f>'Heure par heure'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$6</f>
+              <f>'Heure par heure'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$6</f>
+              <f>'Heure par heure'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$6</f>
+              <f>'Heure par heure'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$6</f>
+              <f>'Heure par heure'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$6</f>
+              <f>'Heure par heure'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$6</f>
+              <f>'Heure par heure'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$6</f>
+              <f>'Heure par heure'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$6</f>
+              <f>'Heure par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$6</f>
+              <f>'Heure par heure'!$M$2:$M$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$6</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$6</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$6</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$6</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$6</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$6</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$6</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$6</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$6</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$6</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$6</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6213,6 +6213,50 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 22:00</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" s="3">
+        <f>SUM(C7:L7)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6225,7 +6269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6521,6 +6565,56 @@
       </c>
       <c r="L6" s="3">
         <f>SUM(B6:K6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <f>'Heure par heure'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="3">
+        <f>IF('Heure par heure'!C7="","",'Heure par heure'!C7-N('Heure par heure'!C6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>IF('Heure par heure'!D7="","",'Heure par heure'!D7-N('Heure par heure'!D6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>IF('Heure par heure'!E7="","",'Heure par heure'!E7-N('Heure par heure'!E6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>IF('Heure par heure'!F7="","",'Heure par heure'!F7-N('Heure par heure'!F6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="3">
+        <f>IF('Heure par heure'!G7="","",'Heure par heure'!G7-N('Heure par heure'!G6))</f>
+        <v/>
+      </c>
+      <c r="G7" s="3">
+        <f>IF('Heure par heure'!H7="","",'Heure par heure'!H7-N('Heure par heure'!H6))</f>
+        <v/>
+      </c>
+      <c r="H7" s="3">
+        <f>IF('Heure par heure'!I7="","",'Heure par heure'!I7-N('Heure par heure'!I6))</f>
+        <v/>
+      </c>
+      <c r="I7" s="3">
+        <f>IF('Heure par heure'!J7="","",'Heure par heure'!J7-N('Heure par heure'!J6))</f>
+        <v/>
+      </c>
+      <c r="J7" s="3">
+        <f>IF('Heure par heure'!K7="","",'Heure par heure'!K7-N('Heure par heure'!K6))</f>
+        <v/>
+      </c>
+      <c r="K7" s="3">
+        <f>IF('Heure par heure'!L7="","",'Heure par heure'!L7-N('Heure par heure'!L6))</f>
+        <v/>
+      </c>
+      <c r="L7" s="3">
+        <f>SUM(B7:K7)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$7</f>
+              <f>'Heure par heure'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$7</f>
+              <f>'Heure par heure'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$7</f>
+              <f>'Heure par heure'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$7</f>
+              <f>'Heure par heure'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$7</f>
+              <f>'Heure par heure'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$7</f>
+              <f>'Heure par heure'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$7</f>
+              <f>'Heure par heure'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$7</f>
+              <f>'Heure par heure'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$7</f>
+              <f>'Heure par heure'!$K$2:$K$8</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$7</f>
+              <f>'Heure par heure'!$L$2:$L$8</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$7</f>
+              <f>'Heure par heure'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$7</f>
+              <f>'Heure par heure'!$M$2:$M$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$7</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$7</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$7</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$7</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$7</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$7</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$7</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$7</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$7</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$7</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$8</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6257,6 +6257,50 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 23:00</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="M8" s="3">
+        <f>SUM(C8:L8)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6269,7 +6313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6615,6 +6659,56 @@
       </c>
       <c r="L7" s="3">
         <f>SUM(B7:K7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <f>'Heure par heure'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="3">
+        <f>IF('Heure par heure'!C8="","",'Heure par heure'!C8-N('Heure par heure'!C7))</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF('Heure par heure'!D8="","",'Heure par heure'!D8-N('Heure par heure'!D7))</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF('Heure par heure'!E8="","",'Heure par heure'!E8-N('Heure par heure'!E7))</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>IF('Heure par heure'!F8="","",'Heure par heure'!F8-N('Heure par heure'!F7))</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>IF('Heure par heure'!G8="","",'Heure par heure'!G8-N('Heure par heure'!G7))</f>
+        <v/>
+      </c>
+      <c r="G8" s="3">
+        <f>IF('Heure par heure'!H8="","",'Heure par heure'!H8-N('Heure par heure'!H7))</f>
+        <v/>
+      </c>
+      <c r="H8" s="3">
+        <f>IF('Heure par heure'!I8="","",'Heure par heure'!I8-N('Heure par heure'!I7))</f>
+        <v/>
+      </c>
+      <c r="I8" s="3">
+        <f>IF('Heure par heure'!J8="","",'Heure par heure'!J8-N('Heure par heure'!J7))</f>
+        <v/>
+      </c>
+      <c r="J8" s="3">
+        <f>IF('Heure par heure'!K8="","",'Heure par heure'!K8-N('Heure par heure'!K7))</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>IF('Heure par heure'!L8="","",'Heure par heure'!L8-N('Heure par heure'!L7))</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$8</f>
+              <f>'Heure par heure'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$8</f>
+              <f>'Heure par heure'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$8</f>
+              <f>'Heure par heure'!$E$2:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$8</f>
+              <f>'Heure par heure'!$F$2:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$8</f>
+              <f>'Heure par heure'!$G$2:$G$9</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$8</f>
+              <f>'Heure par heure'!$H$2:$H$9</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$8</f>
+              <f>'Heure par heure'!$I$2:$I$9</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$8</f>
+              <f>'Heure par heure'!$J$2:$J$9</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$8</f>
+              <f>'Heure par heure'!$K$2:$K$9</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$8</f>
+              <f>'Heure par heure'!$L$2:$L$9</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$8</f>
+              <f>'Heure par heure'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$8</f>
+              <f>'Heure par heure'!$M$2:$M$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$8</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$8</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$8</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$8</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$8</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$8</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$9</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$8</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$9</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$8</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$9</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$8</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$9</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$8</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$9</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6301,6 +6301,50 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:00</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="M9" s="3">
+        <f>SUM(C9:L9)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6313,7 +6357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6709,6 +6753,56 @@
       </c>
       <c r="L8" s="3">
         <f>SUM(B8:K8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <f>'Heure par heure'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="3">
+        <f>IF('Heure par heure'!C9="","",'Heure par heure'!C9-N('Heure par heure'!C8))</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>IF('Heure par heure'!D9="","",'Heure par heure'!D9-N('Heure par heure'!D8))</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IF('Heure par heure'!E9="","",'Heure par heure'!E9-N('Heure par heure'!E8))</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>IF('Heure par heure'!F9="","",'Heure par heure'!F9-N('Heure par heure'!F8))</f>
+        <v/>
+      </c>
+      <c r="F9" s="3">
+        <f>IF('Heure par heure'!G9="","",'Heure par heure'!G9-N('Heure par heure'!G8))</f>
+        <v/>
+      </c>
+      <c r="G9" s="3">
+        <f>IF('Heure par heure'!H9="","",'Heure par heure'!H9-N('Heure par heure'!H8))</f>
+        <v/>
+      </c>
+      <c r="H9" s="3">
+        <f>IF('Heure par heure'!I9="","",'Heure par heure'!I9-N('Heure par heure'!I8))</f>
+        <v/>
+      </c>
+      <c r="I9" s="3">
+        <f>IF('Heure par heure'!J9="","",'Heure par heure'!J9-N('Heure par heure'!J8))</f>
+        <v/>
+      </c>
+      <c r="J9" s="3">
+        <f>IF('Heure par heure'!K9="","",'Heure par heure'!K9-N('Heure par heure'!K8))</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>IF('Heure par heure'!L9="","",'Heure par heure'!L9-N('Heure par heure'!L8))</f>
+        <v/>
+      </c>
+      <c r="L9" s="3">
+        <f>SUM(B9:K9)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$9</f>
+              <f>'Heure par heure'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$9</f>
+              <f>'Heure par heure'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$9</f>
+              <f>'Heure par heure'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$9</f>
+              <f>'Heure par heure'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$9</f>
+              <f>'Heure par heure'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$9</f>
+              <f>'Heure par heure'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$9</f>
+              <f>'Heure par heure'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$9</f>
+              <f>'Heure par heure'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$9</f>
+              <f>'Heure par heure'!$K$2:$K$10</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$9</f>
+              <f>'Heure par heure'!$L$2:$L$10</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$9</f>
+              <f>'Heure par heure'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$9</f>
+              <f>'Heure par heure'!$M$2:$M$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$9</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$9</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$9</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$9</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$9</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$9</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$9</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$9</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$9</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$9</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$10</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6345,6 +6345,50 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:00</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="M10" s="3">
+        <f>SUM(C10:L10)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6357,7 +6401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6803,6 +6847,56 @@
       </c>
       <c r="L9" s="3">
         <f>SUM(B9:K9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <f>'Heure par heure'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="3">
+        <f>IF('Heure par heure'!C10="","",'Heure par heure'!C10-N('Heure par heure'!C9))</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>IF('Heure par heure'!D10="","",'Heure par heure'!D10-N('Heure par heure'!D9))</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IF('Heure par heure'!E10="","",'Heure par heure'!E10-N('Heure par heure'!E9))</f>
+        <v/>
+      </c>
+      <c r="E10" s="3">
+        <f>IF('Heure par heure'!F10="","",'Heure par heure'!F10-N('Heure par heure'!F9))</f>
+        <v/>
+      </c>
+      <c r="F10" s="3">
+        <f>IF('Heure par heure'!G10="","",'Heure par heure'!G10-N('Heure par heure'!G9))</f>
+        <v/>
+      </c>
+      <c r="G10" s="3">
+        <f>IF('Heure par heure'!H10="","",'Heure par heure'!H10-N('Heure par heure'!H9))</f>
+        <v/>
+      </c>
+      <c r="H10" s="3">
+        <f>IF('Heure par heure'!I10="","",'Heure par heure'!I10-N('Heure par heure'!I9))</f>
+        <v/>
+      </c>
+      <c r="I10" s="3">
+        <f>IF('Heure par heure'!J10="","",'Heure par heure'!J10-N('Heure par heure'!J9))</f>
+        <v/>
+      </c>
+      <c r="J10" s="3">
+        <f>IF('Heure par heure'!K10="","",'Heure par heure'!K10-N('Heure par heure'!K9))</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>IF('Heure par heure'!L10="","",'Heure par heure'!L10-N('Heure par heure'!L9))</f>
+        <v/>
+      </c>
+      <c r="L10" s="3">
+        <f>SUM(B10:K10)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$10</f>
+              <f>'Heure par heure'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$10</f>
+              <f>'Heure par heure'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$10</f>
+              <f>'Heure par heure'!$E$2:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$10</f>
+              <f>'Heure par heure'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$10</f>
+              <f>'Heure par heure'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$10</f>
+              <f>'Heure par heure'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$10</f>
+              <f>'Heure par heure'!$I$2:$I$11</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$10</f>
+              <f>'Heure par heure'!$J$2:$J$11</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$10</f>
+              <f>'Heure par heure'!$K$2:$K$11</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$10</f>
+              <f>'Heure par heure'!$L$2:$L$11</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$10</f>
+              <f>'Heure par heure'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$10</f>
+              <f>'Heure par heure'!$M$2:$M$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$10</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$10</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$10</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$10</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$10</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$10</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$10</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$10</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$11</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$10</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$11</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$10</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$11</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -5914,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6389,6 +6389,50 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 08:00</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="M11" s="3">
+        <f>SUM(C11:L11)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6401,7 +6445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6897,6 +6941,56 @@
       </c>
       <c r="L10" s="3">
         <f>SUM(B10:K10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <f>'Heure par heure'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="3">
+        <f>IF('Heure par heure'!C11="","",'Heure par heure'!C11-N('Heure par heure'!C10))</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>IF('Heure par heure'!D11="","",'Heure par heure'!D11-N('Heure par heure'!D10))</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IF('Heure par heure'!E11="","",'Heure par heure'!E11-N('Heure par heure'!E10))</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>IF('Heure par heure'!F11="","",'Heure par heure'!F11-N('Heure par heure'!F10))</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>IF('Heure par heure'!G11="","",'Heure par heure'!G11-N('Heure par heure'!G10))</f>
+        <v/>
+      </c>
+      <c r="G11" s="3">
+        <f>IF('Heure par heure'!H11="","",'Heure par heure'!H11-N('Heure par heure'!H10))</f>
+        <v/>
+      </c>
+      <c r="H11" s="3">
+        <f>IF('Heure par heure'!I11="","",'Heure par heure'!I11-N('Heure par heure'!I10))</f>
+        <v/>
+      </c>
+      <c r="I11" s="3">
+        <f>IF('Heure par heure'!J11="","",'Heure par heure'!J11-N('Heure par heure'!J10))</f>
+        <v/>
+      </c>
+      <c r="J11" s="3">
+        <f>IF('Heure par heure'!K11="","",'Heure par heure'!K11-N('Heure par heure'!K10))</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>IF('Heure par heure'!L11="","",'Heure par heure'!L11-N('Heure par heure'!L10))</f>
+        <v/>
+      </c>
+      <c r="L11" s="3">
+        <f>SUM(B11:K11)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$8</f>
+              <f>'Jour par jour'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$8</f>
+              <f>'Jour par jour'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1244,12 +1244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$39</f>
+              <f>'Stories'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$39</f>
+              <f>'Stories'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -1346,12 +1346,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$8</f>
+              <f>'Jour par jour'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$8</f>
+              <f>'Jour par jour'!$E$2:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -1373,12 +1373,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$8</f>
+              <f>'Jour par jour'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$8</f>
+              <f>'Jour par jour'!$L$2:$L$9</f>
             </numRef>
           </val>
         </ser>
@@ -1486,12 +1486,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$8</f>
+              <f>'Jour par jour'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$8</f>
+              <f>'Jour par jour'!$F$2:$F$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1526,12 +1526,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$8</f>
+              <f>'Jour par jour'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$8</f>
+              <f>'Jour par jour'!$H$2:$H$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1628,12 +1628,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$8</f>
+              <f>'Jour par jour'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$8</f>
+              <f>'Jour par jour'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -2121,12 +2121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$8</f>
+              <f>'Évolution par vidéo'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$8</f>
+              <f>'Évolution par vidéo'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -2185,12 +2185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$8</f>
+              <f>'Évolution par vidéo'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -2217,12 +2217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$8</f>
+              <f>'Évolution par vidéo'!$E$2:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -2249,12 +2249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$8</f>
+              <f>'Évolution par vidéo'!$F$2:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -2281,12 +2281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$8</f>
+              <f>'Évolution par vidéo'!$G$2:$G$9</f>
             </numRef>
           </val>
         </ser>
@@ -2313,12 +2313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$8</f>
+              <f>'Évolution par vidéo'!$H$2:$H$9</f>
             </numRef>
           </val>
         </ser>
@@ -2345,12 +2345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$8</f>
+              <f>'Évolution par vidéo'!$I$2:$I$9</f>
             </numRef>
           </val>
         </ser>
@@ -2377,12 +2377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$8</f>
+              <f>'Évolution par vidéo'!$J$2:$J$9</f>
             </numRef>
           </val>
         </ser>
@@ -2409,12 +2409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$8</f>
+              <f>'Évolution par vidéo'!$K$2:$K$9</f>
             </numRef>
           </val>
         </ser>
@@ -2441,12 +2441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$8</f>
+              <f>'Évolution par vidéo'!$L$2:$L$9</f>
             </numRef>
           </val>
         </ser>
@@ -2473,12 +2473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$8</f>
+              <f>'Évolution par vidéo'!$M$2:$M$9</f>
             </numRef>
           </val>
         </ser>
@@ -2505,12 +2505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$8</f>
+              <f>'Évolution par vidéo'!$N$2:$N$9</f>
             </numRef>
           </val>
         </ser>
@@ -2537,12 +2537,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$8</f>
+              <f>'Évolution par vidéo'!$O$2:$O$9</f>
             </numRef>
           </val>
         </ser>
@@ -2569,12 +2569,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$8</f>
+              <f>'Évolution par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$8</f>
+              <f>'Évolution par vidéo'!$P$2:$P$9</f>
             </numRef>
           </val>
         </ser>
@@ -2667,12 +2667,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$8</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$8</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -2715,12 +2715,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$8</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -2739,12 +2739,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$8</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -2763,12 +2763,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$8</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -2787,12 +2787,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$8</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$9</f>
             </numRef>
           </val>
         </ser>
@@ -2811,12 +2811,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$8</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$9</f>
             </numRef>
           </val>
         </ser>
@@ -2835,12 +2835,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$8</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$9</f>
             </numRef>
           </val>
         </ser>
@@ -2859,12 +2859,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$8</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$9</f>
             </numRef>
           </val>
         </ser>
@@ -2883,12 +2883,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$8</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$9</f>
             </numRef>
           </val>
         </ser>
@@ -2907,12 +2907,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$8</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$9</f>
             </numRef>
           </val>
         </ser>
@@ -2931,12 +2931,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$8</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$9</f>
             </numRef>
           </val>
         </ser>
@@ -2955,12 +2955,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$8</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$9</f>
             </numRef>
           </val>
         </ser>
@@ -2979,12 +2979,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$8</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$9</f>
             </numRef>
           </val>
         </ser>
@@ -3003,12 +3003,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$8</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$9</f>
             </numRef>
           </val>
         </ser>
@@ -3221,7 +3221,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3248,7 +3248,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -3683,7 +3683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4077,10 +4077,55 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <f>IF(ROW()=2,"",B9-B8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1749</v>
+      </c>
+      <c r="E9" s="3">
+        <f>IF(ROW()=2,D9,D9-D8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>451</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4177,12 +4222,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:52</t>
+          <t>2026-10-18 20:18</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>👑 Vendredi soir : Macron au concert de Céline</t>
+          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4191,25 +4236,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1155</v>
+        <v>121</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1003</v>
+        <v>109</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>20</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -4223,12 +4268,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 20:18</t>
+          <t>2026-10-19 06:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
+          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4237,13 +4282,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -4255,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
@@ -4269,12 +4314,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 06:14</t>
+          <t>2026-10-19 08:14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
+          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4283,10 +4328,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>1</v>
@@ -4315,12 +4360,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:14</t>
+          <t>2026-10-19 09:09</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
+          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4329,10 +4374,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
@@ -4361,12 +4406,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-19 12:05</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4375,13 +4420,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -4393,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -4407,12 +4452,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4421,13 +4466,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -4439,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5">
         <f>IFERROR((F7+G7+H7+I7)/IF(E7&gt;0,E7,D7),0)</f>
@@ -4453,12 +4498,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4467,13 +4512,13 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -4482,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K8" s="5">
         <f>IFERROR((F8+G8+H8+I8)/IF(E8&gt;0,E8,D8),0)</f>
@@ -4499,12 +4544,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4513,13 +4558,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -4528,10 +4573,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
         <f>IFERROR((F9+G9+H9+I9)/IF(E9&gt;0,E9,D9),0)</f>
@@ -4545,12 +4590,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4559,13 +4604,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -4577,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
@@ -4591,12 +4636,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4605,13 +4650,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -4637,12 +4682,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4651,10 +4696,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -4669,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
@@ -4683,12 +4728,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:08</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou non ? Réponds en co</t>
+          <t>Couper les réseaux sociaux pendant les émeute</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4697,10 +4742,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
@@ -4729,12 +4774,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-24 12:30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux pendant les émeute</t>
+          <t>À toi de juger : il faut une enquête indépend</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4743,13 +4788,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -4761,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" s="5">
         <f>IFERROR((F14+G14+H14+I14)/IF(E14&gt;0,E14,D14),0)</f>
@@ -4775,12 +4820,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 12:30</t>
+          <t>2026-10-24 13:56</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une enquête indépend</t>
+          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4789,13 +4834,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -4807,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="5">
         <f>IFERROR((F15+G15+H15+I15)/IF(E15&gt;0,E15,D15),0)</f>
@@ -4821,12 +4866,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:56</t>
+          <t>2026-10-24 18:14</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
+          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4835,10 +4880,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6</v>
+        <v>133</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -4893,7 +4938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4922,77 +4967,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
     </row>
@@ -5002,9 +5047,7 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>174</v>
-      </c>
+      <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
@@ -5027,23 +5070,21 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1125</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="G3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
@@ -5061,29 +5102,27 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1155</v>
+        <v>120</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="I4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
@@ -5099,38 +5138,36 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1155</v>
+        <v>120</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="L5" s="3" t="n">
         <v>69</v>
       </c>
+      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
@@ -5143,44 +5180,42 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1155</v>
+        <v>121</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>128</v>
-      </c>
       <c r="M6" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="N6" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n"/>
     </row>
@@ -5191,44 +5226,42 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1155</v>
+        <v>121</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>128</v>
-      </c>
       <c r="M7" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="N7" s="3" t="n">
         <v>74</v>
       </c>
+      <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
     </row>
@@ -5239,49 +5272,99 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1155</v>
+        <v>121</v>
       </c>
       <c r="C8" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="C9" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="G9" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="H9" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="K9" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>6</v>
+      <c r="N9" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -5296,7 +5379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5326,77 +5409,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">👑 Vendredi soir : Macron au </t>
+          <t>😱 Ma réaction à ce qui t'att</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>🧮 Quiz : ta manif dégénère e</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -5899,6 +5982,77 @@
       </c>
       <c r="Q8" s="3">
         <f>SUM(B8:P8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>IF('Évolution par vidéo'!B9="","",'Évolution par vidéo'!B9-N('Évolution par vidéo'!B8))</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>IF('Évolution par vidéo'!C9="","",'Évolution par vidéo'!C9-N('Évolution par vidéo'!C8))</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IF('Évolution par vidéo'!D9="","",'Évolution par vidéo'!D9-N('Évolution par vidéo'!D8))</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>IF('Évolution par vidéo'!E9="","",'Évolution par vidéo'!E9-N('Évolution par vidéo'!E8))</f>
+        <v/>
+      </c>
+      <c r="F9" s="3">
+        <f>IF('Évolution par vidéo'!F9="","",'Évolution par vidéo'!F9-N('Évolution par vidéo'!F8))</f>
+        <v/>
+      </c>
+      <c r="G9" s="3">
+        <f>IF('Évolution par vidéo'!G9="","",'Évolution par vidéo'!G9-N('Évolution par vidéo'!G8))</f>
+        <v/>
+      </c>
+      <c r="H9" s="3">
+        <f>IF('Évolution par vidéo'!H9="","",'Évolution par vidéo'!H9-N('Évolution par vidéo'!H8))</f>
+        <v/>
+      </c>
+      <c r="I9" s="3">
+        <f>IF('Évolution par vidéo'!I9="","",'Évolution par vidéo'!I9-N('Évolution par vidéo'!I8))</f>
+        <v/>
+      </c>
+      <c r="J9" s="3">
+        <f>IF('Évolution par vidéo'!J9="","",'Évolution par vidéo'!J9-N('Évolution par vidéo'!J8))</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>IF('Évolution par vidéo'!K9="","",'Évolution par vidéo'!K9-N('Évolution par vidéo'!K8))</f>
+        <v/>
+      </c>
+      <c r="L9" s="3">
+        <f>IF('Évolution par vidéo'!L9="","",'Évolution par vidéo'!L9-N('Évolution par vidéo'!L8))</f>
+        <v/>
+      </c>
+      <c r="M9" s="3">
+        <f>IF('Évolution par vidéo'!M9="","",'Évolution par vidéo'!M9-N('Évolution par vidéo'!M8))</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>IF('Évolution par vidéo'!N9="","",'Évolution par vidéo'!N9-N('Évolution par vidéo'!N8))</f>
+        <v/>
+      </c>
+      <c r="O9" s="3">
+        <f>IF('Évolution par vidéo'!O9="","",'Évolution par vidéo'!O9-N('Évolution par vidéo'!O8))</f>
+        <v/>
+      </c>
+      <c r="P9" s="3">
+        <f>IF('Évolution par vidéo'!P9="","",'Évolution par vidéo'!P9-N('Évolution par vidéo'!P8))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="3">
+        <f>SUM(B9:P9)</f>
         <v/>
       </c>
     </row>
@@ -7006,7 +7160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8163,7 +8317,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -8181,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -8196,7 +8350,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
@@ -8214,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -8229,7 +8383,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -8247,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -8262,7 +8416,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -8280,7 +8434,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -8295,7 +8449,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -8313,9 +8467,75 @@
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 16:57</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 18:15</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -8361,9 +8581,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId39"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId41"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$11</f>
+              <f>'Heure par heure'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$11</f>
+              <f>'Heure par heure'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$11</f>
+              <f>'Heure par heure'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$11</f>
+              <f>'Heure par heure'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$11</f>
+              <f>'Heure par heure'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$11</f>
+              <f>'Heure par heure'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$11</f>
+              <f>'Heure par heure'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$11</f>
+              <f>'Heure par heure'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$11</f>
+              <f>'Heure par heure'!$K$2:$K$12</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$11</f>
+              <f>'Heure par heure'!$L$2:$L$12</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$11</f>
+              <f>'Heure par heure'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$11</f>
+              <f>'Heure par heure'!$M$2:$M$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$11</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$11</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$11</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$11</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$11</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$11</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$11</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$11</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$11</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$11</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$12</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6068,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6587,6 +6587,50 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 09:00</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M12" s="3">
+        <f>SUM(C12:L12)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6599,7 +6643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7145,6 +7189,56 @@
       </c>
       <c r="L11" s="3">
         <f>SUM(B11:K11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <f>'Heure par heure'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="3">
+        <f>IF('Heure par heure'!C12="","",'Heure par heure'!C12-N('Heure par heure'!C11))</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>IF('Heure par heure'!D12="","",'Heure par heure'!D12-N('Heure par heure'!D11))</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>IF('Heure par heure'!E12="","",'Heure par heure'!E12-N('Heure par heure'!E11))</f>
+        <v/>
+      </c>
+      <c r="E12" s="3">
+        <f>IF('Heure par heure'!F12="","",'Heure par heure'!F12-N('Heure par heure'!F11))</f>
+        <v/>
+      </c>
+      <c r="F12" s="3">
+        <f>IF('Heure par heure'!G12="","",'Heure par heure'!G12-N('Heure par heure'!G11))</f>
+        <v/>
+      </c>
+      <c r="G12" s="3">
+        <f>IF('Heure par heure'!H12="","",'Heure par heure'!H12-N('Heure par heure'!H11))</f>
+        <v/>
+      </c>
+      <c r="H12" s="3">
+        <f>IF('Heure par heure'!I12="","",'Heure par heure'!I12-N('Heure par heure'!I11))</f>
+        <v/>
+      </c>
+      <c r="I12" s="3">
+        <f>IF('Heure par heure'!J12="","",'Heure par heure'!J12-N('Heure par heure'!J11))</f>
+        <v/>
+      </c>
+      <c r="J12" s="3">
+        <f>IF('Heure par heure'!K12="","",'Heure par heure'!K12-N('Heure par heure'!K11))</f>
+        <v/>
+      </c>
+      <c r="K12" s="3">
+        <f>IF('Heure par heure'!L12="","",'Heure par heure'!L12-N('Heure par heure'!L11))</f>
+        <v/>
+      </c>
+      <c r="L12" s="3">
+        <f>SUM(B12:K12)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$12</f>
+              <f>'Heure par heure'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$12</f>
+              <f>'Heure par heure'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$12</f>
+              <f>'Heure par heure'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$12</f>
+              <f>'Heure par heure'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$12</f>
+              <f>'Heure par heure'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$12</f>
+              <f>'Heure par heure'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$12</f>
+              <f>'Heure par heure'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$12</f>
+              <f>'Heure par heure'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$12</f>
+              <f>'Heure par heure'!$K$2:$K$13</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$12</f>
+              <f>'Heure par heure'!$L$2:$L$13</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$12</f>
+              <f>'Heure par heure'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$12</f>
+              <f>'Heure par heure'!$M$2:$M$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$12</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$12</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$12</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$12</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$12</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$12</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$12</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$12</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$12</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$12</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$13</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6068,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6631,6 +6631,50 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M13" s="3">
+        <f>SUM(C13:L13)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6643,7 +6687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7239,6 +7283,56 @@
       </c>
       <c r="L12" s="3">
         <f>SUM(B12:K12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <f>'Heure par heure'!A13</f>
+        <v/>
+      </c>
+      <c r="B13" s="3">
+        <f>IF('Heure par heure'!C13="","",'Heure par heure'!C13-N('Heure par heure'!C12))</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>IF('Heure par heure'!D13="","",'Heure par heure'!D13-N('Heure par heure'!D12))</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF('Heure par heure'!E13="","",'Heure par heure'!E13-N('Heure par heure'!E12))</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>IF('Heure par heure'!F13="","",'Heure par heure'!F13-N('Heure par heure'!F12))</f>
+        <v/>
+      </c>
+      <c r="F13" s="3">
+        <f>IF('Heure par heure'!G13="","",'Heure par heure'!G13-N('Heure par heure'!G12))</f>
+        <v/>
+      </c>
+      <c r="G13" s="3">
+        <f>IF('Heure par heure'!H13="","",'Heure par heure'!H13-N('Heure par heure'!H12))</f>
+        <v/>
+      </c>
+      <c r="H13" s="3">
+        <f>IF('Heure par heure'!I13="","",'Heure par heure'!I13-N('Heure par heure'!I12))</f>
+        <v/>
+      </c>
+      <c r="I13" s="3">
+        <f>IF('Heure par heure'!J13="","",'Heure par heure'!J13-N('Heure par heure'!J12))</f>
+        <v/>
+      </c>
+      <c r="J13" s="3">
+        <f>IF('Heure par heure'!K13="","",'Heure par heure'!K13-N('Heure par heure'!K12))</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>IF('Heure par heure'!L13="","",'Heure par heure'!L13-N('Heure par heure'!L12))</f>
+        <v/>
+      </c>
+      <c r="L13" s="3">
+        <f>SUM(B13:K13)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>2</v>
@@ -4097,17 +4097,17 @@
         <v/>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1749</v>
+        <v>1774</v>
       </c>
       <c r="E9" s="3">
         <f>IF(ROW()=2,D9,D9-D8)</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>9</v>
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>1</v>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>3</v>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -5358,13 +5358,13 @@
         <v>76</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -4097,17 +4097,17 @@
         <v/>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="E9" s="3">
         <f>IF(ROW()=2,D9,D9-D8)</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>9</v>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>114</v>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>3</v>
@@ -5358,10 +5358,10 @@
         <v>76</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>134</v>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$13</f>
+              <f>'Heure par heure'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$13</f>
+              <f>'Heure par heure'!$D$2:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$13</f>
+              <f>'Heure par heure'!$E$2:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$13</f>
+              <f>'Heure par heure'!$F$2:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$13</f>
+              <f>'Heure par heure'!$G$2:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$13</f>
+              <f>'Heure par heure'!$H$2:$H$14</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$13</f>
+              <f>'Heure par heure'!$I$2:$I$14</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$13</f>
+              <f>'Heure par heure'!$J$2:$J$14</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$13</f>
+              <f>'Heure par heure'!$K$2:$K$14</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$13</f>
+              <f>'Heure par heure'!$L$2:$L$14</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$13</f>
+              <f>'Heure par heure'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$13</f>
+              <f>'Heure par heure'!$M$2:$M$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$13</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$13</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$13</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$13</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$13</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$13</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$13</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$14</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$13</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$14</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$13</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$14</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$13</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$14</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6068,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6675,6 +6675,50 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:00</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M14" s="3">
+        <f>SUM(C14:L14)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6687,7 +6731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7333,6 +7377,56 @@
       </c>
       <c r="L13" s="3">
         <f>SUM(B13:K13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <f>'Heure par heure'!A14</f>
+        <v/>
+      </c>
+      <c r="B14" s="3">
+        <f>IF('Heure par heure'!C14="","",'Heure par heure'!C14-N('Heure par heure'!C13))</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>IF('Heure par heure'!D14="","",'Heure par heure'!D14-N('Heure par heure'!D13))</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>IF('Heure par heure'!E14="","",'Heure par heure'!E14-N('Heure par heure'!E13))</f>
+        <v/>
+      </c>
+      <c r="E14" s="3">
+        <f>IF('Heure par heure'!F14="","",'Heure par heure'!F14-N('Heure par heure'!F13))</f>
+        <v/>
+      </c>
+      <c r="F14" s="3">
+        <f>IF('Heure par heure'!G14="","",'Heure par heure'!G14-N('Heure par heure'!G13))</f>
+        <v/>
+      </c>
+      <c r="G14" s="3">
+        <f>IF('Heure par heure'!H14="","",'Heure par heure'!H14-N('Heure par heure'!H13))</f>
+        <v/>
+      </c>
+      <c r="H14" s="3">
+        <f>IF('Heure par heure'!I14="","",'Heure par heure'!I14-N('Heure par heure'!I13))</f>
+        <v/>
+      </c>
+      <c r="I14" s="3">
+        <f>IF('Heure par heure'!J14="","",'Heure par heure'!J14-N('Heure par heure'!J13))</f>
+        <v/>
+      </c>
+      <c r="J14" s="3">
+        <f>IF('Heure par heure'!K14="","",'Heure par heure'!K14-N('Heure par heure'!K13))</f>
+        <v/>
+      </c>
+      <c r="K14" s="3">
+        <f>IF('Heure par heure'!L14="","",'Heure par heure'!L14-N('Heure par heure'!L13))</f>
+        <v/>
+      </c>
+      <c r="L14" s="3">
+        <f>SUM(B14:K14)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -4104,10 +4104,10 @@
         <v/>
       </c>
       <c r="F9" s="3" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>9</v>
@@ -4791,7 +4791,7 @@
         <v>131</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>1</v>
@@ -4837,7 +4837,7 @@
         <v>204</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>3</v>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$14</f>
+              <f>'Heure par heure'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$14</f>
+              <f>'Heure par heure'!$D$2:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$14</f>
+              <f>'Heure par heure'!$E$2:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$14</f>
+              <f>'Heure par heure'!$F$2:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$14</f>
+              <f>'Heure par heure'!$G$2:$G$15</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$14</f>
+              <f>'Heure par heure'!$H$2:$H$15</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$14</f>
+              <f>'Heure par heure'!$I$2:$I$15</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$14</f>
+              <f>'Heure par heure'!$J$2:$J$15</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$14</f>
+              <f>'Heure par heure'!$K$2:$K$15</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$14</f>
+              <f>'Heure par heure'!$L$2:$L$15</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$14</f>
+              <f>'Heure par heure'!$B$2:$B$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$14</f>
+              <f>'Heure par heure'!$M$2:$M$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$14</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$14</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$14</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$14</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$14</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$14</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$15</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$14</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$15</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$14</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$15</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$14</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$15</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$14</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$15</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6068,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6719,6 +6719,50 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:00</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M15" s="3">
+        <f>SUM(C15:L15)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6731,7 +6775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7427,6 +7471,56 @@
       </c>
       <c r="L14" s="3">
         <f>SUM(B14:K14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <f>'Heure par heure'!A15</f>
+        <v/>
+      </c>
+      <c r="B15" s="3">
+        <f>IF('Heure par heure'!C15="","",'Heure par heure'!C15-N('Heure par heure'!C14))</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>IF('Heure par heure'!D15="","",'Heure par heure'!D15-N('Heure par heure'!D14))</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>IF('Heure par heure'!E15="","",'Heure par heure'!E15-N('Heure par heure'!E14))</f>
+        <v/>
+      </c>
+      <c r="E15" s="3">
+        <f>IF('Heure par heure'!F15="","",'Heure par heure'!F15-N('Heure par heure'!F14))</f>
+        <v/>
+      </c>
+      <c r="F15" s="3">
+        <f>IF('Heure par heure'!G15="","",'Heure par heure'!G15-N('Heure par heure'!G14))</f>
+        <v/>
+      </c>
+      <c r="G15" s="3">
+        <f>IF('Heure par heure'!H15="","",'Heure par heure'!H15-N('Heure par heure'!H14))</f>
+        <v/>
+      </c>
+      <c r="H15" s="3">
+        <f>IF('Heure par heure'!I15="","",'Heure par heure'!I15-N('Heure par heure'!I14))</f>
+        <v/>
+      </c>
+      <c r="I15" s="3">
+        <f>IF('Heure par heure'!J15="","",'Heure par heure'!J15-N('Heure par heure'!J14))</f>
+        <v/>
+      </c>
+      <c r="J15" s="3">
+        <f>IF('Heure par heure'!K15="","",'Heure par heure'!K15-N('Heure par heure'!K14))</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>IF('Heure par heure'!L15="","",'Heure par heure'!L15-N('Heure par heure'!L14))</f>
+        <v/>
+      </c>
+      <c r="L15" s="3">
+        <f>SUM(B15:K15)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$15</f>
+              <f>'Heure par heure'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$15</f>
+              <f>'Heure par heure'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$15</f>
+              <f>'Heure par heure'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$15</f>
+              <f>'Heure par heure'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$15</f>
+              <f>'Heure par heure'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$15</f>
+              <f>'Heure par heure'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$15</f>
+              <f>'Heure par heure'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$15</f>
+              <f>'Heure par heure'!$J$2:$J$16</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$15</f>
+              <f>'Heure par heure'!$K$2:$K$16</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$15</f>
+              <f>'Heure par heure'!$L$2:$L$16</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$15</f>
+              <f>'Heure par heure'!$B$2:$B$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$15</f>
+              <f>'Heure par heure'!$M$2:$M$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$15</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$15</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$15</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$15</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$15</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$15</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$15</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$15</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$15</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$16</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$15</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$16</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6068,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6763,6 +6763,50 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:00</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M16" s="3">
+        <f>SUM(C16:L16)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6775,7 +6819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7521,6 +7565,56 @@
       </c>
       <c r="L15" s="3">
         <f>SUM(B15:K15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <f>'Heure par heure'!A16</f>
+        <v/>
+      </c>
+      <c r="B16" s="3">
+        <f>IF('Heure par heure'!C16="","",'Heure par heure'!C16-N('Heure par heure'!C15))</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>IF('Heure par heure'!D16="","",'Heure par heure'!D16-N('Heure par heure'!D15))</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>IF('Heure par heure'!E16="","",'Heure par heure'!E16-N('Heure par heure'!E15))</f>
+        <v/>
+      </c>
+      <c r="E16" s="3">
+        <f>IF('Heure par heure'!F16="","",'Heure par heure'!F16-N('Heure par heure'!F15))</f>
+        <v/>
+      </c>
+      <c r="F16" s="3">
+        <f>IF('Heure par heure'!G16="","",'Heure par heure'!G16-N('Heure par heure'!G15))</f>
+        <v/>
+      </c>
+      <c r="G16" s="3">
+        <f>IF('Heure par heure'!H16="","",'Heure par heure'!H16-N('Heure par heure'!H15))</f>
+        <v/>
+      </c>
+      <c r="H16" s="3">
+        <f>IF('Heure par heure'!I16="","",'Heure par heure'!I16-N('Heure par heure'!I15))</f>
+        <v/>
+      </c>
+      <c r="I16" s="3">
+        <f>IF('Heure par heure'!J16="","",'Heure par heure'!J16-N('Heure par heure'!J15))</f>
+        <v/>
+      </c>
+      <c r="J16" s="3">
+        <f>IF('Heure par heure'!K16="","",'Heure par heure'!K16-N('Heure par heure'!K15))</f>
+        <v/>
+      </c>
+      <c r="K16" s="3">
+        <f>IF('Heure par heure'!L16="","",'Heure par heure'!L16-N('Heure par heure'!L15))</f>
+        <v/>
+      </c>
+      <c r="L16" s="3">
+        <f>SUM(B16:K16)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$16</f>
+              <f>'Heure par heure'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$16</f>
+              <f>'Heure par heure'!$D$2:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$16</f>
+              <f>'Heure par heure'!$E$2:$E$17</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$16</f>
+              <f>'Heure par heure'!$F$2:$F$17</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$16</f>
+              <f>'Heure par heure'!$G$2:$G$17</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$16</f>
+              <f>'Heure par heure'!$H$2:$H$17</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$16</f>
+              <f>'Heure par heure'!$I$2:$I$17</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$16</f>
+              <f>'Heure par heure'!$J$2:$J$17</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$16</f>
+              <f>'Heure par heure'!$K$2:$K$17</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$16</f>
+              <f>'Heure par heure'!$L$2:$L$17</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$16</f>
+              <f>'Heure par heure'!$B$2:$B$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$16</f>
+              <f>'Heure par heure'!$M$2:$M$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$16</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$16</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$16</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$16</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$17</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$16</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$17</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$16</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$17</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$16</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$17</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$16</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$17</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$16</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$17</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$16</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$17</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6068,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6807,6 +6807,50 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:00</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M17" s="3">
+        <f>SUM(C17:L17)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6819,7 +6863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7615,6 +7659,56 @@
       </c>
       <c r="L16" s="3">
         <f>SUM(B16:K16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <f>'Heure par heure'!A17</f>
+        <v/>
+      </c>
+      <c r="B17" s="3">
+        <f>IF('Heure par heure'!C17="","",'Heure par heure'!C17-N('Heure par heure'!C16))</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>IF('Heure par heure'!D17="","",'Heure par heure'!D17-N('Heure par heure'!D16))</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>IF('Heure par heure'!E17="","",'Heure par heure'!E17-N('Heure par heure'!E16))</f>
+        <v/>
+      </c>
+      <c r="E17" s="3">
+        <f>IF('Heure par heure'!F17="","",'Heure par heure'!F17-N('Heure par heure'!F16))</f>
+        <v/>
+      </c>
+      <c r="F17" s="3">
+        <f>IF('Heure par heure'!G17="","",'Heure par heure'!G17-N('Heure par heure'!G16))</f>
+        <v/>
+      </c>
+      <c r="G17" s="3">
+        <f>IF('Heure par heure'!H17="","",'Heure par heure'!H17-N('Heure par heure'!H16))</f>
+        <v/>
+      </c>
+      <c r="H17" s="3">
+        <f>IF('Heure par heure'!I17="","",'Heure par heure'!I17-N('Heure par heure'!I16))</f>
+        <v/>
+      </c>
+      <c r="I17" s="3">
+        <f>IF('Heure par heure'!J17="","",'Heure par heure'!J17-N('Heure par heure'!J16))</f>
+        <v/>
+      </c>
+      <c r="J17" s="3">
+        <f>IF('Heure par heure'!K17="","",'Heure par heure'!K17-N('Heure par heure'!K16))</f>
+        <v/>
+      </c>
+      <c r="K17" s="3">
+        <f>IF('Heure par heure'!L17="","",'Heure par heure'!L17-N('Heure par heure'!L16))</f>
+        <v/>
+      </c>
+      <c r="L17" s="3">
+        <f>SUM(B17:K17)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$17</f>
+              <f>'Heure par heure'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$17</f>
+              <f>'Heure par heure'!$D$2:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$17</f>
+              <f>'Heure par heure'!$E$2:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$17</f>
+              <f>'Heure par heure'!$F$2:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$17</f>
+              <f>'Heure par heure'!$G$2:$G$18</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$17</f>
+              <f>'Heure par heure'!$H$2:$H$18</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$17</f>
+              <f>'Heure par heure'!$I$2:$I$18</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$17</f>
+              <f>'Heure par heure'!$J$2:$J$18</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$17</f>
+              <f>'Heure par heure'!$K$2:$K$18</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$17</f>
+              <f>'Heure par heure'!$L$2:$L$18</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$17</f>
+              <f>'Heure par heure'!$B$2:$B$18</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$17</f>
+              <f>'Heure par heure'!$M$2:$M$18</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$17</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$17</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$17</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$17</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$17</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$17</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$18</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$17</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$18</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$17</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$18</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$17</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$18</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$17</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$18</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6068,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6099,52 +6099,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-19 📖 Il était une fois de</t>
+          <t>10-20 Couvre-feu pour les ad</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
+          <t>10-21 Les syndicats de salar</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-20 Couvre-feu pour les ad</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -6163,32 +6163,28 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="K2" s="3" t="n">
         <v>124</v>
       </c>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3">
         <f>SUM(C2:L2)</f>
@@ -6205,32 +6201,28 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="K3" s="3" t="n">
         <v>130</v>
       </c>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3">
         <f>SUM(C3:L3)</f>
@@ -6247,32 +6239,28 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="K4" s="3" t="n">
         <v>135</v>
       </c>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3">
         <f>SUM(C4:L4)</f>
@@ -6289,35 +6277,31 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3">
         <f>SUM(C5:L5)</f>
         <v/>
@@ -6333,35 +6317,31 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="L6" s="3" t="n">
         <v>34</v>
       </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
       <c r="M6" s="3">
         <f>SUM(C6:L6)</f>
         <v/>
@@ -6377,35 +6357,31 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="L7" s="3" t="n">
         <v>44</v>
       </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
       <c r="M7" s="3">
         <f>SUM(C7:L7)</f>
         <v/>
@@ -6421,35 +6397,31 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="L8" s="3" t="n">
         <v>70</v>
       </c>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
       <c r="M8" s="3">
         <f>SUM(C8:L8)</f>
         <v/>
@@ -6465,35 +6437,31 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="L9" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
       <c r="M9" s="3">
         <f>SUM(C9:L9)</f>
         <v/>
@@ -6509,35 +6477,31 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
       <c r="M10" s="3">
         <f>SUM(C10:L10)</f>
         <v/>
@@ -6553,35 +6517,31 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
       <c r="M11" s="3">
         <f>SUM(C11:L11)</f>
         <v/>
@@ -6597,35 +6557,31 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="L12" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
       <c r="M12" s="3">
         <f>SUM(C12:L12)</f>
         <v/>
@@ -6641,35 +6597,31 @@
         <v>6</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="L13" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
       <c r="M13" s="3">
         <f>SUM(C13:L13)</f>
         <v/>
@@ -6685,35 +6637,31 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="L14" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
       <c r="M14" s="3">
         <f>SUM(C14:L14)</f>
         <v/>
@@ -6729,35 +6677,31 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="L15" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
       <c r="M15" s="3">
         <f>SUM(C15:L15)</f>
         <v/>
@@ -6773,35 +6717,31 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="L16" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3">
         <f>SUM(C16:L16)</f>
         <v/>
@@ -6817,37 +6757,77 @@
         <v>6</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="L17" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
       <c r="M17" s="3">
         <f>SUM(C17:L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 15:00</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <f>SUM(C18:L18)</f>
         <v/>
       </c>
     </row>
@@ -6863,7 +6843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6888,52 +6868,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>10-19 📖 Il était une fois de</t>
+          <t>10-20 Couvre-feu pour les ad</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-20 Couvre-feux, manifs « </t>
+          <t>10-21 Les syndicats de salar</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-20 Couvre-feu pour les ad</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -7709,6 +7689,56 @@
       </c>
       <c r="L17" s="3">
         <f>SUM(B17:K17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <f>'Heure par heure'!A18</f>
+        <v/>
+      </c>
+      <c r="B18" s="3">
+        <f>IF('Heure par heure'!C18="","",'Heure par heure'!C18-N('Heure par heure'!C17))</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>IF('Heure par heure'!D18="","",'Heure par heure'!D18-N('Heure par heure'!D17))</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>IF('Heure par heure'!E18="","",'Heure par heure'!E18-N('Heure par heure'!E17))</f>
+        <v/>
+      </c>
+      <c r="E18" s="3">
+        <f>IF('Heure par heure'!F18="","",'Heure par heure'!F18-N('Heure par heure'!F17))</f>
+        <v/>
+      </c>
+      <c r="F18" s="3">
+        <f>IF('Heure par heure'!G18="","",'Heure par heure'!G18-N('Heure par heure'!G17))</f>
+        <v/>
+      </c>
+      <c r="G18" s="3">
+        <f>IF('Heure par heure'!H18="","",'Heure par heure'!H18-N('Heure par heure'!H17))</f>
+        <v/>
+      </c>
+      <c r="H18" s="3">
+        <f>IF('Heure par heure'!I18="","",'Heure par heure'!I18-N('Heure par heure'!I17))</f>
+        <v/>
+      </c>
+      <c r="I18" s="3">
+        <f>IF('Heure par heure'!J18="","",'Heure par heure'!J18-N('Heure par heure'!J17))</f>
+        <v/>
+      </c>
+      <c r="J18" s="3">
+        <f>IF('Heure par heure'!K18="","",'Heure par heure'!K18-N('Heure par heure'!K17))</f>
+        <v/>
+      </c>
+      <c r="K18" s="3">
+        <f>IF('Heure par heure'!L18="","",'Heure par heure'!L18-N('Heure par heure'!L17))</f>
+        <v/>
+      </c>
+      <c r="L18" s="3">
+        <f>SUM(B18:K18)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -1244,12 +1244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$41</f>
+              <f>'Stories'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$41</f>
+              <f>'Stories'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>2</v>
@@ -4097,26 +4097,26 @@
         <v/>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1778</v>
+        <v>1609</v>
       </c>
       <c r="E9" s="3">
         <f>IF(ROW()=2,D9,D9-D8)</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>483</v>
+        <v>529</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4222,12 +4222,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 20:18</t>
+          <t>2026-10-19 08:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'attend le 1er novemb</t>
+          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4236,13 +4236,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -4268,12 +4268,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 06:14</t>
+          <t>2026-10-19 09:09</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère et tu restes après</t>
+          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>1</v>
@@ -4314,12 +4314,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:14</t>
+          <t>2026-10-19 12:05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4328,13 +4328,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -4360,12 +4360,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
@@ -4406,12 +4406,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4420,13 +4420,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -4452,12 +4452,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4466,13 +4466,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <f>IFERROR((F7+G7+H7+I7)/IF(E7&gt;0,E7,D7),0)</f>
@@ -4498,12 +4498,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4512,13 +4512,13 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K8" s="5">
         <f>IFERROR((F8+G8+H8+I8)/IF(E8&gt;0,E8,D8),0)</f>
@@ -4544,12 +4544,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="5">
         <f>IFERROR((F9+G9+H9+I9)/IF(E9&gt;0,E9,D9),0)</f>
@@ -4590,12 +4590,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4604,13 +4604,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
@@ -4636,12 +4636,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Couper les réseaux sociaux pendant les émeute</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
@@ -4682,12 +4682,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:08</t>
+          <t>2026-10-24 12:30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou non ? Réponds en co</t>
+          <t>À toi de juger : il faut une enquête indépend</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4696,13 +4696,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
@@ -4728,12 +4728,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-24 13:56</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux pendant les émeute</t>
+          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4742,13 +4742,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -4757,10 +4757,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K13" s="5">
         <f>IFERROR((F13+G13+H13+I13)/IF(E13&gt;0,E13,D13),0)</f>
@@ -4774,12 +4774,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 12:30</t>
+          <t>2026-10-24 18:14</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une enquête indépend</t>
+          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4788,13 +4788,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>115</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5">
         <f>IFERROR((F14+G14+H14+I14)/IF(E14&gt;0,E14,D14),0)</f>
@@ -4820,12 +4820,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:56</t>
+          <t>2026-10-25 13:58</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
+          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>204</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="5">
         <f>IFERROR((F15+G15+H15+I15)/IF(E15&gt;0,E15,D15),0)</f>
@@ -4866,12 +4866,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 18:14</t>
+          <t>2026-10-25 13:59</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
+          <t>Vendredi, Macron au concert de Céline Dion. S</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -4967,77 +4967,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
     </row>
@@ -5070,20 +5070,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="F3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
@@ -5102,26 +5098,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="H4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
@@ -5138,35 +5130,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="K5" s="3" t="n">
         <v>69</v>
       </c>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
@@ -5180,41 +5168,37 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>105</v>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="M6" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n"/>
@@ -5226,41 +5210,37 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>105</v>
-      </c>
       <c r="K7" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="M7" s="3" t="n">
         <v>74</v>
       </c>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
@@ -5272,47 +5252,43 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="O8" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n"/>
     </row>
     <row r="9">
@@ -5322,49 +5298,49 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>204</v>
+        <v>10</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>134</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -5409,77 +5385,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>😱 Ma réaction à ce qui t'att</t>
+          <t>Et soudain, 718 stations san</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>🧮 Quiz : ta manif dégénère e</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -7754,7 +7730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9076,7 +9052,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -9109,7 +9085,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -9130,6 +9106,138 @@
         <v>0</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:08</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:58</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:00</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:25</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -9177,9 +9285,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId41"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$18</f>
+              <f>'Heure par heure'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$18</f>
+              <f>'Heure par heure'!$D$2:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$18</f>
+              <f>'Heure par heure'!$E$2:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$18</f>
+              <f>'Heure par heure'!$F$2:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$18</f>
+              <f>'Heure par heure'!$G$2:$G$19</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$18</f>
+              <f>'Heure par heure'!$H$2:$H$19</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$18</f>
+              <f>'Heure par heure'!$I$2:$I$19</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$18</f>
+              <f>'Heure par heure'!$J$2:$J$19</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$18</f>
+              <f>'Heure par heure'!$K$2:$K$19</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$18</f>
+              <f>'Heure par heure'!$L$2:$L$19</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$18</f>
+              <f>'Heure par heure'!$B$2:$B$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$18</f>
+              <f>'Heure par heure'!$M$2:$M$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$18</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$18</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$18</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$18</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$18</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$18</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$19</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$18</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$19</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$18</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$19</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$18</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$19</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$18</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$19</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6807,6 +6807,50 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 16:00</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="M19" s="3">
+        <f>SUM(C19:L19)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6819,7 +6863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7715,6 +7759,56 @@
       </c>
       <c r="L18" s="3">
         <f>SUM(B18:K18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <f>'Heure par heure'!A19</f>
+        <v/>
+      </c>
+      <c r="B19" s="3">
+        <f>IF('Heure par heure'!C19="","",'Heure par heure'!C19-N('Heure par heure'!C18))</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>IF('Heure par heure'!D19="","",'Heure par heure'!D19-N('Heure par heure'!D18))</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>IF('Heure par heure'!E19="","",'Heure par heure'!E19-N('Heure par heure'!E18))</f>
+        <v/>
+      </c>
+      <c r="E19" s="3">
+        <f>IF('Heure par heure'!F19="","",'Heure par heure'!F19-N('Heure par heure'!F18))</f>
+        <v/>
+      </c>
+      <c r="F19" s="3">
+        <f>IF('Heure par heure'!G19="","",'Heure par heure'!G19-N('Heure par heure'!G18))</f>
+        <v/>
+      </c>
+      <c r="G19" s="3">
+        <f>IF('Heure par heure'!H19="","",'Heure par heure'!H19-N('Heure par heure'!H18))</f>
+        <v/>
+      </c>
+      <c r="H19" s="3">
+        <f>IF('Heure par heure'!I19="","",'Heure par heure'!I19-N('Heure par heure'!I18))</f>
+        <v/>
+      </c>
+      <c r="I19" s="3">
+        <f>IF('Heure par heure'!J19="","",'Heure par heure'!J19-N('Heure par heure'!J18))</f>
+        <v/>
+      </c>
+      <c r="J19" s="3">
+        <f>IF('Heure par heure'!K19="","",'Heure par heure'!K19-N('Heure par heure'!K18))</f>
+        <v/>
+      </c>
+      <c r="K19" s="3">
+        <f>IF('Heure par heure'!L19="","",'Heure par heure'!L19-N('Heure par heure'!L18))</f>
+        <v/>
+      </c>
+      <c r="L19" s="3">
+        <f>SUM(B19:K19)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$19</f>
+              <f>'Heure par heure'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$19</f>
+              <f>'Heure par heure'!$D$2:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$19</f>
+              <f>'Heure par heure'!$E$2:$E$20</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$19</f>
+              <f>'Heure par heure'!$F$2:$F$20</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$19</f>
+              <f>'Heure par heure'!$G$2:$G$20</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$19</f>
+              <f>'Heure par heure'!$H$2:$H$20</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$19</f>
+              <f>'Heure par heure'!$I$2:$I$20</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$19</f>
+              <f>'Heure par heure'!$J$2:$J$20</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$19</f>
+              <f>'Heure par heure'!$K$2:$K$20</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$19</f>
+              <f>'Heure par heure'!$L$2:$L$20</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$19</f>
+              <f>'Heure par heure'!$B$2:$B$20</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$19</f>
+              <f>'Heure par heure'!$M$2:$M$20</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$19</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$19</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$19</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$19</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$20</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$19</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$20</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$19</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$20</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$19</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$20</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$19</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$20</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$19</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$20</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$19</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$20</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6851,6 +6851,50 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 17:00</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="M20" s="3">
+        <f>SUM(C20:L20)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6863,7 +6907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7809,6 +7853,56 @@
       </c>
       <c r="L19" s="3">
         <f>SUM(B19:K19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <f>'Heure par heure'!A20</f>
+        <v/>
+      </c>
+      <c r="B20" s="3">
+        <f>IF('Heure par heure'!C20="","",'Heure par heure'!C20-N('Heure par heure'!C19))</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>IF('Heure par heure'!D20="","",'Heure par heure'!D20-N('Heure par heure'!D19))</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>IF('Heure par heure'!E20="","",'Heure par heure'!E20-N('Heure par heure'!E19))</f>
+        <v/>
+      </c>
+      <c r="E20" s="3">
+        <f>IF('Heure par heure'!F20="","",'Heure par heure'!F20-N('Heure par heure'!F19))</f>
+        <v/>
+      </c>
+      <c r="F20" s="3">
+        <f>IF('Heure par heure'!G20="","",'Heure par heure'!G20-N('Heure par heure'!G19))</f>
+        <v/>
+      </c>
+      <c r="G20" s="3">
+        <f>IF('Heure par heure'!H20="","",'Heure par heure'!H20-N('Heure par heure'!H19))</f>
+        <v/>
+      </c>
+      <c r="H20" s="3">
+        <f>IF('Heure par heure'!I20="","",'Heure par heure'!I20-N('Heure par heure'!I19))</f>
+        <v/>
+      </c>
+      <c r="I20" s="3">
+        <f>IF('Heure par heure'!J20="","",'Heure par heure'!J20-N('Heure par heure'!J19))</f>
+        <v/>
+      </c>
+      <c r="J20" s="3">
+        <f>IF('Heure par heure'!K20="","",'Heure par heure'!K20-N('Heure par heure'!K19))</f>
+        <v/>
+      </c>
+      <c r="K20" s="3">
+        <f>IF('Heure par heure'!L20="","",'Heure par heure'!L20-N('Heure par heure'!L19))</f>
+        <v/>
+      </c>
+      <c r="L20" s="3">
+        <f>SUM(B20:K20)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$20</f>
+              <f>'Heure par heure'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$20</f>
+              <f>'Heure par heure'!$D$2:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$20</f>
+              <f>'Heure par heure'!$E$2:$E$21</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$20</f>
+              <f>'Heure par heure'!$F$2:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$20</f>
+              <f>'Heure par heure'!$G$2:$G$21</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$20</f>
+              <f>'Heure par heure'!$H$2:$H$21</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$20</f>
+              <f>'Heure par heure'!$I$2:$I$21</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$20</f>
+              <f>'Heure par heure'!$J$2:$J$21</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$20</f>
+              <f>'Heure par heure'!$K$2:$K$21</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$20</f>
+              <f>'Heure par heure'!$L$2:$L$21</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$20</f>
+              <f>'Heure par heure'!$B$2:$B$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$20</f>
+              <f>'Heure par heure'!$M$2:$M$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$20</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$20</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$20</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$20</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$21</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$20</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$20</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$21</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$20</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$21</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$20</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$21</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$20</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$21</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$20</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$21</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6075,52 +6075,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-20 Couvre-feu pour les ad</t>
+          <t>10-21 Les syndicats de salar</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Des millions publics p</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Vendredi, Macron au co</t>
+          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -6139,26 +6139,24 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="I2" s="3" t="n">
         <v>124</v>
       </c>
+      <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
@@ -6177,26 +6175,24 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="I3" s="3" t="n">
         <v>130</v>
       </c>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
@@ -6215,26 +6211,24 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="I4" s="3" t="n">
         <v>135</v>
       </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
@@ -6253,29 +6247,27 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3">
@@ -6293,29 +6285,27 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="J6" s="3" t="n">
         <v>34</v>
       </c>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3">
@@ -6333,29 +6323,27 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="J7" s="3" t="n">
         <v>44</v>
       </c>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3">
@@ -6373,29 +6361,27 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="J8" s="3" t="n">
         <v>70</v>
       </c>
+      <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3">
@@ -6413,29 +6399,27 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="J9" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3">
@@ -6453,29 +6437,27 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="J10" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3">
@@ -6493,29 +6475,27 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="J11" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3">
@@ -6533,29 +6513,27 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="J12" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3">
@@ -6573,29 +6551,27 @@
         <v>6</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>130</v>
+        <v>199</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="J13" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3">
@@ -6613,29 +6589,27 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="J14" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3">
@@ -6653,29 +6627,27 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="J15" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3">
@@ -6693,29 +6665,27 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="J16" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3">
@@ -6733,29 +6703,27 @@
         <v>6</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="J17" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3">
@@ -6773,35 +6741,33 @@
         <v>6</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>240</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L18" s="3" t="n"/>
       <c r="M18" s="3">
         <f>SUM(C18:L18)</f>
         <v/>
@@ -6817,35 +6783,33 @@
         <v>7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L19" s="3" t="n">
         <v>53</v>
       </c>
+      <c r="L19" s="3" t="n"/>
       <c r="M19" s="3">
         <f>SUM(C19:L19)</f>
         <v/>
@@ -6861,37 +6825,79 @@
         <v>7</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L20" s="3" t="n">
         <v>80</v>
       </c>
+      <c r="L20" s="3" t="n"/>
       <c r="M20" s="3">
         <f>SUM(C20:L20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 18:00</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <f>SUM(C21:L21)</f>
         <v/>
       </c>
     </row>
@@ -6907,7 +6913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6932,52 +6938,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>10-20 Couvre-feu pour les ad</t>
+          <t>10-21 Les syndicats de salar</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Des millions publics p</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Vendredi, Macron au co</t>
+          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -7903,6 +7909,56 @@
       </c>
       <c r="L20" s="3">
         <f>SUM(B20:K20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <f>'Heure par heure'!A21</f>
+        <v/>
+      </c>
+      <c r="B21" s="3">
+        <f>IF('Heure par heure'!C21="","",'Heure par heure'!C21-N('Heure par heure'!C20))</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>IF('Heure par heure'!D21="","",'Heure par heure'!D21-N('Heure par heure'!D20))</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>IF('Heure par heure'!E21="","",'Heure par heure'!E21-N('Heure par heure'!E20))</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>IF('Heure par heure'!F21="","",'Heure par heure'!F21-N('Heure par heure'!F20))</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>IF('Heure par heure'!G21="","",'Heure par heure'!G21-N('Heure par heure'!G20))</f>
+        <v/>
+      </c>
+      <c r="G21" s="3">
+        <f>IF('Heure par heure'!H21="","",'Heure par heure'!H21-N('Heure par heure'!H20))</f>
+        <v/>
+      </c>
+      <c r="H21" s="3">
+        <f>IF('Heure par heure'!I21="","",'Heure par heure'!I21-N('Heure par heure'!I20))</f>
+        <v/>
+      </c>
+      <c r="I21" s="3">
+        <f>IF('Heure par heure'!J21="","",'Heure par heure'!J21-N('Heure par heure'!J20))</f>
+        <v/>
+      </c>
+      <c r="J21" s="3">
+        <f>IF('Heure par heure'!K21="","",'Heure par heure'!K21-N('Heure par heure'!K20))</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>IF('Heure par heure'!L21="","",'Heure par heure'!L21-N('Heure par heure'!L20))</f>
+        <v/>
+      </c>
+      <c r="L21" s="3">
+        <f>SUM(B21:K21)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$21</f>
+              <f>'Heure par heure'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$21</f>
+              <f>'Heure par heure'!$D$2:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$21</f>
+              <f>'Heure par heure'!$E$2:$E$22</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$21</f>
+              <f>'Heure par heure'!$F$2:$F$22</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$21</f>
+              <f>'Heure par heure'!$G$2:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$21</f>
+              <f>'Heure par heure'!$H$2:$H$22</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$21</f>
+              <f>'Heure par heure'!$I$2:$I$22</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$21</f>
+              <f>'Heure par heure'!$J$2:$J$22</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$21</f>
+              <f>'Heure par heure'!$K$2:$K$22</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$21</f>
+              <f>'Heure par heure'!$L$2:$L$22</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$21</f>
+              <f>'Heure par heure'!$B$2:$B$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$21</f>
+              <f>'Heure par heure'!$M$2:$M$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$21</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$21</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$21</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$21</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$22</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$21</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$22</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$21</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$21</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$22</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$21</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$22</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$21</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$22</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$21</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$22</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6901,6 +6901,50 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 19:00</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="M22" s="3">
+        <f>SUM(C22:L22)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6913,7 +6957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7959,6 +8003,56 @@
       </c>
       <c r="L21" s="3">
         <f>SUM(B21:K21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <f>'Heure par heure'!A22</f>
+        <v/>
+      </c>
+      <c r="B22" s="3">
+        <f>IF('Heure par heure'!C22="","",'Heure par heure'!C22-N('Heure par heure'!C21))</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>IF('Heure par heure'!D22="","",'Heure par heure'!D22-N('Heure par heure'!D21))</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>IF('Heure par heure'!E22="","",'Heure par heure'!E22-N('Heure par heure'!E21))</f>
+        <v/>
+      </c>
+      <c r="E22" s="3">
+        <f>IF('Heure par heure'!F22="","",'Heure par heure'!F22-N('Heure par heure'!F21))</f>
+        <v/>
+      </c>
+      <c r="F22" s="3">
+        <f>IF('Heure par heure'!G22="","",'Heure par heure'!G22-N('Heure par heure'!G21))</f>
+        <v/>
+      </c>
+      <c r="G22" s="3">
+        <f>IF('Heure par heure'!H22="","",'Heure par heure'!H22-N('Heure par heure'!H21))</f>
+        <v/>
+      </c>
+      <c r="H22" s="3">
+        <f>IF('Heure par heure'!I22="","",'Heure par heure'!I22-N('Heure par heure'!I21))</f>
+        <v/>
+      </c>
+      <c r="I22" s="3">
+        <f>IF('Heure par heure'!J22="","",'Heure par heure'!J22-N('Heure par heure'!J21))</f>
+        <v/>
+      </c>
+      <c r="J22" s="3">
+        <f>IF('Heure par heure'!K22="","",'Heure par heure'!K22-N('Heure par heure'!K21))</f>
+        <v/>
+      </c>
+      <c r="K22" s="3">
+        <f>IF('Heure par heure'!L22="","",'Heure par heure'!L22-N('Heure par heure'!L21))</f>
+        <v/>
+      </c>
+      <c r="L22" s="3">
+        <f>SUM(B22:K22)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$22</f>
+              <f>'Heure par heure'!$C$2:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$22</f>
+              <f>'Heure par heure'!$D$2:$D$23</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$22</f>
+              <f>'Heure par heure'!$E$2:$E$23</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$22</f>
+              <f>'Heure par heure'!$F$2:$F$23</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$22</f>
+              <f>'Heure par heure'!$G$2:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$22</f>
+              <f>'Heure par heure'!$H$2:$H$23</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$22</f>
+              <f>'Heure par heure'!$I$2:$I$23</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$22</f>
+              <f>'Heure par heure'!$J$2:$J$23</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$22</f>
+              <f>'Heure par heure'!$K$2:$K$23</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$22</f>
+              <f>'Heure par heure'!$L$2:$L$23</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$22</f>
+              <f>'Heure par heure'!$B$2:$B$23</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$22</f>
+              <f>'Heure par heure'!$M$2:$M$23</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$22</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$22</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$22</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$23</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$22</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$23</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$22</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$23</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$22</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$22</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$23</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$22</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$23</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$22</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$23</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$22</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$23</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6945,6 +6945,50 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:00</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="M23" s="3">
+        <f>SUM(C23:L23)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6957,7 +7001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8053,6 +8097,56 @@
       </c>
       <c r="L22" s="3">
         <f>SUM(B22:K22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <f>'Heure par heure'!A23</f>
+        <v/>
+      </c>
+      <c r="B23" s="3">
+        <f>IF('Heure par heure'!C23="","",'Heure par heure'!C23-N('Heure par heure'!C22))</f>
+        <v/>
+      </c>
+      <c r="C23" s="3">
+        <f>IF('Heure par heure'!D23="","",'Heure par heure'!D23-N('Heure par heure'!D22))</f>
+        <v/>
+      </c>
+      <c r="D23" s="3">
+        <f>IF('Heure par heure'!E23="","",'Heure par heure'!E23-N('Heure par heure'!E22))</f>
+        <v/>
+      </c>
+      <c r="E23" s="3">
+        <f>IF('Heure par heure'!F23="","",'Heure par heure'!F23-N('Heure par heure'!F22))</f>
+        <v/>
+      </c>
+      <c r="F23" s="3">
+        <f>IF('Heure par heure'!G23="","",'Heure par heure'!G23-N('Heure par heure'!G22))</f>
+        <v/>
+      </c>
+      <c r="G23" s="3">
+        <f>IF('Heure par heure'!H23="","",'Heure par heure'!H23-N('Heure par heure'!H22))</f>
+        <v/>
+      </c>
+      <c r="H23" s="3">
+        <f>IF('Heure par heure'!I23="","",'Heure par heure'!I23-N('Heure par heure'!I22))</f>
+        <v/>
+      </c>
+      <c r="I23" s="3">
+        <f>IF('Heure par heure'!J23="","",'Heure par heure'!J23-N('Heure par heure'!J22))</f>
+        <v/>
+      </c>
+      <c r="J23" s="3">
+        <f>IF('Heure par heure'!K23="","",'Heure par heure'!K23-N('Heure par heure'!K22))</f>
+        <v/>
+      </c>
+      <c r="K23" s="3">
+        <f>IF('Heure par heure'!L23="","",'Heure par heure'!L23-N('Heure par heure'!L22))</f>
+        <v/>
+      </c>
+      <c r="L23" s="3">
+        <f>SUM(B23:K23)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$23</f>
+              <f>'Heure par heure'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$23</f>
+              <f>'Heure par heure'!$D$2:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$23</f>
+              <f>'Heure par heure'!$E$2:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$23</f>
+              <f>'Heure par heure'!$F$2:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$23</f>
+              <f>'Heure par heure'!$G$2:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$23</f>
+              <f>'Heure par heure'!$H$2:$H$24</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$23</f>
+              <f>'Heure par heure'!$I$2:$I$24</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$23</f>
+              <f>'Heure par heure'!$J$2:$J$24</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$23</f>
+              <f>'Heure par heure'!$K$2:$K$24</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$23</f>
+              <f>'Heure par heure'!$L$2:$L$24</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$23</f>
+              <f>'Heure par heure'!$B$2:$B$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$23</f>
+              <f>'Heure par heure'!$M$2:$M$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$23</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$23</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$23</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$23</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$23</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$23</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$23</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$24</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$23</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$24</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$23</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$24</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$23</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$24</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6989,6 +6989,50 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:00</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="M24" s="3">
+        <f>SUM(C24:L24)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7001,7 +7045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8147,6 +8191,56 @@
       </c>
       <c r="L23" s="3">
         <f>SUM(B23:K23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <f>'Heure par heure'!A24</f>
+        <v/>
+      </c>
+      <c r="B24" s="3">
+        <f>IF('Heure par heure'!C24="","",'Heure par heure'!C24-N('Heure par heure'!C23))</f>
+        <v/>
+      </c>
+      <c r="C24" s="3">
+        <f>IF('Heure par heure'!D24="","",'Heure par heure'!D24-N('Heure par heure'!D23))</f>
+        <v/>
+      </c>
+      <c r="D24" s="3">
+        <f>IF('Heure par heure'!E24="","",'Heure par heure'!E24-N('Heure par heure'!E23))</f>
+        <v/>
+      </c>
+      <c r="E24" s="3">
+        <f>IF('Heure par heure'!F24="","",'Heure par heure'!F24-N('Heure par heure'!F23))</f>
+        <v/>
+      </c>
+      <c r="F24" s="3">
+        <f>IF('Heure par heure'!G24="","",'Heure par heure'!G24-N('Heure par heure'!G23))</f>
+        <v/>
+      </c>
+      <c r="G24" s="3">
+        <f>IF('Heure par heure'!H24="","",'Heure par heure'!H24-N('Heure par heure'!H23))</f>
+        <v/>
+      </c>
+      <c r="H24" s="3">
+        <f>IF('Heure par heure'!I24="","",'Heure par heure'!I24-N('Heure par heure'!I23))</f>
+        <v/>
+      </c>
+      <c r="I24" s="3">
+        <f>IF('Heure par heure'!J24="","",'Heure par heure'!J24-N('Heure par heure'!J23))</f>
+        <v/>
+      </c>
+      <c r="J24" s="3">
+        <f>IF('Heure par heure'!K24="","",'Heure par heure'!K24-N('Heure par heure'!K23))</f>
+        <v/>
+      </c>
+      <c r="K24" s="3">
+        <f>IF('Heure par heure'!L24="","",'Heure par heure'!L24-N('Heure par heure'!L23))</f>
+        <v/>
+      </c>
+      <c r="L24" s="3">
+        <f>SUM(B24:K24)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$24</f>
+              <f>'Heure par heure'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$24</f>
+              <f>'Heure par heure'!$D$2:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$24</f>
+              <f>'Heure par heure'!$E$2:$E$25</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$24</f>
+              <f>'Heure par heure'!$F$2:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$24</f>
+              <f>'Heure par heure'!$G$2:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$24</f>
+              <f>'Heure par heure'!$H$2:$H$25</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$24</f>
+              <f>'Heure par heure'!$I$2:$I$25</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$24</f>
+              <f>'Heure par heure'!$J$2:$J$25</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$24</f>
+              <f>'Heure par heure'!$K$2:$K$25</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$24</f>
+              <f>'Heure par heure'!$L$2:$L$25</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$24</f>
+              <f>'Heure par heure'!$B$2:$B$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$24</f>
+              <f>'Heure par heure'!$M$2:$M$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$24</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$24</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$24</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$24</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$25</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$24</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$24</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$24</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$25</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$24</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$25</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$24</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$25</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$24</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$25</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7033,6 +7033,50 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 22:00</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="M25" s="3">
+        <f>SUM(C25:L25)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7045,7 +7089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8241,6 +8285,56 @@
       </c>
       <c r="L24" s="3">
         <f>SUM(B24:K24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <f>'Heure par heure'!A25</f>
+        <v/>
+      </c>
+      <c r="B25" s="3">
+        <f>IF('Heure par heure'!C25="","",'Heure par heure'!C25-N('Heure par heure'!C24))</f>
+        <v/>
+      </c>
+      <c r="C25" s="3">
+        <f>IF('Heure par heure'!D25="","",'Heure par heure'!D25-N('Heure par heure'!D24))</f>
+        <v/>
+      </c>
+      <c r="D25" s="3">
+        <f>IF('Heure par heure'!E25="","",'Heure par heure'!E25-N('Heure par heure'!E24))</f>
+        <v/>
+      </c>
+      <c r="E25" s="3">
+        <f>IF('Heure par heure'!F25="","",'Heure par heure'!F25-N('Heure par heure'!F24))</f>
+        <v/>
+      </c>
+      <c r="F25" s="3">
+        <f>IF('Heure par heure'!G25="","",'Heure par heure'!G25-N('Heure par heure'!G24))</f>
+        <v/>
+      </c>
+      <c r="G25" s="3">
+        <f>IF('Heure par heure'!H25="","",'Heure par heure'!H25-N('Heure par heure'!H24))</f>
+        <v/>
+      </c>
+      <c r="H25" s="3">
+        <f>IF('Heure par heure'!I25="","",'Heure par heure'!I25-N('Heure par heure'!I24))</f>
+        <v/>
+      </c>
+      <c r="I25" s="3">
+        <f>IF('Heure par heure'!J25="","",'Heure par heure'!J25-N('Heure par heure'!J24))</f>
+        <v/>
+      </c>
+      <c r="J25" s="3">
+        <f>IF('Heure par heure'!K25="","",'Heure par heure'!K25-N('Heure par heure'!K24))</f>
+        <v/>
+      </c>
+      <c r="K25" s="3">
+        <f>IF('Heure par heure'!L25="","",'Heure par heure'!L25-N('Heure par heure'!L24))</f>
+        <v/>
+      </c>
+      <c r="L25" s="3">
+        <f>SUM(B25:K25)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$25</f>
+              <f>'Heure par heure'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$25</f>
+              <f>'Heure par heure'!$D$2:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$25</f>
+              <f>'Heure par heure'!$E$2:$E$26</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$25</f>
+              <f>'Heure par heure'!$F$2:$F$26</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$25</f>
+              <f>'Heure par heure'!$G$2:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$25</f>
+              <f>'Heure par heure'!$H$2:$H$26</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$25</f>
+              <f>'Heure par heure'!$I$2:$I$26</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$25</f>
+              <f>'Heure par heure'!$J$2:$J$26</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$25</f>
+              <f>'Heure par heure'!$K$2:$K$26</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$25</f>
+              <f>'Heure par heure'!$L$2:$L$26</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$25</f>
+              <f>'Heure par heure'!$B$2:$B$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$25</f>
+              <f>'Heure par heure'!$M$2:$M$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$25</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$25</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$25</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$25</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$26</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$25</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$26</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$25</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$25</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$26</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$25</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$26</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$25</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$26</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$25</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$26</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7077,6 +7077,50 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:00</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="M26" s="3">
+        <f>SUM(C26:L26)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7089,7 +7133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8335,6 +8379,56 @@
       </c>
       <c r="L25" s="3">
         <f>SUM(B25:K25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <f>'Heure par heure'!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="3">
+        <f>IF('Heure par heure'!C26="","",'Heure par heure'!C26-N('Heure par heure'!C25))</f>
+        <v/>
+      </c>
+      <c r="C26" s="3">
+        <f>IF('Heure par heure'!D26="","",'Heure par heure'!D26-N('Heure par heure'!D25))</f>
+        <v/>
+      </c>
+      <c r="D26" s="3">
+        <f>IF('Heure par heure'!E26="","",'Heure par heure'!E26-N('Heure par heure'!E25))</f>
+        <v/>
+      </c>
+      <c r="E26" s="3">
+        <f>IF('Heure par heure'!F26="","",'Heure par heure'!F26-N('Heure par heure'!F25))</f>
+        <v/>
+      </c>
+      <c r="F26" s="3">
+        <f>IF('Heure par heure'!G26="","",'Heure par heure'!G26-N('Heure par heure'!G25))</f>
+        <v/>
+      </c>
+      <c r="G26" s="3">
+        <f>IF('Heure par heure'!H26="","",'Heure par heure'!H26-N('Heure par heure'!H25))</f>
+        <v/>
+      </c>
+      <c r="H26" s="3">
+        <f>IF('Heure par heure'!I26="","",'Heure par heure'!I26-N('Heure par heure'!I25))</f>
+        <v/>
+      </c>
+      <c r="I26" s="3">
+        <f>IF('Heure par heure'!J26="","",'Heure par heure'!J26-N('Heure par heure'!J25))</f>
+        <v/>
+      </c>
+      <c r="J26" s="3">
+        <f>IF('Heure par heure'!K26="","",'Heure par heure'!K26-N('Heure par heure'!K25))</f>
+        <v/>
+      </c>
+      <c r="K26" s="3">
+        <f>IF('Heure par heure'!L26="","",'Heure par heure'!L26-N('Heure par heure'!L25))</f>
+        <v/>
+      </c>
+      <c r="L26" s="3">
+        <f>SUM(B26:K26)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$26</f>
+              <f>'Heure par heure'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$26</f>
+              <f>'Heure par heure'!$D$2:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$26</f>
+              <f>'Heure par heure'!$E$2:$E$27</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$26</f>
+              <f>'Heure par heure'!$F$2:$F$27</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$26</f>
+              <f>'Heure par heure'!$G$2:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$26</f>
+              <f>'Heure par heure'!$H$2:$H$27</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$26</f>
+              <f>'Heure par heure'!$I$2:$I$27</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$26</f>
+              <f>'Heure par heure'!$J$2:$J$27</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$26</f>
+              <f>'Heure par heure'!$K$2:$K$27</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$26</f>
+              <f>'Heure par heure'!$L$2:$L$27</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$26</f>
+              <f>'Heure par heure'!$B$2:$B$27</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$26</f>
+              <f>'Heure par heure'!$M$2:$M$27</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$26</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$26</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$26</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$26</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$27</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$26</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$27</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$26</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$26</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$27</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$26</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$27</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$26</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$27</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$26</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$27</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7121,6 +7121,50 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:00</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="M27" s="3">
+        <f>SUM(C27:L27)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7133,7 +7177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8429,6 +8473,56 @@
       </c>
       <c r="L26" s="3">
         <f>SUM(B26:K26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <f>'Heure par heure'!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="3">
+        <f>IF('Heure par heure'!C27="","",'Heure par heure'!C27-N('Heure par heure'!C26))</f>
+        <v/>
+      </c>
+      <c r="C27" s="3">
+        <f>IF('Heure par heure'!D27="","",'Heure par heure'!D27-N('Heure par heure'!D26))</f>
+        <v/>
+      </c>
+      <c r="D27" s="3">
+        <f>IF('Heure par heure'!E27="","",'Heure par heure'!E27-N('Heure par heure'!E26))</f>
+        <v/>
+      </c>
+      <c r="E27" s="3">
+        <f>IF('Heure par heure'!F27="","",'Heure par heure'!F27-N('Heure par heure'!F26))</f>
+        <v/>
+      </c>
+      <c r="F27" s="3">
+        <f>IF('Heure par heure'!G27="","",'Heure par heure'!G27-N('Heure par heure'!G26))</f>
+        <v/>
+      </c>
+      <c r="G27" s="3">
+        <f>IF('Heure par heure'!H27="","",'Heure par heure'!H27-N('Heure par heure'!H26))</f>
+        <v/>
+      </c>
+      <c r="H27" s="3">
+        <f>IF('Heure par heure'!I27="","",'Heure par heure'!I27-N('Heure par heure'!I26))</f>
+        <v/>
+      </c>
+      <c r="I27" s="3">
+        <f>IF('Heure par heure'!J27="","",'Heure par heure'!J27-N('Heure par heure'!J26))</f>
+        <v/>
+      </c>
+      <c r="J27" s="3">
+        <f>IF('Heure par heure'!K27="","",'Heure par heure'!K27-N('Heure par heure'!K26))</f>
+        <v/>
+      </c>
+      <c r="K27" s="3">
+        <f>IF('Heure par heure'!L27="","",'Heure par heure'!L27-N('Heure par heure'!L26))</f>
+        <v/>
+      </c>
+      <c r="L27" s="3">
+        <f>SUM(B27:K27)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$27</f>
+              <f>'Heure par heure'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$27</f>
+              <f>'Heure par heure'!$D$2:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$27</f>
+              <f>'Heure par heure'!$E$2:$E$28</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$27</f>
+              <f>'Heure par heure'!$F$2:$F$28</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$27</f>
+              <f>'Heure par heure'!$G$2:$G$28</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$27</f>
+              <f>'Heure par heure'!$H$2:$H$28</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$27</f>
+              <f>'Heure par heure'!$I$2:$I$28</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$27</f>
+              <f>'Heure par heure'!$J$2:$J$28</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$27</f>
+              <f>'Heure par heure'!$K$2:$K$28</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$27</f>
+              <f>'Heure par heure'!$L$2:$L$28</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$27</f>
+              <f>'Heure par heure'!$B$2:$B$28</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$27</f>
+              <f>'Heure par heure'!$M$2:$M$28</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$27</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$27</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$27</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$27</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$28</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$27</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$28</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$27</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$28</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$27</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$28</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$27</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$28</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$27</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$28</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$27</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$28</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6044,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7165,6 +7165,50 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:00</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="M28" s="3">
+        <f>SUM(C28:L28)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7177,7 +7221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8523,6 +8567,56 @@
       </c>
       <c r="L27" s="3">
         <f>SUM(B27:K27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <f>'Heure par heure'!A28</f>
+        <v/>
+      </c>
+      <c r="B28" s="3">
+        <f>IF('Heure par heure'!C28="","",'Heure par heure'!C28-N('Heure par heure'!C27))</f>
+        <v/>
+      </c>
+      <c r="C28" s="3">
+        <f>IF('Heure par heure'!D28="","",'Heure par heure'!D28-N('Heure par heure'!D27))</f>
+        <v/>
+      </c>
+      <c r="D28" s="3">
+        <f>IF('Heure par heure'!E28="","",'Heure par heure'!E28-N('Heure par heure'!E27))</f>
+        <v/>
+      </c>
+      <c r="E28" s="3">
+        <f>IF('Heure par heure'!F28="","",'Heure par heure'!F28-N('Heure par heure'!F27))</f>
+        <v/>
+      </c>
+      <c r="F28" s="3">
+        <f>IF('Heure par heure'!G28="","",'Heure par heure'!G28-N('Heure par heure'!G27))</f>
+        <v/>
+      </c>
+      <c r="G28" s="3">
+        <f>IF('Heure par heure'!H28="","",'Heure par heure'!H28-N('Heure par heure'!H27))</f>
+        <v/>
+      </c>
+      <c r="H28" s="3">
+        <f>IF('Heure par heure'!I28="","",'Heure par heure'!I28-N('Heure par heure'!I27))</f>
+        <v/>
+      </c>
+      <c r="I28" s="3">
+        <f>IF('Heure par heure'!J28="","",'Heure par heure'!J28-N('Heure par heure'!J27))</f>
+        <v/>
+      </c>
+      <c r="J28" s="3">
+        <f>IF('Heure par heure'!K28="","",'Heure par heure'!K28-N('Heure par heure'!K27))</f>
+        <v/>
+      </c>
+      <c r="K28" s="3">
+        <f>IF('Heure par heure'!L28="","",'Heure par heure'!L28-N('Heure par heure'!L27))</f>
+        <v/>
+      </c>
+      <c r="L28" s="3">
+        <f>SUM(B28:K28)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$9</f>
+              <f>'Jour par jour'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$9</f>
+              <f>'Jour par jour'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1244,12 +1244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$45</f>
+              <f>'Stories'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$45</f>
+              <f>'Stories'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -1346,12 +1346,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$9</f>
+              <f>'Jour par jour'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$9</f>
+              <f>'Jour par jour'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -1373,12 +1373,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$9</f>
+              <f>'Jour par jour'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$9</f>
+              <f>'Jour par jour'!$L$2:$L$10</f>
             </numRef>
           </val>
         </ser>
@@ -1486,12 +1486,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$9</f>
+              <f>'Jour par jour'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$9</f>
+              <f>'Jour par jour'!$F$2:$F$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1526,12 +1526,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$9</f>
+              <f>'Jour par jour'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$9</f>
+              <f>'Jour par jour'!$H$2:$H$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1628,12 +1628,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$9</f>
+              <f>'Jour par jour'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$9</f>
+              <f>'Jour par jour'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -2121,12 +2121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$9</f>
+              <f>'Évolution par vidéo'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$9</f>
+              <f>'Évolution par vidéo'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -2185,12 +2185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$9</f>
+              <f>'Évolution par vidéo'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -2217,12 +2217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$9</f>
+              <f>'Évolution par vidéo'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -2249,12 +2249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$9</f>
+              <f>'Évolution par vidéo'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -2281,12 +2281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$9</f>
+              <f>'Évolution par vidéo'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -2313,12 +2313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$9</f>
+              <f>'Évolution par vidéo'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -2345,12 +2345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$9</f>
+              <f>'Évolution par vidéo'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -2377,12 +2377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$9</f>
+              <f>'Évolution par vidéo'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -2409,12 +2409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$9</f>
+              <f>'Évolution par vidéo'!$K$2:$K$10</f>
             </numRef>
           </val>
         </ser>
@@ -2441,12 +2441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$9</f>
+              <f>'Évolution par vidéo'!$L$2:$L$10</f>
             </numRef>
           </val>
         </ser>
@@ -2473,12 +2473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$9</f>
+              <f>'Évolution par vidéo'!$M$2:$M$10</f>
             </numRef>
           </val>
         </ser>
@@ -2505,12 +2505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$9</f>
+              <f>'Évolution par vidéo'!$N$2:$N$10</f>
             </numRef>
           </val>
         </ser>
@@ -2537,12 +2537,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$9</f>
+              <f>'Évolution par vidéo'!$O$2:$O$10</f>
             </numRef>
           </val>
         </ser>
@@ -2569,12 +2569,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$9</f>
+              <f>'Évolution par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$9</f>
+              <f>'Évolution par vidéo'!$P$2:$P$10</f>
             </numRef>
           </val>
         </ser>
@@ -2667,12 +2667,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$9</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$9</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -2715,12 +2715,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$9</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -2739,12 +2739,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$9</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -2763,12 +2763,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$9</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -2787,12 +2787,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$9</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -2811,12 +2811,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$9</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -2835,12 +2835,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$9</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -2859,12 +2859,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$9</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -2883,12 +2883,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$9</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$10</f>
             </numRef>
           </val>
         </ser>
@@ -2907,12 +2907,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$9</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$10</f>
             </numRef>
           </val>
         </ser>
@@ -2931,12 +2931,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$9</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$10</f>
             </numRef>
           </val>
         </ser>
@@ -2955,12 +2955,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$9</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$10</f>
             </numRef>
           </val>
         </ser>
@@ -2979,12 +2979,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$9</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$10</f>
             </numRef>
           </val>
         </ser>
@@ -3003,12 +3003,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$9</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$9</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$10</f>
             </numRef>
           </val>
         </ser>
@@ -3221,7 +3221,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3248,7 +3248,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -3683,7 +3683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4122,10 +4122,55 @@
         <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3">
+        <f>IF(ROW()=2,"",B10-B9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E10" s="3">
+        <f>IF(ROW()=2,D10,D10-D9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>443</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4222,12 +4267,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:14</t>
+          <t>2026-10-19 09:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations sans gazole. Ta stat</t>
+          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4236,10 +4281,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
@@ -4268,12 +4313,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-19 12:05</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4282,13 +4327,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -4300,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
@@ -4314,12 +4359,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4328,13 +4373,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -4346,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -4360,12 +4405,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4374,13 +4419,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -4389,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
@@ -4406,12 +4451,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4420,13 +4465,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -4435,10 +4480,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -4452,12 +4497,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4466,13 +4511,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -4484,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5">
         <f>IFERROR((F7+G7+H7+I7)/IF(E7&gt;0,E7,D7),0)</f>
@@ -4498,12 +4543,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4512,13 +4557,13 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -4544,12 +4589,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4558,10 +4603,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -4576,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
         <f>IFERROR((F9+G9+H9+I9)/IF(E9&gt;0,E9,D9),0)</f>
@@ -4590,12 +4635,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:08</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou non ? Réponds en co</t>
+          <t>Couper les réseaux sociaux pendant les émeute</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4604,10 +4649,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -4636,12 +4681,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-24 12:30</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux pendant les émeute</t>
+          <t>À toi de juger : il faut une enquête indépend</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4650,13 +4695,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -4668,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
@@ -4682,12 +4727,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 12:30</t>
+          <t>2026-10-24 13:56</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une enquête indépend</t>
+          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4696,25 +4741,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="F12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
@@ -4728,12 +4773,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:56</t>
+          <t>2026-10-24 18:14</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
+          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4742,13 +4787,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -4757,10 +4802,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="5">
         <f>IFERROR((F13+G13+H13+I13)/IF(E13&gt;0,E13,D13),0)</f>
@@ -4774,12 +4819,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 18:14</t>
+          <t>2026-10-25 13:58</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
+          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4788,10 +4833,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -4820,12 +4865,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:58</t>
+          <t>2026-10-25 13:59</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
+          <t>Vendredi, Macron au concert de Céline Dion. S</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4834,14 +4879,14 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="E15" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
@@ -4852,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="5">
         <f>IFERROR((F15+G15+H15+I15)/IF(E15&gt;0,E15,D15),0)</f>
@@ -4866,12 +4911,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:59</t>
+          <t>2026-10-25 17:26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Vendredi, Macron au concert de Céline Dion. S</t>
+          <t>2 513 gardes à vue et 67 incarcérations après</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4880,10 +4925,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -4938,7 +4983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4967,77 +5012,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Des millions publics promis.</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi, Macron au concert </t>
+          <t>2 513 gardes à vue et 67 inc</t>
         </is>
       </c>
     </row>
@@ -5070,14 +5115,12 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="D3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -5098,20 +5141,18 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="F4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
@@ -5130,29 +5171,27 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="I5" s="3" t="n">
         <v>69</v>
       </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
@@ -5168,35 +5207,33 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>128</v>
-      </c>
       <c r="J6" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="K6" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
@@ -5210,35 +5247,33 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C7" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>128</v>
-      </c>
       <c r="J7" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="K7" s="3" t="n">
         <v>74</v>
       </c>
+      <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
@@ -5252,41 +5287,39 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="M8" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n"/>
@@ -5298,49 +5331,99 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C9" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="C10" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="M9" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="N9" s="3" t="n">
+      <c r="L10" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="M10" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="O9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>13</v>
+      <c r="N10" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -5355,7 +5438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5385,77 +5468,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Et soudain, 718 stations san</t>
+          <t>Les vitrines d'abord. Toi, a</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Des millions publics promis.</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi, Macron au concert </t>
+          <t>2 513 gardes à vue et 67 inc</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -6029,6 +6112,77 @@
       </c>
       <c r="Q9" s="3">
         <f>SUM(B9:P9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>IF('Évolution par vidéo'!B10="","",'Évolution par vidéo'!B10-N('Évolution par vidéo'!B9))</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>IF('Évolution par vidéo'!C10="","",'Évolution par vidéo'!C10-N('Évolution par vidéo'!C9))</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IF('Évolution par vidéo'!D10="","",'Évolution par vidéo'!D10-N('Évolution par vidéo'!D9))</f>
+        <v/>
+      </c>
+      <c r="E10" s="3">
+        <f>IF('Évolution par vidéo'!E10="","",'Évolution par vidéo'!E10-N('Évolution par vidéo'!E9))</f>
+        <v/>
+      </c>
+      <c r="F10" s="3">
+        <f>IF('Évolution par vidéo'!F10="","",'Évolution par vidéo'!F10-N('Évolution par vidéo'!F9))</f>
+        <v/>
+      </c>
+      <c r="G10" s="3">
+        <f>IF('Évolution par vidéo'!G10="","",'Évolution par vidéo'!G10-N('Évolution par vidéo'!G9))</f>
+        <v/>
+      </c>
+      <c r="H10" s="3">
+        <f>IF('Évolution par vidéo'!H10="","",'Évolution par vidéo'!H10-N('Évolution par vidéo'!H9))</f>
+        <v/>
+      </c>
+      <c r="I10" s="3">
+        <f>IF('Évolution par vidéo'!I10="","",'Évolution par vidéo'!I10-N('Évolution par vidéo'!I9))</f>
+        <v/>
+      </c>
+      <c r="J10" s="3">
+        <f>IF('Évolution par vidéo'!J10="","",'Évolution par vidéo'!J10-N('Évolution par vidéo'!J9))</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>IF('Évolution par vidéo'!K10="","",'Évolution par vidéo'!K10-N('Évolution par vidéo'!K9))</f>
+        <v/>
+      </c>
+      <c r="L10" s="3">
+        <f>IF('Évolution par vidéo'!L10="","",'Évolution par vidéo'!L10-N('Évolution par vidéo'!L9))</f>
+        <v/>
+      </c>
+      <c r="M10" s="3">
+        <f>IF('Évolution par vidéo'!M10="","",'Évolution par vidéo'!M10-N('Évolution par vidéo'!M9))</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>IF('Évolution par vidéo'!N10="","",'Évolution par vidéo'!N10-N('Évolution par vidéo'!N9))</f>
+        <v/>
+      </c>
+      <c r="O10" s="3">
+        <f>IF('Évolution par vidéo'!O10="","",'Évolution par vidéo'!O10-N('Évolution par vidéo'!O9))</f>
+        <v/>
+      </c>
+      <c r="P10" s="3">
+        <f>IF('Évolution par vidéo'!P10="","",'Évolution par vidéo'!P10-N('Évolution par vidéo'!P9))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="3">
+        <f>SUM(B10:P10)</f>
         <v/>
       </c>
     </row>
@@ -8632,7 +8786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10020,7 +10174,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -10053,7 +10207,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -10086,7 +10240,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -10119,7 +10273,7 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -10140,6 +10294,39 @@
         <v>0</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 17:26</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -10191,9 +10378,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId46"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$28</f>
+              <f>'Heure par heure'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$28</f>
+              <f>'Heure par heure'!$D$2:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$28</f>
+              <f>'Heure par heure'!$E$2:$E$29</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$28</f>
+              <f>'Heure par heure'!$F$2:$F$29</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$28</f>
+              <f>'Heure par heure'!$G$2:$G$29</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$28</f>
+              <f>'Heure par heure'!$H$2:$H$29</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$28</f>
+              <f>'Heure par heure'!$I$2:$I$29</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$28</f>
+              <f>'Heure par heure'!$J$2:$J$29</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$28</f>
+              <f>'Heure par heure'!$K$2:$K$29</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$28</f>
+              <f>'Heure par heure'!$L$2:$L$29</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$28</f>
+              <f>'Heure par heure'!$B$2:$B$29</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$28</f>
+              <f>'Heure par heure'!$M$2:$M$29</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$28</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$28</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$28</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$28</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$29</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$28</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$29</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$28</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$29</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$28</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$29</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$28</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$29</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$28</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$29</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$28</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$29</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7363,6 +7363,50 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:00</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="M29" s="3">
+        <f>SUM(C29:L29)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7375,7 +7419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8771,6 +8815,56 @@
       </c>
       <c r="L28" s="3">
         <f>SUM(B28:K28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <f>'Heure par heure'!A29</f>
+        <v/>
+      </c>
+      <c r="B29" s="3">
+        <f>IF('Heure par heure'!C29="","",'Heure par heure'!C29-N('Heure par heure'!C28))</f>
+        <v/>
+      </c>
+      <c r="C29" s="3">
+        <f>IF('Heure par heure'!D29="","",'Heure par heure'!D29-N('Heure par heure'!D28))</f>
+        <v/>
+      </c>
+      <c r="D29" s="3">
+        <f>IF('Heure par heure'!E29="","",'Heure par heure'!E29-N('Heure par heure'!E28))</f>
+        <v/>
+      </c>
+      <c r="E29" s="3">
+        <f>IF('Heure par heure'!F29="","",'Heure par heure'!F29-N('Heure par heure'!F28))</f>
+        <v/>
+      </c>
+      <c r="F29" s="3">
+        <f>IF('Heure par heure'!G29="","",'Heure par heure'!G29-N('Heure par heure'!G28))</f>
+        <v/>
+      </c>
+      <c r="G29" s="3">
+        <f>IF('Heure par heure'!H29="","",'Heure par heure'!H29-N('Heure par heure'!H28))</f>
+        <v/>
+      </c>
+      <c r="H29" s="3">
+        <f>IF('Heure par heure'!I29="","",'Heure par heure'!I29-N('Heure par heure'!I28))</f>
+        <v/>
+      </c>
+      <c r="I29" s="3">
+        <f>IF('Heure par heure'!J29="","",'Heure par heure'!J29-N('Heure par heure'!J28))</f>
+        <v/>
+      </c>
+      <c r="J29" s="3">
+        <f>IF('Heure par heure'!K29="","",'Heure par heure'!K29-N('Heure par heure'!K28))</f>
+        <v/>
+      </c>
+      <c r="K29" s="3">
+        <f>IF('Heure par heure'!L29="","",'Heure par heure'!L29-N('Heure par heure'!L28))</f>
+        <v/>
+      </c>
+      <c r="L29" s="3">
+        <f>SUM(B29:K29)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$29</f>
+              <f>'Heure par heure'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$29</f>
+              <f>'Heure par heure'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$29</f>
+              <f>'Heure par heure'!$E$2:$E$30</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$29</f>
+              <f>'Heure par heure'!$F$2:$F$30</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$29</f>
+              <f>'Heure par heure'!$G$2:$G$30</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$29</f>
+              <f>'Heure par heure'!$H$2:$H$30</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$29</f>
+              <f>'Heure par heure'!$I$2:$I$30</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$29</f>
+              <f>'Heure par heure'!$J$2:$J$30</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$29</f>
+              <f>'Heure par heure'!$K$2:$K$30</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$29</f>
+              <f>'Heure par heure'!$L$2:$L$30</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$29</f>
+              <f>'Heure par heure'!$B$2:$B$30</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$29</f>
+              <f>'Heure par heure'!$M$2:$M$30</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$29</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$29</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$29</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$29</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$30</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$29</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$30</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$29</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$30</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$29</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$30</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$29</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$30</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$29</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$30</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$29</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$30</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7407,6 +7407,50 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:00</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="M30" s="3">
+        <f>SUM(C30:L30)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7419,7 +7463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8865,6 +8909,56 @@
       </c>
       <c r="L29" s="3">
         <f>SUM(B29:K29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <f>'Heure par heure'!A30</f>
+        <v/>
+      </c>
+      <c r="B30" s="3">
+        <f>IF('Heure par heure'!C30="","",'Heure par heure'!C30-N('Heure par heure'!C29))</f>
+        <v/>
+      </c>
+      <c r="C30" s="3">
+        <f>IF('Heure par heure'!D30="","",'Heure par heure'!D30-N('Heure par heure'!D29))</f>
+        <v/>
+      </c>
+      <c r="D30" s="3">
+        <f>IF('Heure par heure'!E30="","",'Heure par heure'!E30-N('Heure par heure'!E29))</f>
+        <v/>
+      </c>
+      <c r="E30" s="3">
+        <f>IF('Heure par heure'!F30="","",'Heure par heure'!F30-N('Heure par heure'!F29))</f>
+        <v/>
+      </c>
+      <c r="F30" s="3">
+        <f>IF('Heure par heure'!G30="","",'Heure par heure'!G30-N('Heure par heure'!G29))</f>
+        <v/>
+      </c>
+      <c r="G30" s="3">
+        <f>IF('Heure par heure'!H30="","",'Heure par heure'!H30-N('Heure par heure'!H29))</f>
+        <v/>
+      </c>
+      <c r="H30" s="3">
+        <f>IF('Heure par heure'!I30="","",'Heure par heure'!I30-N('Heure par heure'!I29))</f>
+        <v/>
+      </c>
+      <c r="I30" s="3">
+        <f>IF('Heure par heure'!J30="","",'Heure par heure'!J30-N('Heure par heure'!J29))</f>
+        <v/>
+      </c>
+      <c r="J30" s="3">
+        <f>IF('Heure par heure'!K30="","",'Heure par heure'!K30-N('Heure par heure'!K29))</f>
+        <v/>
+      </c>
+      <c r="K30" s="3">
+        <f>IF('Heure par heure'!L30="","",'Heure par heure'!L30-N('Heure par heure'!L29))</f>
+        <v/>
+      </c>
+      <c r="L30" s="3">
+        <f>SUM(B30:K30)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$30</f>
+              <f>'Heure par heure'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$30</f>
+              <f>'Heure par heure'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$30</f>
+              <f>'Heure par heure'!$E$2:$E$31</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$30</f>
+              <f>'Heure par heure'!$F$2:$F$31</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$30</f>
+              <f>'Heure par heure'!$G$2:$G$31</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$30</f>
+              <f>'Heure par heure'!$H$2:$H$31</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$30</f>
+              <f>'Heure par heure'!$I$2:$I$31</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$30</f>
+              <f>'Heure par heure'!$J$2:$J$31</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$30</f>
+              <f>'Heure par heure'!$K$2:$K$31</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$30</f>
+              <f>'Heure par heure'!$L$2:$L$31</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$30</f>
+              <f>'Heure par heure'!$B$2:$B$31</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$30</f>
+              <f>'Heure par heure'!$M$2:$M$31</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$30</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$30</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$30</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$30</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$31</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$30</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$31</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$30</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$31</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$30</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$31</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$30</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$31</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$30</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$31</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$30</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$31</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7451,6 +7451,50 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:00</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="M31" s="3">
+        <f>SUM(C31:L31)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7463,7 +7507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8959,6 +9003,56 @@
       </c>
       <c r="L30" s="3">
         <f>SUM(B30:K30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <f>'Heure par heure'!A31</f>
+        <v/>
+      </c>
+      <c r="B31" s="3">
+        <f>IF('Heure par heure'!C31="","",'Heure par heure'!C31-N('Heure par heure'!C30))</f>
+        <v/>
+      </c>
+      <c r="C31" s="3">
+        <f>IF('Heure par heure'!D31="","",'Heure par heure'!D31-N('Heure par heure'!D30))</f>
+        <v/>
+      </c>
+      <c r="D31" s="3">
+        <f>IF('Heure par heure'!E31="","",'Heure par heure'!E31-N('Heure par heure'!E30))</f>
+        <v/>
+      </c>
+      <c r="E31" s="3">
+        <f>IF('Heure par heure'!F31="","",'Heure par heure'!F31-N('Heure par heure'!F30))</f>
+        <v/>
+      </c>
+      <c r="F31" s="3">
+        <f>IF('Heure par heure'!G31="","",'Heure par heure'!G31-N('Heure par heure'!G30))</f>
+        <v/>
+      </c>
+      <c r="G31" s="3">
+        <f>IF('Heure par heure'!H31="","",'Heure par heure'!H31-N('Heure par heure'!H30))</f>
+        <v/>
+      </c>
+      <c r="H31" s="3">
+        <f>IF('Heure par heure'!I31="","",'Heure par heure'!I31-N('Heure par heure'!I30))</f>
+        <v/>
+      </c>
+      <c r="I31" s="3">
+        <f>IF('Heure par heure'!J31="","",'Heure par heure'!J31-N('Heure par heure'!J30))</f>
+        <v/>
+      </c>
+      <c r="J31" s="3">
+        <f>IF('Heure par heure'!K31="","",'Heure par heure'!K31-N('Heure par heure'!K30))</f>
+        <v/>
+      </c>
+      <c r="K31" s="3">
+        <f>IF('Heure par heure'!L31="","",'Heure par heure'!L31-N('Heure par heure'!L30))</f>
+        <v/>
+      </c>
+      <c r="L31" s="3">
+        <f>SUM(B31:K31)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$31</f>
+              <f>'Heure par heure'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$31</f>
+              <f>'Heure par heure'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$31</f>
+              <f>'Heure par heure'!$E$2:$E$32</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$31</f>
+              <f>'Heure par heure'!$F$2:$F$32</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$31</f>
+              <f>'Heure par heure'!$G$2:$G$32</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$31</f>
+              <f>'Heure par heure'!$H$2:$H$32</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$31</f>
+              <f>'Heure par heure'!$I$2:$I$32</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$31</f>
+              <f>'Heure par heure'!$J$2:$J$32</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$31</f>
+              <f>'Heure par heure'!$K$2:$K$32</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$31</f>
+              <f>'Heure par heure'!$L$2:$L$32</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$31</f>
+              <f>'Heure par heure'!$B$2:$B$32</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$31</f>
+              <f>'Heure par heure'!$M$2:$M$32</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$31</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$31</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$31</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$31</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$32</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$31</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$32</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$31</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$32</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$31</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$32</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$31</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$32</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$31</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$32</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$31</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$32</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7495,6 +7495,50 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:00</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="M32" s="3">
+        <f>SUM(C32:L32)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7507,7 +7551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9053,6 +9097,56 @@
       </c>
       <c r="L31" s="3">
         <f>SUM(B31:K31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <f>'Heure par heure'!A32</f>
+        <v/>
+      </c>
+      <c r="B32" s="3">
+        <f>IF('Heure par heure'!C32="","",'Heure par heure'!C32-N('Heure par heure'!C31))</f>
+        <v/>
+      </c>
+      <c r="C32" s="3">
+        <f>IF('Heure par heure'!D32="","",'Heure par heure'!D32-N('Heure par heure'!D31))</f>
+        <v/>
+      </c>
+      <c r="D32" s="3">
+        <f>IF('Heure par heure'!E32="","",'Heure par heure'!E32-N('Heure par heure'!E31))</f>
+        <v/>
+      </c>
+      <c r="E32" s="3">
+        <f>IF('Heure par heure'!F32="","",'Heure par heure'!F32-N('Heure par heure'!F31))</f>
+        <v/>
+      </c>
+      <c r="F32" s="3">
+        <f>IF('Heure par heure'!G32="","",'Heure par heure'!G32-N('Heure par heure'!G31))</f>
+        <v/>
+      </c>
+      <c r="G32" s="3">
+        <f>IF('Heure par heure'!H32="","",'Heure par heure'!H32-N('Heure par heure'!H31))</f>
+        <v/>
+      </c>
+      <c r="H32" s="3">
+        <f>IF('Heure par heure'!I32="","",'Heure par heure'!I32-N('Heure par heure'!I31))</f>
+        <v/>
+      </c>
+      <c r="I32" s="3">
+        <f>IF('Heure par heure'!J32="","",'Heure par heure'!J32-N('Heure par heure'!J31))</f>
+        <v/>
+      </c>
+      <c r="J32" s="3">
+        <f>IF('Heure par heure'!K32="","",'Heure par heure'!K32-N('Heure par heure'!K31))</f>
+        <v/>
+      </c>
+      <c r="K32" s="3">
+        <f>IF('Heure par heure'!L32="","",'Heure par heure'!L32-N('Heure par heure'!L31))</f>
+        <v/>
+      </c>
+      <c r="L32" s="3">
+        <f>SUM(B32:K32)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$32</f>
+              <f>'Heure par heure'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$32</f>
+              <f>'Heure par heure'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$32</f>
+              <f>'Heure par heure'!$E$2:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$32</f>
+              <f>'Heure par heure'!$F$2:$F$33</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$32</f>
+              <f>'Heure par heure'!$G$2:$G$33</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$32</f>
+              <f>'Heure par heure'!$H$2:$H$33</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$32</f>
+              <f>'Heure par heure'!$I$2:$I$33</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$32</f>
+              <f>'Heure par heure'!$J$2:$J$33</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$32</f>
+              <f>'Heure par heure'!$K$2:$K$33</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$32</f>
+              <f>'Heure par heure'!$L$2:$L$33</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$32</f>
+              <f>'Heure par heure'!$B$2:$B$33</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$32</f>
+              <f>'Heure par heure'!$M$2:$M$33</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$32</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$32</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$32</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$32</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$32</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$33</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$32</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$33</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$32</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$33</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$32</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$33</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$32</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$33</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$32</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$33</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7539,6 +7539,50 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:00</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M33" s="3">
+        <f>SUM(C33:L33)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7551,7 +7595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9147,6 +9191,56 @@
       </c>
       <c r="L32" s="3">
         <f>SUM(B32:K32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <f>'Heure par heure'!A33</f>
+        <v/>
+      </c>
+      <c r="B33" s="3">
+        <f>IF('Heure par heure'!C33="","",'Heure par heure'!C33-N('Heure par heure'!C32))</f>
+        <v/>
+      </c>
+      <c r="C33" s="3">
+        <f>IF('Heure par heure'!D33="","",'Heure par heure'!D33-N('Heure par heure'!D32))</f>
+        <v/>
+      </c>
+      <c r="D33" s="3">
+        <f>IF('Heure par heure'!E33="","",'Heure par heure'!E33-N('Heure par heure'!E32))</f>
+        <v/>
+      </c>
+      <c r="E33" s="3">
+        <f>IF('Heure par heure'!F33="","",'Heure par heure'!F33-N('Heure par heure'!F32))</f>
+        <v/>
+      </c>
+      <c r="F33" s="3">
+        <f>IF('Heure par heure'!G33="","",'Heure par heure'!G33-N('Heure par heure'!G32))</f>
+        <v/>
+      </c>
+      <c r="G33" s="3">
+        <f>IF('Heure par heure'!H33="","",'Heure par heure'!H33-N('Heure par heure'!H32))</f>
+        <v/>
+      </c>
+      <c r="H33" s="3">
+        <f>IF('Heure par heure'!I33="","",'Heure par heure'!I33-N('Heure par heure'!I32))</f>
+        <v/>
+      </c>
+      <c r="I33" s="3">
+        <f>IF('Heure par heure'!J33="","",'Heure par heure'!J33-N('Heure par heure'!J32))</f>
+        <v/>
+      </c>
+      <c r="J33" s="3">
+        <f>IF('Heure par heure'!K33="","",'Heure par heure'!K33-N('Heure par heure'!K32))</f>
+        <v/>
+      </c>
+      <c r="K33" s="3">
+        <f>IF('Heure par heure'!L33="","",'Heure par heure'!L33-N('Heure par heure'!L32))</f>
+        <v/>
+      </c>
+      <c r="L33" s="3">
+        <f>SUM(B33:K33)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$33</f>
+              <f>'Heure par heure'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$33</f>
+              <f>'Heure par heure'!$D$2:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$33</f>
+              <f>'Heure par heure'!$E$2:$E$34</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$33</f>
+              <f>'Heure par heure'!$F$2:$F$34</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$33</f>
+              <f>'Heure par heure'!$G$2:$G$34</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$33</f>
+              <f>'Heure par heure'!$H$2:$H$34</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$33</f>
+              <f>'Heure par heure'!$I$2:$I$34</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$33</f>
+              <f>'Heure par heure'!$J$2:$J$34</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$33</f>
+              <f>'Heure par heure'!$K$2:$K$34</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$33</f>
+              <f>'Heure par heure'!$L$2:$L$34</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$33</f>
+              <f>'Heure par heure'!$B$2:$B$34</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$33</f>
+              <f>'Heure par heure'!$M$2:$M$34</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$33</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$33</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$33</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$33</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$34</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$33</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$34</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$33</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$34</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$33</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$34</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$33</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$34</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$33</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$34</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$33</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$34</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7583,6 +7583,50 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:00</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M34" s="3">
+        <f>SUM(C34:L34)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7595,7 +7639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9241,6 +9285,56 @@
       </c>
       <c r="L33" s="3">
         <f>SUM(B33:K33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <f>'Heure par heure'!A34</f>
+        <v/>
+      </c>
+      <c r="B34" s="3">
+        <f>IF('Heure par heure'!C34="","",'Heure par heure'!C34-N('Heure par heure'!C33))</f>
+        <v/>
+      </c>
+      <c r="C34" s="3">
+        <f>IF('Heure par heure'!D34="","",'Heure par heure'!D34-N('Heure par heure'!D33))</f>
+        <v/>
+      </c>
+      <c r="D34" s="3">
+        <f>IF('Heure par heure'!E34="","",'Heure par heure'!E34-N('Heure par heure'!E33))</f>
+        <v/>
+      </c>
+      <c r="E34" s="3">
+        <f>IF('Heure par heure'!F34="","",'Heure par heure'!F34-N('Heure par heure'!F33))</f>
+        <v/>
+      </c>
+      <c r="F34" s="3">
+        <f>IF('Heure par heure'!G34="","",'Heure par heure'!G34-N('Heure par heure'!G33))</f>
+        <v/>
+      </c>
+      <c r="G34" s="3">
+        <f>IF('Heure par heure'!H34="","",'Heure par heure'!H34-N('Heure par heure'!H33))</f>
+        <v/>
+      </c>
+      <c r="H34" s="3">
+        <f>IF('Heure par heure'!I34="","",'Heure par heure'!I34-N('Heure par heure'!I33))</f>
+        <v/>
+      </c>
+      <c r="I34" s="3">
+        <f>IF('Heure par heure'!J34="","",'Heure par heure'!J34-N('Heure par heure'!J33))</f>
+        <v/>
+      </c>
+      <c r="J34" s="3">
+        <f>IF('Heure par heure'!K34="","",'Heure par heure'!K34-N('Heure par heure'!K33))</f>
+        <v/>
+      </c>
+      <c r="K34" s="3">
+        <f>IF('Heure par heure'!L34="","",'Heure par heure'!L34-N('Heure par heure'!L33))</f>
+        <v/>
+      </c>
+      <c r="L34" s="3">
+        <f>SUM(B34:K34)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>2</v>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="E10" s="3">
         <f>IF(ROW()=2,D10,D10-D9)</f>
@@ -4152,16 +4152,16 @@
         <v>373</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>102</v>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>110</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -5417,13 +5417,13 @@
         <v>134</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -10888,7 +10888,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$34</f>
+              <f>'Heure par heure'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$34</f>
+              <f>'Heure par heure'!$D$2:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$34</f>
+              <f>'Heure par heure'!$E$2:$E$35</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$34</f>
+              <f>'Heure par heure'!$F$2:$F$35</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$34</f>
+              <f>'Heure par heure'!$G$2:$G$35</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$34</f>
+              <f>'Heure par heure'!$H$2:$H$35</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$34</f>
+              <f>'Heure par heure'!$I$2:$I$35</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$34</f>
+              <f>'Heure par heure'!$J$2:$J$35</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$34</f>
+              <f>'Heure par heure'!$K$2:$K$35</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$34</f>
+              <f>'Heure par heure'!$L$2:$L$35</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$34</f>
+              <f>'Heure par heure'!$B$2:$B$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$34</f>
+              <f>'Heure par heure'!$M$2:$M$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$34</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$34</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$34</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$34</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$35</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$34</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$35</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$34</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$35</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$34</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$35</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$34</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$35</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$34</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$35</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$34</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$35</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7627,6 +7627,50 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 17:00</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M35" s="3">
+        <f>SUM(C35:L35)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7639,7 +7683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9335,6 +9379,56 @@
       </c>
       <c r="L34" s="3">
         <f>SUM(B34:K34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <f>'Heure par heure'!A35</f>
+        <v/>
+      </c>
+      <c r="B35" s="3">
+        <f>IF('Heure par heure'!C35="","",'Heure par heure'!C35-N('Heure par heure'!C34))</f>
+        <v/>
+      </c>
+      <c r="C35" s="3">
+        <f>IF('Heure par heure'!D35="","",'Heure par heure'!D35-N('Heure par heure'!D34))</f>
+        <v/>
+      </c>
+      <c r="D35" s="3">
+        <f>IF('Heure par heure'!E35="","",'Heure par heure'!E35-N('Heure par heure'!E34))</f>
+        <v/>
+      </c>
+      <c r="E35" s="3">
+        <f>IF('Heure par heure'!F35="","",'Heure par heure'!F35-N('Heure par heure'!F34))</f>
+        <v/>
+      </c>
+      <c r="F35" s="3">
+        <f>IF('Heure par heure'!G35="","",'Heure par heure'!G35-N('Heure par heure'!G34))</f>
+        <v/>
+      </c>
+      <c r="G35" s="3">
+        <f>IF('Heure par heure'!H35="","",'Heure par heure'!H35-N('Heure par heure'!H34))</f>
+        <v/>
+      </c>
+      <c r="H35" s="3">
+        <f>IF('Heure par heure'!I35="","",'Heure par heure'!I35-N('Heure par heure'!I34))</f>
+        <v/>
+      </c>
+      <c r="I35" s="3">
+        <f>IF('Heure par heure'!J35="","",'Heure par heure'!J35-N('Heure par heure'!J34))</f>
+        <v/>
+      </c>
+      <c r="J35" s="3">
+        <f>IF('Heure par heure'!K35="","",'Heure par heure'!K35-N('Heure par heure'!K34))</f>
+        <v/>
+      </c>
+      <c r="K35" s="3">
+        <f>IF('Heure par heure'!L35="","",'Heure par heure'!L35-N('Heure par heure'!L34))</f>
+        <v/>
+      </c>
+      <c r="L35" s="3">
+        <f>SUM(B35:K35)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$35</f>
+              <f>'Heure par heure'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$35</f>
+              <f>'Heure par heure'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$35</f>
+              <f>'Heure par heure'!$E$2:$E$36</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$35</f>
+              <f>'Heure par heure'!$F$2:$F$36</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$35</f>
+              <f>'Heure par heure'!$G$2:$G$36</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$35</f>
+              <f>'Heure par heure'!$H$2:$H$36</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$35</f>
+              <f>'Heure par heure'!$I$2:$I$36</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$35</f>
+              <f>'Heure par heure'!$J$2:$J$36</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$35</f>
+              <f>'Heure par heure'!$K$2:$K$36</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$35</f>
+              <f>'Heure par heure'!$L$2:$L$36</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$35</f>
+              <f>'Heure par heure'!$B$2:$B$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$35</f>
+              <f>'Heure par heure'!$M$2:$M$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$35</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$35</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$35</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$35</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$36</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$35</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$36</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$35</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$36</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$35</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$36</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$35</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$36</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$35</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$36</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$35</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$36</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7671,6 +7671,50 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:00</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M36" s="3">
+        <f>SUM(C36:L36)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7683,7 +7727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9429,6 +9473,56 @@
       </c>
       <c r="L35" s="3">
         <f>SUM(B35:K35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <f>'Heure par heure'!A36</f>
+        <v/>
+      </c>
+      <c r="B36" s="3">
+        <f>IF('Heure par heure'!C36="","",'Heure par heure'!C36-N('Heure par heure'!C35))</f>
+        <v/>
+      </c>
+      <c r="C36" s="3">
+        <f>IF('Heure par heure'!D36="","",'Heure par heure'!D36-N('Heure par heure'!D35))</f>
+        <v/>
+      </c>
+      <c r="D36" s="3">
+        <f>IF('Heure par heure'!E36="","",'Heure par heure'!E36-N('Heure par heure'!E35))</f>
+        <v/>
+      </c>
+      <c r="E36" s="3">
+        <f>IF('Heure par heure'!F36="","",'Heure par heure'!F36-N('Heure par heure'!F35))</f>
+        <v/>
+      </c>
+      <c r="F36" s="3">
+        <f>IF('Heure par heure'!G36="","",'Heure par heure'!G36-N('Heure par heure'!G35))</f>
+        <v/>
+      </c>
+      <c r="G36" s="3">
+        <f>IF('Heure par heure'!H36="","",'Heure par heure'!H36-N('Heure par heure'!H35))</f>
+        <v/>
+      </c>
+      <c r="H36" s="3">
+        <f>IF('Heure par heure'!I36="","",'Heure par heure'!I36-N('Heure par heure'!I35))</f>
+        <v/>
+      </c>
+      <c r="I36" s="3">
+        <f>IF('Heure par heure'!J36="","",'Heure par heure'!J36-N('Heure par heure'!J35))</f>
+        <v/>
+      </c>
+      <c r="J36" s="3">
+        <f>IF('Heure par heure'!K36="","",'Heure par heure'!K36-N('Heure par heure'!K35))</f>
+        <v/>
+      </c>
+      <c r="K36" s="3">
+        <f>IF('Heure par heure'!L36="","",'Heure par heure'!L36-N('Heure par heure'!L35))</f>
+        <v/>
+      </c>
+      <c r="L36" s="3">
+        <f>SUM(B36:K36)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$36</f>
+              <f>'Heure par heure'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$36</f>
+              <f>'Heure par heure'!$D$2:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$36</f>
+              <f>'Heure par heure'!$E$2:$E$37</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$36</f>
+              <f>'Heure par heure'!$F$2:$F$37</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$36</f>
+              <f>'Heure par heure'!$G$2:$G$37</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$36</f>
+              <f>'Heure par heure'!$H$2:$H$37</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$36</f>
+              <f>'Heure par heure'!$I$2:$I$37</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$36</f>
+              <f>'Heure par heure'!$J$2:$J$37</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$36</f>
+              <f>'Heure par heure'!$K$2:$K$37</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$36</f>
+              <f>'Heure par heure'!$L$2:$L$37</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$36</f>
+              <f>'Heure par heure'!$B$2:$B$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$36</f>
+              <f>'Heure par heure'!$M$2:$M$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$36</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$36</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$36</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$36</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$37</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$36</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$37</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$36</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$37</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$36</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$37</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$36</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$37</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$36</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$37</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$36</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$37</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7715,6 +7715,50 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 19:00</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M37" s="3">
+        <f>SUM(C37:L37)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7727,7 +7771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9523,6 +9567,56 @@
       </c>
       <c r="L36" s="3">
         <f>SUM(B36:K36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <f>'Heure par heure'!A37</f>
+        <v/>
+      </c>
+      <c r="B37" s="3">
+        <f>IF('Heure par heure'!C37="","",'Heure par heure'!C37-N('Heure par heure'!C36))</f>
+        <v/>
+      </c>
+      <c r="C37" s="3">
+        <f>IF('Heure par heure'!D37="","",'Heure par heure'!D37-N('Heure par heure'!D36))</f>
+        <v/>
+      </c>
+      <c r="D37" s="3">
+        <f>IF('Heure par heure'!E37="","",'Heure par heure'!E37-N('Heure par heure'!E36))</f>
+        <v/>
+      </c>
+      <c r="E37" s="3">
+        <f>IF('Heure par heure'!F37="","",'Heure par heure'!F37-N('Heure par heure'!F36))</f>
+        <v/>
+      </c>
+      <c r="F37" s="3">
+        <f>IF('Heure par heure'!G37="","",'Heure par heure'!G37-N('Heure par heure'!G36))</f>
+        <v/>
+      </c>
+      <c r="G37" s="3">
+        <f>IF('Heure par heure'!H37="","",'Heure par heure'!H37-N('Heure par heure'!H36))</f>
+        <v/>
+      </c>
+      <c r="H37" s="3">
+        <f>IF('Heure par heure'!I37="","",'Heure par heure'!I37-N('Heure par heure'!I36))</f>
+        <v/>
+      </c>
+      <c r="I37" s="3">
+        <f>IF('Heure par heure'!J37="","",'Heure par heure'!J37-N('Heure par heure'!J36))</f>
+        <v/>
+      </c>
+      <c r="J37" s="3">
+        <f>IF('Heure par heure'!K37="","",'Heure par heure'!K37-N('Heure par heure'!K36))</f>
+        <v/>
+      </c>
+      <c r="K37" s="3">
+        <f>IF('Heure par heure'!L37="","",'Heure par heure'!L37-N('Heure par heure'!L36))</f>
+        <v/>
+      </c>
+      <c r="L37" s="3">
+        <f>SUM(B37:K37)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$37</f>
+              <f>'Heure par heure'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$37</f>
+              <f>'Heure par heure'!$D$2:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$37</f>
+              <f>'Heure par heure'!$E$2:$E$38</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$37</f>
+              <f>'Heure par heure'!$F$2:$F$38</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$37</f>
+              <f>'Heure par heure'!$G$2:$G$38</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$37</f>
+              <f>'Heure par heure'!$H$2:$H$38</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$37</f>
+              <f>'Heure par heure'!$I$2:$I$38</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$37</f>
+              <f>'Heure par heure'!$J$2:$J$38</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$37</f>
+              <f>'Heure par heure'!$K$2:$K$38</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$37</f>
+              <f>'Heure par heure'!$L$2:$L$38</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$37</f>
+              <f>'Heure par heure'!$B$2:$B$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$37</f>
+              <f>'Heure par heure'!$M$2:$M$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$37</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$37</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$37</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$37</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$38</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$37</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$38</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$37</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$38</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$37</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$38</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$37</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$38</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$37</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$38</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$37</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$38</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7759,6 +7759,50 @@
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 20:00</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M38" s="3">
+        <f>SUM(C38:L38)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7771,7 +7815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9617,6 +9661,56 @@
       </c>
       <c r="L37" s="3">
         <f>SUM(B37:K37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <f>'Heure par heure'!A38</f>
+        <v/>
+      </c>
+      <c r="B38" s="3">
+        <f>IF('Heure par heure'!C38="","",'Heure par heure'!C38-N('Heure par heure'!C37))</f>
+        <v/>
+      </c>
+      <c r="C38" s="3">
+        <f>IF('Heure par heure'!D38="","",'Heure par heure'!D38-N('Heure par heure'!D37))</f>
+        <v/>
+      </c>
+      <c r="D38" s="3">
+        <f>IF('Heure par heure'!E38="","",'Heure par heure'!E38-N('Heure par heure'!E37))</f>
+        <v/>
+      </c>
+      <c r="E38" s="3">
+        <f>IF('Heure par heure'!F38="","",'Heure par heure'!F38-N('Heure par heure'!F37))</f>
+        <v/>
+      </c>
+      <c r="F38" s="3">
+        <f>IF('Heure par heure'!G38="","",'Heure par heure'!G38-N('Heure par heure'!G37))</f>
+        <v/>
+      </c>
+      <c r="G38" s="3">
+        <f>IF('Heure par heure'!H38="","",'Heure par heure'!H38-N('Heure par heure'!H37))</f>
+        <v/>
+      </c>
+      <c r="H38" s="3">
+        <f>IF('Heure par heure'!I38="","",'Heure par heure'!I38-N('Heure par heure'!I37))</f>
+        <v/>
+      </c>
+      <c r="I38" s="3">
+        <f>IF('Heure par heure'!J38="","",'Heure par heure'!J38-N('Heure par heure'!J37))</f>
+        <v/>
+      </c>
+      <c r="J38" s="3">
+        <f>IF('Heure par heure'!K38="","",'Heure par heure'!K38-N('Heure par heure'!K37))</f>
+        <v/>
+      </c>
+      <c r="K38" s="3">
+        <f>IF('Heure par heure'!L38="","",'Heure par heure'!L38-N('Heure par heure'!L37))</f>
+        <v/>
+      </c>
+      <c r="L38" s="3">
+        <f>SUM(B38:K38)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$38</f>
+              <f>'Heure par heure'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$38</f>
+              <f>'Heure par heure'!$D$2:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$38</f>
+              <f>'Heure par heure'!$E$2:$E$39</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$38</f>
+              <f>'Heure par heure'!$F$2:$F$39</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$38</f>
+              <f>'Heure par heure'!$G$2:$G$39</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$38</f>
+              <f>'Heure par heure'!$H$2:$H$39</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$38</f>
+              <f>'Heure par heure'!$I$2:$I$39</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$38</f>
+              <f>'Heure par heure'!$J$2:$J$39</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$38</f>
+              <f>'Heure par heure'!$K$2:$K$39</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$38</f>
+              <f>'Heure par heure'!$L$2:$L$39</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$38</f>
+              <f>'Heure par heure'!$B$2:$B$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$38</f>
+              <f>'Heure par heure'!$M$2:$M$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$38</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$38</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$38</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$38</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$39</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$38</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$39</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$38</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$39</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$38</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$39</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$38</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$39</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$38</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$39</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$38</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$39</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7803,6 +7803,50 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:00</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M39" s="3">
+        <f>SUM(C39:L39)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7815,7 +7859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9711,6 +9755,56 @@
       </c>
       <c r="L38" s="3">
         <f>SUM(B38:K38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <f>'Heure par heure'!A39</f>
+        <v/>
+      </c>
+      <c r="B39" s="3">
+        <f>IF('Heure par heure'!C39="","",'Heure par heure'!C39-N('Heure par heure'!C38))</f>
+        <v/>
+      </c>
+      <c r="C39" s="3">
+        <f>IF('Heure par heure'!D39="","",'Heure par heure'!D39-N('Heure par heure'!D38))</f>
+        <v/>
+      </c>
+      <c r="D39" s="3">
+        <f>IF('Heure par heure'!E39="","",'Heure par heure'!E39-N('Heure par heure'!E38))</f>
+        <v/>
+      </c>
+      <c r="E39" s="3">
+        <f>IF('Heure par heure'!F39="","",'Heure par heure'!F39-N('Heure par heure'!F38))</f>
+        <v/>
+      </c>
+      <c r="F39" s="3">
+        <f>IF('Heure par heure'!G39="","",'Heure par heure'!G39-N('Heure par heure'!G38))</f>
+        <v/>
+      </c>
+      <c r="G39" s="3">
+        <f>IF('Heure par heure'!H39="","",'Heure par heure'!H39-N('Heure par heure'!H38))</f>
+        <v/>
+      </c>
+      <c r="H39" s="3">
+        <f>IF('Heure par heure'!I39="","",'Heure par heure'!I39-N('Heure par heure'!I38))</f>
+        <v/>
+      </c>
+      <c r="I39" s="3">
+        <f>IF('Heure par heure'!J39="","",'Heure par heure'!J39-N('Heure par heure'!J38))</f>
+        <v/>
+      </c>
+      <c r="J39" s="3">
+        <f>IF('Heure par heure'!K39="","",'Heure par heure'!K39-N('Heure par heure'!K38))</f>
+        <v/>
+      </c>
+      <c r="K39" s="3">
+        <f>IF('Heure par heure'!L39="","",'Heure par heure'!L39-N('Heure par heure'!L38))</f>
+        <v/>
+      </c>
+      <c r="L39" s="3">
+        <f>SUM(B39:K39)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$39</f>
+              <f>'Heure par heure'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$39</f>
+              <f>'Heure par heure'!$D$2:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$39</f>
+              <f>'Heure par heure'!$E$2:$E$40</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$39</f>
+              <f>'Heure par heure'!$F$2:$F$40</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$39</f>
+              <f>'Heure par heure'!$G$2:$G$40</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$39</f>
+              <f>'Heure par heure'!$H$2:$H$40</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$39</f>
+              <f>'Heure par heure'!$I$2:$I$40</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$39</f>
+              <f>'Heure par heure'!$J$2:$J$40</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$39</f>
+              <f>'Heure par heure'!$K$2:$K$40</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$39</f>
+              <f>'Heure par heure'!$L$2:$L$40</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$39</f>
+              <f>'Heure par heure'!$B$2:$B$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$39</f>
+              <f>'Heure par heure'!$M$2:$M$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$39</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$39</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$39</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$39</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$40</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$39</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$40</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$39</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$40</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$39</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$40</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$39</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$40</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$39</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$40</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$39</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$40</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6198,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6229,52 +6229,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Des millions publics p</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Vendredi, Macron au co</t>
+          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
+          <t>10-27 54 milliards d'efforts</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -6293,23 +6293,21 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="H2" s="3" t="n">
         <v>124</v>
       </c>
+      <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
@@ -6329,23 +6327,21 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="H3" s="3" t="n">
         <v>130</v>
       </c>
+      <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
@@ -6365,23 +6361,21 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="H4" s="3" t="n">
         <v>135</v>
       </c>
+      <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
@@ -6401,26 +6395,24 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
@@ -6439,26 +6431,24 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="I6" s="3" t="n">
         <v>34</v>
       </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
@@ -6477,26 +6467,24 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="I7" s="3" t="n">
         <v>44</v>
       </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
@@ -6515,26 +6503,24 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="I8" s="3" t="n">
         <v>70</v>
       </c>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
@@ -6553,26 +6539,24 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="I9" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
@@ -6591,26 +6575,24 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="I10" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
@@ -6629,26 +6611,24 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="I11" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
@@ -6667,26 +6647,24 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="I12" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
@@ -6705,26 +6683,24 @@
         <v>6</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>130</v>
+        <v>199</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="I13" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
@@ -6743,26 +6719,24 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="I14" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
@@ -6781,26 +6755,24 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="I15" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
@@ -6819,26 +6791,24 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="I16" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
@@ -6857,26 +6827,24 @@
         <v>6</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="I17" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
@@ -6895,32 +6863,30 @@
         <v>6</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>240</v>
+        <v>134</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3">
         <f>SUM(C18:L18)</f>
@@ -6937,32 +6903,30 @@
         <v>7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K19" s="3" t="n">
         <v>53</v>
       </c>
+      <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3">
         <f>SUM(C19:L19)</f>
@@ -6979,32 +6943,30 @@
         <v>7</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="K20" s="3" t="n">
         <v>80</v>
       </c>
+      <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3">
         <f>SUM(C20:L20)</f>
@@ -7021,35 +6983,33 @@
         <v>7</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>35</v>
-      </c>
       <c r="K21" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n"/>
       <c r="M21" s="3">
         <f>SUM(C21:L21)</f>
         <v/>
@@ -7065,35 +7025,33 @@
         <v>7</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>243</v>
+        <v>134</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="L22" s="3" t="n">
         <v>43</v>
       </c>
+      <c r="L22" s="3" t="n"/>
       <c r="M22" s="3">
         <f>SUM(C22:L22)</f>
         <v/>
@@ -7109,35 +7067,33 @@
         <v>7</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>243</v>
+        <v>134</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="L23" s="3" t="n">
         <v>64</v>
       </c>
+      <c r="L23" s="3" t="n"/>
       <c r="M23" s="3">
         <f>SUM(C23:L23)</f>
         <v/>
@@ -7153,35 +7109,33 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="L24" s="3" t="n">
         <v>99</v>
       </c>
+      <c r="L24" s="3" t="n"/>
       <c r="M24" s="3">
         <f>SUM(C24:L24)</f>
         <v/>
@@ -7197,35 +7151,33 @@
         <v>7</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="L25" s="3" t="n">
         <v>111</v>
       </c>
+      <c r="L25" s="3" t="n"/>
       <c r="M25" s="3">
         <f>SUM(C25:L25)</f>
         <v/>
@@ -7241,35 +7193,33 @@
         <v>7</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="L26" s="3" t="n">
         <v>115</v>
       </c>
+      <c r="L26" s="3" t="n"/>
       <c r="M26" s="3">
         <f>SUM(C26:L26)</f>
         <v/>
@@ -7285,35 +7235,33 @@
         <v>7</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="L27" s="3" t="n">
         <v>115</v>
       </c>
+      <c r="L27" s="3" t="n"/>
       <c r="M27" s="3">
         <f>SUM(C27:L27)</f>
         <v/>
@@ -7329,35 +7277,33 @@
         <v>7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="L28" s="3" t="n">
         <v>115</v>
       </c>
+      <c r="L28" s="3" t="n"/>
       <c r="M28" s="3">
         <f>SUM(C28:L28)</f>
         <v/>
@@ -7373,35 +7319,33 @@
         <v>7</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E29" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I29" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J29" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L29" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="L29" s="3" t="n"/>
       <c r="M29" s="3">
         <f>SUM(C29:L29)</f>
         <v/>
@@ -7417,35 +7361,33 @@
         <v>7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E30" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J30" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L30" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="L30" s="3" t="n"/>
       <c r="M30" s="3">
         <f>SUM(C30:L30)</f>
         <v/>
@@ -7461,35 +7403,33 @@
         <v>7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E31" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I31" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J31" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L31" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="L31" s="3" t="n"/>
       <c r="M31" s="3">
         <f>SUM(C31:L31)</f>
         <v/>
@@ -7505,35 +7445,33 @@
         <v>7</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E32" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I32" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J32" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L32" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="L32" s="3" t="n"/>
       <c r="M32" s="3">
         <f>SUM(C32:L32)</f>
         <v/>
@@ -7549,35 +7487,33 @@
         <v>7</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E33" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I33" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J33" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L33" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="L33" s="3" t="n"/>
       <c r="M33" s="3">
         <f>SUM(C33:L33)</f>
         <v/>
@@ -7593,35 +7529,33 @@
         <v>7</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J34" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L34" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="L34" s="3" t="n"/>
       <c r="M34" s="3">
         <f>SUM(C34:L34)</f>
         <v/>
@@ -7637,35 +7571,33 @@
         <v>7</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E35" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I35" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J35" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L35" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="L35" s="3" t="n"/>
       <c r="M35" s="3">
         <f>SUM(C35:L35)</f>
         <v/>
@@ -7681,35 +7613,33 @@
         <v>7</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E36" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I36" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J36" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L36" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="L36" s="3" t="n"/>
       <c r="M36" s="3">
         <f>SUM(C36:L36)</f>
         <v/>
@@ -7725,35 +7655,33 @@
         <v>7</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E37" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I37" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J37" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L37" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="L37" s="3" t="n"/>
       <c r="M37" s="3">
         <f>SUM(C37:L37)</f>
         <v/>
@@ -7769,35 +7697,33 @@
         <v>7</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E38" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I38" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J38" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L38" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="L38" s="3" t="n"/>
       <c r="M38" s="3">
         <f>SUM(C38:L38)</f>
         <v/>
@@ -7813,37 +7739,79 @@
         <v>7</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E39" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I39" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="J39" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="L39" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="L39" s="3" t="n"/>
       <c r="M39" s="3">
         <f>SUM(C39:L39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 08:00</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
+        <f>SUM(C40:L40)</f>
         <v/>
       </c>
     </row>
@@ -7859,7 +7827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7884,52 +7852,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Les syndicats de salar</t>
+          <t>10-21 À toi de juger : taxer</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Des millions publics p</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Vendredi, Macron au co</t>
+          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
+          <t>10-27 54 milliards d'efforts</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -9805,6 +9773,56 @@
       </c>
       <c r="L39" s="3">
         <f>SUM(B39:K39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <f>'Heure par heure'!A40</f>
+        <v/>
+      </c>
+      <c r="B40" s="3">
+        <f>IF('Heure par heure'!C40="","",'Heure par heure'!C40-N('Heure par heure'!C39))</f>
+        <v/>
+      </c>
+      <c r="C40" s="3">
+        <f>IF('Heure par heure'!D40="","",'Heure par heure'!D40-N('Heure par heure'!D39))</f>
+        <v/>
+      </c>
+      <c r="D40" s="3">
+        <f>IF('Heure par heure'!E40="","",'Heure par heure'!E40-N('Heure par heure'!E39))</f>
+        <v/>
+      </c>
+      <c r="E40" s="3">
+        <f>IF('Heure par heure'!F40="","",'Heure par heure'!F40-N('Heure par heure'!F39))</f>
+        <v/>
+      </c>
+      <c r="F40" s="3">
+        <f>IF('Heure par heure'!G40="","",'Heure par heure'!G40-N('Heure par heure'!G39))</f>
+        <v/>
+      </c>
+      <c r="G40" s="3">
+        <f>IF('Heure par heure'!H40="","",'Heure par heure'!H40-N('Heure par heure'!H39))</f>
+        <v/>
+      </c>
+      <c r="H40" s="3">
+        <f>IF('Heure par heure'!I40="","",'Heure par heure'!I40-N('Heure par heure'!I39))</f>
+        <v/>
+      </c>
+      <c r="I40" s="3">
+        <f>IF('Heure par heure'!J40="","",'Heure par heure'!J40-N('Heure par heure'!J39))</f>
+        <v/>
+      </c>
+      <c r="J40" s="3">
+        <f>IF('Heure par heure'!K40="","",'Heure par heure'!K40-N('Heure par heure'!K39))</f>
+        <v/>
+      </c>
+      <c r="K40" s="3">
+        <f>IF('Heure par heure'!L40="","",'Heure par heure'!L40-N('Heure par heure'!L39))</f>
+        <v/>
+      </c>
+      <c r="L40" s="3">
+        <f>SUM(B40:K40)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$10</f>
+              <f>'Jour par jour'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$10</f>
+              <f>'Jour par jour'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1244,12 +1244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$46</f>
+              <f>'Stories'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$46</f>
+              <f>'Stories'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -1346,12 +1346,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$10</f>
+              <f>'Jour par jour'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$10</f>
+              <f>'Jour par jour'!$E$2:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -1373,12 +1373,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$10</f>
+              <f>'Jour par jour'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$10</f>
+              <f>'Jour par jour'!$L$2:$L$11</f>
             </numRef>
           </val>
         </ser>
@@ -1486,12 +1486,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$10</f>
+              <f>'Jour par jour'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$10</f>
+              <f>'Jour par jour'!$F$2:$F$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1526,12 +1526,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$10</f>
+              <f>'Jour par jour'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$10</f>
+              <f>'Jour par jour'!$H$2:$H$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1628,12 +1628,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$10</f>
+              <f>'Jour par jour'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$10</f>
+              <f>'Jour par jour'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -2121,12 +2121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$10</f>
+              <f>'Évolution par vidéo'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$10</f>
+              <f>'Évolution par vidéo'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -2185,12 +2185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$10</f>
+              <f>'Évolution par vidéo'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -2217,12 +2217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$10</f>
+              <f>'Évolution par vidéo'!$E$2:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -2249,12 +2249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$10</f>
+              <f>'Évolution par vidéo'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -2281,12 +2281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$10</f>
+              <f>'Évolution par vidéo'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -2313,12 +2313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$10</f>
+              <f>'Évolution par vidéo'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -2345,12 +2345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$10</f>
+              <f>'Évolution par vidéo'!$I$2:$I$11</f>
             </numRef>
           </val>
         </ser>
@@ -2377,12 +2377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$10</f>
+              <f>'Évolution par vidéo'!$J$2:$J$11</f>
             </numRef>
           </val>
         </ser>
@@ -2409,12 +2409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$10</f>
+              <f>'Évolution par vidéo'!$K$2:$K$11</f>
             </numRef>
           </val>
         </ser>
@@ -2441,12 +2441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$10</f>
+              <f>'Évolution par vidéo'!$L$2:$L$11</f>
             </numRef>
           </val>
         </ser>
@@ -2473,12 +2473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$10</f>
+              <f>'Évolution par vidéo'!$M$2:$M$11</f>
             </numRef>
           </val>
         </ser>
@@ -2505,12 +2505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$10</f>
+              <f>'Évolution par vidéo'!$N$2:$N$11</f>
             </numRef>
           </val>
         </ser>
@@ -2537,12 +2537,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$10</f>
+              <f>'Évolution par vidéo'!$O$2:$O$11</f>
             </numRef>
           </val>
         </ser>
@@ -2569,12 +2569,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$10</f>
+              <f>'Évolution par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$10</f>
+              <f>'Évolution par vidéo'!$P$2:$P$11</f>
             </numRef>
           </val>
         </ser>
@@ -2667,12 +2667,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$10</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$10</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -2715,12 +2715,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$10</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -2739,12 +2739,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$10</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -2763,12 +2763,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$10</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -2787,12 +2787,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$10</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -2811,12 +2811,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$10</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -2835,12 +2835,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$10</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$11</f>
             </numRef>
           </val>
         </ser>
@@ -2859,12 +2859,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$10</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$11</f>
             </numRef>
           </val>
         </ser>
@@ -2883,12 +2883,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$10</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$11</f>
             </numRef>
           </val>
         </ser>
@@ -2907,12 +2907,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$10</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$11</f>
             </numRef>
           </val>
         </ser>
@@ -2931,12 +2931,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$10</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$11</f>
             </numRef>
           </val>
         </ser>
@@ -2955,12 +2955,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$10</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$11</f>
             </numRef>
           </val>
         </ser>
@@ -2979,12 +2979,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$10</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$11</f>
             </numRef>
           </val>
         </ser>
@@ -3003,12 +3003,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$10</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$10</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$11</f>
             </numRef>
           </val>
         </ser>
@@ -3221,7 +3221,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3248,7 +3248,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -3683,7 +3683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4171,6 +4171,51 @@
       </c>
       <c r="M10" s="3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3">
+        <f>IF(ROW()=2,"",B11-B10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1778</v>
+      </c>
+      <c r="E11" s="3">
+        <f>IF(ROW()=2,D11,D11-D10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4267,12 +4312,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-19 12:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, après. Pour les co</t>
+          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4281,13 +4326,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -4299,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -4313,12 +4358,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4327,13 +4372,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -4345,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
@@ -4359,12 +4404,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4373,13 +4418,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -4388,10 +4433,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -4405,12 +4450,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4419,13 +4464,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -4434,10 +4479,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
@@ -4451,12 +4496,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4465,13 +4510,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -4483,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <f>IFERROR((F6+G6+H6+I6)/IF(E6&gt;0,E6,D6),0)</f>
@@ -4497,12 +4542,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4511,13 +4556,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -4543,12 +4588,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4557,10 +4602,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4575,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5">
         <f>IFERROR((F8+G8+H8+I8)/IF(E8&gt;0,E8,D8),0)</f>
@@ -4589,12 +4634,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:08</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou non ? Réponds en co</t>
+          <t>Couper les réseaux sociaux pendant les émeute</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4603,10 +4648,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -4635,12 +4680,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-24 12:30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux pendant les émeute</t>
+          <t>À toi de juger : il faut une enquête indépend</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4649,13 +4694,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -4667,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
@@ -4681,12 +4726,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 12:30</t>
+          <t>2026-10-24 13:56</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une enquête indépend</t>
+          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4695,25 +4740,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="F11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
@@ -4727,12 +4772,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:56</t>
+          <t>2026-10-24 18:14</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
+          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4741,13 +4786,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>224</v>
+        <v>115</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -4756,10 +4801,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR((F12+G12+H12+I12)/IF(E12&gt;0,E12,D12),0)</f>
@@ -4773,12 +4818,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 18:14</t>
+          <t>2026-10-25 13:58</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
+          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4787,10 +4832,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
@@ -4819,12 +4864,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:58</t>
+          <t>2026-10-25 13:59</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
+          <t>Vendredi, Macron au concert de Céline Dion. S</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4833,13 +4878,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -4851,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="5">
         <f>IFERROR((F14+G14+H14+I14)/IF(E14&gt;0,E14,D14),0)</f>
@@ -4865,12 +4910,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:59</t>
+          <t>2026-10-25 17:26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Vendredi, Macron au concert de Céline Dion. S</t>
+          <t>2 513 gardes à vue et 67 incarcérations après</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4879,13 +4924,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -4897,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="5">
         <f>IFERROR((F15+G15+H15+I15)/IF(E15&gt;0,E15,D15),0)</f>
@@ -4911,12 +4956,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 17:26</t>
+          <t>2026-10-27 07:08</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2 513 gardes à vue et 67 incarcérations après</t>
+          <t xml:space="preserve">54 milliards d'efforts demandés aux Français </t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4925,10 +4970,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -4983,7 +5028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5012,77 +5057,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Des millions publics promis.</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi, Macron au concert </t>
+          <t>2 513 gardes à vue et 67 inc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>2 513 gardes à vue et 67 inc</t>
+          <t>54 milliards d'efforts deman</t>
         </is>
       </c>
     </row>
@@ -5115,11 +5160,9 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -5141,17 +5184,15 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="E4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
@@ -5171,26 +5212,24 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H5" s="3" t="n">
         <v>69</v>
       </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
@@ -5207,32 +5246,30 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>128</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="J6" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
@@ -5247,32 +5284,30 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>128</v>
-      </c>
       <c r="I7" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="J7" s="3" t="n">
         <v>74</v>
       </c>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
@@ -5287,38 +5322,36 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="L8" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n"/>
@@ -5331,47 +5364,45 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n"/>
     </row>
     <row r="10">
@@ -5381,49 +5412,99 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="P10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="C11" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="G11" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="H11" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="I11" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="K11" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="P10" s="3" t="n">
-        <v>117</v>
+      <c r="O11" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +5519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5468,77 +5549,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Les vitrines d'abord. Toi, a</t>
+          <t>📩 « Jeudi 5 novembre, la Fra</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Des millions publics promis.</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi, Macron au concert </t>
+          <t>2 513 gardes à vue et 67 inc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>2 513 gardes à vue et 67 inc</t>
+          <t>54 milliards d'efforts deman</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -6183,6 +6264,77 @@
       </c>
       <c r="Q10" s="3">
         <f>SUM(B10:P10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>IF('Évolution par vidéo'!B11="","",'Évolution par vidéo'!B11-N('Évolution par vidéo'!B10))</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>IF('Évolution par vidéo'!C11="","",'Évolution par vidéo'!C11-N('Évolution par vidéo'!C10))</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IF('Évolution par vidéo'!D11="","",'Évolution par vidéo'!D11-N('Évolution par vidéo'!D10))</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>IF('Évolution par vidéo'!E11="","",'Évolution par vidéo'!E11-N('Évolution par vidéo'!E10))</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>IF('Évolution par vidéo'!F11="","",'Évolution par vidéo'!F11-N('Évolution par vidéo'!F10))</f>
+        <v/>
+      </c>
+      <c r="G11" s="3">
+        <f>IF('Évolution par vidéo'!G11="","",'Évolution par vidéo'!G11-N('Évolution par vidéo'!G10))</f>
+        <v/>
+      </c>
+      <c r="H11" s="3">
+        <f>IF('Évolution par vidéo'!H11="","",'Évolution par vidéo'!H11-N('Évolution par vidéo'!H10))</f>
+        <v/>
+      </c>
+      <c r="I11" s="3">
+        <f>IF('Évolution par vidéo'!I11="","",'Évolution par vidéo'!I11-N('Évolution par vidéo'!I10))</f>
+        <v/>
+      </c>
+      <c r="J11" s="3">
+        <f>IF('Évolution par vidéo'!J11="","",'Évolution par vidéo'!J11-N('Évolution par vidéo'!J10))</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>IF('Évolution par vidéo'!K11="","",'Évolution par vidéo'!K11-N('Évolution par vidéo'!K10))</f>
+        <v/>
+      </c>
+      <c r="L11" s="3">
+        <f>IF('Évolution par vidéo'!L11="","",'Évolution par vidéo'!L11-N('Évolution par vidéo'!L10))</f>
+        <v/>
+      </c>
+      <c r="M11" s="3">
+        <f>IF('Évolution par vidéo'!M11="","",'Évolution par vidéo'!M11-N('Évolution par vidéo'!M10))</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>IF('Évolution par vidéo'!N11="","",'Évolution par vidéo'!N11-N('Évolution par vidéo'!N10))</f>
+        <v/>
+      </c>
+      <c r="O11" s="3">
+        <f>IF('Évolution par vidéo'!O11="","",'Évolution par vidéo'!O11-N('Évolution par vidéo'!O10))</f>
+        <v/>
+      </c>
+      <c r="P11" s="3">
+        <f>IF('Évolution par vidéo'!P11="","",'Évolution par vidéo'!P11-N('Évolution par vidéo'!P10))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="3">
+        <f>SUM(B11:P11)</f>
         <v/>
       </c>
     </row>
@@ -9838,7 +9990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11379,6 +11531,39 @@
         <v>1</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:09</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -11431,9 +11616,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId46"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId47"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$40</f>
+              <f>'Heure par heure'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$40</f>
+              <f>'Heure par heure'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$40</f>
+              <f>'Heure par heure'!$E$2:$E$41</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$40</f>
+              <f>'Heure par heure'!$F$2:$F$41</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$40</f>
+              <f>'Heure par heure'!$G$2:$G$41</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$40</f>
+              <f>'Heure par heure'!$H$2:$H$41</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$40</f>
+              <f>'Heure par heure'!$I$2:$I$41</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$40</f>
+              <f>'Heure par heure'!$J$2:$J$41</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$40</f>
+              <f>'Heure par heure'!$K$2:$K$41</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$40</f>
+              <f>'Heure par heure'!$L$2:$L$41</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$40</f>
+              <f>'Heure par heure'!$B$2:$B$41</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$40</f>
+              <f>'Heure par heure'!$M$2:$M$41</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$40</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$40</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$40</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$40</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$41</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$40</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$41</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$40</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$41</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$40</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$41</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$40</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$41</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$40</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$41</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$40</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$41</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7967,6 +7967,50 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="M41" s="3">
+        <f>SUM(C41:L41)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7979,7 +8023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9975,6 +10019,56 @@
       </c>
       <c r="L40" s="3">
         <f>SUM(B40:K40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <f>'Heure par heure'!A41</f>
+        <v/>
+      </c>
+      <c r="B41" s="3">
+        <f>IF('Heure par heure'!C41="","",'Heure par heure'!C41-N('Heure par heure'!C40))</f>
+        <v/>
+      </c>
+      <c r="C41" s="3">
+        <f>IF('Heure par heure'!D41="","",'Heure par heure'!D41-N('Heure par heure'!D40))</f>
+        <v/>
+      </c>
+      <c r="D41" s="3">
+        <f>IF('Heure par heure'!E41="","",'Heure par heure'!E41-N('Heure par heure'!E40))</f>
+        <v/>
+      </c>
+      <c r="E41" s="3">
+        <f>IF('Heure par heure'!F41="","",'Heure par heure'!F41-N('Heure par heure'!F40))</f>
+        <v/>
+      </c>
+      <c r="F41" s="3">
+        <f>IF('Heure par heure'!G41="","",'Heure par heure'!G41-N('Heure par heure'!G40))</f>
+        <v/>
+      </c>
+      <c r="G41" s="3">
+        <f>IF('Heure par heure'!H41="","",'Heure par heure'!H41-N('Heure par heure'!H40))</f>
+        <v/>
+      </c>
+      <c r="H41" s="3">
+        <f>IF('Heure par heure'!I41="","",'Heure par heure'!I41-N('Heure par heure'!I40))</f>
+        <v/>
+      </c>
+      <c r="I41" s="3">
+        <f>IF('Heure par heure'!J41="","",'Heure par heure'!J41-N('Heure par heure'!J40))</f>
+        <v/>
+      </c>
+      <c r="J41" s="3">
+        <f>IF('Heure par heure'!K41="","",'Heure par heure'!K41-N('Heure par heure'!K40))</f>
+        <v/>
+      </c>
+      <c r="K41" s="3">
+        <f>IF('Heure par heure'!L41="","",'Heure par heure'!L41-N('Heure par heure'!L40))</f>
+        <v/>
+      </c>
+      <c r="L41" s="3">
+        <f>SUM(B41:K41)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$41</f>
+              <f>'Heure par heure'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$41</f>
+              <f>'Heure par heure'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$41</f>
+              <f>'Heure par heure'!$E$2:$E$42</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$41</f>
+              <f>'Heure par heure'!$F$2:$F$42</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$41</f>
+              <f>'Heure par heure'!$G$2:$G$42</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$41</f>
+              <f>'Heure par heure'!$H$2:$H$42</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$41</f>
+              <f>'Heure par heure'!$I$2:$I$42</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$41</f>
+              <f>'Heure par heure'!$J$2:$J$42</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$41</f>
+              <f>'Heure par heure'!$K$2:$K$42</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$41</f>
+              <f>'Heure par heure'!$L$2:$L$42</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$41</f>
+              <f>'Heure par heure'!$B$2:$B$42</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$41</f>
+              <f>'Heure par heure'!$M$2:$M$42</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$41</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$41</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$41</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$41</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$42</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$41</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$42</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$41</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$42</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$41</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$42</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$41</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$42</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$41</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$42</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$41</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$42</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8011,6 +8011,50 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:00</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="M42" s="3">
+        <f>SUM(C42:L42)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8023,7 +8067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10069,6 +10113,56 @@
       </c>
       <c r="L41" s="3">
         <f>SUM(B41:K41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <f>'Heure par heure'!A42</f>
+        <v/>
+      </c>
+      <c r="B42" s="3">
+        <f>IF('Heure par heure'!C42="","",'Heure par heure'!C42-N('Heure par heure'!C41))</f>
+        <v/>
+      </c>
+      <c r="C42" s="3">
+        <f>IF('Heure par heure'!D42="","",'Heure par heure'!D42-N('Heure par heure'!D41))</f>
+        <v/>
+      </c>
+      <c r="D42" s="3">
+        <f>IF('Heure par heure'!E42="","",'Heure par heure'!E42-N('Heure par heure'!E41))</f>
+        <v/>
+      </c>
+      <c r="E42" s="3">
+        <f>IF('Heure par heure'!F42="","",'Heure par heure'!F42-N('Heure par heure'!F41))</f>
+        <v/>
+      </c>
+      <c r="F42" s="3">
+        <f>IF('Heure par heure'!G42="","",'Heure par heure'!G42-N('Heure par heure'!G41))</f>
+        <v/>
+      </c>
+      <c r="G42" s="3">
+        <f>IF('Heure par heure'!H42="","",'Heure par heure'!H42-N('Heure par heure'!H41))</f>
+        <v/>
+      </c>
+      <c r="H42" s="3">
+        <f>IF('Heure par heure'!I42="","",'Heure par heure'!I42-N('Heure par heure'!I41))</f>
+        <v/>
+      </c>
+      <c r="I42" s="3">
+        <f>IF('Heure par heure'!J42="","",'Heure par heure'!J42-N('Heure par heure'!J41))</f>
+        <v/>
+      </c>
+      <c r="J42" s="3">
+        <f>IF('Heure par heure'!K42="","",'Heure par heure'!K42-N('Heure par heure'!K41))</f>
+        <v/>
+      </c>
+      <c r="K42" s="3">
+        <f>IF('Heure par heure'!L42="","",'Heure par heure'!L42-N('Heure par heure'!L41))</f>
+        <v/>
+      </c>
+      <c r="L42" s="3">
+        <f>SUM(B42:K42)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$42</f>
+              <f>'Heure par heure'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$42</f>
+              <f>'Heure par heure'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$42</f>
+              <f>'Heure par heure'!$E$2:$E$43</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$42</f>
+              <f>'Heure par heure'!$F$2:$F$43</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$42</f>
+              <f>'Heure par heure'!$G$2:$G$43</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$42</f>
+              <f>'Heure par heure'!$H$2:$H$43</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$42</f>
+              <f>'Heure par heure'!$I$2:$I$43</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$42</f>
+              <f>'Heure par heure'!$J$2:$J$43</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$42</f>
+              <f>'Heure par heure'!$K$2:$K$43</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$42</f>
+              <f>'Heure par heure'!$L$2:$L$43</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$42</f>
+              <f>'Heure par heure'!$B$2:$B$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$42</f>
+              <f>'Heure par heure'!$M$2:$M$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$42</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$42</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$42</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$42</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$43</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$42</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$43</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$42</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$43</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$42</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$43</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$42</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$43</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$42</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$43</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$42</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$43</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8055,6 +8055,50 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:00</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="M43" s="3">
+        <f>SUM(C43:L43)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8067,7 +8111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10163,6 +10207,56 @@
       </c>
       <c r="L42" s="3">
         <f>SUM(B42:K42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <f>'Heure par heure'!A43</f>
+        <v/>
+      </c>
+      <c r="B43" s="3">
+        <f>IF('Heure par heure'!C43="","",'Heure par heure'!C43-N('Heure par heure'!C42))</f>
+        <v/>
+      </c>
+      <c r="C43" s="3">
+        <f>IF('Heure par heure'!D43="","",'Heure par heure'!D43-N('Heure par heure'!D42))</f>
+        <v/>
+      </c>
+      <c r="D43" s="3">
+        <f>IF('Heure par heure'!E43="","",'Heure par heure'!E43-N('Heure par heure'!E42))</f>
+        <v/>
+      </c>
+      <c r="E43" s="3">
+        <f>IF('Heure par heure'!F43="","",'Heure par heure'!F43-N('Heure par heure'!F42))</f>
+        <v/>
+      </c>
+      <c r="F43" s="3">
+        <f>IF('Heure par heure'!G43="","",'Heure par heure'!G43-N('Heure par heure'!G42))</f>
+        <v/>
+      </c>
+      <c r="G43" s="3">
+        <f>IF('Heure par heure'!H43="","",'Heure par heure'!H43-N('Heure par heure'!H42))</f>
+        <v/>
+      </c>
+      <c r="H43" s="3">
+        <f>IF('Heure par heure'!I43="","",'Heure par heure'!I43-N('Heure par heure'!I42))</f>
+        <v/>
+      </c>
+      <c r="I43" s="3">
+        <f>IF('Heure par heure'!J43="","",'Heure par heure'!J43-N('Heure par heure'!J42))</f>
+        <v/>
+      </c>
+      <c r="J43" s="3">
+        <f>IF('Heure par heure'!K43="","",'Heure par heure'!K43-N('Heure par heure'!K42))</f>
+        <v/>
+      </c>
+      <c r="K43" s="3">
+        <f>IF('Heure par heure'!L43="","",'Heure par heure'!L43-N('Heure par heure'!L42))</f>
+        <v/>
+      </c>
+      <c r="L43" s="3">
+        <f>SUM(B43:K43)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$43</f>
+              <f>'Heure par heure'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$43</f>
+              <f>'Heure par heure'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$43</f>
+              <f>'Heure par heure'!$E$2:$E$44</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$43</f>
+              <f>'Heure par heure'!$F$2:$F$44</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$43</f>
+              <f>'Heure par heure'!$G$2:$G$44</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$43</f>
+              <f>'Heure par heure'!$H$2:$H$44</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$43</f>
+              <f>'Heure par heure'!$I$2:$I$44</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$43</f>
+              <f>'Heure par heure'!$J$2:$J$44</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$43</f>
+              <f>'Heure par heure'!$K$2:$K$44</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$43</f>
+              <f>'Heure par heure'!$L$2:$L$44</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$43</f>
+              <f>'Heure par heure'!$B$2:$B$44</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$43</f>
+              <f>'Heure par heure'!$M$2:$M$44</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$43</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$43</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$43</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$43</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$44</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$43</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$44</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$43</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$44</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$43</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$44</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$43</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$44</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$43</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$44</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$43</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$44</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8099,6 +8099,50 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:00</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="M44" s="3">
+        <f>SUM(C44:L44)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8111,7 +8155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10257,6 +10301,56 @@
       </c>
       <c r="L43" s="3">
         <f>SUM(B43:K43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <f>'Heure par heure'!A44</f>
+        <v/>
+      </c>
+      <c r="B44" s="3">
+        <f>IF('Heure par heure'!C44="","",'Heure par heure'!C44-N('Heure par heure'!C43))</f>
+        <v/>
+      </c>
+      <c r="C44" s="3">
+        <f>IF('Heure par heure'!D44="","",'Heure par heure'!D44-N('Heure par heure'!D43))</f>
+        <v/>
+      </c>
+      <c r="D44" s="3">
+        <f>IF('Heure par heure'!E44="","",'Heure par heure'!E44-N('Heure par heure'!E43))</f>
+        <v/>
+      </c>
+      <c r="E44" s="3">
+        <f>IF('Heure par heure'!F44="","",'Heure par heure'!F44-N('Heure par heure'!F43))</f>
+        <v/>
+      </c>
+      <c r="F44" s="3">
+        <f>IF('Heure par heure'!G44="","",'Heure par heure'!G44-N('Heure par heure'!G43))</f>
+        <v/>
+      </c>
+      <c r="G44" s="3">
+        <f>IF('Heure par heure'!H44="","",'Heure par heure'!H44-N('Heure par heure'!H43))</f>
+        <v/>
+      </c>
+      <c r="H44" s="3">
+        <f>IF('Heure par heure'!I44="","",'Heure par heure'!I44-N('Heure par heure'!I43))</f>
+        <v/>
+      </c>
+      <c r="I44" s="3">
+        <f>IF('Heure par heure'!J44="","",'Heure par heure'!J44-N('Heure par heure'!J43))</f>
+        <v/>
+      </c>
+      <c r="J44" s="3">
+        <f>IF('Heure par heure'!K44="","",'Heure par heure'!K44-N('Heure par heure'!K43))</f>
+        <v/>
+      </c>
+      <c r="K44" s="3">
+        <f>IF('Heure par heure'!L44="","",'Heure par heure'!L44-N('Heure par heure'!L43))</f>
+        <v/>
+      </c>
+      <c r="L44" s="3">
+        <f>SUM(B44:K44)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$44</f>
+              <f>'Heure par heure'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$44</f>
+              <f>'Heure par heure'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$44</f>
+              <f>'Heure par heure'!$E$2:$E$45</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$44</f>
+              <f>'Heure par heure'!$F$2:$F$45</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$44</f>
+              <f>'Heure par heure'!$G$2:$G$45</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$44</f>
+              <f>'Heure par heure'!$H$2:$H$45</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$44</f>
+              <f>'Heure par heure'!$I$2:$I$45</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$44</f>
+              <f>'Heure par heure'!$J$2:$J$45</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$44</f>
+              <f>'Heure par heure'!$K$2:$K$45</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$44</f>
+              <f>'Heure par heure'!$L$2:$L$45</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$44</f>
+              <f>'Heure par heure'!$B$2:$B$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$44</f>
+              <f>'Heure par heure'!$M$2:$M$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$44</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$44</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$44</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$44</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$45</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$44</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$45</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$44</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$45</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$44</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$45</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$44</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$45</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$44</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$45</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$44</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$45</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8143,6 +8143,50 @@
         <v/>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:00</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="M45" s="3">
+        <f>SUM(C45:L45)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8155,7 +8199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10351,6 +10395,56 @@
       </c>
       <c r="L44" s="3">
         <f>SUM(B44:K44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <f>'Heure par heure'!A45</f>
+        <v/>
+      </c>
+      <c r="B45" s="3">
+        <f>IF('Heure par heure'!C45="","",'Heure par heure'!C45-N('Heure par heure'!C44))</f>
+        <v/>
+      </c>
+      <c r="C45" s="3">
+        <f>IF('Heure par heure'!D45="","",'Heure par heure'!D45-N('Heure par heure'!D44))</f>
+        <v/>
+      </c>
+      <c r="D45" s="3">
+        <f>IF('Heure par heure'!E45="","",'Heure par heure'!E45-N('Heure par heure'!E44))</f>
+        <v/>
+      </c>
+      <c r="E45" s="3">
+        <f>IF('Heure par heure'!F45="","",'Heure par heure'!F45-N('Heure par heure'!F44))</f>
+        <v/>
+      </c>
+      <c r="F45" s="3">
+        <f>IF('Heure par heure'!G45="","",'Heure par heure'!G45-N('Heure par heure'!G44))</f>
+        <v/>
+      </c>
+      <c r="G45" s="3">
+        <f>IF('Heure par heure'!H45="","",'Heure par heure'!H45-N('Heure par heure'!H44))</f>
+        <v/>
+      </c>
+      <c r="H45" s="3">
+        <f>IF('Heure par heure'!I45="","",'Heure par heure'!I45-N('Heure par heure'!I44))</f>
+        <v/>
+      </c>
+      <c r="I45" s="3">
+        <f>IF('Heure par heure'!J45="","",'Heure par heure'!J45-N('Heure par heure'!J44))</f>
+        <v/>
+      </c>
+      <c r="J45" s="3">
+        <f>IF('Heure par heure'!K45="","",'Heure par heure'!K45-N('Heure par heure'!K44))</f>
+        <v/>
+      </c>
+      <c r="K45" s="3">
+        <f>IF('Heure par heure'!L45="","",'Heure par heure'!L45-N('Heure par heure'!L44))</f>
+        <v/>
+      </c>
+      <c r="L45" s="3">
+        <f>SUM(B45:K45)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$45</f>
+              <f>'Heure par heure'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$45</f>
+              <f>'Heure par heure'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$45</f>
+              <f>'Heure par heure'!$E$2:$E$46</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$45</f>
+              <f>'Heure par heure'!$F$2:$F$46</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$45</f>
+              <f>'Heure par heure'!$G$2:$G$46</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$45</f>
+              <f>'Heure par heure'!$H$2:$H$46</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$45</f>
+              <f>'Heure par heure'!$I$2:$I$46</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$45</f>
+              <f>'Heure par heure'!$J$2:$J$46</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$45</f>
+              <f>'Heure par heure'!$K$2:$K$46</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$45</f>
+              <f>'Heure par heure'!$L$2:$L$46</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$45</f>
+              <f>'Heure par heure'!$B$2:$B$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$45</f>
+              <f>'Heure par heure'!$M$2:$M$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$45</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$45</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$45</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$45</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$46</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$45</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$46</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$45</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$46</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$45</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$46</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$45</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$46</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$45</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$46</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$45</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$46</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8187,6 +8187,50 @@
         <v/>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="M46" s="3">
+        <f>SUM(C46:L46)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8199,7 +8243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10445,6 +10489,56 @@
       </c>
       <c r="L45" s="3">
         <f>SUM(B45:K45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <f>'Heure par heure'!A46</f>
+        <v/>
+      </c>
+      <c r="B46" s="3">
+        <f>IF('Heure par heure'!C46="","",'Heure par heure'!C46-N('Heure par heure'!C45))</f>
+        <v/>
+      </c>
+      <c r="C46" s="3">
+        <f>IF('Heure par heure'!D46="","",'Heure par heure'!D46-N('Heure par heure'!D45))</f>
+        <v/>
+      </c>
+      <c r="D46" s="3">
+        <f>IF('Heure par heure'!E46="","",'Heure par heure'!E46-N('Heure par heure'!E45))</f>
+        <v/>
+      </c>
+      <c r="E46" s="3">
+        <f>IF('Heure par heure'!F46="","",'Heure par heure'!F46-N('Heure par heure'!F45))</f>
+        <v/>
+      </c>
+      <c r="F46" s="3">
+        <f>IF('Heure par heure'!G46="","",'Heure par heure'!G46-N('Heure par heure'!G45))</f>
+        <v/>
+      </c>
+      <c r="G46" s="3">
+        <f>IF('Heure par heure'!H46="","",'Heure par heure'!H46-N('Heure par heure'!H45))</f>
+        <v/>
+      </c>
+      <c r="H46" s="3">
+        <f>IF('Heure par heure'!I46="","",'Heure par heure'!I46-N('Heure par heure'!I45))</f>
+        <v/>
+      </c>
+      <c r="I46" s="3">
+        <f>IF('Heure par heure'!J46="","",'Heure par heure'!J46-N('Heure par heure'!J45))</f>
+        <v/>
+      </c>
+      <c r="J46" s="3">
+        <f>IF('Heure par heure'!K46="","",'Heure par heure'!K46-N('Heure par heure'!K45))</f>
+        <v/>
+      </c>
+      <c r="K46" s="3">
+        <f>IF('Heure par heure'!L46="","",'Heure par heure'!L46-N('Heure par heure'!L45))</f>
+        <v/>
+      </c>
+      <c r="L46" s="3">
+        <f>SUM(B46:K46)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$46</f>
+              <f>'Heure par heure'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$46</f>
+              <f>'Heure par heure'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$46</f>
+              <f>'Heure par heure'!$E$2:$E$47</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$46</f>
+              <f>'Heure par heure'!$F$2:$F$47</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$46</f>
+              <f>'Heure par heure'!$G$2:$G$47</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$46</f>
+              <f>'Heure par heure'!$H$2:$H$47</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$46</f>
+              <f>'Heure par heure'!$I$2:$I$47</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$46</f>
+              <f>'Heure par heure'!$J$2:$J$47</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$46</f>
+              <f>'Heure par heure'!$K$2:$K$47</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$46</f>
+              <f>'Heure par heure'!$L$2:$L$47</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$46</f>
+              <f>'Heure par heure'!$B$2:$B$47</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$46</f>
+              <f>'Heure par heure'!$M$2:$M$47</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$46</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$46</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$46</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$46</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$47</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$46</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$47</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$46</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$47</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$46</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$47</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$46</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$47</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$46</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$47</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$46</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$47</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8231,6 +8231,50 @@
         <v/>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="M47" s="3">
+        <f>SUM(C47:L47)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8243,7 +8287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10539,6 +10583,56 @@
       </c>
       <c r="L46" s="3">
         <f>SUM(B46:K46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <f>'Heure par heure'!A47</f>
+        <v/>
+      </c>
+      <c r="B47" s="3">
+        <f>IF('Heure par heure'!C47="","",'Heure par heure'!C47-N('Heure par heure'!C46))</f>
+        <v/>
+      </c>
+      <c r="C47" s="3">
+        <f>IF('Heure par heure'!D47="","",'Heure par heure'!D47-N('Heure par heure'!D46))</f>
+        <v/>
+      </c>
+      <c r="D47" s="3">
+        <f>IF('Heure par heure'!E47="","",'Heure par heure'!E47-N('Heure par heure'!E46))</f>
+        <v/>
+      </c>
+      <c r="E47" s="3">
+        <f>IF('Heure par heure'!F47="","",'Heure par heure'!F47-N('Heure par heure'!F46))</f>
+        <v/>
+      </c>
+      <c r="F47" s="3">
+        <f>IF('Heure par heure'!G47="","",'Heure par heure'!G47-N('Heure par heure'!G46))</f>
+        <v/>
+      </c>
+      <c r="G47" s="3">
+        <f>IF('Heure par heure'!H47="","",'Heure par heure'!H47-N('Heure par heure'!H46))</f>
+        <v/>
+      </c>
+      <c r="H47" s="3">
+        <f>IF('Heure par heure'!I47="","",'Heure par heure'!I47-N('Heure par heure'!I46))</f>
+        <v/>
+      </c>
+      <c r="I47" s="3">
+        <f>IF('Heure par heure'!J47="","",'Heure par heure'!J47-N('Heure par heure'!J46))</f>
+        <v/>
+      </c>
+      <c r="J47" s="3">
+        <f>IF('Heure par heure'!K47="","",'Heure par heure'!K47-N('Heure par heure'!K46))</f>
+        <v/>
+      </c>
+      <c r="K47" s="3">
+        <f>IF('Heure par heure'!L47="","",'Heure par heure'!L47-N('Heure par heure'!L46))</f>
+        <v/>
+      </c>
+      <c r="L47" s="3">
+        <f>SUM(B47:K47)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -1244,12 +1244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$47</f>
+              <f>'Stories'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$47</f>
+              <f>'Stories'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -4187,20 +4187,20 @@
         <v/>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1778</v>
+        <v>1844</v>
       </c>
       <c r="E11" s="3">
         <f>IF(ROW()=2,D11,D11-D10)</f>
         <v/>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>1</v>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -5504,7 +5504,7 @@
         <v>118</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>26</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -10648,7 +10648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12222,6 +12222,39 @@
         <v>0</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:11</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -12275,9 +12308,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId47"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId48"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$47</f>
+              <f>'Heure par heure'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$47</f>
+              <f>'Heure par heure'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$47</f>
+              <f>'Heure par heure'!$E$2:$E$48</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$47</f>
+              <f>'Heure par heure'!$F$2:$F$48</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$47</f>
+              <f>'Heure par heure'!$G$2:$G$48</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$47</f>
+              <f>'Heure par heure'!$H$2:$H$48</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$47</f>
+              <f>'Heure par heure'!$I$2:$I$48</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$47</f>
+              <f>'Heure par heure'!$J$2:$J$48</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$47</f>
+              <f>'Heure par heure'!$K$2:$K$48</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$47</f>
+              <f>'Heure par heure'!$L$2:$L$48</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$47</f>
+              <f>'Heure par heure'!$B$2:$B$48</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$47</f>
+              <f>'Heure par heure'!$M$2:$M$48</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$47</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$47</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$47</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$47</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$48</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$47</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$48</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$47</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$48</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$47</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$48</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$47</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$48</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$47</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$48</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$47</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$48</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8275,6 +8275,50 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:00</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="M48" s="3">
+        <f>SUM(C48:L48)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8287,7 +8331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10633,6 +10677,56 @@
       </c>
       <c r="L47" s="3">
         <f>SUM(B47:K47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <f>'Heure par heure'!A48</f>
+        <v/>
+      </c>
+      <c r="B48" s="3">
+        <f>IF('Heure par heure'!C48="","",'Heure par heure'!C48-N('Heure par heure'!C47))</f>
+        <v/>
+      </c>
+      <c r="C48" s="3">
+        <f>IF('Heure par heure'!D48="","",'Heure par heure'!D48-N('Heure par heure'!D47))</f>
+        <v/>
+      </c>
+      <c r="D48" s="3">
+        <f>IF('Heure par heure'!E48="","",'Heure par heure'!E48-N('Heure par heure'!E47))</f>
+        <v/>
+      </c>
+      <c r="E48" s="3">
+        <f>IF('Heure par heure'!F48="","",'Heure par heure'!F48-N('Heure par heure'!F47))</f>
+        <v/>
+      </c>
+      <c r="F48" s="3">
+        <f>IF('Heure par heure'!G48="","",'Heure par heure'!G48-N('Heure par heure'!G47))</f>
+        <v/>
+      </c>
+      <c r="G48" s="3">
+        <f>IF('Heure par heure'!H48="","",'Heure par heure'!H48-N('Heure par heure'!H47))</f>
+        <v/>
+      </c>
+      <c r="H48" s="3">
+        <f>IF('Heure par heure'!I48="","",'Heure par heure'!I48-N('Heure par heure'!I47))</f>
+        <v/>
+      </c>
+      <c r="I48" s="3">
+        <f>IF('Heure par heure'!J48="","",'Heure par heure'!J48-N('Heure par heure'!J47))</f>
+        <v/>
+      </c>
+      <c r="J48" s="3">
+        <f>IF('Heure par heure'!K48="","",'Heure par heure'!K48-N('Heure par heure'!K47))</f>
+        <v/>
+      </c>
+      <c r="K48" s="3">
+        <f>IF('Heure par heure'!L48="","",'Heure par heure'!L48-N('Heure par heure'!L47))</f>
+        <v/>
+      </c>
+      <c r="L48" s="3">
+        <f>SUM(B48:K48)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$48</f>
+              <f>'Heure par heure'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$48</f>
+              <f>'Heure par heure'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$48</f>
+              <f>'Heure par heure'!$E$2:$E$49</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$48</f>
+              <f>'Heure par heure'!$F$2:$F$49</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$48</f>
+              <f>'Heure par heure'!$G$2:$G$49</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$48</f>
+              <f>'Heure par heure'!$H$2:$H$49</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$48</f>
+              <f>'Heure par heure'!$I$2:$I$49</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$48</f>
+              <f>'Heure par heure'!$J$2:$J$49</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$48</f>
+              <f>'Heure par heure'!$K$2:$K$49</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$48</f>
+              <f>'Heure par heure'!$L$2:$L$49</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$48</f>
+              <f>'Heure par heure'!$B$2:$B$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$48</f>
+              <f>'Heure par heure'!$M$2:$M$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$48</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$48</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$48</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$48</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$49</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$48</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$49</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$48</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$49</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$48</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$49</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$48</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$49</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$48</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$49</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$48</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$49</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8319,6 +8319,50 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:00</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="M49" s="3">
+        <f>SUM(C49:L49)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8331,7 +8375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10727,6 +10771,56 @@
       </c>
       <c r="L48" s="3">
         <f>SUM(B48:K48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <f>'Heure par heure'!A49</f>
+        <v/>
+      </c>
+      <c r="B49" s="3">
+        <f>IF('Heure par heure'!C49="","",'Heure par heure'!C49-N('Heure par heure'!C48))</f>
+        <v/>
+      </c>
+      <c r="C49" s="3">
+        <f>IF('Heure par heure'!D49="","",'Heure par heure'!D49-N('Heure par heure'!D48))</f>
+        <v/>
+      </c>
+      <c r="D49" s="3">
+        <f>IF('Heure par heure'!E49="","",'Heure par heure'!E49-N('Heure par heure'!E48))</f>
+        <v/>
+      </c>
+      <c r="E49" s="3">
+        <f>IF('Heure par heure'!F49="","",'Heure par heure'!F49-N('Heure par heure'!F48))</f>
+        <v/>
+      </c>
+      <c r="F49" s="3">
+        <f>IF('Heure par heure'!G49="","",'Heure par heure'!G49-N('Heure par heure'!G48))</f>
+        <v/>
+      </c>
+      <c r="G49" s="3">
+        <f>IF('Heure par heure'!H49="","",'Heure par heure'!H49-N('Heure par heure'!H48))</f>
+        <v/>
+      </c>
+      <c r="H49" s="3">
+        <f>IF('Heure par heure'!I49="","",'Heure par heure'!I49-N('Heure par heure'!I48))</f>
+        <v/>
+      </c>
+      <c r="I49" s="3">
+        <f>IF('Heure par heure'!J49="","",'Heure par heure'!J49-N('Heure par heure'!J48))</f>
+        <v/>
+      </c>
+      <c r="J49" s="3">
+        <f>IF('Heure par heure'!K49="","",'Heure par heure'!K49-N('Heure par heure'!K48))</f>
+        <v/>
+      </c>
+      <c r="K49" s="3">
+        <f>IF('Heure par heure'!L49="","",'Heure par heure'!L49-N('Heure par heure'!L48))</f>
+        <v/>
+      </c>
+      <c r="L49" s="3">
+        <f>SUM(B49:K49)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$49</f>
+              <f>'Heure par heure'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$49</f>
+              <f>'Heure par heure'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$49</f>
+              <f>'Heure par heure'!$E$2:$E$50</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$49</f>
+              <f>'Heure par heure'!$F$2:$F$50</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$49</f>
+              <f>'Heure par heure'!$G$2:$G$50</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$49</f>
+              <f>'Heure par heure'!$H$2:$H$50</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$49</f>
+              <f>'Heure par heure'!$I$2:$I$50</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$49</f>
+              <f>'Heure par heure'!$J$2:$J$50</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$49</f>
+              <f>'Heure par heure'!$K$2:$K$50</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$49</f>
+              <f>'Heure par heure'!$L$2:$L$50</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$49</f>
+              <f>'Heure par heure'!$B$2:$B$50</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$49</f>
+              <f>'Heure par heure'!$M$2:$M$50</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$49</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$49</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$49</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$49</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$50</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$49</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$50</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$49</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$50</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$49</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$50</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$49</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$50</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$49</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$50</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$49</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$50</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8363,6 +8363,50 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:00</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="M50" s="3">
+        <f>SUM(C50:L50)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8375,7 +8419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10821,6 +10865,56 @@
       </c>
       <c r="L49" s="3">
         <f>SUM(B49:K49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <f>'Heure par heure'!A50</f>
+        <v/>
+      </c>
+      <c r="B50" s="3">
+        <f>IF('Heure par heure'!C50="","",'Heure par heure'!C50-N('Heure par heure'!C49))</f>
+        <v/>
+      </c>
+      <c r="C50" s="3">
+        <f>IF('Heure par heure'!D50="","",'Heure par heure'!D50-N('Heure par heure'!D49))</f>
+        <v/>
+      </c>
+      <c r="D50" s="3">
+        <f>IF('Heure par heure'!E50="","",'Heure par heure'!E50-N('Heure par heure'!E49))</f>
+        <v/>
+      </c>
+      <c r="E50" s="3">
+        <f>IF('Heure par heure'!F50="","",'Heure par heure'!F50-N('Heure par heure'!F49))</f>
+        <v/>
+      </c>
+      <c r="F50" s="3">
+        <f>IF('Heure par heure'!G50="","",'Heure par heure'!G50-N('Heure par heure'!G49))</f>
+        <v/>
+      </c>
+      <c r="G50" s="3">
+        <f>IF('Heure par heure'!H50="","",'Heure par heure'!H50-N('Heure par heure'!H49))</f>
+        <v/>
+      </c>
+      <c r="H50" s="3">
+        <f>IF('Heure par heure'!I50="","",'Heure par heure'!I50-N('Heure par heure'!I49))</f>
+        <v/>
+      </c>
+      <c r="I50" s="3">
+        <f>IF('Heure par heure'!J50="","",'Heure par heure'!J50-N('Heure par heure'!J49))</f>
+        <v/>
+      </c>
+      <c r="J50" s="3">
+        <f>IF('Heure par heure'!K50="","",'Heure par heure'!K50-N('Heure par heure'!K49))</f>
+        <v/>
+      </c>
+      <c r="K50" s="3">
+        <f>IF('Heure par heure'!L50="","",'Heure par heure'!L50-N('Heure par heure'!L49))</f>
+        <v/>
+      </c>
+      <c r="L50" s="3">
+        <f>SUM(B50:K50)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$50</f>
+              <f>'Heure par heure'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$50</f>
+              <f>'Heure par heure'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$50</f>
+              <f>'Heure par heure'!$E$2:$E$51</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$50</f>
+              <f>'Heure par heure'!$F$2:$F$51</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$50</f>
+              <f>'Heure par heure'!$G$2:$G$51</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$50</f>
+              <f>'Heure par heure'!$H$2:$H$51</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$50</f>
+              <f>'Heure par heure'!$I$2:$I$51</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$50</f>
+              <f>'Heure par heure'!$J$2:$J$51</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$50</f>
+              <f>'Heure par heure'!$K$2:$K$51</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$50</f>
+              <f>'Heure par heure'!$L$2:$L$51</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$50</f>
+              <f>'Heure par heure'!$B$2:$B$51</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$50</f>
+              <f>'Heure par heure'!$M$2:$M$51</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$50</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$50</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$50</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$50</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$51</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$50</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$51</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$50</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$51</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$50</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$51</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$50</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$51</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$50</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$51</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$50</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$51</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8407,6 +8407,50 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:00</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="M51" s="3">
+        <f>SUM(C51:L51)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8419,7 +8463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10915,6 +10959,56 @@
       </c>
       <c r="L50" s="3">
         <f>SUM(B50:K50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <f>'Heure par heure'!A51</f>
+        <v/>
+      </c>
+      <c r="B51" s="3">
+        <f>IF('Heure par heure'!C51="","",'Heure par heure'!C51-N('Heure par heure'!C50))</f>
+        <v/>
+      </c>
+      <c r="C51" s="3">
+        <f>IF('Heure par heure'!D51="","",'Heure par heure'!D51-N('Heure par heure'!D50))</f>
+        <v/>
+      </c>
+      <c r="D51" s="3">
+        <f>IF('Heure par heure'!E51="","",'Heure par heure'!E51-N('Heure par heure'!E50))</f>
+        <v/>
+      </c>
+      <c r="E51" s="3">
+        <f>IF('Heure par heure'!F51="","",'Heure par heure'!F51-N('Heure par heure'!F50))</f>
+        <v/>
+      </c>
+      <c r="F51" s="3">
+        <f>IF('Heure par heure'!G51="","",'Heure par heure'!G51-N('Heure par heure'!G50))</f>
+        <v/>
+      </c>
+      <c r="G51" s="3">
+        <f>IF('Heure par heure'!H51="","",'Heure par heure'!H51-N('Heure par heure'!H50))</f>
+        <v/>
+      </c>
+      <c r="H51" s="3">
+        <f>IF('Heure par heure'!I51="","",'Heure par heure'!I51-N('Heure par heure'!I50))</f>
+        <v/>
+      </c>
+      <c r="I51" s="3">
+        <f>IF('Heure par heure'!J51="","",'Heure par heure'!J51-N('Heure par heure'!J50))</f>
+        <v/>
+      </c>
+      <c r="J51" s="3">
+        <f>IF('Heure par heure'!K51="","",'Heure par heure'!K51-N('Heure par heure'!K50))</f>
+        <v/>
+      </c>
+      <c r="K51" s="3">
+        <f>IF('Heure par heure'!L51="","",'Heure par heure'!L51-N('Heure par heure'!L50))</f>
+        <v/>
+      </c>
+      <c r="L51" s="3">
+        <f>SUM(B51:K51)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$51</f>
+              <f>'Heure par heure'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$51</f>
+              <f>'Heure par heure'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$51</f>
+              <f>'Heure par heure'!$E$2:$E$52</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$51</f>
+              <f>'Heure par heure'!$F$2:$F$52</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$51</f>
+              <f>'Heure par heure'!$G$2:$G$52</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$51</f>
+              <f>'Heure par heure'!$H$2:$H$52</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$51</f>
+              <f>'Heure par heure'!$I$2:$I$52</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$51</f>
+              <f>'Heure par heure'!$J$2:$J$52</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$51</f>
+              <f>'Heure par heure'!$K$2:$K$52</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$51</f>
+              <f>'Heure par heure'!$L$2:$L$52</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$51</f>
+              <f>'Heure par heure'!$B$2:$B$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$51</f>
+              <f>'Heure par heure'!$M$2:$M$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$51</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$51</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$51</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$51</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$52</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$51</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$52</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$51</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$52</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$51</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$52</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$51</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$52</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$51</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$52</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$51</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$52</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8451,6 +8451,50 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 20:00</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="M52" s="3">
+        <f>SUM(C52:L52)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8463,7 +8507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11009,6 +11053,56 @@
       </c>
       <c r="L51" s="3">
         <f>SUM(B51:K51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <f>'Heure par heure'!A52</f>
+        <v/>
+      </c>
+      <c r="B52" s="3">
+        <f>IF('Heure par heure'!C52="","",'Heure par heure'!C52-N('Heure par heure'!C51))</f>
+        <v/>
+      </c>
+      <c r="C52" s="3">
+        <f>IF('Heure par heure'!D52="","",'Heure par heure'!D52-N('Heure par heure'!D51))</f>
+        <v/>
+      </c>
+      <c r="D52" s="3">
+        <f>IF('Heure par heure'!E52="","",'Heure par heure'!E52-N('Heure par heure'!E51))</f>
+        <v/>
+      </c>
+      <c r="E52" s="3">
+        <f>IF('Heure par heure'!F52="","",'Heure par heure'!F52-N('Heure par heure'!F51))</f>
+        <v/>
+      </c>
+      <c r="F52" s="3">
+        <f>IF('Heure par heure'!G52="","",'Heure par heure'!G52-N('Heure par heure'!G51))</f>
+        <v/>
+      </c>
+      <c r="G52" s="3">
+        <f>IF('Heure par heure'!H52="","",'Heure par heure'!H52-N('Heure par heure'!H51))</f>
+        <v/>
+      </c>
+      <c r="H52" s="3">
+        <f>IF('Heure par heure'!I52="","",'Heure par heure'!I52-N('Heure par heure'!I51))</f>
+        <v/>
+      </c>
+      <c r="I52" s="3">
+        <f>IF('Heure par heure'!J52="","",'Heure par heure'!J52-N('Heure par heure'!J51))</f>
+        <v/>
+      </c>
+      <c r="J52" s="3">
+        <f>IF('Heure par heure'!K52="","",'Heure par heure'!K52-N('Heure par heure'!K51))</f>
+        <v/>
+      </c>
+      <c r="K52" s="3">
+        <f>IF('Heure par heure'!L52="","",'Heure par heure'!L52-N('Heure par heure'!L51))</f>
+        <v/>
+      </c>
+      <c r="L52" s="3">
+        <f>SUM(B52:K52)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$52</f>
+              <f>'Heure par heure'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$52</f>
+              <f>'Heure par heure'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$52</f>
+              <f>'Heure par heure'!$E$2:$E$53</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$52</f>
+              <f>'Heure par heure'!$F$2:$F$53</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$52</f>
+              <f>'Heure par heure'!$G$2:$G$53</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$52</f>
+              <f>'Heure par heure'!$H$2:$H$53</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$52</f>
+              <f>'Heure par heure'!$I$2:$I$53</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$52</f>
+              <f>'Heure par heure'!$J$2:$J$53</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$52</f>
+              <f>'Heure par heure'!$K$2:$K$53</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$52</f>
+              <f>'Heure par heure'!$L$2:$L$53</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$52</f>
+              <f>'Heure par heure'!$B$2:$B$53</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$52</f>
+              <f>'Heure par heure'!$M$2:$M$53</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$52</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$52</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$52</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$52</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$53</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$52</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$53</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$52</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$53</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$52</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$53</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$52</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$53</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$52</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$53</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$52</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$53</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8495,6 +8495,50 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:00</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="M53" s="3">
+        <f>SUM(C53:L53)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8507,7 +8551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11103,6 +11147,56 @@
       </c>
       <c r="L52" s="3">
         <f>SUM(B52:K52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <f>'Heure par heure'!A53</f>
+        <v/>
+      </c>
+      <c r="B53" s="3">
+        <f>IF('Heure par heure'!C53="","",'Heure par heure'!C53-N('Heure par heure'!C52))</f>
+        <v/>
+      </c>
+      <c r="C53" s="3">
+        <f>IF('Heure par heure'!D53="","",'Heure par heure'!D53-N('Heure par heure'!D52))</f>
+        <v/>
+      </c>
+      <c r="D53" s="3">
+        <f>IF('Heure par heure'!E53="","",'Heure par heure'!E53-N('Heure par heure'!E52))</f>
+        <v/>
+      </c>
+      <c r="E53" s="3">
+        <f>IF('Heure par heure'!F53="","",'Heure par heure'!F53-N('Heure par heure'!F52))</f>
+        <v/>
+      </c>
+      <c r="F53" s="3">
+        <f>IF('Heure par heure'!G53="","",'Heure par heure'!G53-N('Heure par heure'!G52))</f>
+        <v/>
+      </c>
+      <c r="G53" s="3">
+        <f>IF('Heure par heure'!H53="","",'Heure par heure'!H53-N('Heure par heure'!H52))</f>
+        <v/>
+      </c>
+      <c r="H53" s="3">
+        <f>IF('Heure par heure'!I53="","",'Heure par heure'!I53-N('Heure par heure'!I52))</f>
+        <v/>
+      </c>
+      <c r="I53" s="3">
+        <f>IF('Heure par heure'!J53="","",'Heure par heure'!J53-N('Heure par heure'!J52))</f>
+        <v/>
+      </c>
+      <c r="J53" s="3">
+        <f>IF('Heure par heure'!K53="","",'Heure par heure'!K53-N('Heure par heure'!K52))</f>
+        <v/>
+      </c>
+      <c r="K53" s="3">
+        <f>IF('Heure par heure'!L53="","",'Heure par heure'!L53-N('Heure par heure'!L52))</f>
+        <v/>
+      </c>
+      <c r="L53" s="3">
+        <f>SUM(B53:K53)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$53</f>
+              <f>'Heure par heure'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$53</f>
+              <f>'Heure par heure'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$53</f>
+              <f>'Heure par heure'!$E$2:$E$54</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$53</f>
+              <f>'Heure par heure'!$F$2:$F$54</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$53</f>
+              <f>'Heure par heure'!$G$2:$G$54</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$53</f>
+              <f>'Heure par heure'!$H$2:$H$54</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$53</f>
+              <f>'Heure par heure'!$I$2:$I$54</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$53</f>
+              <f>'Heure par heure'!$J$2:$J$54</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$53</f>
+              <f>'Heure par heure'!$K$2:$K$54</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$53</f>
+              <f>'Heure par heure'!$L$2:$L$54</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$53</f>
+              <f>'Heure par heure'!$B$2:$B$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$53</f>
+              <f>'Heure par heure'!$M$2:$M$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$53</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$53</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$53</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$53</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$54</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$53</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$54</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$53</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$54</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$53</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$54</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$53</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$54</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$53</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$54</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$53</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$54</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8539,6 +8539,50 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:00</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="M54" s="3">
+        <f>SUM(C54:L54)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8551,7 +8595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11197,6 +11241,56 @@
       </c>
       <c r="L53" s="3">
         <f>SUM(B53:K53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <f>'Heure par heure'!A54</f>
+        <v/>
+      </c>
+      <c r="B54" s="3">
+        <f>IF('Heure par heure'!C54="","",'Heure par heure'!C54-N('Heure par heure'!C53))</f>
+        <v/>
+      </c>
+      <c r="C54" s="3">
+        <f>IF('Heure par heure'!D54="","",'Heure par heure'!D54-N('Heure par heure'!D53))</f>
+        <v/>
+      </c>
+      <c r="D54" s="3">
+        <f>IF('Heure par heure'!E54="","",'Heure par heure'!E54-N('Heure par heure'!E53))</f>
+        <v/>
+      </c>
+      <c r="E54" s="3">
+        <f>IF('Heure par heure'!F54="","",'Heure par heure'!F54-N('Heure par heure'!F53))</f>
+        <v/>
+      </c>
+      <c r="F54" s="3">
+        <f>IF('Heure par heure'!G54="","",'Heure par heure'!G54-N('Heure par heure'!G53))</f>
+        <v/>
+      </c>
+      <c r="G54" s="3">
+        <f>IF('Heure par heure'!H54="","",'Heure par heure'!H54-N('Heure par heure'!H53))</f>
+        <v/>
+      </c>
+      <c r="H54" s="3">
+        <f>IF('Heure par heure'!I54="","",'Heure par heure'!I54-N('Heure par heure'!I53))</f>
+        <v/>
+      </c>
+      <c r="I54" s="3">
+        <f>IF('Heure par heure'!J54="","",'Heure par heure'!J54-N('Heure par heure'!J53))</f>
+        <v/>
+      </c>
+      <c r="J54" s="3">
+        <f>IF('Heure par heure'!K54="","",'Heure par heure'!K54-N('Heure par heure'!K53))</f>
+        <v/>
+      </c>
+      <c r="K54" s="3">
+        <f>IF('Heure par heure'!L54="","",'Heure par heure'!L54-N('Heure par heure'!L53))</f>
+        <v/>
+      </c>
+      <c r="L54" s="3">
+        <f>SUM(B54:K54)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$54</f>
+              <f>'Heure par heure'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$54</f>
+              <f>'Heure par heure'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$54</f>
+              <f>'Heure par heure'!$E$2:$E$55</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$54</f>
+              <f>'Heure par heure'!$F$2:$F$55</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$54</f>
+              <f>'Heure par heure'!$G$2:$G$55</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$54</f>
+              <f>'Heure par heure'!$H$2:$H$55</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$54</f>
+              <f>'Heure par heure'!$I$2:$I$55</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$54</f>
+              <f>'Heure par heure'!$J$2:$J$55</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$54</f>
+              <f>'Heure par heure'!$K$2:$K$55</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$54</f>
+              <f>'Heure par heure'!$L$2:$L$55</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$54</f>
+              <f>'Heure par heure'!$B$2:$B$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$54</f>
+              <f>'Heure par heure'!$M$2:$M$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$54</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$54</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$54</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$54</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$55</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$54</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$55</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$54</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$55</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$54</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$55</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$54</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$55</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$54</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$55</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$54</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$55</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8583,6 +8583,50 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:00</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M55" s="3">
+        <f>SUM(C55:L55)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8595,7 +8639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11291,6 +11335,56 @@
       </c>
       <c r="L54" s="3">
         <f>SUM(B54:K54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <f>'Heure par heure'!A55</f>
+        <v/>
+      </c>
+      <c r="B55" s="3">
+        <f>IF('Heure par heure'!C55="","",'Heure par heure'!C55-N('Heure par heure'!C54))</f>
+        <v/>
+      </c>
+      <c r="C55" s="3">
+        <f>IF('Heure par heure'!D55="","",'Heure par heure'!D55-N('Heure par heure'!D54))</f>
+        <v/>
+      </c>
+      <c r="D55" s="3">
+        <f>IF('Heure par heure'!E55="","",'Heure par heure'!E55-N('Heure par heure'!E54))</f>
+        <v/>
+      </c>
+      <c r="E55" s="3">
+        <f>IF('Heure par heure'!F55="","",'Heure par heure'!F55-N('Heure par heure'!F54))</f>
+        <v/>
+      </c>
+      <c r="F55" s="3">
+        <f>IF('Heure par heure'!G55="","",'Heure par heure'!G55-N('Heure par heure'!G54))</f>
+        <v/>
+      </c>
+      <c r="G55" s="3">
+        <f>IF('Heure par heure'!H55="","",'Heure par heure'!H55-N('Heure par heure'!H54))</f>
+        <v/>
+      </c>
+      <c r="H55" s="3">
+        <f>IF('Heure par heure'!I55="","",'Heure par heure'!I55-N('Heure par heure'!I54))</f>
+        <v/>
+      </c>
+      <c r="I55" s="3">
+        <f>IF('Heure par heure'!J55="","",'Heure par heure'!J55-N('Heure par heure'!J54))</f>
+        <v/>
+      </c>
+      <c r="J55" s="3">
+        <f>IF('Heure par heure'!K55="","",'Heure par heure'!K55-N('Heure par heure'!K54))</f>
+        <v/>
+      </c>
+      <c r="K55" s="3">
+        <f>IF('Heure par heure'!L55="","",'Heure par heure'!L55-N('Heure par heure'!L54))</f>
+        <v/>
+      </c>
+      <c r="L55" s="3">
+        <f>SUM(B55:K55)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$55</f>
+              <f>'Heure par heure'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$55</f>
+              <f>'Heure par heure'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$55</f>
+              <f>'Heure par heure'!$E$2:$E$56</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$55</f>
+              <f>'Heure par heure'!$F$2:$F$56</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$55</f>
+              <f>'Heure par heure'!$G$2:$G$56</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$55</f>
+              <f>'Heure par heure'!$H$2:$H$56</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$55</f>
+              <f>'Heure par heure'!$I$2:$I$56</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$55</f>
+              <f>'Heure par heure'!$J$2:$J$56</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$55</f>
+              <f>'Heure par heure'!$K$2:$K$56</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$55</f>
+              <f>'Heure par heure'!$L$2:$L$56</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$55</f>
+              <f>'Heure par heure'!$B$2:$B$56</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$55</f>
+              <f>'Heure par heure'!$M$2:$M$56</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$55</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$55</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$55</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$55</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$56</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$55</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$56</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$55</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$56</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$55</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$56</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$55</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$56</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$55</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$56</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$55</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$56</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8627,6 +8627,50 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 06:00</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M56" s="3">
+        <f>SUM(C56:L56)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8639,7 +8683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11385,6 +11429,56 @@
       </c>
       <c r="L55" s="3">
         <f>SUM(B55:K55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <f>'Heure par heure'!A56</f>
+        <v/>
+      </c>
+      <c r="B56" s="3">
+        <f>IF('Heure par heure'!C56="","",'Heure par heure'!C56-N('Heure par heure'!C55))</f>
+        <v/>
+      </c>
+      <c r="C56" s="3">
+        <f>IF('Heure par heure'!D56="","",'Heure par heure'!D56-N('Heure par heure'!D55))</f>
+        <v/>
+      </c>
+      <c r="D56" s="3">
+        <f>IF('Heure par heure'!E56="","",'Heure par heure'!E56-N('Heure par heure'!E55))</f>
+        <v/>
+      </c>
+      <c r="E56" s="3">
+        <f>IF('Heure par heure'!F56="","",'Heure par heure'!F56-N('Heure par heure'!F55))</f>
+        <v/>
+      </c>
+      <c r="F56" s="3">
+        <f>IF('Heure par heure'!G56="","",'Heure par heure'!G56-N('Heure par heure'!G55))</f>
+        <v/>
+      </c>
+      <c r="G56" s="3">
+        <f>IF('Heure par heure'!H56="","",'Heure par heure'!H56-N('Heure par heure'!H55))</f>
+        <v/>
+      </c>
+      <c r="H56" s="3">
+        <f>IF('Heure par heure'!I56="","",'Heure par heure'!I56-N('Heure par heure'!I55))</f>
+        <v/>
+      </c>
+      <c r="I56" s="3">
+        <f>IF('Heure par heure'!J56="","",'Heure par heure'!J56-N('Heure par heure'!J55))</f>
+        <v/>
+      </c>
+      <c r="J56" s="3">
+        <f>IF('Heure par heure'!K56="","",'Heure par heure'!K56-N('Heure par heure'!K55))</f>
+        <v/>
+      </c>
+      <c r="K56" s="3">
+        <f>IF('Heure par heure'!L56="","",'Heure par heure'!L56-N('Heure par heure'!L55))</f>
+        <v/>
+      </c>
+      <c r="L56" s="3">
+        <f>SUM(B56:K56)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$56</f>
+              <f>'Heure par heure'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$56</f>
+              <f>'Heure par heure'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$56</f>
+              <f>'Heure par heure'!$E$2:$E$57</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$56</f>
+              <f>'Heure par heure'!$F$2:$F$57</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$56</f>
+              <f>'Heure par heure'!$G$2:$G$57</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$56</f>
+              <f>'Heure par heure'!$H$2:$H$57</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$56</f>
+              <f>'Heure par heure'!$I$2:$I$57</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$56</f>
+              <f>'Heure par heure'!$J$2:$J$57</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$56</f>
+              <f>'Heure par heure'!$K$2:$K$57</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$56</f>
+              <f>'Heure par heure'!$L$2:$L$57</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$56</f>
+              <f>'Heure par heure'!$B$2:$B$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$56</f>
+              <f>'Heure par heure'!$M$2:$M$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$56</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$56</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$56</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$56</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$57</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$56</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$57</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$56</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$57</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$56</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$57</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$56</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$57</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$56</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$57</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$56</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$57</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8671,6 +8671,50 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 07:00</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M57" s="3">
+        <f>SUM(C57:L57)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8683,7 +8727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11479,6 +11523,56 @@
       </c>
       <c r="L56" s="3">
         <f>SUM(B56:K56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <f>'Heure par heure'!A57</f>
+        <v/>
+      </c>
+      <c r="B57" s="3">
+        <f>IF('Heure par heure'!C57="","",'Heure par heure'!C57-N('Heure par heure'!C56))</f>
+        <v/>
+      </c>
+      <c r="C57" s="3">
+        <f>IF('Heure par heure'!D57="","",'Heure par heure'!D57-N('Heure par heure'!D56))</f>
+        <v/>
+      </c>
+      <c r="D57" s="3">
+        <f>IF('Heure par heure'!E57="","",'Heure par heure'!E57-N('Heure par heure'!E56))</f>
+        <v/>
+      </c>
+      <c r="E57" s="3">
+        <f>IF('Heure par heure'!F57="","",'Heure par heure'!F57-N('Heure par heure'!F56))</f>
+        <v/>
+      </c>
+      <c r="F57" s="3">
+        <f>IF('Heure par heure'!G57="","",'Heure par heure'!G57-N('Heure par heure'!G56))</f>
+        <v/>
+      </c>
+      <c r="G57" s="3">
+        <f>IF('Heure par heure'!H57="","",'Heure par heure'!H57-N('Heure par heure'!H56))</f>
+        <v/>
+      </c>
+      <c r="H57" s="3">
+        <f>IF('Heure par heure'!I57="","",'Heure par heure'!I57-N('Heure par heure'!I56))</f>
+        <v/>
+      </c>
+      <c r="I57" s="3">
+        <f>IF('Heure par heure'!J57="","",'Heure par heure'!J57-N('Heure par heure'!J56))</f>
+        <v/>
+      </c>
+      <c r="J57" s="3">
+        <f>IF('Heure par heure'!K57="","",'Heure par heure'!K57-N('Heure par heure'!K56))</f>
+        <v/>
+      </c>
+      <c r="K57" s="3">
+        <f>IF('Heure par heure'!L57="","",'Heure par heure'!L57-N('Heure par heure'!L56))</f>
+        <v/>
+      </c>
+      <c r="L57" s="3">
+        <f>SUM(B57:K57)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$57</f>
+              <f>'Heure par heure'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$57</f>
+              <f>'Heure par heure'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$57</f>
+              <f>'Heure par heure'!$E$2:$E$58</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$57</f>
+              <f>'Heure par heure'!$F$2:$F$58</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$57</f>
+              <f>'Heure par heure'!$G$2:$G$58</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$57</f>
+              <f>'Heure par heure'!$H$2:$H$58</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$57</f>
+              <f>'Heure par heure'!$I$2:$I$58</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$57</f>
+              <f>'Heure par heure'!$J$2:$J$58</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$57</f>
+              <f>'Heure par heure'!$K$2:$K$58</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$57</f>
+              <f>'Heure par heure'!$L$2:$L$58</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$57</f>
+              <f>'Heure par heure'!$B$2:$B$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$57</f>
+              <f>'Heure par heure'!$M$2:$M$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$57</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$57</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$57</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$57</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$58</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$57</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$58</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$57</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$58</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$57</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$58</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$57</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$58</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$57</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$58</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$57</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$58</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6350,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8715,6 +8715,50 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:00</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M58" s="3">
+        <f>SUM(C58:L58)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8727,7 +8771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11573,6 +11617,56 @@
       </c>
       <c r="L57" s="3">
         <f>SUM(B57:K57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <f>'Heure par heure'!A58</f>
+        <v/>
+      </c>
+      <c r="B58" s="3">
+        <f>IF('Heure par heure'!C58="","",'Heure par heure'!C58-N('Heure par heure'!C57))</f>
+        <v/>
+      </c>
+      <c r="C58" s="3">
+        <f>IF('Heure par heure'!D58="","",'Heure par heure'!D58-N('Heure par heure'!D57))</f>
+        <v/>
+      </c>
+      <c r="D58" s="3">
+        <f>IF('Heure par heure'!E58="","",'Heure par heure'!E58-N('Heure par heure'!E57))</f>
+        <v/>
+      </c>
+      <c r="E58" s="3">
+        <f>IF('Heure par heure'!F58="","",'Heure par heure'!F58-N('Heure par heure'!F57))</f>
+        <v/>
+      </c>
+      <c r="F58" s="3">
+        <f>IF('Heure par heure'!G58="","",'Heure par heure'!G58-N('Heure par heure'!G57))</f>
+        <v/>
+      </c>
+      <c r="G58" s="3">
+        <f>IF('Heure par heure'!H58="","",'Heure par heure'!H58-N('Heure par heure'!H57))</f>
+        <v/>
+      </c>
+      <c r="H58" s="3">
+        <f>IF('Heure par heure'!I58="","",'Heure par heure'!I58-N('Heure par heure'!I57))</f>
+        <v/>
+      </c>
+      <c r="I58" s="3">
+        <f>IF('Heure par heure'!J58="","",'Heure par heure'!J58-N('Heure par heure'!J57))</f>
+        <v/>
+      </c>
+      <c r="J58" s="3">
+        <f>IF('Heure par heure'!K58="","",'Heure par heure'!K58-N('Heure par heure'!K57))</f>
+        <v/>
+      </c>
+      <c r="K58" s="3">
+        <f>IF('Heure par heure'!L58="","",'Heure par heure'!L58-N('Heure par heure'!L57))</f>
+        <v/>
+      </c>
+      <c r="L58" s="3">
+        <f>SUM(B58:K58)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$11</f>
+              <f>'Jour par jour'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$11</f>
+              <f>'Jour par jour'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1346,12 +1346,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$11</f>
+              <f>'Jour par jour'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$11</f>
+              <f>'Jour par jour'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -1373,12 +1373,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$11</f>
+              <f>'Jour par jour'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$11</f>
+              <f>'Jour par jour'!$L$2:$L$12</f>
             </numRef>
           </val>
         </ser>
@@ -1486,12 +1486,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$11</f>
+              <f>'Jour par jour'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$11</f>
+              <f>'Jour par jour'!$F$2:$F$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1526,12 +1526,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$11</f>
+              <f>'Jour par jour'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$11</f>
+              <f>'Jour par jour'!$H$2:$H$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1628,12 +1628,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$11</f>
+              <f>'Jour par jour'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$11</f>
+              <f>'Jour par jour'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -2121,12 +2121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$11</f>
+              <f>'Évolution par vidéo'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$11</f>
+              <f>'Évolution par vidéo'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -2185,12 +2185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$11</f>
+              <f>'Évolution par vidéo'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -2217,12 +2217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$11</f>
+              <f>'Évolution par vidéo'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -2249,12 +2249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$11</f>
+              <f>'Évolution par vidéo'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -2281,12 +2281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$11</f>
+              <f>'Évolution par vidéo'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -2313,12 +2313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$11</f>
+              <f>'Évolution par vidéo'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -2345,12 +2345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$11</f>
+              <f>'Évolution par vidéo'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -2377,12 +2377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$11</f>
+              <f>'Évolution par vidéo'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -2409,12 +2409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$11</f>
+              <f>'Évolution par vidéo'!$K$2:$K$12</f>
             </numRef>
           </val>
         </ser>
@@ -2441,12 +2441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$11</f>
+              <f>'Évolution par vidéo'!$L$2:$L$12</f>
             </numRef>
           </val>
         </ser>
@@ -2473,12 +2473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$11</f>
+              <f>'Évolution par vidéo'!$M$2:$M$12</f>
             </numRef>
           </val>
         </ser>
@@ -2505,12 +2505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$11</f>
+              <f>'Évolution par vidéo'!$N$2:$N$12</f>
             </numRef>
           </val>
         </ser>
@@ -2537,12 +2537,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$11</f>
+              <f>'Évolution par vidéo'!$O$2:$O$12</f>
             </numRef>
           </val>
         </ser>
@@ -2569,12 +2569,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$11</f>
+              <f>'Évolution par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$11</f>
+              <f>'Évolution par vidéo'!$P$2:$P$12</f>
             </numRef>
           </val>
         </ser>
@@ -2667,12 +2667,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$11</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$11</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -2715,12 +2715,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$11</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -2739,12 +2739,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$11</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -2763,12 +2763,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$11</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -2787,12 +2787,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$11</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -2811,12 +2811,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$11</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -2835,12 +2835,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$11</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -2859,12 +2859,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$11</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -2883,12 +2883,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$11</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$12</f>
             </numRef>
           </val>
         </ser>
@@ -2907,12 +2907,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$11</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$12</f>
             </numRef>
           </val>
         </ser>
@@ -2931,12 +2931,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$11</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$12</f>
             </numRef>
           </val>
         </ser>
@@ -2955,12 +2955,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$11</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$12</f>
             </numRef>
           </val>
         </ser>
@@ -2979,12 +2979,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$11</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$12</f>
             </numRef>
           </val>
         </ser>
@@ -3003,12 +3003,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$11</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$11</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$12</f>
             </numRef>
           </val>
         </ser>
@@ -3221,7 +3221,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3248,7 +3248,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -3683,7 +3683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4212,10 +4212,55 @@
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3">
+        <f>IF(ROW()=2,"",B12-B11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1859</v>
+      </c>
+      <c r="E12" s="3">
+        <f>IF(ROW()=2,D12,D12-D11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4970,10 +5015,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -5028,7 +5073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5507,6 +5552,58 @@
         <v>92</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5519,7 +5616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6335,6 +6432,77 @@
       </c>
       <c r="Q11" s="3">
         <f>SUM(B11:P11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>IF('Évolution par vidéo'!B12="","",'Évolution par vidéo'!B12-N('Évolution par vidéo'!B11))</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>IF('Évolution par vidéo'!C12="","",'Évolution par vidéo'!C12-N('Évolution par vidéo'!C11))</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>IF('Évolution par vidéo'!D12="","",'Évolution par vidéo'!D12-N('Évolution par vidéo'!D11))</f>
+        <v/>
+      </c>
+      <c r="E12" s="3">
+        <f>IF('Évolution par vidéo'!E12="","",'Évolution par vidéo'!E12-N('Évolution par vidéo'!E11))</f>
+        <v/>
+      </c>
+      <c r="F12" s="3">
+        <f>IF('Évolution par vidéo'!F12="","",'Évolution par vidéo'!F12-N('Évolution par vidéo'!F11))</f>
+        <v/>
+      </c>
+      <c r="G12" s="3">
+        <f>IF('Évolution par vidéo'!G12="","",'Évolution par vidéo'!G12-N('Évolution par vidéo'!G11))</f>
+        <v/>
+      </c>
+      <c r="H12" s="3">
+        <f>IF('Évolution par vidéo'!H12="","",'Évolution par vidéo'!H12-N('Évolution par vidéo'!H11))</f>
+        <v/>
+      </c>
+      <c r="I12" s="3">
+        <f>IF('Évolution par vidéo'!I12="","",'Évolution par vidéo'!I12-N('Évolution par vidéo'!I11))</f>
+        <v/>
+      </c>
+      <c r="J12" s="3">
+        <f>IF('Évolution par vidéo'!J12="","",'Évolution par vidéo'!J12-N('Évolution par vidéo'!J11))</f>
+        <v/>
+      </c>
+      <c r="K12" s="3">
+        <f>IF('Évolution par vidéo'!K12="","",'Évolution par vidéo'!K12-N('Évolution par vidéo'!K11))</f>
+        <v/>
+      </c>
+      <c r="L12" s="3">
+        <f>IF('Évolution par vidéo'!L12="","",'Évolution par vidéo'!L12-N('Évolution par vidéo'!L11))</f>
+        <v/>
+      </c>
+      <c r="M12" s="3">
+        <f>IF('Évolution par vidéo'!M12="","",'Évolution par vidéo'!M12-N('Évolution par vidéo'!M11))</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>IF('Évolution par vidéo'!N12="","",'Évolution par vidéo'!N12-N('Évolution par vidéo'!N11))</f>
+        <v/>
+      </c>
+      <c r="O12" s="3">
+        <f>IF('Évolution par vidéo'!O12="","",'Évolution par vidéo'!O12-N('Évolution par vidéo'!O11))</f>
+        <v/>
+      </c>
+      <c r="P12" s="3">
+        <f>IF('Évolution par vidéo'!P12="","",'Évolution par vidéo'!P12-N('Évolution par vidéo'!P11))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="3">
+        <f>SUM(B12:P12)</f>
         <v/>
       </c>
     </row>
@@ -13268,7 +13436,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$58</f>
+              <f>'Heure par heure'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$58</f>
+              <f>'Heure par heure'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$58</f>
+              <f>'Heure par heure'!$E$2:$E$59</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$58</f>
+              <f>'Heure par heure'!$F$2:$F$59</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$58</f>
+              <f>'Heure par heure'!$G$2:$G$59</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$58</f>
+              <f>'Heure par heure'!$H$2:$H$59</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$58</f>
+              <f>'Heure par heure'!$I$2:$I$59</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$58</f>
+              <f>'Heure par heure'!$J$2:$J$59</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$58</f>
+              <f>'Heure par heure'!$K$2:$K$59</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$58</f>
+              <f>'Heure par heure'!$L$2:$L$59</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$58</f>
+              <f>'Heure par heure'!$B$2:$B$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$58</f>
+              <f>'Heure par heure'!$M$2:$M$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$58</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$58</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$58</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$58</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$59</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$58</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$59</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$58</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$59</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$58</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$59</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$58</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$59</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$58</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$59</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$58</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$59</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8927,6 +8927,50 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:00</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M59" s="3">
+        <f>SUM(C59:L59)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8939,7 +8983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11835,6 +11879,56 @@
       </c>
       <c r="L58" s="3">
         <f>SUM(B58:K58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <f>'Heure par heure'!A59</f>
+        <v/>
+      </c>
+      <c r="B59" s="3">
+        <f>IF('Heure par heure'!C59="","",'Heure par heure'!C59-N('Heure par heure'!C58))</f>
+        <v/>
+      </c>
+      <c r="C59" s="3">
+        <f>IF('Heure par heure'!D59="","",'Heure par heure'!D59-N('Heure par heure'!D58))</f>
+        <v/>
+      </c>
+      <c r="D59" s="3">
+        <f>IF('Heure par heure'!E59="","",'Heure par heure'!E59-N('Heure par heure'!E58))</f>
+        <v/>
+      </c>
+      <c r="E59" s="3">
+        <f>IF('Heure par heure'!F59="","",'Heure par heure'!F59-N('Heure par heure'!F58))</f>
+        <v/>
+      </c>
+      <c r="F59" s="3">
+        <f>IF('Heure par heure'!G59="","",'Heure par heure'!G59-N('Heure par heure'!G58))</f>
+        <v/>
+      </c>
+      <c r="G59" s="3">
+        <f>IF('Heure par heure'!H59="","",'Heure par heure'!H59-N('Heure par heure'!H58))</f>
+        <v/>
+      </c>
+      <c r="H59" s="3">
+        <f>IF('Heure par heure'!I59="","",'Heure par heure'!I59-N('Heure par heure'!I58))</f>
+        <v/>
+      </c>
+      <c r="I59" s="3">
+        <f>IF('Heure par heure'!J59="","",'Heure par heure'!J59-N('Heure par heure'!J58))</f>
+        <v/>
+      </c>
+      <c r="J59" s="3">
+        <f>IF('Heure par heure'!K59="","",'Heure par heure'!K59-N('Heure par heure'!K58))</f>
+        <v/>
+      </c>
+      <c r="K59" s="3">
+        <f>IF('Heure par heure'!L59="","",'Heure par heure'!L59-N('Heure par heure'!L58))</f>
+        <v/>
+      </c>
+      <c r="L59" s="3">
+        <f>SUM(B59:K59)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$59</f>
+              <f>'Heure par heure'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$59</f>
+              <f>'Heure par heure'!$D$2:$D$60</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$59</f>
+              <f>'Heure par heure'!$E$2:$E$60</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$59</f>
+              <f>'Heure par heure'!$F$2:$F$60</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$59</f>
+              <f>'Heure par heure'!$G$2:$G$60</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$59</f>
+              <f>'Heure par heure'!$H$2:$H$60</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$59</f>
+              <f>'Heure par heure'!$I$2:$I$60</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$59</f>
+              <f>'Heure par heure'!$J$2:$J$60</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$59</f>
+              <f>'Heure par heure'!$K$2:$K$60</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$59</f>
+              <f>'Heure par heure'!$L$2:$L$60</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$59</f>
+              <f>'Heure par heure'!$B$2:$B$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$59</f>
+              <f>'Heure par heure'!$M$2:$M$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$59</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$59</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$59</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$60</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$59</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$60</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$59</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$60</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$59</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$60</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$59</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$60</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$59</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$60</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$59</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$60</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$59</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$60</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8971,6 +8971,50 @@
         <v/>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:00</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M60" s="3">
+        <f>SUM(C60:L60)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8983,7 +9027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11929,6 +11973,56 @@
       </c>
       <c r="L59" s="3">
         <f>SUM(B59:K59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <f>'Heure par heure'!A60</f>
+        <v/>
+      </c>
+      <c r="B60" s="3">
+        <f>IF('Heure par heure'!C60="","",'Heure par heure'!C60-N('Heure par heure'!C59))</f>
+        <v/>
+      </c>
+      <c r="C60" s="3">
+        <f>IF('Heure par heure'!D60="","",'Heure par heure'!D60-N('Heure par heure'!D59))</f>
+        <v/>
+      </c>
+      <c r="D60" s="3">
+        <f>IF('Heure par heure'!E60="","",'Heure par heure'!E60-N('Heure par heure'!E59))</f>
+        <v/>
+      </c>
+      <c r="E60" s="3">
+        <f>IF('Heure par heure'!F60="","",'Heure par heure'!F60-N('Heure par heure'!F59))</f>
+        <v/>
+      </c>
+      <c r="F60" s="3">
+        <f>IF('Heure par heure'!G60="","",'Heure par heure'!G60-N('Heure par heure'!G59))</f>
+        <v/>
+      </c>
+      <c r="G60" s="3">
+        <f>IF('Heure par heure'!H60="","",'Heure par heure'!H60-N('Heure par heure'!H59))</f>
+        <v/>
+      </c>
+      <c r="H60" s="3">
+        <f>IF('Heure par heure'!I60="","",'Heure par heure'!I60-N('Heure par heure'!I59))</f>
+        <v/>
+      </c>
+      <c r="I60" s="3">
+        <f>IF('Heure par heure'!J60="","",'Heure par heure'!J60-N('Heure par heure'!J59))</f>
+        <v/>
+      </c>
+      <c r="J60" s="3">
+        <f>IF('Heure par heure'!K60="","",'Heure par heure'!K60-N('Heure par heure'!K59))</f>
+        <v/>
+      </c>
+      <c r="K60" s="3">
+        <f>IF('Heure par heure'!L60="","",'Heure par heure'!L60-N('Heure par heure'!L59))</f>
+        <v/>
+      </c>
+      <c r="L60" s="3">
+        <f>SUM(B60:K60)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$60</f>
+              <f>'Heure par heure'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$60</f>
+              <f>'Heure par heure'!$D$2:$D$61</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$60</f>
+              <f>'Heure par heure'!$E$2:$E$61</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$60</f>
+              <f>'Heure par heure'!$F$2:$F$61</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$60</f>
+              <f>'Heure par heure'!$G$2:$G$61</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$60</f>
+              <f>'Heure par heure'!$H$2:$H$61</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$60</f>
+              <f>'Heure par heure'!$I$2:$I$61</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$60</f>
+              <f>'Heure par heure'!$J$2:$J$61</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$60</f>
+              <f>'Heure par heure'!$K$2:$K$61</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$60</f>
+              <f>'Heure par heure'!$L$2:$L$61</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$60</f>
+              <f>'Heure par heure'!$B$2:$B$61</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$60</f>
+              <f>'Heure par heure'!$M$2:$M$61</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$60</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$60</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$60</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$61</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$60</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$61</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$60</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$61</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$60</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$61</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$60</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$61</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$60</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$61</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$60</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$61</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$60</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$61</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9015,6 +9015,50 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M61" s="3">
+        <f>SUM(C61:L61)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9027,7 +9071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12023,6 +12067,56 @@
       </c>
       <c r="L60" s="3">
         <f>SUM(B60:K60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <f>'Heure par heure'!A61</f>
+        <v/>
+      </c>
+      <c r="B61" s="3">
+        <f>IF('Heure par heure'!C61="","",'Heure par heure'!C61-N('Heure par heure'!C60))</f>
+        <v/>
+      </c>
+      <c r="C61" s="3">
+        <f>IF('Heure par heure'!D61="","",'Heure par heure'!D61-N('Heure par heure'!D60))</f>
+        <v/>
+      </c>
+      <c r="D61" s="3">
+        <f>IF('Heure par heure'!E61="","",'Heure par heure'!E61-N('Heure par heure'!E60))</f>
+        <v/>
+      </c>
+      <c r="E61" s="3">
+        <f>IF('Heure par heure'!F61="","",'Heure par heure'!F61-N('Heure par heure'!F60))</f>
+        <v/>
+      </c>
+      <c r="F61" s="3">
+        <f>IF('Heure par heure'!G61="","",'Heure par heure'!G61-N('Heure par heure'!G60))</f>
+        <v/>
+      </c>
+      <c r="G61" s="3">
+        <f>IF('Heure par heure'!H61="","",'Heure par heure'!H61-N('Heure par heure'!H60))</f>
+        <v/>
+      </c>
+      <c r="H61" s="3">
+        <f>IF('Heure par heure'!I61="","",'Heure par heure'!I61-N('Heure par heure'!I60))</f>
+        <v/>
+      </c>
+      <c r="I61" s="3">
+        <f>IF('Heure par heure'!J61="","",'Heure par heure'!J61-N('Heure par heure'!J60))</f>
+        <v/>
+      </c>
+      <c r="J61" s="3">
+        <f>IF('Heure par heure'!K61="","",'Heure par heure'!K61-N('Heure par heure'!K60))</f>
+        <v/>
+      </c>
+      <c r="K61" s="3">
+        <f>IF('Heure par heure'!L61="","",'Heure par heure'!L61-N('Heure par heure'!L60))</f>
+        <v/>
+      </c>
+      <c r="L61" s="3">
+        <f>SUM(B61:K61)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$61</f>
+              <f>'Heure par heure'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$61</f>
+              <f>'Heure par heure'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$61</f>
+              <f>'Heure par heure'!$E$2:$E$62</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$61</f>
+              <f>'Heure par heure'!$F$2:$F$62</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$61</f>
+              <f>'Heure par heure'!$G$2:$G$62</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$61</f>
+              <f>'Heure par heure'!$H$2:$H$62</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$61</f>
+              <f>'Heure par heure'!$I$2:$I$62</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$61</f>
+              <f>'Heure par heure'!$J$2:$J$62</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$61</f>
+              <f>'Heure par heure'!$K$2:$K$62</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$61</f>
+              <f>'Heure par heure'!$L$2:$L$62</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$61</f>
+              <f>'Heure par heure'!$B$2:$B$62</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$61</f>
+              <f>'Heure par heure'!$M$2:$M$62</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$61</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$61</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$61</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$61</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$62</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$61</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$62</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$61</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$62</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$61</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$62</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$61</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$62</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$61</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$62</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$61</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$62</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9059,6 +9059,50 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:00</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M62" s="3">
+        <f>SUM(C62:L62)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9071,7 +9115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12117,6 +12161,56 @@
       </c>
       <c r="L61" s="3">
         <f>SUM(B61:K61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <f>'Heure par heure'!A62</f>
+        <v/>
+      </c>
+      <c r="B62" s="3">
+        <f>IF('Heure par heure'!C62="","",'Heure par heure'!C62-N('Heure par heure'!C61))</f>
+        <v/>
+      </c>
+      <c r="C62" s="3">
+        <f>IF('Heure par heure'!D62="","",'Heure par heure'!D62-N('Heure par heure'!D61))</f>
+        <v/>
+      </c>
+      <c r="D62" s="3">
+        <f>IF('Heure par heure'!E62="","",'Heure par heure'!E62-N('Heure par heure'!E61))</f>
+        <v/>
+      </c>
+      <c r="E62" s="3">
+        <f>IF('Heure par heure'!F62="","",'Heure par heure'!F62-N('Heure par heure'!F61))</f>
+        <v/>
+      </c>
+      <c r="F62" s="3">
+        <f>IF('Heure par heure'!G62="","",'Heure par heure'!G62-N('Heure par heure'!G61))</f>
+        <v/>
+      </c>
+      <c r="G62" s="3">
+        <f>IF('Heure par heure'!H62="","",'Heure par heure'!H62-N('Heure par heure'!H61))</f>
+        <v/>
+      </c>
+      <c r="H62" s="3">
+        <f>IF('Heure par heure'!I62="","",'Heure par heure'!I62-N('Heure par heure'!I61))</f>
+        <v/>
+      </c>
+      <c r="I62" s="3">
+        <f>IF('Heure par heure'!J62="","",'Heure par heure'!J62-N('Heure par heure'!J61))</f>
+        <v/>
+      </c>
+      <c r="J62" s="3">
+        <f>IF('Heure par heure'!K62="","",'Heure par heure'!K62-N('Heure par heure'!K61))</f>
+        <v/>
+      </c>
+      <c r="K62" s="3">
+        <f>IF('Heure par heure'!L62="","",'Heure par heure'!L62-N('Heure par heure'!L61))</f>
+        <v/>
+      </c>
+      <c r="L62" s="3">
+        <f>SUM(B62:K62)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$62</f>
+              <f>'Heure par heure'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$62</f>
+              <f>'Heure par heure'!$D$2:$D$63</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$62</f>
+              <f>'Heure par heure'!$E$2:$E$63</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$62</f>
+              <f>'Heure par heure'!$F$2:$F$63</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$62</f>
+              <f>'Heure par heure'!$G$2:$G$63</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$62</f>
+              <f>'Heure par heure'!$H$2:$H$63</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$62</f>
+              <f>'Heure par heure'!$I$2:$I$63</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$62</f>
+              <f>'Heure par heure'!$J$2:$J$63</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$62</f>
+              <f>'Heure par heure'!$K$2:$K$63</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$62</f>
+              <f>'Heure par heure'!$L$2:$L$63</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$62</f>
+              <f>'Heure par heure'!$B$2:$B$63</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$62</f>
+              <f>'Heure par heure'!$M$2:$M$63</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$62</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$62</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$62</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$63</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$62</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$63</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$62</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$63</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$62</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$63</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$62</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$63</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$62</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$63</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$62</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$63</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$62</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$63</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9103,6 +9103,50 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:00</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M63" s="3">
+        <f>SUM(C63:L63)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9115,7 +9159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12211,6 +12255,56 @@
       </c>
       <c r="L62" s="3">
         <f>SUM(B62:K62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <f>'Heure par heure'!A63</f>
+        <v/>
+      </c>
+      <c r="B63" s="3">
+        <f>IF('Heure par heure'!C63="","",'Heure par heure'!C63-N('Heure par heure'!C62))</f>
+        <v/>
+      </c>
+      <c r="C63" s="3">
+        <f>IF('Heure par heure'!D63="","",'Heure par heure'!D63-N('Heure par heure'!D62))</f>
+        <v/>
+      </c>
+      <c r="D63" s="3">
+        <f>IF('Heure par heure'!E63="","",'Heure par heure'!E63-N('Heure par heure'!E62))</f>
+        <v/>
+      </c>
+      <c r="E63" s="3">
+        <f>IF('Heure par heure'!F63="","",'Heure par heure'!F63-N('Heure par heure'!F62))</f>
+        <v/>
+      </c>
+      <c r="F63" s="3">
+        <f>IF('Heure par heure'!G63="","",'Heure par heure'!G63-N('Heure par heure'!G62))</f>
+        <v/>
+      </c>
+      <c r="G63" s="3">
+        <f>IF('Heure par heure'!H63="","",'Heure par heure'!H63-N('Heure par heure'!H62))</f>
+        <v/>
+      </c>
+      <c r="H63" s="3">
+        <f>IF('Heure par heure'!I63="","",'Heure par heure'!I63-N('Heure par heure'!I62))</f>
+        <v/>
+      </c>
+      <c r="I63" s="3">
+        <f>IF('Heure par heure'!J63="","",'Heure par heure'!J63-N('Heure par heure'!J62))</f>
+        <v/>
+      </c>
+      <c r="J63" s="3">
+        <f>IF('Heure par heure'!K63="","",'Heure par heure'!K63-N('Heure par heure'!K62))</f>
+        <v/>
+      </c>
+      <c r="K63" s="3">
+        <f>IF('Heure par heure'!L63="","",'Heure par heure'!L63-N('Heure par heure'!L62))</f>
+        <v/>
+      </c>
+      <c r="L63" s="3">
+        <f>SUM(B63:K63)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$63</f>
+              <f>'Heure par heure'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$63</f>
+              <f>'Heure par heure'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$63</f>
+              <f>'Heure par heure'!$E$2:$E$64</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$63</f>
+              <f>'Heure par heure'!$F$2:$F$64</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$63</f>
+              <f>'Heure par heure'!$G$2:$G$64</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$63</f>
+              <f>'Heure par heure'!$H$2:$H$64</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$63</f>
+              <f>'Heure par heure'!$I$2:$I$64</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$63</f>
+              <f>'Heure par heure'!$J$2:$J$64</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$63</f>
+              <f>'Heure par heure'!$K$2:$K$64</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$63</f>
+              <f>'Heure par heure'!$L$2:$L$64</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$63</f>
+              <f>'Heure par heure'!$B$2:$B$64</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$63</f>
+              <f>'Heure par heure'!$M$2:$M$64</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$63</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$63</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$63</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$63</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$64</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$63</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$64</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$63</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$64</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$63</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$64</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$63</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$64</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$63</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$64</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$63</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$64</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9147,6 +9147,50 @@
         <v/>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:00</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M64" s="3">
+        <f>SUM(C64:L64)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9159,7 +9203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12305,6 +12349,56 @@
       </c>
       <c r="L63" s="3">
         <f>SUM(B63:K63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <f>'Heure par heure'!A64</f>
+        <v/>
+      </c>
+      <c r="B64" s="3">
+        <f>IF('Heure par heure'!C64="","",'Heure par heure'!C64-N('Heure par heure'!C63))</f>
+        <v/>
+      </c>
+      <c r="C64" s="3">
+        <f>IF('Heure par heure'!D64="","",'Heure par heure'!D64-N('Heure par heure'!D63))</f>
+        <v/>
+      </c>
+      <c r="D64" s="3">
+        <f>IF('Heure par heure'!E64="","",'Heure par heure'!E64-N('Heure par heure'!E63))</f>
+        <v/>
+      </c>
+      <c r="E64" s="3">
+        <f>IF('Heure par heure'!F64="","",'Heure par heure'!F64-N('Heure par heure'!F63))</f>
+        <v/>
+      </c>
+      <c r="F64" s="3">
+        <f>IF('Heure par heure'!G64="","",'Heure par heure'!G64-N('Heure par heure'!G63))</f>
+        <v/>
+      </c>
+      <c r="G64" s="3">
+        <f>IF('Heure par heure'!H64="","",'Heure par heure'!H64-N('Heure par heure'!H63))</f>
+        <v/>
+      </c>
+      <c r="H64" s="3">
+        <f>IF('Heure par heure'!I64="","",'Heure par heure'!I64-N('Heure par heure'!I63))</f>
+        <v/>
+      </c>
+      <c r="I64" s="3">
+        <f>IF('Heure par heure'!J64="","",'Heure par heure'!J64-N('Heure par heure'!J63))</f>
+        <v/>
+      </c>
+      <c r="J64" s="3">
+        <f>IF('Heure par heure'!K64="","",'Heure par heure'!K64-N('Heure par heure'!K63))</f>
+        <v/>
+      </c>
+      <c r="K64" s="3">
+        <f>IF('Heure par heure'!L64="","",'Heure par heure'!L64-N('Heure par heure'!L63))</f>
+        <v/>
+      </c>
+      <c r="L64" s="3">
+        <f>SUM(B64:K64)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$64</f>
+              <f>'Heure par heure'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$64</f>
+              <f>'Heure par heure'!$D$2:$D$65</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$64</f>
+              <f>'Heure par heure'!$E$2:$E$65</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$64</f>
+              <f>'Heure par heure'!$F$2:$F$65</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$64</f>
+              <f>'Heure par heure'!$G$2:$G$65</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$64</f>
+              <f>'Heure par heure'!$H$2:$H$65</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$64</f>
+              <f>'Heure par heure'!$I$2:$I$65</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$64</f>
+              <f>'Heure par heure'!$J$2:$J$65</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$64</f>
+              <f>'Heure par heure'!$K$2:$K$65</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$64</f>
+              <f>'Heure par heure'!$L$2:$L$65</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$64</f>
+              <f>'Heure par heure'!$B$2:$B$65</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$64</f>
+              <f>'Heure par heure'!$M$2:$M$65</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$64</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$64</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$64</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$65</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$64</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$65</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$64</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$65</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$64</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$65</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$64</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$65</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$64</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$65</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$64</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$65</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$64</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$65</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9191,6 +9191,50 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M65" s="3">
+        <f>SUM(C65:L65)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9203,7 +9247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12399,6 +12443,56 @@
       </c>
       <c r="L64" s="3">
         <f>SUM(B64:K64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <f>'Heure par heure'!A65</f>
+        <v/>
+      </c>
+      <c r="B65" s="3">
+        <f>IF('Heure par heure'!C65="","",'Heure par heure'!C65-N('Heure par heure'!C64))</f>
+        <v/>
+      </c>
+      <c r="C65" s="3">
+        <f>IF('Heure par heure'!D65="","",'Heure par heure'!D65-N('Heure par heure'!D64))</f>
+        <v/>
+      </c>
+      <c r="D65" s="3">
+        <f>IF('Heure par heure'!E65="","",'Heure par heure'!E65-N('Heure par heure'!E64))</f>
+        <v/>
+      </c>
+      <c r="E65" s="3">
+        <f>IF('Heure par heure'!F65="","",'Heure par heure'!F65-N('Heure par heure'!F64))</f>
+        <v/>
+      </c>
+      <c r="F65" s="3">
+        <f>IF('Heure par heure'!G65="","",'Heure par heure'!G65-N('Heure par heure'!G64))</f>
+        <v/>
+      </c>
+      <c r="G65" s="3">
+        <f>IF('Heure par heure'!H65="","",'Heure par heure'!H65-N('Heure par heure'!H64))</f>
+        <v/>
+      </c>
+      <c r="H65" s="3">
+        <f>IF('Heure par heure'!I65="","",'Heure par heure'!I65-N('Heure par heure'!I64))</f>
+        <v/>
+      </c>
+      <c r="I65" s="3">
+        <f>IF('Heure par heure'!J65="","",'Heure par heure'!J65-N('Heure par heure'!J64))</f>
+        <v/>
+      </c>
+      <c r="J65" s="3">
+        <f>IF('Heure par heure'!K65="","",'Heure par heure'!K65-N('Heure par heure'!K64))</f>
+        <v/>
+      </c>
+      <c r="K65" s="3">
+        <f>IF('Heure par heure'!L65="","",'Heure par heure'!L65-N('Heure par heure'!L64))</f>
+        <v/>
+      </c>
+      <c r="L65" s="3">
+        <f>SUM(B65:K65)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$65</f>
+              <f>'Heure par heure'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$65</f>
+              <f>'Heure par heure'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$65</f>
+              <f>'Heure par heure'!$E$2:$E$66</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$65</f>
+              <f>'Heure par heure'!$F$2:$F$66</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$65</f>
+              <f>'Heure par heure'!$G$2:$G$66</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$65</f>
+              <f>'Heure par heure'!$H$2:$H$66</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$65</f>
+              <f>'Heure par heure'!$I$2:$I$66</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$65</f>
+              <f>'Heure par heure'!$J$2:$J$66</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$65</f>
+              <f>'Heure par heure'!$K$2:$K$66</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$65</f>
+              <f>'Heure par heure'!$L$2:$L$66</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$65</f>
+              <f>'Heure par heure'!$B$2:$B$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$65</f>
+              <f>'Heure par heure'!$M$2:$M$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$65</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$65</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$65</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$65</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$66</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$65</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$66</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$65</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$66</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$65</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$66</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$65</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$66</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$65</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$66</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$65</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$66</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9235,6 +9235,50 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:00</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M66" s="3">
+        <f>SUM(C66:L66)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9247,7 +9291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12493,6 +12537,56 @@
       </c>
       <c r="L65" s="3">
         <f>SUM(B65:K65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <f>'Heure par heure'!A66</f>
+        <v/>
+      </c>
+      <c r="B66" s="3">
+        <f>IF('Heure par heure'!C66="","",'Heure par heure'!C66-N('Heure par heure'!C65))</f>
+        <v/>
+      </c>
+      <c r="C66" s="3">
+        <f>IF('Heure par heure'!D66="","",'Heure par heure'!D66-N('Heure par heure'!D65))</f>
+        <v/>
+      </c>
+      <c r="D66" s="3">
+        <f>IF('Heure par heure'!E66="","",'Heure par heure'!E66-N('Heure par heure'!E65))</f>
+        <v/>
+      </c>
+      <c r="E66" s="3">
+        <f>IF('Heure par heure'!F66="","",'Heure par heure'!F66-N('Heure par heure'!F65))</f>
+        <v/>
+      </c>
+      <c r="F66" s="3">
+        <f>IF('Heure par heure'!G66="","",'Heure par heure'!G66-N('Heure par heure'!G65))</f>
+        <v/>
+      </c>
+      <c r="G66" s="3">
+        <f>IF('Heure par heure'!H66="","",'Heure par heure'!H66-N('Heure par heure'!H65))</f>
+        <v/>
+      </c>
+      <c r="H66" s="3">
+        <f>IF('Heure par heure'!I66="","",'Heure par heure'!I66-N('Heure par heure'!I65))</f>
+        <v/>
+      </c>
+      <c r="I66" s="3">
+        <f>IF('Heure par heure'!J66="","",'Heure par heure'!J66-N('Heure par heure'!J65))</f>
+        <v/>
+      </c>
+      <c r="J66" s="3">
+        <f>IF('Heure par heure'!K66="","",'Heure par heure'!K66-N('Heure par heure'!K65))</f>
+        <v/>
+      </c>
+      <c r="K66" s="3">
+        <f>IF('Heure par heure'!L66="","",'Heure par heure'!L66-N('Heure par heure'!L65))</f>
+        <v/>
+      </c>
+      <c r="L66" s="3">
+        <f>SUM(B66:K66)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$66</f>
+              <f>'Heure par heure'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$66</f>
+              <f>'Heure par heure'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$66</f>
+              <f>'Heure par heure'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$66</f>
+              <f>'Heure par heure'!$F$2:$F$67</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$66</f>
+              <f>'Heure par heure'!$G$2:$G$67</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$66</f>
+              <f>'Heure par heure'!$H$2:$H$67</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$66</f>
+              <f>'Heure par heure'!$I$2:$I$67</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$66</f>
+              <f>'Heure par heure'!$J$2:$J$67</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$66</f>
+              <f>'Heure par heure'!$K$2:$K$67</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$66</f>
+              <f>'Heure par heure'!$L$2:$L$67</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$66</f>
+              <f>'Heure par heure'!$B$2:$B$67</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$66</f>
+              <f>'Heure par heure'!$M$2:$M$67</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$66</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$66</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$66</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$66</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$66</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$67</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$66</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$67</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$66</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$67</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$66</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$67</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$66</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$67</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$66</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$67</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9279,6 +9279,50 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:00</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M67" s="3">
+        <f>SUM(C67:L67)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9291,7 +9335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12587,6 +12631,56 @@
       </c>
       <c r="L66" s="3">
         <f>SUM(B66:K66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <f>'Heure par heure'!A67</f>
+        <v/>
+      </c>
+      <c r="B67" s="3">
+        <f>IF('Heure par heure'!C67="","",'Heure par heure'!C67-N('Heure par heure'!C66))</f>
+        <v/>
+      </c>
+      <c r="C67" s="3">
+        <f>IF('Heure par heure'!D67="","",'Heure par heure'!D67-N('Heure par heure'!D66))</f>
+        <v/>
+      </c>
+      <c r="D67" s="3">
+        <f>IF('Heure par heure'!E67="","",'Heure par heure'!E67-N('Heure par heure'!E66))</f>
+        <v/>
+      </c>
+      <c r="E67" s="3">
+        <f>IF('Heure par heure'!F67="","",'Heure par heure'!F67-N('Heure par heure'!F66))</f>
+        <v/>
+      </c>
+      <c r="F67" s="3">
+        <f>IF('Heure par heure'!G67="","",'Heure par heure'!G67-N('Heure par heure'!G66))</f>
+        <v/>
+      </c>
+      <c r="G67" s="3">
+        <f>IF('Heure par heure'!H67="","",'Heure par heure'!H67-N('Heure par heure'!H66))</f>
+        <v/>
+      </c>
+      <c r="H67" s="3">
+        <f>IF('Heure par heure'!I67="","",'Heure par heure'!I67-N('Heure par heure'!I66))</f>
+        <v/>
+      </c>
+      <c r="I67" s="3">
+        <f>IF('Heure par heure'!J67="","",'Heure par heure'!J67-N('Heure par heure'!J66))</f>
+        <v/>
+      </c>
+      <c r="J67" s="3">
+        <f>IF('Heure par heure'!K67="","",'Heure par heure'!K67-N('Heure par heure'!K66))</f>
+        <v/>
+      </c>
+      <c r="K67" s="3">
+        <f>IF('Heure par heure'!L67="","",'Heure par heure'!L67-N('Heure par heure'!L66))</f>
+        <v/>
+      </c>
+      <c r="L67" s="3">
+        <f>SUM(B67:K67)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$67</f>
+              <f>'Heure par heure'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$67</f>
+              <f>'Heure par heure'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$67</f>
+              <f>'Heure par heure'!$E$2:$E$68</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$67</f>
+              <f>'Heure par heure'!$F$2:$F$68</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$67</f>
+              <f>'Heure par heure'!$G$2:$G$68</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$67</f>
+              <f>'Heure par heure'!$H$2:$H$68</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$67</f>
+              <f>'Heure par heure'!$I$2:$I$68</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$67</f>
+              <f>'Heure par heure'!$J$2:$J$68</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$67</f>
+              <f>'Heure par heure'!$K$2:$K$68</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$67</f>
+              <f>'Heure par heure'!$L$2:$L$68</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$67</f>
+              <f>'Heure par heure'!$B$2:$B$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$67</f>
+              <f>'Heure par heure'!$M$2:$M$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$67</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$67</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$67</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$67</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$68</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$67</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$68</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$67</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$68</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$67</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$68</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$67</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$68</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$67</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$68</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$67</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$68</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9323,6 +9323,50 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:00</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M68" s="3">
+        <f>SUM(C68:L68)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9335,7 +9379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12681,6 +12725,56 @@
       </c>
       <c r="L67" s="3">
         <f>SUM(B67:K67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <f>'Heure par heure'!A68</f>
+        <v/>
+      </c>
+      <c r="B68" s="3">
+        <f>IF('Heure par heure'!C68="","",'Heure par heure'!C68-N('Heure par heure'!C67))</f>
+        <v/>
+      </c>
+      <c r="C68" s="3">
+        <f>IF('Heure par heure'!D68="","",'Heure par heure'!D68-N('Heure par heure'!D67))</f>
+        <v/>
+      </c>
+      <c r="D68" s="3">
+        <f>IF('Heure par heure'!E68="","",'Heure par heure'!E68-N('Heure par heure'!E67))</f>
+        <v/>
+      </c>
+      <c r="E68" s="3">
+        <f>IF('Heure par heure'!F68="","",'Heure par heure'!F68-N('Heure par heure'!F67))</f>
+        <v/>
+      </c>
+      <c r="F68" s="3">
+        <f>IF('Heure par heure'!G68="","",'Heure par heure'!G68-N('Heure par heure'!G67))</f>
+        <v/>
+      </c>
+      <c r="G68" s="3">
+        <f>IF('Heure par heure'!H68="","",'Heure par heure'!H68-N('Heure par heure'!H67))</f>
+        <v/>
+      </c>
+      <c r="H68" s="3">
+        <f>IF('Heure par heure'!I68="","",'Heure par heure'!I68-N('Heure par heure'!I67))</f>
+        <v/>
+      </c>
+      <c r="I68" s="3">
+        <f>IF('Heure par heure'!J68="","",'Heure par heure'!J68-N('Heure par heure'!J67))</f>
+        <v/>
+      </c>
+      <c r="J68" s="3">
+        <f>IF('Heure par heure'!K68="","",'Heure par heure'!K68-N('Heure par heure'!K67))</f>
+        <v/>
+      </c>
+      <c r="K68" s="3">
+        <f>IF('Heure par heure'!L68="","",'Heure par heure'!L68-N('Heure par heure'!L67))</f>
+        <v/>
+      </c>
+      <c r="L68" s="3">
+        <f>SUM(B68:K68)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$68</f>
+              <f>'Heure par heure'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$68</f>
+              <f>'Heure par heure'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$68</f>
+              <f>'Heure par heure'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$68</f>
+              <f>'Heure par heure'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$68</f>
+              <f>'Heure par heure'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$68</f>
+              <f>'Heure par heure'!$H$2:$H$69</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$68</f>
+              <f>'Heure par heure'!$I$2:$I$69</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$68</f>
+              <f>'Heure par heure'!$J$2:$J$69</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$68</f>
+              <f>'Heure par heure'!$K$2:$K$69</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$68</f>
+              <f>'Heure par heure'!$L$2:$L$69</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$68</f>
+              <f>'Heure par heure'!$B$2:$B$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$68</f>
+              <f>'Heure par heure'!$M$2:$M$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$68</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$68</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$68</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$68</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$68</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$68</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$68</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$69</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$68</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$69</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$68</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$69</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$68</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$69</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9367,6 +9367,50 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:00</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M69" s="3">
+        <f>SUM(C69:L69)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9379,7 +9423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12775,6 +12819,56 @@
       </c>
       <c r="L68" s="3">
         <f>SUM(B68:K68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <f>'Heure par heure'!A69</f>
+        <v/>
+      </c>
+      <c r="B69" s="3">
+        <f>IF('Heure par heure'!C69="","",'Heure par heure'!C69-N('Heure par heure'!C68))</f>
+        <v/>
+      </c>
+      <c r="C69" s="3">
+        <f>IF('Heure par heure'!D69="","",'Heure par heure'!D69-N('Heure par heure'!D68))</f>
+        <v/>
+      </c>
+      <c r="D69" s="3">
+        <f>IF('Heure par heure'!E69="","",'Heure par heure'!E69-N('Heure par heure'!E68))</f>
+        <v/>
+      </c>
+      <c r="E69" s="3">
+        <f>IF('Heure par heure'!F69="","",'Heure par heure'!F69-N('Heure par heure'!F68))</f>
+        <v/>
+      </c>
+      <c r="F69" s="3">
+        <f>IF('Heure par heure'!G69="","",'Heure par heure'!G69-N('Heure par heure'!G68))</f>
+        <v/>
+      </c>
+      <c r="G69" s="3">
+        <f>IF('Heure par heure'!H69="","",'Heure par heure'!H69-N('Heure par heure'!H68))</f>
+        <v/>
+      </c>
+      <c r="H69" s="3">
+        <f>IF('Heure par heure'!I69="","",'Heure par heure'!I69-N('Heure par heure'!I68))</f>
+        <v/>
+      </c>
+      <c r="I69" s="3">
+        <f>IF('Heure par heure'!J69="","",'Heure par heure'!J69-N('Heure par heure'!J68))</f>
+        <v/>
+      </c>
+      <c r="J69" s="3">
+        <f>IF('Heure par heure'!K69="","",'Heure par heure'!K69-N('Heure par heure'!K68))</f>
+        <v/>
+      </c>
+      <c r="K69" s="3">
+        <f>IF('Heure par heure'!L69="","",'Heure par heure'!L69-N('Heure par heure'!L68))</f>
+        <v/>
+      </c>
+      <c r="L69" s="3">
+        <f>SUM(B69:K69)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$69</f>
+              <f>'Heure par heure'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$69</f>
+              <f>'Heure par heure'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$69</f>
+              <f>'Heure par heure'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$69</f>
+              <f>'Heure par heure'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$69</f>
+              <f>'Heure par heure'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$69</f>
+              <f>'Heure par heure'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$69</f>
+              <f>'Heure par heure'!$I$2:$I$70</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$69</f>
+              <f>'Heure par heure'!$J$2:$J$70</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$69</f>
+              <f>'Heure par heure'!$K$2:$K$70</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$69</f>
+              <f>'Heure par heure'!$L$2:$L$70</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$69</f>
+              <f>'Heure par heure'!$B$2:$B$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$69</f>
+              <f>'Heure par heure'!$M$2:$M$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$69</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$69</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$69</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$69</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$69</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$69</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$69</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$69</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$70</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$69</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$70</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$69</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$70</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9411,6 +9411,50 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:00</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M70" s="3">
+        <f>SUM(C70:L70)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9423,7 +9467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12869,6 +12913,56 @@
       </c>
       <c r="L69" s="3">
         <f>SUM(B69:K69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <f>'Heure par heure'!A70</f>
+        <v/>
+      </c>
+      <c r="B70" s="3">
+        <f>IF('Heure par heure'!C70="","",'Heure par heure'!C70-N('Heure par heure'!C69))</f>
+        <v/>
+      </c>
+      <c r="C70" s="3">
+        <f>IF('Heure par heure'!D70="","",'Heure par heure'!D70-N('Heure par heure'!D69))</f>
+        <v/>
+      </c>
+      <c r="D70" s="3">
+        <f>IF('Heure par heure'!E70="","",'Heure par heure'!E70-N('Heure par heure'!E69))</f>
+        <v/>
+      </c>
+      <c r="E70" s="3">
+        <f>IF('Heure par heure'!F70="","",'Heure par heure'!F70-N('Heure par heure'!F69))</f>
+        <v/>
+      </c>
+      <c r="F70" s="3">
+        <f>IF('Heure par heure'!G70="","",'Heure par heure'!G70-N('Heure par heure'!G69))</f>
+        <v/>
+      </c>
+      <c r="G70" s="3">
+        <f>IF('Heure par heure'!H70="","",'Heure par heure'!H70-N('Heure par heure'!H69))</f>
+        <v/>
+      </c>
+      <c r="H70" s="3">
+        <f>IF('Heure par heure'!I70="","",'Heure par heure'!I70-N('Heure par heure'!I69))</f>
+        <v/>
+      </c>
+      <c r="I70" s="3">
+        <f>IF('Heure par heure'!J70="","",'Heure par heure'!J70-N('Heure par heure'!J69))</f>
+        <v/>
+      </c>
+      <c r="J70" s="3">
+        <f>IF('Heure par heure'!K70="","",'Heure par heure'!K70-N('Heure par heure'!K69))</f>
+        <v/>
+      </c>
+      <c r="K70" s="3">
+        <f>IF('Heure par heure'!L70="","",'Heure par heure'!L70-N('Heure par heure'!L69))</f>
+        <v/>
+      </c>
+      <c r="L70" s="3">
+        <f>SUM(B70:K70)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$70</f>
+              <f>'Heure par heure'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$70</f>
+              <f>'Heure par heure'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$70</f>
+              <f>'Heure par heure'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$70</f>
+              <f>'Heure par heure'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$70</f>
+              <f>'Heure par heure'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$70</f>
+              <f>'Heure par heure'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$70</f>
+              <f>'Heure par heure'!$I$2:$I$71</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$70</f>
+              <f>'Heure par heure'!$J$2:$J$71</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$70</f>
+              <f>'Heure par heure'!$K$2:$K$71</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$70</f>
+              <f>'Heure par heure'!$L$2:$L$71</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$70</f>
+              <f>'Heure par heure'!$B$2:$B$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$70</f>
+              <f>'Heure par heure'!$M$2:$M$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$70</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$70</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$70</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$70</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$70</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$70</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$70</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$70</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$71</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$70</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$71</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$70</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$71</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9455,6 +9455,50 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M71" s="3">
+        <f>SUM(C71:L71)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9467,7 +9511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12963,6 +13007,56 @@
       </c>
       <c r="L70" s="3">
         <f>SUM(B70:K70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <f>'Heure par heure'!A71</f>
+        <v/>
+      </c>
+      <c r="B71" s="3">
+        <f>IF('Heure par heure'!C71="","",'Heure par heure'!C71-N('Heure par heure'!C70))</f>
+        <v/>
+      </c>
+      <c r="C71" s="3">
+        <f>IF('Heure par heure'!D71="","",'Heure par heure'!D71-N('Heure par heure'!D70))</f>
+        <v/>
+      </c>
+      <c r="D71" s="3">
+        <f>IF('Heure par heure'!E71="","",'Heure par heure'!E71-N('Heure par heure'!E70))</f>
+        <v/>
+      </c>
+      <c r="E71" s="3">
+        <f>IF('Heure par heure'!F71="","",'Heure par heure'!F71-N('Heure par heure'!F70))</f>
+        <v/>
+      </c>
+      <c r="F71" s="3">
+        <f>IF('Heure par heure'!G71="","",'Heure par heure'!G71-N('Heure par heure'!G70))</f>
+        <v/>
+      </c>
+      <c r="G71" s="3">
+        <f>IF('Heure par heure'!H71="","",'Heure par heure'!H71-N('Heure par heure'!H70))</f>
+        <v/>
+      </c>
+      <c r="H71" s="3">
+        <f>IF('Heure par heure'!I71="","",'Heure par heure'!I71-N('Heure par heure'!I70))</f>
+        <v/>
+      </c>
+      <c r="I71" s="3">
+        <f>IF('Heure par heure'!J71="","",'Heure par heure'!J71-N('Heure par heure'!J70))</f>
+        <v/>
+      </c>
+      <c r="J71" s="3">
+        <f>IF('Heure par heure'!K71="","",'Heure par heure'!K71-N('Heure par heure'!K70))</f>
+        <v/>
+      </c>
+      <c r="K71" s="3">
+        <f>IF('Heure par heure'!L71="","",'Heure par heure'!L71-N('Heure par heure'!L70))</f>
+        <v/>
+      </c>
+      <c r="L71" s="3">
+        <f>SUM(B71:K71)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$71</f>
+              <f>'Heure par heure'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$71</f>
+              <f>'Heure par heure'!$D$2:$D$72</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$71</f>
+              <f>'Heure par heure'!$E$2:$E$72</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$71</f>
+              <f>'Heure par heure'!$F$2:$F$72</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$71</f>
+              <f>'Heure par heure'!$G$2:$G$72</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$71</f>
+              <f>'Heure par heure'!$H$2:$H$72</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$71</f>
+              <f>'Heure par heure'!$I$2:$I$72</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$71</f>
+              <f>'Heure par heure'!$J$2:$J$72</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$71</f>
+              <f>'Heure par heure'!$K$2:$K$72</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$71</f>
+              <f>'Heure par heure'!$L$2:$L$72</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$71</f>
+              <f>'Heure par heure'!$B$2:$B$72</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$71</f>
+              <f>'Heure par heure'!$M$2:$M$72</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$71</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$71</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$71</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$72</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$71</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$72</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$71</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$72</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$71</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$72</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$71</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$72</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$71</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$72</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$71</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$72</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$71</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$72</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9499,6 +9499,50 @@
         <v/>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:00</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M72" s="3">
+        <f>SUM(C72:L72)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9511,7 +9555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13057,6 +13101,56 @@
       </c>
       <c r="L71" s="3">
         <f>SUM(B71:K71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <f>'Heure par heure'!A72</f>
+        <v/>
+      </c>
+      <c r="B72" s="3">
+        <f>IF('Heure par heure'!C72="","",'Heure par heure'!C72-N('Heure par heure'!C71))</f>
+        <v/>
+      </c>
+      <c r="C72" s="3">
+        <f>IF('Heure par heure'!D72="","",'Heure par heure'!D72-N('Heure par heure'!D71))</f>
+        <v/>
+      </c>
+      <c r="D72" s="3">
+        <f>IF('Heure par heure'!E72="","",'Heure par heure'!E72-N('Heure par heure'!E71))</f>
+        <v/>
+      </c>
+      <c r="E72" s="3">
+        <f>IF('Heure par heure'!F72="","",'Heure par heure'!F72-N('Heure par heure'!F71))</f>
+        <v/>
+      </c>
+      <c r="F72" s="3">
+        <f>IF('Heure par heure'!G72="","",'Heure par heure'!G72-N('Heure par heure'!G71))</f>
+        <v/>
+      </c>
+      <c r="G72" s="3">
+        <f>IF('Heure par heure'!H72="","",'Heure par heure'!H72-N('Heure par heure'!H71))</f>
+        <v/>
+      </c>
+      <c r="H72" s="3">
+        <f>IF('Heure par heure'!I72="","",'Heure par heure'!I72-N('Heure par heure'!I71))</f>
+        <v/>
+      </c>
+      <c r="I72" s="3">
+        <f>IF('Heure par heure'!J72="","",'Heure par heure'!J72-N('Heure par heure'!J71))</f>
+        <v/>
+      </c>
+      <c r="J72" s="3">
+        <f>IF('Heure par heure'!K72="","",'Heure par heure'!K72-N('Heure par heure'!K71))</f>
+        <v/>
+      </c>
+      <c r="K72" s="3">
+        <f>IF('Heure par heure'!L72="","",'Heure par heure'!L72-N('Heure par heure'!L71))</f>
+        <v/>
+      </c>
+      <c r="L72" s="3">
+        <f>SUM(B72:K72)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$72</f>
+              <f>'Heure par heure'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$72</f>
+              <f>'Heure par heure'!$D$2:$D$73</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$72</f>
+              <f>'Heure par heure'!$E$2:$E$73</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$72</f>
+              <f>'Heure par heure'!$F$2:$F$73</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$72</f>
+              <f>'Heure par heure'!$G$2:$G$73</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$72</f>
+              <f>'Heure par heure'!$H$2:$H$73</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$72</f>
+              <f>'Heure par heure'!$I$2:$I$73</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$72</f>
+              <f>'Heure par heure'!$J$2:$J$73</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$72</f>
+              <f>'Heure par heure'!$K$2:$K$73</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$72</f>
+              <f>'Heure par heure'!$L$2:$L$73</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$72</f>
+              <f>'Heure par heure'!$B$2:$B$73</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$72</f>
+              <f>'Heure par heure'!$M$2:$M$73</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$72</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$72</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$72</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$73</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$72</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$73</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$72</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$73</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$72</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$73</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$72</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$73</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$72</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$73</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$72</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$73</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$72</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$73</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9543,6 +9543,50 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:00</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M73" s="3">
+        <f>SUM(C73:L73)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9555,7 +9599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13151,6 +13195,56 @@
       </c>
       <c r="L72" s="3">
         <f>SUM(B72:K72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <f>'Heure par heure'!A73</f>
+        <v/>
+      </c>
+      <c r="B73" s="3">
+        <f>IF('Heure par heure'!C73="","",'Heure par heure'!C73-N('Heure par heure'!C72))</f>
+        <v/>
+      </c>
+      <c r="C73" s="3">
+        <f>IF('Heure par heure'!D73="","",'Heure par heure'!D73-N('Heure par heure'!D72))</f>
+        <v/>
+      </c>
+      <c r="D73" s="3">
+        <f>IF('Heure par heure'!E73="","",'Heure par heure'!E73-N('Heure par heure'!E72))</f>
+        <v/>
+      </c>
+      <c r="E73" s="3">
+        <f>IF('Heure par heure'!F73="","",'Heure par heure'!F73-N('Heure par heure'!F72))</f>
+        <v/>
+      </c>
+      <c r="F73" s="3">
+        <f>IF('Heure par heure'!G73="","",'Heure par heure'!G73-N('Heure par heure'!G72))</f>
+        <v/>
+      </c>
+      <c r="G73" s="3">
+        <f>IF('Heure par heure'!H73="","",'Heure par heure'!H73-N('Heure par heure'!H72))</f>
+        <v/>
+      </c>
+      <c r="H73" s="3">
+        <f>IF('Heure par heure'!I73="","",'Heure par heure'!I73-N('Heure par heure'!I72))</f>
+        <v/>
+      </c>
+      <c r="I73" s="3">
+        <f>IF('Heure par heure'!J73="","",'Heure par heure'!J73-N('Heure par heure'!J72))</f>
+        <v/>
+      </c>
+      <c r="J73" s="3">
+        <f>IF('Heure par heure'!K73="","",'Heure par heure'!K73-N('Heure par heure'!K72))</f>
+        <v/>
+      </c>
+      <c r="K73" s="3">
+        <f>IF('Heure par heure'!L73="","",'Heure par heure'!L73-N('Heure par heure'!L72))</f>
+        <v/>
+      </c>
+      <c r="L73" s="3">
+        <f>SUM(B73:K73)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$73</f>
+              <f>'Heure par heure'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$73</f>
+              <f>'Heure par heure'!$D$2:$D$74</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$73</f>
+              <f>'Heure par heure'!$E$2:$E$74</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$73</f>
+              <f>'Heure par heure'!$F$2:$F$74</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$73</f>
+              <f>'Heure par heure'!$G$2:$G$74</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$73</f>
+              <f>'Heure par heure'!$H$2:$H$74</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$73</f>
+              <f>'Heure par heure'!$I$2:$I$74</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$73</f>
+              <f>'Heure par heure'!$J$2:$J$74</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$73</f>
+              <f>'Heure par heure'!$K$2:$K$74</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$73</f>
+              <f>'Heure par heure'!$L$2:$L$74</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$73</f>
+              <f>'Heure par heure'!$B$2:$B$74</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$73</f>
+              <f>'Heure par heure'!$M$2:$M$74</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$73</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$73</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$73</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$74</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$73</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$74</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$73</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$74</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$73</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$74</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$73</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$74</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$73</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$74</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$73</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$74</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$73</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$74</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9587,6 +9587,50 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:00</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M74" s="3">
+        <f>SUM(C74:L74)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9599,7 +9643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13245,6 +13289,56 @@
       </c>
       <c r="L73" s="3">
         <f>SUM(B73:K73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <f>'Heure par heure'!A74</f>
+        <v/>
+      </c>
+      <c r="B74" s="3">
+        <f>IF('Heure par heure'!C74="","",'Heure par heure'!C74-N('Heure par heure'!C73))</f>
+        <v/>
+      </c>
+      <c r="C74" s="3">
+        <f>IF('Heure par heure'!D74="","",'Heure par heure'!D74-N('Heure par heure'!D73))</f>
+        <v/>
+      </c>
+      <c r="D74" s="3">
+        <f>IF('Heure par heure'!E74="","",'Heure par heure'!E74-N('Heure par heure'!E73))</f>
+        <v/>
+      </c>
+      <c r="E74" s="3">
+        <f>IF('Heure par heure'!F74="","",'Heure par heure'!F74-N('Heure par heure'!F73))</f>
+        <v/>
+      </c>
+      <c r="F74" s="3">
+        <f>IF('Heure par heure'!G74="","",'Heure par heure'!G74-N('Heure par heure'!G73))</f>
+        <v/>
+      </c>
+      <c r="G74" s="3">
+        <f>IF('Heure par heure'!H74="","",'Heure par heure'!H74-N('Heure par heure'!H73))</f>
+        <v/>
+      </c>
+      <c r="H74" s="3">
+        <f>IF('Heure par heure'!I74="","",'Heure par heure'!I74-N('Heure par heure'!I73))</f>
+        <v/>
+      </c>
+      <c r="I74" s="3">
+        <f>IF('Heure par heure'!J74="","",'Heure par heure'!J74-N('Heure par heure'!J73))</f>
+        <v/>
+      </c>
+      <c r="J74" s="3">
+        <f>IF('Heure par heure'!K74="","",'Heure par heure'!K74-N('Heure par heure'!K73))</f>
+        <v/>
+      </c>
+      <c r="K74" s="3">
+        <f>IF('Heure par heure'!L74="","",'Heure par heure'!L74-N('Heure par heure'!L73))</f>
+        <v/>
+      </c>
+      <c r="L74" s="3">
+        <f>SUM(B74:K74)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$74</f>
+              <f>'Heure par heure'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$74</f>
+              <f>'Heure par heure'!$D$2:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$74</f>
+              <f>'Heure par heure'!$E$2:$E$75</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$74</f>
+              <f>'Heure par heure'!$F$2:$F$75</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$74</f>
+              <f>'Heure par heure'!$G$2:$G$75</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$74</f>
+              <f>'Heure par heure'!$H$2:$H$75</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$74</f>
+              <f>'Heure par heure'!$I$2:$I$75</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$74</f>
+              <f>'Heure par heure'!$J$2:$J$75</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$74</f>
+              <f>'Heure par heure'!$K$2:$K$75</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$74</f>
+              <f>'Heure par heure'!$L$2:$L$75</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$74</f>
+              <f>'Heure par heure'!$B$2:$B$75</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$74</f>
+              <f>'Heure par heure'!$M$2:$M$75</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$74</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$74</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$74</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$74</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$75</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$74</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$75</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$74</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$75</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$74</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$75</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$74</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$75</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$74</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$75</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$74</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$75</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6549,52 +6549,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Des millions publics p</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Vendredi, Macron au co</t>
+          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
+          <t>10-27 54 milliards d'efforts</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>10-27 54 milliards d'efforts</t>
+          <t>10-29 Macron demande aux bra</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -6613,20 +6613,18 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="G2" s="3" t="n">
         <v>124</v>
       </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
@@ -6647,20 +6645,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="G3" s="3" t="n">
         <v>130</v>
       </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
@@ -6681,20 +6677,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="G4" s="3" t="n">
         <v>135</v>
       </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
@@ -6715,23 +6709,21 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
@@ -6751,23 +6743,21 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="H6" s="3" t="n">
         <v>34</v>
       </c>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
@@ -6787,23 +6777,21 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="H7" s="3" t="n">
         <v>44</v>
       </c>
+      <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
@@ -6823,23 +6811,21 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="H8" s="3" t="n">
         <v>70</v>
       </c>
+      <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
@@ -6859,23 +6845,21 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="H9" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
@@ -6895,23 +6879,21 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="H10" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
@@ -6931,23 +6913,21 @@
         <v>6</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="H11" s="3" t="n">
         <v>133</v>
       </c>
+      <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
@@ -6967,23 +6947,21 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="H12" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
@@ -7003,23 +6981,21 @@
         <v>6</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>130</v>
+        <v>199</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="H13" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
@@ -7039,23 +7015,21 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="H14" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
@@ -7075,23 +7049,21 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="H15" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
@@ -7111,23 +7083,21 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="H16" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
@@ -7147,23 +7117,21 @@
         <v>6</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="H17" s="3" t="n">
         <v>134</v>
       </c>
+      <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
@@ -7183,29 +7151,27 @@
         <v>6</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>240</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3">
@@ -7223,29 +7189,27 @@
         <v>7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="J19" s="3" t="n">
         <v>53</v>
       </c>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3">
@@ -7263,29 +7227,27 @@
         <v>7</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="J20" s="3" t="n">
         <v>80</v>
       </c>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3">
@@ -7303,32 +7265,30 @@
         <v>7</v>
       </c>
       <c r="C21" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I21" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>35</v>
-      </c>
       <c r="J21" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3">
         <f>SUM(C21:L21)</f>
@@ -7345,32 +7305,30 @@
         <v>7</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>243</v>
+        <v>134</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="K22" s="3" t="n">
         <v>43</v>
       </c>
+      <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3">
         <f>SUM(C22:L22)</f>
@@ -7387,32 +7345,30 @@
         <v>7</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>243</v>
+        <v>134</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="K23" s="3" t="n">
         <v>64</v>
       </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3">
         <f>SUM(C23:L23)</f>
@@ -7429,32 +7385,30 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="K24" s="3" t="n">
         <v>99</v>
       </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3">
         <f>SUM(C24:L24)</f>
@@ -7471,32 +7425,30 @@
         <v>7</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="K25" s="3" t="n">
         <v>111</v>
       </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3">
         <f>SUM(C25:L25)</f>
@@ -7513,32 +7465,30 @@
         <v>7</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="K26" s="3" t="n">
         <v>115</v>
       </c>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3">
         <f>SUM(C26:L26)</f>
@@ -7555,32 +7505,30 @@
         <v>7</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="K27" s="3" t="n">
         <v>115</v>
       </c>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3">
         <f>SUM(C27:L27)</f>
@@ -7597,32 +7545,30 @@
         <v>7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="K28" s="3" t="n">
         <v>115</v>
       </c>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3">
         <f>SUM(C28:L28)</f>
@@ -7639,32 +7585,30 @@
         <v>7</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D29" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I29" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K29" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3">
         <f>SUM(C29:L29)</f>
@@ -7681,32 +7625,30 @@
         <v>7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H30" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I30" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K30" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3">
         <f>SUM(C30:L30)</f>
@@ -7723,32 +7665,30 @@
         <v>7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I31" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K31" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3">
         <f>SUM(C31:L31)</f>
@@ -7765,32 +7705,30 @@
         <v>7</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D32" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H32" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E32" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I32" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K32" s="3" t="n">
         <v>116</v>
       </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3">
         <f>SUM(C32:L32)</f>
@@ -7807,32 +7745,30 @@
         <v>7</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I33" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K33" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3">
         <f>SUM(C33:L33)</f>
@@ -7849,32 +7785,30 @@
         <v>7</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D34" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K34" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3">
         <f>SUM(C34:L34)</f>
@@ -7891,32 +7825,30 @@
         <v>7</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D35" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I35" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K35" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3">
         <f>SUM(C35:L35)</f>
@@ -7933,32 +7865,30 @@
         <v>7</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D36" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I36" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K36" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="3">
         <f>SUM(C36:L36)</f>
@@ -7975,32 +7905,30 @@
         <v>7</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D37" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H37" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I37" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K37" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3">
         <f>SUM(C37:L37)</f>
@@ -8017,32 +7945,30 @@
         <v>7</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D38" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E38" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I38" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K38" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3">
         <f>SUM(C38:L38)</f>
@@ -8059,32 +7985,30 @@
         <v>7</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D39" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I39" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="K39" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="3">
         <f>SUM(C39:L39)</f>
@@ -8101,35 +8025,33 @@
         <v>7</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D40" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I40" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3">
         <f>SUM(C40:L40)</f>
         <v/>
@@ -8145,35 +8067,33 @@
         <v>7</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I41" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L41" s="3" t="n">
         <v>46</v>
       </c>
+      <c r="L41" s="3" t="n"/>
       <c r="M41" s="3">
         <f>SUM(C41:L41)</f>
         <v/>
@@ -8189,35 +8109,33 @@
         <v>7</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D42" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I42" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L42" s="3" t="n">
         <v>77</v>
       </c>
+      <c r="L42" s="3" t="n"/>
       <c r="M42" s="3">
         <f>SUM(C42:L42)</f>
         <v/>
@@ -8233,35 +8151,33 @@
         <v>7</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I43" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L43" s="3" t="n">
         <v>83</v>
       </c>
+      <c r="L43" s="3" t="n"/>
       <c r="M43" s="3">
         <f>SUM(C43:L43)</f>
         <v/>
@@ -8277,35 +8193,33 @@
         <v>7</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D44" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E44" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L44" s="3" t="n">
         <v>89</v>
       </c>
+      <c r="L44" s="3" t="n"/>
       <c r="M44" s="3">
         <f>SUM(C44:L44)</f>
         <v/>
@@ -8321,35 +8235,33 @@
         <v>7</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D45" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I45" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L45" s="3" t="n">
         <v>91</v>
       </c>
+      <c r="L45" s="3" t="n"/>
       <c r="M45" s="3">
         <f>SUM(C45:L45)</f>
         <v/>
@@ -8365,35 +8277,33 @@
         <v>7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I46" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L46" s="3" t="n">
         <v>92</v>
       </c>
+      <c r="L46" s="3" t="n"/>
       <c r="M46" s="3">
         <f>SUM(C46:L46)</f>
         <v/>
@@ -8409,35 +8319,33 @@
         <v>7</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D47" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H47" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E47" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I47" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L47" s="3" t="n">
         <v>92</v>
       </c>
+      <c r="L47" s="3" t="n"/>
       <c r="M47" s="3">
         <f>SUM(C47:L47)</f>
         <v/>
@@ -8453,35 +8361,33 @@
         <v>7</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D48" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H48" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E48" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I48" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L48" s="3" t="n">
         <v>92</v>
       </c>
+      <c r="L48" s="3" t="n"/>
       <c r="M48" s="3">
         <f>SUM(C48:L48)</f>
         <v/>
@@ -8497,35 +8403,33 @@
         <v>7</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D49" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H49" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E49" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I49" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L49" s="3" t="n">
         <v>94</v>
       </c>
+      <c r="L49" s="3" t="n"/>
       <c r="M49" s="3">
         <f>SUM(C49:L49)</f>
         <v/>
@@ -8541,35 +8445,33 @@
         <v>7</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D50" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H50" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E50" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I50" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L50" s="3" t="n">
         <v>95</v>
       </c>
+      <c r="L50" s="3" t="n"/>
       <c r="M50" s="3">
         <f>SUM(C50:L50)</f>
         <v/>
@@ -8585,35 +8487,33 @@
         <v>7</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D51" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H51" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E51" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I51" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L51" s="3" t="n">
         <v>95</v>
       </c>
+      <c r="L51" s="3" t="n"/>
       <c r="M51" s="3">
         <f>SUM(C51:L51)</f>
         <v/>
@@ -8629,35 +8529,33 @@
         <v>7</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D52" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H52" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E52" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I52" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L52" s="3" t="n">
         <v>98</v>
       </c>
+      <c r="L52" s="3" t="n"/>
       <c r="M52" s="3">
         <f>SUM(C52:L52)</f>
         <v/>
@@ -8673,35 +8571,33 @@
         <v>7</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D53" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H53" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E53" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I53" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L53" s="3" t="n">
         <v>98</v>
       </c>
+      <c r="L53" s="3" t="n"/>
       <c r="M53" s="3">
         <f>SUM(C53:L53)</f>
         <v/>
@@ -8717,35 +8613,33 @@
         <v>7</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D54" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H54" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E54" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I54" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L54" s="3" t="n">
         <v>105</v>
       </c>
+      <c r="L54" s="3" t="n"/>
       <c r="M54" s="3">
         <f>SUM(C54:L54)</f>
         <v/>
@@ -8761,35 +8655,33 @@
         <v>7</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D55" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H55" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E55" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I55" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L55" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L55" s="3" t="n"/>
       <c r="M55" s="3">
         <f>SUM(C55:L55)</f>
         <v/>
@@ -8805,35 +8697,33 @@
         <v>7</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D56" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H56" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E56" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I56" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L56" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L56" s="3" t="n"/>
       <c r="M56" s="3">
         <f>SUM(C56:L56)</f>
         <v/>
@@ -8849,35 +8739,33 @@
         <v>7</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D57" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H57" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E57" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I57" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L57" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L57" s="3" t="n"/>
       <c r="M57" s="3">
         <f>SUM(C57:L57)</f>
         <v/>
@@ -8893,35 +8781,33 @@
         <v>7</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D58" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H58" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E58" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I58" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L58" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L58" s="3" t="n"/>
       <c r="M58" s="3">
         <f>SUM(C58:L58)</f>
         <v/>
@@ -8937,35 +8823,33 @@
         <v>7</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D59" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H59" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E59" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I59" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L59" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L59" s="3" t="n"/>
       <c r="M59" s="3">
         <f>SUM(C59:L59)</f>
         <v/>
@@ -8981,35 +8865,33 @@
         <v>7</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H60" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E60" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I60" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L60" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L60" s="3" t="n"/>
       <c r="M60" s="3">
         <f>SUM(C60:L60)</f>
         <v/>
@@ -9025,35 +8907,33 @@
         <v>7</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D61" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H61" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E61" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I61" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L61" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L61" s="3" t="n"/>
       <c r="M61" s="3">
         <f>SUM(C61:L61)</f>
         <v/>
@@ -9069,35 +8949,33 @@
         <v>7</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D62" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H62" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E62" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I62" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L62" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L62" s="3" t="n"/>
       <c r="M62" s="3">
         <f>SUM(C62:L62)</f>
         <v/>
@@ -9113,35 +8991,33 @@
         <v>7</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D63" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H63" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E63" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I63" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L63" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L63" s="3" t="n"/>
       <c r="M63" s="3">
         <f>SUM(C63:L63)</f>
         <v/>
@@ -9157,35 +9033,33 @@
         <v>7</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D64" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H64" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E64" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I64" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L64" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L64" s="3" t="n"/>
       <c r="M64" s="3">
         <f>SUM(C64:L64)</f>
         <v/>
@@ -9201,35 +9075,33 @@
         <v>7</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D65" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H65" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E65" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I65" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L65" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L65" s="3" t="n"/>
       <c r="M65" s="3">
         <f>SUM(C65:L65)</f>
         <v/>
@@ -9245,35 +9117,33 @@
         <v>7</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D66" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H66" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E66" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I66" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L66" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L66" s="3" t="n"/>
       <c r="M66" s="3">
         <f>SUM(C66:L66)</f>
         <v/>
@@ -9289,35 +9159,33 @@
         <v>7</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D67" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H67" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E67" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I67" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L67" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L67" s="3" t="n"/>
       <c r="M67" s="3">
         <f>SUM(C67:L67)</f>
         <v/>
@@ -9333,35 +9201,33 @@
         <v>7</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D68" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H68" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E68" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I68" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L68" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L68" s="3" t="n"/>
       <c r="M68" s="3">
         <f>SUM(C68:L68)</f>
         <v/>
@@ -9377,35 +9243,33 @@
         <v>7</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D69" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H69" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E69" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I69" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L69" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L69" s="3" t="n"/>
       <c r="M69" s="3">
         <f>SUM(C69:L69)</f>
         <v/>
@@ -9421,35 +9285,33 @@
         <v>7</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D70" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H70" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E70" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I70" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L70" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L70" s="3" t="n"/>
       <c r="M70" s="3">
         <f>SUM(C70:L70)</f>
         <v/>
@@ -9465,35 +9327,33 @@
         <v>7</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D71" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H71" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E71" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I71" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L71" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L71" s="3" t="n"/>
       <c r="M71" s="3">
         <f>SUM(C71:L71)</f>
         <v/>
@@ -9509,35 +9369,33 @@
         <v>7</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D72" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H72" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E72" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I72" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L72" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L72" s="3" t="n"/>
       <c r="M72" s="3">
         <f>SUM(C72:L72)</f>
         <v/>
@@ -9553,35 +9411,33 @@
         <v>7</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D73" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H73" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I73" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L73" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L73" s="3" t="n"/>
       <c r="M73" s="3">
         <f>SUM(C73:L73)</f>
         <v/>
@@ -9597,37 +9453,79 @@
         <v>7</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D74" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H74" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="E74" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="I74" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="L74" s="3" t="n">
         <v>107</v>
       </c>
+      <c r="L74" s="3" t="n"/>
       <c r="M74" s="3">
         <f>SUM(C74:L74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 08:00</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <f>SUM(C75:L75)</f>
         <v/>
       </c>
     </row>
@@ -9643,7 +9541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9668,52 +9566,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>10-21 À toi de juger : taxer</t>
+          <t>10-21 Gel des pensions : oui</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>10-21 Gel des pensions : oui</t>
+          <t>10-22 Couper les réseaux soc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>10-22 Couper les réseaux soc</t>
+          <t>10-24 À toi de juger : il fa</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>10-24 À toi de juger : il fa</t>
+          <t>10-24 « Oui, nous avons perd</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>10-24 « Oui, nous avons perd</t>
+          <t>10-24 Cinq infos de la semai</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>10-24 Cinq infos de la semai</t>
+          <t>10-25 Des millions publics p</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Des millions publics p</t>
+          <t>10-25 Vendredi, Macron au co</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>10-25 Vendredi, Macron au co</t>
+          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-25 2 513 gardes à vue et </t>
+          <t>10-27 54 milliards d'efforts</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10-27 54 milliards d'efforts</t>
+          <t>10-29 Macron demande aux bra</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -13339,6 +13237,56 @@
       </c>
       <c r="L74" s="3">
         <f>SUM(B74:K74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <f>'Heure par heure'!A75</f>
+        <v/>
+      </c>
+      <c r="B75" s="3">
+        <f>IF('Heure par heure'!C75="","",'Heure par heure'!C75-N('Heure par heure'!C74))</f>
+        <v/>
+      </c>
+      <c r="C75" s="3">
+        <f>IF('Heure par heure'!D75="","",'Heure par heure'!D75-N('Heure par heure'!D74))</f>
+        <v/>
+      </c>
+      <c r="D75" s="3">
+        <f>IF('Heure par heure'!E75="","",'Heure par heure'!E75-N('Heure par heure'!E74))</f>
+        <v/>
+      </c>
+      <c r="E75" s="3">
+        <f>IF('Heure par heure'!F75="","",'Heure par heure'!F75-N('Heure par heure'!F74))</f>
+        <v/>
+      </c>
+      <c r="F75" s="3">
+        <f>IF('Heure par heure'!G75="","",'Heure par heure'!G75-N('Heure par heure'!G74))</f>
+        <v/>
+      </c>
+      <c r="G75" s="3">
+        <f>IF('Heure par heure'!H75="","",'Heure par heure'!H75-N('Heure par heure'!H74))</f>
+        <v/>
+      </c>
+      <c r="H75" s="3">
+        <f>IF('Heure par heure'!I75="","",'Heure par heure'!I75-N('Heure par heure'!I74))</f>
+        <v/>
+      </c>
+      <c r="I75" s="3">
+        <f>IF('Heure par heure'!J75="","",'Heure par heure'!J75-N('Heure par heure'!J74))</f>
+        <v/>
+      </c>
+      <c r="J75" s="3">
+        <f>IF('Heure par heure'!K75="","",'Heure par heure'!K75-N('Heure par heure'!K74))</f>
+        <v/>
+      </c>
+      <c r="K75" s="3">
+        <f>IF('Heure par heure'!L75="","",'Heure par heure'!L75-N('Heure par heure'!L74))</f>
+        <v/>
+      </c>
+      <c r="L75" s="3">
+        <f>SUM(B75:K75)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$12</f>
+              <f>'Jour par jour'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$12</f>
+              <f>'Jour par jour'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1244,12 +1244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$48</f>
+              <f>'Stories'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$48</f>
+              <f>'Stories'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -1346,12 +1346,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$12</f>
+              <f>'Jour par jour'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$12</f>
+              <f>'Jour par jour'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -1373,12 +1373,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$12</f>
+              <f>'Jour par jour'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$12</f>
+              <f>'Jour par jour'!$L$2:$L$13</f>
             </numRef>
           </val>
         </ser>
@@ -1486,12 +1486,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$12</f>
+              <f>'Jour par jour'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$12</f>
+              <f>'Jour par jour'!$F$2:$F$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1526,12 +1526,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$12</f>
+              <f>'Jour par jour'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$12</f>
+              <f>'Jour par jour'!$H$2:$H$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1628,12 +1628,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$12</f>
+              <f>'Jour par jour'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$12</f>
+              <f>'Jour par jour'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -2121,12 +2121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$12</f>
+              <f>'Évolution par vidéo'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$12</f>
+              <f>'Évolution par vidéo'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -2185,12 +2185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$12</f>
+              <f>'Évolution par vidéo'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -2217,12 +2217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$12</f>
+              <f>'Évolution par vidéo'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -2249,12 +2249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$F$2:$F$12</f>
+              <f>'Évolution par vidéo'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -2281,12 +2281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$G$2:$G$12</f>
+              <f>'Évolution par vidéo'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -2313,12 +2313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$H$2:$H$12</f>
+              <f>'Évolution par vidéo'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -2345,12 +2345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$I$2:$I$12</f>
+              <f>'Évolution par vidéo'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -2377,12 +2377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$J$2:$J$12</f>
+              <f>'Évolution par vidéo'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -2409,12 +2409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$K$2:$K$12</f>
+              <f>'Évolution par vidéo'!$K$2:$K$13</f>
             </numRef>
           </val>
         </ser>
@@ -2441,12 +2441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$L$2:$L$12</f>
+              <f>'Évolution par vidéo'!$L$2:$L$13</f>
             </numRef>
           </val>
         </ser>
@@ -2473,12 +2473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$M$2:$M$12</f>
+              <f>'Évolution par vidéo'!$M$2:$M$13</f>
             </numRef>
           </val>
         </ser>
@@ -2505,12 +2505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$N$2:$N$12</f>
+              <f>'Évolution par vidéo'!$N$2:$N$13</f>
             </numRef>
           </val>
         </ser>
@@ -2537,12 +2537,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$O$2:$O$12</f>
+              <f>'Évolution par vidéo'!$O$2:$O$13</f>
             </numRef>
           </val>
         </ser>
@@ -2569,12 +2569,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$12</f>
+              <f>'Évolution par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$P$2:$P$12</f>
+              <f>'Évolution par vidéo'!$P$2:$P$13</f>
             </numRef>
           </val>
         </ser>
@@ -2667,12 +2667,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$12</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$12</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -2715,12 +2715,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$12</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -2739,12 +2739,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$12</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -2763,12 +2763,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$F$2:$F$12</f>
+              <f>'Vues du jour par vidéo'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -2787,12 +2787,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$G$2:$G$12</f>
+              <f>'Vues du jour par vidéo'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -2811,12 +2811,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$H$2:$H$12</f>
+              <f>'Vues du jour par vidéo'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -2835,12 +2835,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$I$2:$I$12</f>
+              <f>'Vues du jour par vidéo'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -2859,12 +2859,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$J$2:$J$12</f>
+              <f>'Vues du jour par vidéo'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -2883,12 +2883,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$K$2:$K$12</f>
+              <f>'Vues du jour par vidéo'!$K$2:$K$13</f>
             </numRef>
           </val>
         </ser>
@@ -2907,12 +2907,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$L$2:$L$12</f>
+              <f>'Vues du jour par vidéo'!$L$2:$L$13</f>
             </numRef>
           </val>
         </ser>
@@ -2931,12 +2931,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$M$2:$M$12</f>
+              <f>'Vues du jour par vidéo'!$M$2:$M$13</f>
             </numRef>
           </val>
         </ser>
@@ -2955,12 +2955,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$N$2:$N$12</f>
+              <f>'Vues du jour par vidéo'!$N$2:$N$13</f>
             </numRef>
           </val>
         </ser>
@@ -2979,12 +2979,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$O$2:$O$12</f>
+              <f>'Vues du jour par vidéo'!$O$2:$O$13</f>
             </numRef>
           </val>
         </ser>
@@ -3003,12 +3003,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$12</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$P$2:$P$12</f>
+              <f>'Vues du jour par vidéo'!$P$2:$P$13</f>
             </numRef>
           </val>
         </ser>
@@ -3221,7 +3221,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3248,7 +3248,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -3683,7 +3683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4261,6 +4261,51 @@
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3">
+        <f>IF(ROW()=2,"",B13-B12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1748</v>
+      </c>
+      <c r="E13" s="3">
+        <f>IF(ROW()=2,D13,D13-D12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4357,12 +4402,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:05</t>
+          <t>2026-10-19 17:59</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">📩 « Jeudi 5 novembre, la France s'arrête. -A </t>
+          <t>📖 Il était une fois des agriculteurs en colèr</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4371,13 +4416,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -4389,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -4403,12 +4448,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59</t>
+          <t>2026-10-20 10:33</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agriculteurs en colèr</t>
+          <t>Couvre-feux, manifs « encadrées, voire interd</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4417,13 +4462,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -4432,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
@@ -4449,12 +4494,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33</t>
+          <t>2026-10-20 16:07</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadrées, voire interd</t>
+          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4463,13 +4508,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -4478,10 +4523,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -4495,12 +4540,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:07</t>
+          <t>2026-10-21 08:03</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,6 milliards envol</t>
+          <t>Les syndicats de salariés auraient-ils dû êtr</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4509,13 +4554,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -4527,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
@@ -4541,12 +4586,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:03</t>
+          <t>2026-10-21 12:07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés auraient-ils dû êtr</t>
+          <t>À toi de juger : taxer les profits du pétrole</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4555,13 +4600,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -4587,12 +4632,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:07</t>
+          <t>2026-10-21 16:08</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les profits du pétrole</t>
+          <t>Gel des pensions : oui ou non ? Réponds en co</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4601,10 +4646,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -4619,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <f>IFERROR((F7+G7+H7+I7)/IF(E7&gt;0,E7,D7),0)</f>
@@ -4633,12 +4678,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:08</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou non ? Réponds en co</t>
+          <t>Couper les réseaux sociaux pendant les émeute</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4647,10 +4692,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4679,12 +4724,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-24 12:30</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux pendant les émeute</t>
+          <t>À toi de juger : il faut une enquête indépend</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4693,13 +4738,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -4711,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="5">
         <f>IFERROR((F9+G9+H9+I9)/IF(E9&gt;0,E9,D9),0)</f>
@@ -4725,12 +4770,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 12:30</t>
+          <t>2026-10-24 13:56</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une enquête indépend</t>
+          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4739,25 +4784,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="F10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR((F10+G10+H10+I10)/IF(E10&gt;0,E10,D10),0)</f>
@@ -4771,12 +4816,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:56</t>
+          <t>2026-10-24 18:14</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le contrôle. » Le min</t>
+          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4785,13 +4830,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>225</v>
+        <v>115</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -4800,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR((F11+G11+H11+I11)/IF(E11&gt;0,E11,D11),0)</f>
@@ -4817,12 +4862,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 18:14</t>
+          <t>2026-10-25 13:58</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cinq infos de la semaine, une même logique : </t>
+          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4831,10 +4876,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -4863,12 +4908,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:58</t>
+          <t>2026-10-25 13:59</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
+          <t>Vendredi, Macron au concert de Céline Dion. S</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4877,13 +4922,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -4895,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="5">
         <f>IFERROR((F13+G13+H13+I13)/IF(E13&gt;0,E13,D13),0)</f>
@@ -4909,12 +4954,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:59</t>
+          <t>2026-10-25 17:26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Vendredi, Macron au concert de Céline Dion. S</t>
+          <t>2 513 gardes à vue et 67 incarcérations après</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4923,13 +4968,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -4941,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5">
         <f>IFERROR((F14+G14+H14+I14)/IF(E14&gt;0,E14,D14),0)</f>
@@ -4955,12 +5000,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 17:26</t>
+          <t>2026-10-27 07:08</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 513 gardes à vue et 67 incarcérations après</t>
+          <t xml:space="preserve">54 milliards d'efforts demandés aux Français </t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4969,10 +5014,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -5001,12 +5046,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 07:08</t>
+          <t>2026-10-29 07:55</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54 milliards d'efforts demandés aux Français </t>
+          <t xml:space="preserve">Macron demande aux branches de négocier : 52 </t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -5015,10 +5060,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -5073,7 +5118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5102,77 +5147,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Des millions publics promis.</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi, Macron au concert </t>
+          <t>2 513 gardes à vue et 67 inc</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>2 513 gardes à vue et 67 inc</t>
+          <t>54 milliards d'efforts deman</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>54 milliards d'efforts deman</t>
+          <t xml:space="preserve">Macron demande aux branches </t>
         </is>
       </c>
     </row>
@@ -5204,9 +5249,7 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
@@ -5229,14 +5272,12 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="D4" s="3" t="n">
         <v>63</v>
       </c>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
@@ -5257,23 +5298,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="G5" s="3" t="n">
         <v>69</v>
       </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
@@ -5291,29 +5330,27 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="I6" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
@@ -5329,29 +5366,27 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="I7" s="3" t="n">
         <v>74</v>
       </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
@@ -5367,35 +5402,33 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="K8" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
@@ -5409,44 +5442,42 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n"/>
     </row>
@@ -5457,47 +5488,45 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="M10" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="O10" s="3" t="n">
         <v>117</v>
       </c>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
     </row>
     <row r="11">
@@ -5507,50 +5536,48 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="L11" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>134</v>
-      </c>
       <c r="M11" s="3" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>92</v>
       </c>
+      <c r="P11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5559,49 +5586,99 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="P12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="C13" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="I13" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="J13" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="K13" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="L13" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="M13" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="N13" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="O13" s="3" t="n">
         <v>107</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5616,7 +5693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5646,77 +5723,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>📩 « Jeudi 5 novembre, la Fra</t>
+          <t>📖 Il était une fois des agri</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>📖 Il était une fois des agri</t>
+          <t>Couvre-feux, manifs « encadr</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feux, manifs « encadr</t>
+          <t>Couvre-feu pour les ados, 5,</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Couvre-feu pour les ados, 5,</t>
+          <t>Les syndicats de salariés au</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Les syndicats de salariés au</t>
+          <t>À toi de juger : taxer les p</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : taxer les p</t>
+          <t>Gel des pensions : oui ou no</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Gel des pensions : oui ou no</t>
+          <t>Couper les réseaux sociaux p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Couper les réseaux sociaux p</t>
+          <t>À toi de juger : il faut une</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>À toi de juger : il faut une</t>
+          <t>« Oui, nous avons perdu le c</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>« Oui, nous avons perdu le c</t>
+          <t>Cinq infos de la semaine, un</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Cinq infos de la semaine, un</t>
+          <t>Des millions publics promis.</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Des millions publics promis.</t>
+          <t xml:space="preserve">Vendredi, Macron au concert </t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi, Macron au concert </t>
+          <t>2 513 gardes à vue et 67 inc</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>2 513 gardes à vue et 67 inc</t>
+          <t>54 milliards d'efforts deman</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>54 milliards d'efforts deman</t>
+          <t xml:space="preserve">Macron demande aux branches </t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -6503,6 +6580,77 @@
       </c>
       <c r="Q12" s="3">
         <f>SUM(B12:P12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>IF('Évolution par vidéo'!B13="","",'Évolution par vidéo'!B13-N('Évolution par vidéo'!B12))</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>IF('Évolution par vidéo'!C13="","",'Évolution par vidéo'!C13-N('Évolution par vidéo'!C12))</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF('Évolution par vidéo'!D13="","",'Évolution par vidéo'!D13-N('Évolution par vidéo'!D12))</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>IF('Évolution par vidéo'!E13="","",'Évolution par vidéo'!E13-N('Évolution par vidéo'!E12))</f>
+        <v/>
+      </c>
+      <c r="F13" s="3">
+        <f>IF('Évolution par vidéo'!F13="","",'Évolution par vidéo'!F13-N('Évolution par vidéo'!F12))</f>
+        <v/>
+      </c>
+      <c r="G13" s="3">
+        <f>IF('Évolution par vidéo'!G13="","",'Évolution par vidéo'!G13-N('Évolution par vidéo'!G12))</f>
+        <v/>
+      </c>
+      <c r="H13" s="3">
+        <f>IF('Évolution par vidéo'!H13="","",'Évolution par vidéo'!H13-N('Évolution par vidéo'!H12))</f>
+        <v/>
+      </c>
+      <c r="I13" s="3">
+        <f>IF('Évolution par vidéo'!I13="","",'Évolution par vidéo'!I13-N('Évolution par vidéo'!I12))</f>
+        <v/>
+      </c>
+      <c r="J13" s="3">
+        <f>IF('Évolution par vidéo'!J13="","",'Évolution par vidéo'!J13-N('Évolution par vidéo'!J12))</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>IF('Évolution par vidéo'!K13="","",'Évolution par vidéo'!K13-N('Évolution par vidéo'!K12))</f>
+        <v/>
+      </c>
+      <c r="L13" s="3">
+        <f>IF('Évolution par vidéo'!L13="","",'Évolution par vidéo'!L13-N('Évolution par vidéo'!L12))</f>
+        <v/>
+      </c>
+      <c r="M13" s="3">
+        <f>IF('Évolution par vidéo'!M13="","",'Évolution par vidéo'!M13-N('Évolution par vidéo'!M12))</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>IF('Évolution par vidéo'!N13="","",'Évolution par vidéo'!N13-N('Évolution par vidéo'!N12))</f>
+        <v/>
+      </c>
+      <c r="O13" s="3">
+        <f>IF('Évolution par vidéo'!O13="","",'Évolution par vidéo'!O13-N('Évolution par vidéo'!O12))</f>
+        <v/>
+      </c>
+      <c r="P13" s="3">
+        <f>IF('Évolution par vidéo'!P13="","",'Évolution par vidéo'!P13-N('Évolution par vidéo'!P12))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="3">
+        <f>SUM(B13:P13)</f>
         <v/>
       </c>
     </row>
@@ -13302,7 +13450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14909,6 +15057,72 @@
         <v>0</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 05:38</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:55</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
@@ -14963,9 +15177,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId48"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$75</f>
+              <f>'Heure par heure'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$75</f>
+              <f>'Heure par heure'!$D$2:$D$76</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$75</f>
+              <f>'Heure par heure'!$E$2:$E$76</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$75</f>
+              <f>'Heure par heure'!$F$2:$F$76</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$75</f>
+              <f>'Heure par heure'!$G$2:$G$76</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$75</f>
+              <f>'Heure par heure'!$H$2:$H$76</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$75</f>
+              <f>'Heure par heure'!$I$2:$I$76</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$75</f>
+              <f>'Heure par heure'!$J$2:$J$76</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$75</f>
+              <f>'Heure par heure'!$K$2:$K$76</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$75</f>
+              <f>'Heure par heure'!$L$2:$L$76</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$75</f>
+              <f>'Heure par heure'!$B$2:$B$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$75</f>
+              <f>'Heure par heure'!$M$2:$M$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$75</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$75</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$75</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$76</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$75</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$76</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$75</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$76</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$75</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$76</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$75</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$76</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$75</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$76</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$75</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$76</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$75</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$76</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9677,6 +9677,50 @@
         <v/>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:00</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="M76" s="3">
+        <f>SUM(C76:L76)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9689,7 +9733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13435,6 +13479,56 @@
       </c>
       <c r="L75" s="3">
         <f>SUM(B75:K75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <f>'Heure par heure'!A76</f>
+        <v/>
+      </c>
+      <c r="B76" s="3">
+        <f>IF('Heure par heure'!C76="","",'Heure par heure'!C76-N('Heure par heure'!C75))</f>
+        <v/>
+      </c>
+      <c r="C76" s="3">
+        <f>IF('Heure par heure'!D76="","",'Heure par heure'!D76-N('Heure par heure'!D75))</f>
+        <v/>
+      </c>
+      <c r="D76" s="3">
+        <f>IF('Heure par heure'!E76="","",'Heure par heure'!E76-N('Heure par heure'!E75))</f>
+        <v/>
+      </c>
+      <c r="E76" s="3">
+        <f>IF('Heure par heure'!F76="","",'Heure par heure'!F76-N('Heure par heure'!F75))</f>
+        <v/>
+      </c>
+      <c r="F76" s="3">
+        <f>IF('Heure par heure'!G76="","",'Heure par heure'!G76-N('Heure par heure'!G75))</f>
+        <v/>
+      </c>
+      <c r="G76" s="3">
+        <f>IF('Heure par heure'!H76="","",'Heure par heure'!H76-N('Heure par heure'!H75))</f>
+        <v/>
+      </c>
+      <c r="H76" s="3">
+        <f>IF('Heure par heure'!I76="","",'Heure par heure'!I76-N('Heure par heure'!I75))</f>
+        <v/>
+      </c>
+      <c r="I76" s="3">
+        <f>IF('Heure par heure'!J76="","",'Heure par heure'!J76-N('Heure par heure'!J75))</f>
+        <v/>
+      </c>
+      <c r="J76" s="3">
+        <f>IF('Heure par heure'!K76="","",'Heure par heure'!K76-N('Heure par heure'!K75))</f>
+        <v/>
+      </c>
+      <c r="K76" s="3">
+        <f>IF('Heure par heure'!L76="","",'Heure par heure'!L76-N('Heure par heure'!L75))</f>
+        <v/>
+      </c>
+      <c r="L76" s="3">
+        <f>SUM(B76:K76)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$76</f>
+              <f>'Heure par heure'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$76</f>
+              <f>'Heure par heure'!$D$2:$D$77</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$76</f>
+              <f>'Heure par heure'!$E$2:$E$77</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$76</f>
+              <f>'Heure par heure'!$F$2:$F$77</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$76</f>
+              <f>'Heure par heure'!$G$2:$G$77</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$76</f>
+              <f>'Heure par heure'!$H$2:$H$77</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$76</f>
+              <f>'Heure par heure'!$I$2:$I$77</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$76</f>
+              <f>'Heure par heure'!$J$2:$J$77</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$76</f>
+              <f>'Heure par heure'!$K$2:$K$77</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$76</f>
+              <f>'Heure par heure'!$L$2:$L$77</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$76</f>
+              <f>'Heure par heure'!$B$2:$B$77</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$76</f>
+              <f>'Heure par heure'!$M$2:$M$77</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$76</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$76</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$76</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$77</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$76</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$77</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$76</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$77</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$76</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$77</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$76</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$77</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$76</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$77</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$76</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$77</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$76</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$77</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9721,6 +9721,50 @@
         <v/>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 10:00</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="M77" s="3">
+        <f>SUM(C77:L77)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9733,7 +9777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13529,6 +13573,56 @@
       </c>
       <c r="L76" s="3">
         <f>SUM(B76:K76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <f>'Heure par heure'!A77</f>
+        <v/>
+      </c>
+      <c r="B77" s="3">
+        <f>IF('Heure par heure'!C77="","",'Heure par heure'!C77-N('Heure par heure'!C76))</f>
+        <v/>
+      </c>
+      <c r="C77" s="3">
+        <f>IF('Heure par heure'!D77="","",'Heure par heure'!D77-N('Heure par heure'!D76))</f>
+        <v/>
+      </c>
+      <c r="D77" s="3">
+        <f>IF('Heure par heure'!E77="","",'Heure par heure'!E77-N('Heure par heure'!E76))</f>
+        <v/>
+      </c>
+      <c r="E77" s="3">
+        <f>IF('Heure par heure'!F77="","",'Heure par heure'!F77-N('Heure par heure'!F76))</f>
+        <v/>
+      </c>
+      <c r="F77" s="3">
+        <f>IF('Heure par heure'!G77="","",'Heure par heure'!G77-N('Heure par heure'!G76))</f>
+        <v/>
+      </c>
+      <c r="G77" s="3">
+        <f>IF('Heure par heure'!H77="","",'Heure par heure'!H77-N('Heure par heure'!H76))</f>
+        <v/>
+      </c>
+      <c r="H77" s="3">
+        <f>IF('Heure par heure'!I77="","",'Heure par heure'!I77-N('Heure par heure'!I76))</f>
+        <v/>
+      </c>
+      <c r="I77" s="3">
+        <f>IF('Heure par heure'!J77="","",'Heure par heure'!J77-N('Heure par heure'!J76))</f>
+        <v/>
+      </c>
+      <c r="J77" s="3">
+        <f>IF('Heure par heure'!K77="","",'Heure par heure'!K77-N('Heure par heure'!K76))</f>
+        <v/>
+      </c>
+      <c r="K77" s="3">
+        <f>IF('Heure par heure'!L77="","",'Heure par heure'!L77-N('Heure par heure'!L76))</f>
+        <v/>
+      </c>
+      <c r="L77" s="3">
+        <f>SUM(B77:K77)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$77</f>
+              <f>'Heure par heure'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$77</f>
+              <f>'Heure par heure'!$D$2:$D$78</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$77</f>
+              <f>'Heure par heure'!$E$2:$E$78</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$77</f>
+              <f>'Heure par heure'!$F$2:$F$78</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$77</f>
+              <f>'Heure par heure'!$G$2:$G$78</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$77</f>
+              <f>'Heure par heure'!$H$2:$H$78</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$77</f>
+              <f>'Heure par heure'!$I$2:$I$78</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$77</f>
+              <f>'Heure par heure'!$J$2:$J$78</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$77</f>
+              <f>'Heure par heure'!$K$2:$K$78</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$77</f>
+              <f>'Heure par heure'!$L$2:$L$78</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$77</f>
+              <f>'Heure par heure'!$B$2:$B$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$77</f>
+              <f>'Heure par heure'!$M$2:$M$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$77</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$77</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$77</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$78</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$77</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$78</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$77</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$78</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$77</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$78</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$77</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$78</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$77</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$78</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$77</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$78</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$77</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$78</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9765,6 +9765,50 @@
         <v/>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:00</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="M78" s="3">
+        <f>SUM(C78:L78)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9777,7 +9821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13623,6 +13667,56 @@
       </c>
       <c r="L77" s="3">
         <f>SUM(B77:K77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <f>'Heure par heure'!A78</f>
+        <v/>
+      </c>
+      <c r="B78" s="3">
+        <f>IF('Heure par heure'!C78="","",'Heure par heure'!C78-N('Heure par heure'!C77))</f>
+        <v/>
+      </c>
+      <c r="C78" s="3">
+        <f>IF('Heure par heure'!D78="","",'Heure par heure'!D78-N('Heure par heure'!D77))</f>
+        <v/>
+      </c>
+      <c r="D78" s="3">
+        <f>IF('Heure par heure'!E78="","",'Heure par heure'!E78-N('Heure par heure'!E77))</f>
+        <v/>
+      </c>
+      <c r="E78" s="3">
+        <f>IF('Heure par heure'!F78="","",'Heure par heure'!F78-N('Heure par heure'!F77))</f>
+        <v/>
+      </c>
+      <c r="F78" s="3">
+        <f>IF('Heure par heure'!G78="","",'Heure par heure'!G78-N('Heure par heure'!G77))</f>
+        <v/>
+      </c>
+      <c r="G78" s="3">
+        <f>IF('Heure par heure'!H78="","",'Heure par heure'!H78-N('Heure par heure'!H77))</f>
+        <v/>
+      </c>
+      <c r="H78" s="3">
+        <f>IF('Heure par heure'!I78="","",'Heure par heure'!I78-N('Heure par heure'!I77))</f>
+        <v/>
+      </c>
+      <c r="I78" s="3">
+        <f>IF('Heure par heure'!J78="","",'Heure par heure'!J78-N('Heure par heure'!J77))</f>
+        <v/>
+      </c>
+      <c r="J78" s="3">
+        <f>IF('Heure par heure'!K78="","",'Heure par heure'!K78-N('Heure par heure'!K77))</f>
+        <v/>
+      </c>
+      <c r="K78" s="3">
+        <f>IF('Heure par heure'!L78="","",'Heure par heure'!L78-N('Heure par heure'!L77))</f>
+        <v/>
+      </c>
+      <c r="L78" s="3">
+        <f>SUM(B78:K78)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$78</f>
+              <f>'Heure par heure'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$78</f>
+              <f>'Heure par heure'!$D$2:$D$79</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$78</f>
+              <f>'Heure par heure'!$E$2:$E$79</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$78</f>
+              <f>'Heure par heure'!$F$2:$F$79</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$78</f>
+              <f>'Heure par heure'!$G$2:$G$79</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$78</f>
+              <f>'Heure par heure'!$H$2:$H$79</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$78</f>
+              <f>'Heure par heure'!$I$2:$I$79</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$78</f>
+              <f>'Heure par heure'!$J$2:$J$79</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$78</f>
+              <f>'Heure par heure'!$K$2:$K$79</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$78</f>
+              <f>'Heure par heure'!$L$2:$L$79</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$78</f>
+              <f>'Heure par heure'!$B$2:$B$79</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$78</f>
+              <f>'Heure par heure'!$M$2:$M$79</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$78</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$78</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$78</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$79</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$78</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$79</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$78</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$79</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$78</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$79</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$78</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$79</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$78</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$79</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$78</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$79</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$78</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$79</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9809,6 +9809,50 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:00</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="M79" s="3">
+        <f>SUM(C79:L79)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9821,7 +9865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13717,6 +13761,56 @@
       </c>
       <c r="L78" s="3">
         <f>SUM(B78:K78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <f>'Heure par heure'!A79</f>
+        <v/>
+      </c>
+      <c r="B79" s="3">
+        <f>IF('Heure par heure'!C79="","",'Heure par heure'!C79-N('Heure par heure'!C78))</f>
+        <v/>
+      </c>
+      <c r="C79" s="3">
+        <f>IF('Heure par heure'!D79="","",'Heure par heure'!D79-N('Heure par heure'!D78))</f>
+        <v/>
+      </c>
+      <c r="D79" s="3">
+        <f>IF('Heure par heure'!E79="","",'Heure par heure'!E79-N('Heure par heure'!E78))</f>
+        <v/>
+      </c>
+      <c r="E79" s="3">
+        <f>IF('Heure par heure'!F79="","",'Heure par heure'!F79-N('Heure par heure'!F78))</f>
+        <v/>
+      </c>
+      <c r="F79" s="3">
+        <f>IF('Heure par heure'!G79="","",'Heure par heure'!G79-N('Heure par heure'!G78))</f>
+        <v/>
+      </c>
+      <c r="G79" s="3">
+        <f>IF('Heure par heure'!H79="","",'Heure par heure'!H79-N('Heure par heure'!H78))</f>
+        <v/>
+      </c>
+      <c r="H79" s="3">
+        <f>IF('Heure par heure'!I79="","",'Heure par heure'!I79-N('Heure par heure'!I78))</f>
+        <v/>
+      </c>
+      <c r="I79" s="3">
+        <f>IF('Heure par heure'!J79="","",'Heure par heure'!J79-N('Heure par heure'!J78))</f>
+        <v/>
+      </c>
+      <c r="J79" s="3">
+        <f>IF('Heure par heure'!K79="","",'Heure par heure'!K79-N('Heure par heure'!K78))</f>
+        <v/>
+      </c>
+      <c r="K79" s="3">
+        <f>IF('Heure par heure'!L79="","",'Heure par heure'!L79-N('Heure par heure'!L78))</f>
+        <v/>
+      </c>
+      <c r="L79" s="3">
+        <f>SUM(B79:K79)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$79</f>
+              <f>'Heure par heure'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$79</f>
+              <f>'Heure par heure'!$D$2:$D$80</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$79</f>
+              <f>'Heure par heure'!$E$2:$E$80</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$79</f>
+              <f>'Heure par heure'!$F$2:$F$80</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$79</f>
+              <f>'Heure par heure'!$G$2:$G$80</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$79</f>
+              <f>'Heure par heure'!$H$2:$H$80</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$79</f>
+              <f>'Heure par heure'!$I$2:$I$80</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$79</f>
+              <f>'Heure par heure'!$J$2:$J$80</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$79</f>
+              <f>'Heure par heure'!$K$2:$K$80</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$79</f>
+              <f>'Heure par heure'!$L$2:$L$80</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$79</f>
+              <f>'Heure par heure'!$B$2:$B$80</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$79</f>
+              <f>'Heure par heure'!$M$2:$M$80</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$79</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$80</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$79</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$79</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$80</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$79</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$80</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$79</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$80</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$79</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$80</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$79</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$80</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$79</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$80</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$79</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$80</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$79</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$80</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9853,6 +9853,50 @@
         <v/>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="M80" s="3">
+        <f>SUM(C80:L80)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9865,7 +9909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13811,6 +13855,56 @@
       </c>
       <c r="L79" s="3">
         <f>SUM(B79:K79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2">
+        <f>'Heure par heure'!A80</f>
+        <v/>
+      </c>
+      <c r="B80" s="3">
+        <f>IF('Heure par heure'!C80="","",'Heure par heure'!C80-N('Heure par heure'!C79))</f>
+        <v/>
+      </c>
+      <c r="C80" s="3">
+        <f>IF('Heure par heure'!D80="","",'Heure par heure'!D80-N('Heure par heure'!D79))</f>
+        <v/>
+      </c>
+      <c r="D80" s="3">
+        <f>IF('Heure par heure'!E80="","",'Heure par heure'!E80-N('Heure par heure'!E79))</f>
+        <v/>
+      </c>
+      <c r="E80" s="3">
+        <f>IF('Heure par heure'!F80="","",'Heure par heure'!F80-N('Heure par heure'!F79))</f>
+        <v/>
+      </c>
+      <c r="F80" s="3">
+        <f>IF('Heure par heure'!G80="","",'Heure par heure'!G80-N('Heure par heure'!G79))</f>
+        <v/>
+      </c>
+      <c r="G80" s="3">
+        <f>IF('Heure par heure'!H80="","",'Heure par heure'!H80-N('Heure par heure'!H79))</f>
+        <v/>
+      </c>
+      <c r="H80" s="3">
+        <f>IF('Heure par heure'!I80="","",'Heure par heure'!I80-N('Heure par heure'!I79))</f>
+        <v/>
+      </c>
+      <c r="I80" s="3">
+        <f>IF('Heure par heure'!J80="","",'Heure par heure'!J80-N('Heure par heure'!J79))</f>
+        <v/>
+      </c>
+      <c r="J80" s="3">
+        <f>IF('Heure par heure'!K80="","",'Heure par heure'!K80-N('Heure par heure'!K79))</f>
+        <v/>
+      </c>
+      <c r="K80" s="3">
+        <f>IF('Heure par heure'!L80="","",'Heure par heure'!L80-N('Heure par heure'!L79))</f>
+        <v/>
+      </c>
+      <c r="L80" s="3">
+        <f>SUM(B80:K80)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$80</f>
+              <f>'Heure par heure'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$80</f>
+              <f>'Heure par heure'!$D$2:$D$81</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$80</f>
+              <f>'Heure par heure'!$E$2:$E$81</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$80</f>
+              <f>'Heure par heure'!$F$2:$F$81</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$80</f>
+              <f>'Heure par heure'!$G$2:$G$81</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$80</f>
+              <f>'Heure par heure'!$H$2:$H$81</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$80</f>
+              <f>'Heure par heure'!$I$2:$I$81</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$80</f>
+              <f>'Heure par heure'!$J$2:$J$81</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$80</f>
+              <f>'Heure par heure'!$K$2:$K$81</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$80</f>
+              <f>'Heure par heure'!$L$2:$L$81</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$80</f>
+              <f>'Heure par heure'!$B$2:$B$81</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$80</f>
+              <f>'Heure par heure'!$M$2:$M$81</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$80</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$81</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$80</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$80</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$81</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$80</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$81</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$80</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$81</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$80</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$81</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$80</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$81</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$80</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$81</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$80</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$81</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$80</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$81</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9897,6 +9897,50 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:00</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="M81" s="3">
+        <f>SUM(C81:L81)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9909,7 +9953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13905,6 +13949,56 @@
       </c>
       <c r="L80" s="3">
         <f>SUM(B80:K80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <f>'Heure par heure'!A81</f>
+        <v/>
+      </c>
+      <c r="B81" s="3">
+        <f>IF('Heure par heure'!C81="","",'Heure par heure'!C81-N('Heure par heure'!C80))</f>
+        <v/>
+      </c>
+      <c r="C81" s="3">
+        <f>IF('Heure par heure'!D81="","",'Heure par heure'!D81-N('Heure par heure'!D80))</f>
+        <v/>
+      </c>
+      <c r="D81" s="3">
+        <f>IF('Heure par heure'!E81="","",'Heure par heure'!E81-N('Heure par heure'!E80))</f>
+        <v/>
+      </c>
+      <c r="E81" s="3">
+        <f>IF('Heure par heure'!F81="","",'Heure par heure'!F81-N('Heure par heure'!F80))</f>
+        <v/>
+      </c>
+      <c r="F81" s="3">
+        <f>IF('Heure par heure'!G81="","",'Heure par heure'!G81-N('Heure par heure'!G80))</f>
+        <v/>
+      </c>
+      <c r="G81" s="3">
+        <f>IF('Heure par heure'!H81="","",'Heure par heure'!H81-N('Heure par heure'!H80))</f>
+        <v/>
+      </c>
+      <c r="H81" s="3">
+        <f>IF('Heure par heure'!I81="","",'Heure par heure'!I81-N('Heure par heure'!I80))</f>
+        <v/>
+      </c>
+      <c r="I81" s="3">
+        <f>IF('Heure par heure'!J81="","",'Heure par heure'!J81-N('Heure par heure'!J80))</f>
+        <v/>
+      </c>
+      <c r="J81" s="3">
+        <f>IF('Heure par heure'!K81="","",'Heure par heure'!K81-N('Heure par heure'!K80))</f>
+        <v/>
+      </c>
+      <c r="K81" s="3">
+        <f>IF('Heure par heure'!L81="","",'Heure par heure'!L81-N('Heure par heure'!L80))</f>
+        <v/>
+      </c>
+      <c r="L81" s="3">
+        <f>SUM(B81:K81)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$81</f>
+              <f>'Heure par heure'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$81</f>
+              <f>'Heure par heure'!$D$2:$D$82</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$81</f>
+              <f>'Heure par heure'!$E$2:$E$82</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$81</f>
+              <f>'Heure par heure'!$F$2:$F$82</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$81</f>
+              <f>'Heure par heure'!$G$2:$G$82</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$81</f>
+              <f>'Heure par heure'!$H$2:$H$82</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$81</f>
+              <f>'Heure par heure'!$I$2:$I$82</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$81</f>
+              <f>'Heure par heure'!$J$2:$J$82</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$81</f>
+              <f>'Heure par heure'!$K$2:$K$82</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$81</f>
+              <f>'Heure par heure'!$L$2:$L$82</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$81</f>
+              <f>'Heure par heure'!$B$2:$B$82</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$81</f>
+              <f>'Heure par heure'!$M$2:$M$82</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$81</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$82</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$81</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$81</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$82</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$81</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$82</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$81</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$82</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$81</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$82</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$81</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$82</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$81</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$82</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$81</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$82</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$81</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$82</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9941,6 +9941,50 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:00</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="M82" s="3">
+        <f>SUM(C82:L82)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9953,7 +9997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13999,6 +14043,56 @@
       </c>
       <c r="L81" s="3">
         <f>SUM(B81:K81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <f>'Heure par heure'!A82</f>
+        <v/>
+      </c>
+      <c r="B82" s="3">
+        <f>IF('Heure par heure'!C82="","",'Heure par heure'!C82-N('Heure par heure'!C81))</f>
+        <v/>
+      </c>
+      <c r="C82" s="3">
+        <f>IF('Heure par heure'!D82="","",'Heure par heure'!D82-N('Heure par heure'!D81))</f>
+        <v/>
+      </c>
+      <c r="D82" s="3">
+        <f>IF('Heure par heure'!E82="","",'Heure par heure'!E82-N('Heure par heure'!E81))</f>
+        <v/>
+      </c>
+      <c r="E82" s="3">
+        <f>IF('Heure par heure'!F82="","",'Heure par heure'!F82-N('Heure par heure'!F81))</f>
+        <v/>
+      </c>
+      <c r="F82" s="3">
+        <f>IF('Heure par heure'!G82="","",'Heure par heure'!G82-N('Heure par heure'!G81))</f>
+        <v/>
+      </c>
+      <c r="G82" s="3">
+        <f>IF('Heure par heure'!H82="","",'Heure par heure'!H82-N('Heure par heure'!H81))</f>
+        <v/>
+      </c>
+      <c r="H82" s="3">
+        <f>IF('Heure par heure'!I82="","",'Heure par heure'!I82-N('Heure par heure'!I81))</f>
+        <v/>
+      </c>
+      <c r="I82" s="3">
+        <f>IF('Heure par heure'!J82="","",'Heure par heure'!J82-N('Heure par heure'!J81))</f>
+        <v/>
+      </c>
+      <c r="J82" s="3">
+        <f>IF('Heure par heure'!K82="","",'Heure par heure'!K82-N('Heure par heure'!K81))</f>
+        <v/>
+      </c>
+      <c r="K82" s="3">
+        <f>IF('Heure par heure'!L82="","",'Heure par heure'!L82-N('Heure par heure'!L81))</f>
+        <v/>
+      </c>
+      <c r="L82" s="3">
+        <f>SUM(B82:K82)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -4277,32 +4277,32 @@
         <v/>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1748</v>
+        <v>1860</v>
       </c>
       <c r="E13" s="3">
         <f>IF(ROW()=2,D13,D13-D12)</f>
         <v/>
       </c>
       <c r="F13" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>1</v>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
         <v>107</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -15727,7 +15727,7 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0</v>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$82</f>
+              <f>'Heure par heure'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$82</f>
+              <f>'Heure par heure'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$82</f>
+              <f>'Heure par heure'!$E$2:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$82</f>
+              <f>'Heure par heure'!$F$2:$F$83</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$82</f>
+              <f>'Heure par heure'!$G$2:$G$83</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$82</f>
+              <f>'Heure par heure'!$H$2:$H$83</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$82</f>
+              <f>'Heure par heure'!$I$2:$I$83</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$82</f>
+              <f>'Heure par heure'!$J$2:$J$83</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$82</f>
+              <f>'Heure par heure'!$K$2:$K$83</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$82</f>
+              <f>'Heure par heure'!$L$2:$L$83</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$82</f>
+              <f>'Heure par heure'!$B$2:$B$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$82</f>
+              <f>'Heure par heure'!$M$2:$M$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$82</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$82</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$82</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$82</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$82</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$83</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$82</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$83</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$82</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$83</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$82</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$83</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$82</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$83</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$82</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$83</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9985,6 +9985,50 @@
         <v/>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 16:00</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="M83" s="3">
+        <f>SUM(C83:L83)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -9997,7 +10041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14093,6 +14137,56 @@
       </c>
       <c r="L82" s="3">
         <f>SUM(B82:K82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <f>'Heure par heure'!A83</f>
+        <v/>
+      </c>
+      <c r="B83" s="3">
+        <f>IF('Heure par heure'!C83="","",'Heure par heure'!C83-N('Heure par heure'!C82))</f>
+        <v/>
+      </c>
+      <c r="C83" s="3">
+        <f>IF('Heure par heure'!D83="","",'Heure par heure'!D83-N('Heure par heure'!D82))</f>
+        <v/>
+      </c>
+      <c r="D83" s="3">
+        <f>IF('Heure par heure'!E83="","",'Heure par heure'!E83-N('Heure par heure'!E82))</f>
+        <v/>
+      </c>
+      <c r="E83" s="3">
+        <f>IF('Heure par heure'!F83="","",'Heure par heure'!F83-N('Heure par heure'!F82))</f>
+        <v/>
+      </c>
+      <c r="F83" s="3">
+        <f>IF('Heure par heure'!G83="","",'Heure par heure'!G83-N('Heure par heure'!G82))</f>
+        <v/>
+      </c>
+      <c r="G83" s="3">
+        <f>IF('Heure par heure'!H83="","",'Heure par heure'!H83-N('Heure par heure'!H82))</f>
+        <v/>
+      </c>
+      <c r="H83" s="3">
+        <f>IF('Heure par heure'!I83="","",'Heure par heure'!I83-N('Heure par heure'!I82))</f>
+        <v/>
+      </c>
+      <c r="I83" s="3">
+        <f>IF('Heure par heure'!J83="","",'Heure par heure'!J83-N('Heure par heure'!J82))</f>
+        <v/>
+      </c>
+      <c r="J83" s="3">
+        <f>IF('Heure par heure'!K83="","",'Heure par heure'!K83-N('Heure par heure'!K82))</f>
+        <v/>
+      </c>
+      <c r="K83" s="3">
+        <f>IF('Heure par heure'!L83="","",'Heure par heure'!L83-N('Heure par heure'!L82))</f>
+        <v/>
+      </c>
+      <c r="L83" s="3">
+        <f>SUM(B83:K83)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$83</f>
+              <f>'Heure par heure'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$83</f>
+              <f>'Heure par heure'!$D$2:$D$84</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$83</f>
+              <f>'Heure par heure'!$E$2:$E$84</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$83</f>
+              <f>'Heure par heure'!$F$2:$F$84</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$83</f>
+              <f>'Heure par heure'!$G$2:$G$84</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$83</f>
+              <f>'Heure par heure'!$H$2:$H$84</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$83</f>
+              <f>'Heure par heure'!$I$2:$I$84</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$83</f>
+              <f>'Heure par heure'!$J$2:$J$84</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$83</f>
+              <f>'Heure par heure'!$K$2:$K$84</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$83</f>
+              <f>'Heure par heure'!$L$2:$L$84</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$83</f>
+              <f>'Heure par heure'!$B$2:$B$84</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$83</f>
+              <f>'Heure par heure'!$M$2:$M$84</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$83</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$84</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$83</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$83</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$84</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$83</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$84</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$83</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$84</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$83</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$84</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$83</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$84</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$83</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$84</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$83</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$84</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$83</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$84</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10029,6 +10029,50 @@
         <v/>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:00</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="M84" s="3">
+        <f>SUM(C84:L84)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -10041,7 +10085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14187,6 +14231,56 @@
       </c>
       <c r="L83" s="3">
         <f>SUM(B83:K83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <f>'Heure par heure'!A84</f>
+        <v/>
+      </c>
+      <c r="B84" s="3">
+        <f>IF('Heure par heure'!C84="","",'Heure par heure'!C84-N('Heure par heure'!C83))</f>
+        <v/>
+      </c>
+      <c r="C84" s="3">
+        <f>IF('Heure par heure'!D84="","",'Heure par heure'!D84-N('Heure par heure'!D83))</f>
+        <v/>
+      </c>
+      <c r="D84" s="3">
+        <f>IF('Heure par heure'!E84="","",'Heure par heure'!E84-N('Heure par heure'!E83))</f>
+        <v/>
+      </c>
+      <c r="E84" s="3">
+        <f>IF('Heure par heure'!F84="","",'Heure par heure'!F84-N('Heure par heure'!F83))</f>
+        <v/>
+      </c>
+      <c r="F84" s="3">
+        <f>IF('Heure par heure'!G84="","",'Heure par heure'!G84-N('Heure par heure'!G83))</f>
+        <v/>
+      </c>
+      <c r="G84" s="3">
+        <f>IF('Heure par heure'!H84="","",'Heure par heure'!H84-N('Heure par heure'!H83))</f>
+        <v/>
+      </c>
+      <c r="H84" s="3">
+        <f>IF('Heure par heure'!I84="","",'Heure par heure'!I84-N('Heure par heure'!I83))</f>
+        <v/>
+      </c>
+      <c r="I84" s="3">
+        <f>IF('Heure par heure'!J84="","",'Heure par heure'!J84-N('Heure par heure'!J83))</f>
+        <v/>
+      </c>
+      <c r="J84" s="3">
+        <f>IF('Heure par heure'!K84="","",'Heure par heure'!K84-N('Heure par heure'!K83))</f>
+        <v/>
+      </c>
+      <c r="K84" s="3">
+        <f>IF('Heure par heure'!L84="","",'Heure par heure'!L84-N('Heure par heure'!L83))</f>
+        <v/>
+      </c>
+      <c r="L84" s="3">
+        <f>SUM(B84:K84)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$84</f>
+              <f>'Heure par heure'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$84</f>
+              <f>'Heure par heure'!$D$2:$D$85</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$84</f>
+              <f>'Heure par heure'!$E$2:$E$85</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$84</f>
+              <f>'Heure par heure'!$F$2:$F$85</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$84</f>
+              <f>'Heure par heure'!$G$2:$G$85</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$84</f>
+              <f>'Heure par heure'!$H$2:$H$85</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$84</f>
+              <f>'Heure par heure'!$I$2:$I$85</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$84</f>
+              <f>'Heure par heure'!$J$2:$J$85</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$84</f>
+              <f>'Heure par heure'!$K$2:$K$85</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$84</f>
+              <f>'Heure par heure'!$L$2:$L$85</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$84</f>
+              <f>'Heure par heure'!$B$2:$B$85</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$84</f>
+              <f>'Heure par heure'!$M$2:$M$85</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$84</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$85</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$84</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$84</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$85</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$84</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$85</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$84</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$85</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$84</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$85</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$84</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$85</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$84</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$85</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$84</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$85</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$84</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$85</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10073,6 +10073,50 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:00</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="M85" s="3">
+        <f>SUM(C85:L85)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -10085,7 +10129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14281,6 +14325,56 @@
       </c>
       <c r="L84" s="3">
         <f>SUM(B84:K84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <f>'Heure par heure'!A85</f>
+        <v/>
+      </c>
+      <c r="B85" s="3">
+        <f>IF('Heure par heure'!C85="","",'Heure par heure'!C85-N('Heure par heure'!C84))</f>
+        <v/>
+      </c>
+      <c r="C85" s="3">
+        <f>IF('Heure par heure'!D85="","",'Heure par heure'!D85-N('Heure par heure'!D84))</f>
+        <v/>
+      </c>
+      <c r="D85" s="3">
+        <f>IF('Heure par heure'!E85="","",'Heure par heure'!E85-N('Heure par heure'!E84))</f>
+        <v/>
+      </c>
+      <c r="E85" s="3">
+        <f>IF('Heure par heure'!F85="","",'Heure par heure'!F85-N('Heure par heure'!F84))</f>
+        <v/>
+      </c>
+      <c r="F85" s="3">
+        <f>IF('Heure par heure'!G85="","",'Heure par heure'!G85-N('Heure par heure'!G84))</f>
+        <v/>
+      </c>
+      <c r="G85" s="3">
+        <f>IF('Heure par heure'!H85="","",'Heure par heure'!H85-N('Heure par heure'!H84))</f>
+        <v/>
+      </c>
+      <c r="H85" s="3">
+        <f>IF('Heure par heure'!I85="","",'Heure par heure'!I85-N('Heure par heure'!I84))</f>
+        <v/>
+      </c>
+      <c r="I85" s="3">
+        <f>IF('Heure par heure'!J85="","",'Heure par heure'!J85-N('Heure par heure'!J84))</f>
+        <v/>
+      </c>
+      <c r="J85" s="3">
+        <f>IF('Heure par heure'!K85="","",'Heure par heure'!K85-N('Heure par heure'!K84))</f>
+        <v/>
+      </c>
+      <c r="K85" s="3">
+        <f>IF('Heure par heure'!L85="","",'Heure par heure'!L85-N('Heure par heure'!L84))</f>
+        <v/>
+      </c>
+      <c r="L85" s="3">
+        <f>SUM(B85:K85)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_actu.xlsx
+++ b/suivi/Decode_suivi_actu.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$85</f>
+              <f>'Heure par heure'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$85</f>
+              <f>'Heure par heure'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$85</f>
+              <f>'Heure par heure'!$E$2:$E$86</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$85</f>
+              <f>'Heure par heure'!$F$2:$F$86</f>
             </numRef>
           </val>
         </ser>
@@ -456,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$85</f>
+              <f>'Heure par heure'!$G$2:$G$86</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$H$2:$H$85</f>
+              <f>'Heure par heure'!$H$2:$H$86</f>
             </numRef>
           </val>
         </ser>
@@ -520,12 +520,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$I$2:$I$85</f>
+              <f>'Heure par heure'!$I$2:$I$86</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$J$2:$J$85</f>
+              <f>'Heure par heure'!$J$2:$J$86</f>
             </numRef>
           </val>
         </ser>
@@ -584,12 +584,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$K$2:$K$85</f>
+              <f>'Heure par heure'!$K$2:$K$86</f>
             </numRef>
           </val>
         </ser>
@@ -616,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$L$2:$L$85</f>
+              <f>'Heure par heure'!$L$2:$L$86</f>
             </numRef>
           </val>
         </ser>
@@ -728,12 +728,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$85</f>
+              <f>'Heure par heure'!$B$2:$B$86</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -841,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$M$2:$M$85</f>
+              <f>'Heure par heure'!$M$2:$M$86</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,12 +940,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$85</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -964,12 +964,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$85</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +988,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$85</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -1012,12 +1012,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$85</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$86</f>
             </numRef>
           </val>
         </ser>
@@ -1036,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$F$2:$F$85</f>
+              <f>'Vues gagnées par heure'!$F$2:$F$86</f>
             </numRef>
           </val>
         </ser>
@@ -1060,12 +1060,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$G$2:$G$85</f>
+              <f>'Vues gagnées par heure'!$G$2:$G$86</f>
             </numRef>
           </val>
         </ser>
@@ -1084,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$H$2:$H$85</f>
+              <f>'Vues gagnées par heure'!$H$2:$H$86</f>
             </numRef>
           </val>
         </ser>
@@ -1108,12 +1108,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$I$2:$I$85</f>
+              <f>'Vues gagnées par heure'!$I$2:$I$86</f>
             </numRef>
           </val>
         </ser>
@@ -1132,12 +1132,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$J$2:$J$85</f>
+              <f>'Vues gagnées par heure'!$J$2:$J$86</f>
             </numRef>
           </val>
         </ser>
@@ -1156,12 +1156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$K$2:$K$85</f>
+              <f>'Vues gagnées par heure'!$K$2:$K$86</f>
             </numRef>
           </val>
         </ser>
@@ -3275,7 +3275,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3297,7 +3297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3319,7 +3319,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -3346,7 +3346,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10117,6 +10117,50 @@
         <v/>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:00</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n"